--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T91"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -707,7 +707,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>252061</v>
+        <v>254713</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>36.16666666666666</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:14:35</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:14:35</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:45</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4340</v>
+        <v>5996</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -755,17 +755,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O4" t="n">
-        <v>40628</v>
+        <v>40623</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -773,15 +773,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>40628</v>
+        <v>40623</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>0</v>
+        <v>-1.335104166666667</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>254713</v>
+        <v>243569</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>49.96666666666667</v>
+        <v>21.675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:45</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:22:45</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:22:45</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:12:43</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5996</v>
+        <v>2601</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -837,33 +837,31 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-1.383831018518519</v>
+        <v>-429</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -871,7 +869,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>244023</v>
+        <v>252061</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -880,37 +878,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>8.308333333333334</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:12:43</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:46:43</t>
+          <t>14-11-2025 09:15:13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:46:43</t>
+          <t>14-11-2025 09:15:13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:55:01</t>
+          <t>14-11-2025 09:51:23</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>997</v>
+        <v>4340</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -923,35 +921,37 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>70</v>
       </c>
       <c r="O6" t="n">
-        <v>406062</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
+        <v>40628</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-417</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254256</v>
+        <v>244023</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -960,37 +960,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>50.925</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 09:55:01</t>
+          <t>14-11-2025 09:51:23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:01</t>
+          <t>14-11-2025 10:08:23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:01</t>
+          <t>14-11-2025 10:08:23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:06:57</t>
+          <t>14-11-2025 10:16:42</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6111</v>
+        <v>997</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -999,17 +999,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>406422</v>
+        <v>406062</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1019,19 +1019,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-18</v>
+        <v>-417</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254375</v>
+        <v>254256</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1040,37 +1040,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>45.29166666666666</v>
+        <v>50.925</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 11:06:57</t>
+          <t>14-11-2025 10:16:42</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 11:23:57</t>
+          <t>14-11-2025 10:37:42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 11:23:57</t>
+          <t>14-11-2025 10:37:42</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:14</t>
+          <t>14-11-2025 11:28:37</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5435</v>
+        <v>6111</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1079,17 +1079,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>70</v>
       </c>
       <c r="O8" t="n">
-        <v>40624</v>
+        <v>406422</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1099,19 +1099,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254512</v>
+        <v>254375</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1120,37 +1120,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>59.55833333333333</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:14</t>
+          <t>14-11-2025 11:28:37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14-11-2025 12:45:14</t>
+          <t>14-11-2025 11:45:37</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-11-2025 12:45:14</t>
+          <t>14-11-2025 11:45:37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:44:48</t>
+          <t>14-11-2025 12:30:55</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7147</v>
+        <v>5435</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>406232</v>
+        <v>40624</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1179,19 +1179,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>255039</v>
+        <v>254512</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1200,37 +1200,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>9.15</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14-11-2025 13:44:48</t>
+          <t>14-11-2025 12:30:55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:16:48</t>
+          <t>14-11-2025 13:06:55</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:16:48</t>
+          <t>14-11-2025 13:06:55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:25:57</t>
+          <t>14-11-2025 14:06:28</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1098</v>
+        <v>7147</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1239,17 +1239,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O10" t="n">
-        <v>40624</v>
+        <v>406232</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254189</v>
+        <v>255039</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1280,37 +1280,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>55.875</v>
+        <v>9.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:25:57</t>
+          <t>14-11-2025 14:06:28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:42:57</t>
+          <t>14-11-2025 14:38:28</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:42:57</t>
+          <t>14-11-2025 14:38:28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 07:38:49</t>
+          <t>14-11-2025 14:47:37</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6705</v>
+        <v>1098</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1319,17 +1319,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
       <c r="O11" t="n">
-        <v>406552</v>
+        <v>40624</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1339,19 +1339,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254230</v>
+        <v>254189</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>62.475</v>
+        <v>55.875</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 07:38:49</t>
+          <t>14-11-2025 14:47:37</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 07:53:49</t>
+          <t>17-11-2025 07:04:37</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 07:53:49</t>
+          <t>17-11-2025 07:04:37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 08:56:18</t>
+          <t>17-11-2025 08:00:30</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7497</v>
+        <v>6705</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>254433</v>
+        <v>254230</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1440,37 +1440,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>67.84999999999999</v>
+        <v>62.475</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 08:56:18</t>
+          <t>17-11-2025 08:00:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-11-2025 09:11:18</t>
+          <t>17-11-2025 08:15:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-11-2025 09:11:18</t>
+          <t>17-11-2025 08:15:30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-11-2025 10:19:09</t>
+          <t>17-11-2025 09:17:58</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8142</v>
+        <v>7497</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1499,19 +1499,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>253838</v>
+        <v>254198</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1524,33 +1524,33 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>108.3666666666667</v>
+        <v>215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17-11-2025 10:19:09</t>
+          <t>17-11-2025 09:17:58</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17-11-2025 10:40:09</t>
+          <t>17-11-2025 09:49:58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17-11-2025 10:40:09</t>
+          <t>17-11-2025 09:49:58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17-11-2025 12:28:31</t>
+          <t>17-11-2025 13:24:58</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13004</v>
+        <v>25800</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1576,19 +1576,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-21.51980324074074</v>
+        <v>-18.55901041666667</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>253885</v>
+        <v>254903</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1597,37 +1597,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>105.9333333333333</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17-11-2025 12:28:31</t>
+          <t>17-11-2025 13:24:58</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17-11-2025 12:47:31</t>
+          <t>17-11-2025 13:56:58</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17-11-2025 12:47:31</t>
+          <t>17-11-2025 13:56:58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17-11-2025 14:33:27</t>
+          <t>18-11-2025 10:13:37</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12712</v>
+        <v>30797</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1653,14 +1653,14 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-3.6065625</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17-11-2025 14:33:27</t>
+          <t>18-11-2025 10:13:37</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18-11-2025 07:09:27</t>
+          <t>18-11-2025 10:49:37</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18-11-2025 07:09:27</t>
+          <t>18-11-2025 10:49:37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-11-2025 10:32:02</t>
+          <t>18-11-2025 14:12:12</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-29.43891782407407</v>
+        <v>-29.59181134259259</v>
       </c>
       <c r="T16" t="n">
         <v>7</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254605</v>
+        <v>254555</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1755,33 +1755,33 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>39.025</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18-11-2025 10:32:02</t>
+          <t>18-11-2025 14:12:12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18-11-2025 11:12:02</t>
+          <t>18-11-2025 14:50:12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18-11-2025 11:12:02</t>
+          <t>18-11-2025 14:50:12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:04</t>
+          <t>19-11-2025 09:43:11</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4683</v>
+        <v>20758</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1790,14 +1790,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O17" t="n">
+        <v>406232</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1807,19 +1810,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-4.493796296296297</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254653</v>
+        <v>254671</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1828,37 +1831,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>64.40833333333333</v>
+        <v>136.1666666666667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:04</t>
+          <t>19-11-2025 09:43:11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18-11-2025 12:08:04</t>
+          <t>19-11-2025 10:19:11</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18-11-2025 12:08:04</t>
+          <t>19-11-2025 10:19:11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18-11-2025 13:12:28</t>
+          <t>19-11-2025 12:35:21</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7729</v>
+        <v>16340</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1871,7 +1874,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>70</v>
@@ -1884,19 +1887,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254915</v>
+        <v>250284</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1905,37 +1908,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>48.875</v>
+        <v>146.35</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18-11-2025 13:12:28</t>
+          <t>19-11-2025 12:35:21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18-11-2025 13:31:28</t>
+          <t>19-11-2025 12:52:21</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18-11-2025 13:31:28</t>
+          <t>19-11-2025 12:52:21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-11-2025 14:20:21</t>
+          <t>20-11-2025 07:18:42</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5865</v>
+        <v>17562</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1944,15 +1947,18 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>70</v>
       </c>
+      <c r="O19" t="n">
+        <v>406422</v>
+      </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
@@ -1961,11 +1967,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0</v>
+        <v>-254</v>
       </c>
       <c r="T19" t="n">
         <v>7</v>
@@ -1973,7 +1979,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>254339</v>
+        <v>254652</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1982,37 +1988,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E20" t="n">
-        <v>245.9666666666667</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:20:21</t>
+          <t>20-11-2025 07:18:42</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:41:21</t>
+          <t>20-11-2025 07:41:42</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:41:21</t>
+          <t>20-11-2025 07:41:42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19-11-2025 10:47:19</t>
+          <t>20-11-2025 08:10:26</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29516</v>
+        <v>3448</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2025,7 +2031,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
         <v>70</v>
@@ -2038,19 +2044,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-30.44952546296296</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254671</v>
+        <v>254605</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2059,37 +2065,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>136.1666666666667</v>
+        <v>39.025</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19-11-2025 10:47:19</t>
+          <t>20-11-2025 08:10:26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19-11-2025 11:06:19</t>
+          <t>20-11-2025 08:27:26</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19-11-2025 11:06:19</t>
+          <t>20-11-2025 08:27:26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19-11-2025 13:22:29</t>
+          <t>20-11-2025 09:06:28</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>16340</v>
+        <v>4683</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2098,11 +2104,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>70</v>
@@ -2115,11 +2121,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-8.557280092592592</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -2127,46 +2133,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254165</v>
+        <v>254758</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>58.31666666666667</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>20-11-2025 09:06:28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>20-11-2025 09:23:28</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>20-11-2025 09:23:28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>20-11-2025 10:24:51</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6998</v>
+        <v>7366</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2175,41 +2181,36 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
-      </c>
-      <c r="O22" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.3613310185185185</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254156</v>
+        <v>254165</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2222,33 +2223,33 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
-        <v>87.47499999999999</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:42:00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:42:00</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>14-11-2025 08:40:19</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:05:19</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:05:19</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:32:47</t>
-        </is>
-      </c>
       <c r="J23" t="n">
-        <v>10497</v>
+        <v>6998</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2283,7 +2284,7 @@
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.4394386574074074</v>
+        <v>-0.3613310185185185</v>
       </c>
       <c r="T23" t="n">
         <v>7</v>
@@ -2291,7 +2292,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254106</v>
+        <v>254156</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2300,37 +2301,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>107.6416666666667</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>14-11-2025 08:40:19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:05:19</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>14-11-2025 09:05:19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>14-11-2025 10:32:47</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:18:47</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>14-11-2025 11:18:47</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:06:26</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>12917</v>
+        <v>10497</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2339,28 +2340,33 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O24" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-28.54613425925926</v>
+        <v>-0.4394386574074074</v>
       </c>
       <c r="T24" t="n">
         <v>7</v>
@@ -2368,7 +2374,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>243569</v>
+        <v>254309</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2377,37 +2383,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>21.675</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14-11-2025 13:06:26</t>
+          <t>14-11-2025 10:32:47</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14-11-2025 13:48:26</t>
+          <t>14-11-2025 11:12:47</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-11-2025 13:48:26</t>
+          <t>14-11-2025 11:12:47</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-11-2025 14:10:06</t>
+          <t>18-11-2025 10:12:48</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2601</v>
+        <v>108002</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2416,17 +2422,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
-      </c>
-      <c r="O25" t="n">
-        <v>406372</v>
+        <v>152</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2436,19 +2439,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-429</v>
+        <v>-8.425561342592593</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254276</v>
+        <v>254609</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2457,41 +2460,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>37.03333333333333</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-11-2025 14:10:06</t>
+          <t>18-11-2025 10:12:48</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14-11-2025 14:52:06</t>
+          <t>18-11-2025 11:00:48</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-11-2025 14:52:06</t>
+          <t>18-11-2025 11:00:48</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17-11-2025 07:29:08</t>
+          <t>19-11-2025 09:57:28</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4444</v>
+        <v>50000</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2500,10 +2503,13 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>406552</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2513,11 +2519,11 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-24.31190393518519</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>4</v>
@@ -2525,7 +2531,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>253382</v>
+        <v>254653</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2538,33 +2544,33 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>85.09999999999999</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17-11-2025 07:29:08</t>
+          <t>19-11-2025 09:57:28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17-11-2025 08:11:08</t>
+          <t>19-11-2025 10:45:28</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-11-2025 08:11:08</t>
+          <t>19-11-2025 10:45:28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:14</t>
+          <t>19-11-2025 11:49:53</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>10212</v>
+        <v>7729</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2577,13 +2583,10 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>76</v>
-      </c>
-      <c r="O27" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2593,19 +2596,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254188</v>
+        <v>254675</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2614,37 +2617,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>37.44166666666667</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:14</t>
+          <t>19-11-2025 11:49:53</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:14</t>
+          <t>19-11-2025 12:31:53</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:14</t>
+          <t>19-11-2025 12:31:53</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-11-2025 10:55:41</t>
+          <t>20-11-2025 07:05:50</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>4493</v>
+        <v>18475</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2653,17 +2656,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O28" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2673,11 +2676,11 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
@@ -2685,7 +2688,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>254107</v>
+        <v>254252</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2694,37 +2697,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E29" t="n">
-        <v>175.0583333333333</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17-11-2025 10:55:41</t>
+          <t>20-11-2025 07:05:50</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:41</t>
+          <t>20-11-2025 07:47:50</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:41</t>
+          <t>20-11-2025 07:47:50</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17-11-2025 14:21:44</t>
+          <t>20-11-2025 09:08:21</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>21007</v>
+        <v>9662</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2750,19 +2753,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-26.59843171296296</v>
+        <v>-17.38080439814815</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254309</v>
+        <v>254419</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2771,37 +2774,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>900.0166666666667</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17-11-2025 14:21:44</t>
+          <t>20-11-2025 09:08:21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:44</t>
+          <t>20-11-2025 09:39:21</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:44</t>
+          <t>20-11-2025 09:39:21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19-11-2025 14:07:45</t>
+          <t>20-11-2025 10:51:42</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>108002</v>
+        <v>8681</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2810,14 +2813,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2831,54 +2834,54 @@
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-19.58872106481482</v>
+        <v>-10.45256944444444</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>253380</v>
+        <v>253906</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>104.275</v>
+        <v>45.79166666666666</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>20-11-2025 10:51:42</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:00</t>
+          <t>20-11-2025 11:20:42</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:00</t>
+          <t>20-11-2025 11:20:42</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14-11-2025 09:30:16</t>
+          <t>20-11-2025 12:06:29</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12513</v>
+        <v>5495</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2887,33 +2890,28 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="O31" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P31" t="n">
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>25-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-0.3960243055555556</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>7</v>
@@ -2921,46 +2919,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254546</v>
+        <v>254547</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>109.4083333333333</v>
+        <v>68.55</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14-11-2025 09:30:16</t>
+          <t>20-11-2025 12:06:29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14-11-2025 09:55:16</t>
+          <t>20-11-2025 12:35:29</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-11-2025 09:55:16</t>
+          <t>20-11-2025 12:35:29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:41</t>
+          <t>20-11-2025 13:44:02</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>13129</v>
+        <v>8226</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2978,9 +2976,6 @@
       <c r="N32" t="n">
         <v>70</v>
       </c>
-      <c r="O32" t="n">
-        <v>406242</v>
-      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
@@ -2993,7 +2988,7 @@
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-7</v>
+        <v>-1.572251157407407</v>
       </c>
       <c r="T32" t="n">
         <v>7</v>
@@ -3001,50 +2996,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254609</v>
+        <v>254166</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>416.6666666666667</v>
+        <v>38.85</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:41</t>
+          <t>20-11-2025 13:44:02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14-11-2025 12:22:41</t>
+          <t>20-11-2025 14:11:02</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14-11-2025 12:22:41</t>
+          <t>20-11-2025 14:11:02</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-11-2025 11:19:21</t>
+          <t>20-11-2025 14:49:53</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>50000</v>
+        <v>4662</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3053,13 +3048,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>406552</v>
+        <v>70</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -3069,58 +3061,58 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254675</v>
+        <v>254546</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>153.9583333333333</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17-11-2025 11:19:21</t>
+          <t>20-11-2025 14:49:53</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:21</t>
+          <t>21-11-2025 07:16:53</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:21</t>
+          <t>21-11-2025 07:16:53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17-11-2025 14:29:18</t>
+          <t>21-11-2025 09:06:18</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>18475</v>
+        <v>13129</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3129,17 +3121,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O34" t="n">
-        <v>406422</v>
+        <v>406242</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3149,19 +3141,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254437</v>
+        <v>253380</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3170,37 +3162,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E35" t="n">
-        <v>58.05833333333333</v>
+        <v>104.275</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17-11-2025 14:29:18</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18-11-2025 07:01:18</t>
+          <t>14-11-2025 07:46:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18-11-2025 07:01:18</t>
+          <t>14-11-2025 07:46:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18-11-2025 07:59:22</t>
+          <t>14-11-2025 09:30:16</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>6967</v>
+        <v>12513</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3209,39 +3201,41 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
       </c>
       <c r="O35" t="n">
-        <v>406552</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-2</v>
+        <v>-0.3960243055555556</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254457</v>
+        <v>254107</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3250,37 +3244,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>3.925</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>18-11-2025 07:59:22</t>
+          <t>14-11-2025 09:30:16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:22</t>
+          <t>14-11-2025 09:55:16</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:22</t>
+          <t>14-11-2025 09:55:16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18-11-2025 08:18:17</t>
+          <t>14-11-2025 12:50:20</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>471</v>
+        <v>21007</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3298,9 +3292,6 @@
       <c r="N36" t="n">
         <v>70</v>
       </c>
-      <c r="O36" t="n">
-        <v>406372</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
@@ -3309,58 +3300,58 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-1</v>
+        <v>-23.5349537037037</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254481</v>
+        <v>253885</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32.5</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>81.16666666666667</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 12:50:20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 13:07:20</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 13:07:20</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 14:53:16</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>9740</v>
+        <v>12712</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3373,111 +3364,104 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
       </c>
-      <c r="O37" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P37" t="n">
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0</v>
+        <v>-0.6203240740740741</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254762</v>
+        <v>254088</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>34.5</v>
+        <v>21</v>
       </c>
       <c r="E38" t="n">
-        <v>31.85833333333333</v>
+        <v>425.2166666666666</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 14:53:16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>17-11-2025 07:14:16</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>17-11-2025 07:14:16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>17-11-2025 14:19:29</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3823</v>
+        <v>51026</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
       </c>
       <c r="O38" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>-30</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
@@ -3485,65 +3469,65 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>253897</v>
+        <v>254428</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>46.5</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
-        <v>94.01666666666667</v>
+        <v>48.30833333333333</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>17-11-2025 14:19:29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:31</t>
+          <t>17-11-2025 14:32:29</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:31</t>
+          <t>17-11-2025 14:32:29</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:32</t>
+          <t>18-11-2025 07:20:47</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>11282</v>
+        <v>5797</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O39" t="n">
-        <v>40606</v>
+        <v>40649</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3551,27 +3535,27 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>40606</v>
+        <v>40649</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.3892650462962963</v>
+        <v>-8.306105324074075</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254824</v>
+        <v>253650</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3580,33 +3564,33 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>48.5</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>748.225</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:32</t>
+          <t>18-11-2025 07:20:47</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14-11-2025 10:09:02</t>
+          <t>18-11-2025 07:56:47</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14-11-2025 10:09:02</t>
+          <t>18-11-2025 07:56:47</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17-11-2025 14:37:16</t>
+          <t>18-11-2025 12:29:55</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>89787</v>
+        <v>32776</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3615,18 +3599,15 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
         <v>76</v>
       </c>
-      <c r="O40" t="n">
-        <v>406232</v>
-      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
@@ -3635,19 +3616,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0</v>
+        <v>-19.52078125</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254428</v>
+        <v>254481</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3656,56 +3637,56 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="E41" t="n">
-        <v>48.30833333333333</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17-11-2025 14:37:16</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>18-11-2025 07:11:46</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>18-11-2025 07:11:46</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>18-11-2025 08:00:04</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5797</v>
+        <v>9740</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
         <v>70</v>
       </c>
       <c r="O41" t="n">
-        <v>40649</v>
+        <v>40642</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3713,23 +3694,23 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>40649</v>
+        <v>40642</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-8.333385416666667</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254893</v>
+        <v>254762</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3738,37 +3719,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
       <c r="E42" t="n">
-        <v>46.675</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>18-11-2025 08:00:04</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18-11-2025 08:36:34</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18-11-2025 08:36:34</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18-11-2025 09:23:15</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>5601</v>
+        <v>3823</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3786,27 +3767,32 @@
       <c r="N42" t="n">
         <v>70</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
+      <c r="O42" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0</v>
+        <v>-1.291684027777778</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>250284</v>
+        <v>253897</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3815,37 +3801,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40.5</v>
+        <v>46.5</v>
       </c>
       <c r="E43" t="n">
-        <v>146.35</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>18-11-2025 09:23:15</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18-11-2025 10:03:45</t>
+          <t>14-11-2025 07:46:31</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18-11-2025 10:03:45</t>
+          <t>14-11-2025 07:46:31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18-11-2025 12:30:06</t>
+          <t>14-11-2025 09:20:32</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>17562</v>
+        <v>11282</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3858,74 +3844,76 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N43" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O43" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-254</v>
+        <v>-0.3892650462962963</v>
       </c>
       <c r="T43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>253694</v>
+        <v>235572</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="E44" t="n">
-        <v>121.7583333333333</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 09:20:32</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>14-11-2025 10:03:02</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>14-11-2025 10:03:02</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 11:26:01</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>14611</v>
+        <v>9958</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3938,76 +3926,74 @@
         </is>
       </c>
       <c r="M44" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>70</v>
+      </c>
+      <c r="O44" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>06-11-2023 00:00:00</t>
+        </is>
+      </c>
+      <c r="S44" s="1" t="n">
+        <v>-744</v>
+      </c>
+      <c r="T44" t="n">
         <v>4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>76</v>
-      </c>
-      <c r="O44" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>05-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>-0.6158043981481481</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254556</v>
+        <v>254824</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>36.5</v>
       </c>
       <c r="E45" t="n">
-        <v>173.4166666666667</v>
+        <v>748.225</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 11:26:01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>14-11-2025 12:02:31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>14-11-2025 12:02:31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14-11-2025 10:10:10</t>
+          <t>18-11-2025 08:30:45</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>20810</v>
+        <v>89787</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4016,80 +4002,78 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
         <v>76</v>
       </c>
       <c r="O45" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406232</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-1.423732638888889</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254283</v>
+        <v>254599</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>45</v>
+        <v>34.5</v>
       </c>
       <c r="E46" t="n">
-        <v>95.76666666666667</v>
+        <v>44.9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14-11-2025 10:10:10</t>
+          <t>18-11-2025 08:30:45</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14-11-2025 10:55:10</t>
+          <t>18-11-2025 09:05:15</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>14-11-2025 10:55:10</t>
+          <t>18-11-2025 09:05:15</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:56</t>
+          <t>18-11-2025 09:50:09</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>11492</v>
+        <v>5388</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4098,17 +4082,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4118,19 +4102,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254291</v>
+        <v>253694</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4139,37 +4123,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>18.85</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:56</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14-11-2025 13:10:56</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>14-11-2025 13:10:56</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14-11-2025 13:29:47</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2262</v>
+        <v>14611</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4182,19 +4166,21 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O47" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -4202,15 +4188,15 @@
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-14</v>
+        <v>-0.6158043981481481</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254460</v>
+        <v>254556</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4219,37 +4205,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E48" t="n">
-        <v>46.68333333333333</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14-11-2025 13:29:47</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 14:04:47</t>
+          <t>14-11-2025 07:16:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 14:04:47</t>
+          <t>14-11-2025 07:16:45</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14-11-2025 14:51:28</t>
+          <t>14-11-2025 10:10:10</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>5602</v>
+        <v>20810</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4258,36 +4244,41 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>70</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O48" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-32.61907986111111</v>
+        <v>-1.423732638888889</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254198</v>
+        <v>254106</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4300,33 +4291,33 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E49" t="n">
-        <v>215</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14-11-2025 14:51:28</t>
+          <t>14-11-2025 10:10:10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:28</t>
+          <t>14-11-2025 10:50:10</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:28</t>
+          <t>14-11-2025 10:50:10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>17-11-2025 11:11:28</t>
+          <t>14-11-2025 12:37:49</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>25800</v>
+        <v>12917</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4339,10 +4330,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4352,19 +4343,19 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-18.46630208333333</v>
+        <v>-28.52626157407407</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254237</v>
+        <v>254283</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4373,37 +4364,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>184.0916666666667</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17-11-2025 11:11:28</t>
+          <t>14-11-2025 12:37:49</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>17-11-2025 12:11:28</t>
+          <t>14-11-2025 13:17:49</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>17-11-2025 12:11:28</t>
+          <t>14-11-2025 13:17:49</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>18-11-2025 07:15:34</t>
+          <t>14-11-2025 14:53:35</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>22091</v>
+        <v>11492</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4412,43 +4403,39 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>70</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="O50" t="n">
+        <v>406552</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-8.302476851851852</v>
+        <v>-9</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>253865</v>
+        <v>254188</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4457,37 +4444,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>116.7583333333333</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>18-11-2025 07:15:34</t>
+          <t>14-11-2025 14:53:35</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>18-11-2025 07:50:34</t>
+          <t>17-11-2025 07:33:35</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18-11-2025 07:50:34</t>
+          <t>17-11-2025 07:33:35</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>18-11-2025 09:47:19</t>
+          <t>17-11-2025 08:11:01</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>14011</v>
+        <v>4493</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4496,15 +4483,18 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>70</v>
       </c>
+      <c r="O51" t="n">
+        <v>406372</v>
+      </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
@@ -4513,19 +4503,19 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-39.40786458333334</v>
+        <v>-1</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254599</v>
+        <v>254457</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4534,37 +4524,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
-        <v>44.9</v>
+        <v>3.925</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>18-11-2025 09:47:19</t>
+          <t>17-11-2025 08:11:01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18-11-2025 10:17:19</t>
+          <t>17-11-2025 08:36:01</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>18-11-2025 10:17:19</t>
+          <t>17-11-2025 08:36:01</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18-11-2025 11:02:13</t>
+          <t>17-11-2025 08:39:57</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>5388</v>
+        <v>471</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4593,19 +4583,19 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254293</v>
+        <v>254291</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4625,22 +4615,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>18-11-2025 11:02:13</t>
+          <t>17-11-2025 08:39:57</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:13</t>
+          <t>17-11-2025 09:14:57</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:13</t>
+          <t>17-11-2025 09:14:57</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56:04</t>
+          <t>17-11-2025 09:33:48</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4685,7 +4675,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>253614</v>
+        <v>254276</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4694,37 +4684,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E54" t="n">
-        <v>122.45</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56:04</t>
+          <t>17-11-2025 09:33:48</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18-11-2025 12:46:04</t>
+          <t>17-11-2025 10:08:48</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>18-11-2025 12:46:04</t>
+          <t>17-11-2025 10:08:48</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18-11-2025 14:48:31</t>
+          <t>17-11-2025 10:45:50</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>14694</v>
+        <v>4444</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4733,14 +4723,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4750,19 +4740,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0</v>
+        <v>-14.44849537037037</v>
       </c>
       <c r="T54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254758</v>
+        <v>253838</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4771,37 +4761,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E55" t="n">
-        <v>61.38333333333333</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>18-11-2025 14:48:31</t>
+          <t>17-11-2025 10:45:50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>19-11-2025 07:28:31</t>
+          <t>17-11-2025 11:15:50</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>19-11-2025 07:28:31</t>
+          <t>17-11-2025 11:15:50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>19-11-2025 08:29:54</t>
+          <t>17-11-2025 13:04:12</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>7366</v>
+        <v>13004</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4814,7 +4804,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>70</v>
@@ -4827,19 +4817,19 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-2.354103009259259</v>
+        <v>-11.54458333333333</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254166</v>
+        <v>254293</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4848,37 +4838,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>30</v>
       </c>
       <c r="E56" t="n">
-        <v>38.85</v>
+        <v>18.85</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>19-11-2025 08:29:54</t>
+          <t>17-11-2025 13:04:12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>19-11-2025 08:59:54</t>
+          <t>17-11-2025 13:34:12</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>19-11-2025 08:59:54</t>
+          <t>17-11-2025 13:34:12</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:45</t>
+          <t>17-11-2025 13:53:03</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4662</v>
+        <v>2262</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4891,11 +4881,14 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
         <v>70</v>
       </c>
+      <c r="O56" t="n">
+        <v>40624</v>
+      </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
@@ -4904,11 +4897,11 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T56" t="n">
         <v>7</v>
@@ -4916,46 +4909,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254714</v>
+        <v>254237</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E57" t="n">
-        <v>91.47499999999999</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 13:53:03</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>17-11-2025 14:23:03</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>17-11-2025 14:23:03</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:28</t>
+          <t>18-11-2025 09:27:08</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>10977</v>
+        <v>22091</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4964,17 +4957,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>76</v>
-      </c>
-      <c r="O57" t="n">
-        <v>40623</v>
+        <v>70</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -4982,62 +4977,62 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>40623</v>
+        <v>40651</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-1.368385416666667</v>
+        <v>-8.393848379629629</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254365</v>
+        <v>253614</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E58" t="n">
-        <v>67.53333333333333</v>
+        <v>122.45</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:28</t>
+          <t>18-11-2025 09:27:08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14-11-2025 09:28:28</t>
+          <t>18-11-2025 10:22:08</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14-11-2025 09:28:28</t>
+          <t>18-11-2025 10:22:08</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:00</t>
+          <t>18-11-2025 12:24:35</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>8104</v>
+        <v>14694</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5046,14 +5041,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5063,23 +5058,23 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-0.4416724537037037</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>253650</v>
+        <v>254910</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5088,33 +5083,33 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>273.1333333333333</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:00</t>
+          <t>18-11-2025 12:24:35</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:00</t>
+          <t>18-11-2025 13:04:35</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:00</t>
+          <t>18-11-2025 13:04:35</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17-11-2025 07:43:08</t>
+          <t>18-11-2025 14:18:07</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>32776</v>
+        <v>8824</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5123,11 +5118,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
         <v>76</v>
@@ -5140,58 +5135,58 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-18.32162615740741</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>254555</v>
+        <v>254339</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E60" t="n">
-        <v>172.9833333333333</v>
+        <v>245.9666666666667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17-11-2025 07:43:08</t>
+          <t>18-11-2025 14:18:07</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:08</t>
+          <t>18-11-2025 14:58:07</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:08</t>
+          <t>18-11-2025 14:58:07</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>17-11-2025 10:53:07</t>
+          <t>19-11-2025 11:04:05</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>20758</v>
+        <v>29516</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5200,17 +5195,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>76</v>
-      </c>
-      <c r="O60" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5220,58 +5212,58 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0</v>
+        <v>-20.46117476851852</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254451</v>
+        <v>254101</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E61" t="n">
-        <v>321.1416666666667</v>
+        <v>28.425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>17-11-2025 10:53:07</t>
+          <t>19-11-2025 11:04:05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:07</t>
+          <t>19-11-2025 11:34:05</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:07</t>
+          <t>19-11-2025 11:34:05</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>18-11-2025 08:46:16</t>
+          <t>19-11-2025 12:02:31</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>38537</v>
+        <v>3411</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5280,11 +5272,11 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
@@ -5297,58 +5289,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-10.36546296296296</v>
+        <v>-16.50174768518519</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254598</v>
+        <v>254100</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E62" t="n">
-        <v>104.2583333333333</v>
+        <v>28.425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>18-11-2025 08:46:16</t>
+          <t>19-11-2025 12:02:31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18-11-2025 09:21:16</t>
+          <t>19-11-2025 12:27:31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>18-11-2025 09:21:16</t>
+          <t>19-11-2025 12:27:31</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>18-11-2025 11:05:31</t>
+          <t>19-11-2025 12:55:56</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>12511</v>
+        <v>3411</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5357,11 +5349,11 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
@@ -5374,58 +5366,58 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>0</v>
+        <v>-16.53884837962963</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254941</v>
+        <v>254354</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E63" t="n">
-        <v>35.5</v>
+        <v>18.675</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>19-11-2025 12:55:56</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:00</t>
+          <t>19-11-2025 13:25:56</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:00</t>
+          <t>19-11-2025 13:25:56</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>14-11-2025 08:20:30</t>
+          <t>19-11-2025 13:44:37</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>4260</v>
+        <v>2241</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5438,21 +5430,16 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>152</v>
-      </c>
-      <c r="O63" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -5460,54 +5447,54 @@
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-1.347569444444444</v>
+        <v>-5.572650462962963</v>
       </c>
       <c r="T63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254429</v>
+        <v>253974</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>240.2416666666667</v>
+        <v>28.425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14-11-2025 08:20:30</t>
+          <t>19-11-2025 13:44:37</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14-11-2025 08:55:30</t>
+          <t>19-11-2025 14:14:37</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14-11-2025 08:55:30</t>
+          <t>19-11-2025 14:14:37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>14-11-2025 12:55:44</t>
+          <t>19-11-2025 14:43:02</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>28829</v>
+        <v>3411</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5516,18 +5503,15 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
       </c>
-      <c r="O64" t="n">
-        <v>406372</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -5536,11 +5520,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>29-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-9</v>
+        <v>-21.61322337962963</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -5548,46 +5532,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>235572</v>
+        <v>254365</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E65" t="n">
-        <v>82.98333333333333</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>14-11-2025 12:55:44</t>
+          <t>19-11-2025 14:43:02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14-11-2025 13:20:44</t>
+          <t>20-11-2025 07:13:02</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>14-11-2025 13:20:44</t>
+          <t>20-11-2025 07:13:02</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:43</t>
+          <t>20-11-2025 08:20:34</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>9958</v>
+        <v>8104</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5596,7 +5580,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -5605,9 +5589,6 @@
       <c r="N65" t="n">
         <v>70</v>
       </c>
-      <c r="O65" t="n">
-        <v>406372</v>
-      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -5616,23 +5597,23 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>-744</v>
+        <v>-6.347621527777778</v>
       </c>
       <c r="T65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254381</v>
+        <v>254714</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5641,33 +5622,33 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>83.86666666666666</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:43</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>17-11-2025 07:18:43</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>17-11-2025 07:18:43</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>17-11-2025 08:42:35</t>
+          <t>14-11-2025 08:50:28</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>10064</v>
+        <v>10977</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5676,75 +5657,80 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>70</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O66" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-20.36291087962963</v>
+        <v>-1.368385416666667</v>
       </c>
       <c r="T66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>254519</v>
+        <v>253865</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E67" t="n">
-        <v>77.15833333333333</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17-11-2025 08:42:35</t>
+          <t>14-11-2025 08:50:28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:35</t>
+          <t>14-11-2025 09:28:28</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:35</t>
+          <t>14-11-2025 09:28:28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>17-11-2025 10:34:45</t>
+          <t>14-11-2025 11:25:14</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>9259</v>
+        <v>14011</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5753,11 +5739,11 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
@@ -5770,58 +5756,58 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-10.44079861111111</v>
+        <v>-25.47585648148148</v>
       </c>
       <c r="T67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254586</v>
+        <v>254519</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E68" t="n">
-        <v>51.54166666666666</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17-11-2025 10:34:45</t>
+          <t>14-11-2025 11:25:14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17-11-2025 11:09:45</t>
+          <t>14-11-2025 11:44:14</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>17-11-2025 11:09:45</t>
+          <t>14-11-2025 11:44:14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17-11-2025 12:01:17</t>
+          <t>14-11-2025 13:01:23</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>6185</v>
+        <v>9259</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5830,7 +5816,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -5847,23 +5833,23 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>-3.500896990740741</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254088</v>
+        <v>254915</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5872,37 +5858,37 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E69" t="n">
-        <v>425.2166666666666</v>
+        <v>48.875</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17-11-2025 12:01:17</t>
+          <t>14-11-2025 13:01:23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:17</t>
+          <t>14-11-2025 13:18:23</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:17</t>
+          <t>14-11-2025 13:18:23</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18-11-2025 11:46:30</t>
+          <t>14-11-2025 14:07:16</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>51026</v>
+        <v>5865</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5911,14 +5897,11 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
-      <c r="O69" t="n">
-        <v>406372</v>
-      </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
@@ -5927,19 +5910,19 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254903</v>
+        <v>254941</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5948,37 +5931,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E70" t="n">
-        <v>256.6416666666667</v>
+        <v>35.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:46:30</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18-11-2025 12:26:30</t>
+          <t>14-11-2025 07:45:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>18-11-2025 12:26:30</t>
+          <t>14-11-2025 07:45:00</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>19-11-2025 08:43:09</t>
+          <t>14-11-2025 08:20:30</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>30797</v>
+        <v>4260</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5991,24 +5974,29 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>70</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O70" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>0</v>
+        <v>-1.347569444444444</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6016,7 +6004,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254419</v>
+        <v>254381</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6025,37 +6013,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E71" t="n">
-        <v>72.34166666666667</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>19-11-2025 08:43:09</t>
+          <t>14-11-2025 08:20:30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>19-11-2025 09:13:09</t>
+          <t>14-11-2025 08:55:30</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>19-11-2025 09:13:09</t>
+          <t>14-11-2025 08:55:30</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>19-11-2025 10:25:29</t>
+          <t>14-11-2025 10:19:22</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>8681</v>
+        <v>10064</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6064,11 +6052,11 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>70</v>
@@ -6081,11 +6069,11 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-19.43436921296296</v>
+        <v>-7.430115740740741</v>
       </c>
       <c r="T71" t="n">
         <v>7</v>
@@ -6093,46 +6081,46 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254715</v>
+        <v>254429</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>35</v>
       </c>
       <c r="E72" t="n">
-        <v>134.5416666666667</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 10:19:22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 10:54:22</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 10:54:22</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 14:54:36</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>16145</v>
+        <v>28829</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6141,33 +6129,31 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-1.409403935185185</v>
+        <v>-9</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -6175,46 +6161,46 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254287</v>
+        <v>253382</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E73" t="n">
-        <v>129.6333333333333</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 14:54:36</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>17-11-2025 07:34:36</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>17-11-2025 07:34:36</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>17-11-2025 08:59:42</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>15556</v>
+        <v>10212</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6230,10 +6216,10 @@
         <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O73" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -6243,140 +6229,138 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="T73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254427</v>
+        <v>254437</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E74" t="n">
-        <v>55.55833333333333</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>17-11-2025 08:59:42</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>17-11-2025 09:34:42</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>17-11-2025 09:34:42</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>17-11-2025 10:32:46</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>6667</v>
+        <v>6967</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
       <c r="O74" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406552</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-4.590092592592592</v>
+        <v>-2</v>
       </c>
       <c r="T74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254574</v>
+        <v>254451</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E75" t="n">
-        <v>173.6083333333333</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>17-11-2025 10:32:46</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>17-11-2025 11:02:46</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>17-11-2025 11:02:46</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>18-11-2025 08:23:54</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>20833</v>
+        <v>38537</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6385,7 +6369,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -6394,9 +6378,6 @@
       <c r="N75" t="n">
         <v>70</v>
       </c>
-      <c r="O75" t="n">
-        <v>406422</v>
-      </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
@@ -6405,58 +6386,58 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-7</v>
+        <v>-0.3499363425925926</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254245</v>
+        <v>254598</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E76" t="n">
-        <v>89.8</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>18-11-2025 08:23:54</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:13:20</t>
+          <t>18-11-2025 09:38:54</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:13:20</t>
+          <t>18-11-2025 09:38:54</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:08</t>
+          <t>18-11-2025 11:23:10</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>10776</v>
+        <v>12511</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6465,11 +6446,11 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N76" t="n">
         <v>70</v>
@@ -6482,58 +6463,58 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>-18.48829282407407</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254356</v>
+        <v>254756</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E77" t="n">
-        <v>179.6</v>
+        <v>60.625</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:08</t>
+          <t>18-11-2025 11:23:10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:08:08</t>
+          <t>18-11-2025 12:08:10</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:08:08</t>
+          <t>18-11-2025 12:08:10</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:44</t>
+          <t>18-11-2025 13:08:47</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>21552</v>
+        <v>7275</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6542,11 +6523,11 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
@@ -6559,58 +6540,58 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>-10.29704282407407</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>253961</v>
+        <v>254433</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E78" t="n">
-        <v>35.91666666666666</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:44</t>
+          <t>18-11-2025 13:08:47</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:32:44</t>
+          <t>18-11-2025 14:08:47</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:32:44</t>
+          <t>18-11-2025 14:08:47</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18-11-2025 08:08:39</t>
+          <t>19-11-2025 07:16:38</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>4310</v>
+        <v>8142</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6623,11 +6604,14 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
+      <c r="O78" t="n">
+        <v>406552</v>
+      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
@@ -6636,19 +6620,19 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-7.339346064814815</v>
+        <v>-2</v>
       </c>
       <c r="T78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>252811</v>
+        <v>254715</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6657,37 +6641,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E79" t="n">
-        <v>11.875</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:08:39</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:38:39</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:38:39</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:50:32</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1425</v>
+        <v>16145</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6696,36 +6680,41 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>70</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O79" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-15.36842592592593</v>
+        <v>-1.409403935185185</v>
       </c>
       <c r="T79" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254651</v>
+        <v>254287</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -6734,37 +6723,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D80" t="n">
         <v>35</v>
       </c>
       <c r="E80" t="n">
-        <v>22.64166666666667</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18-11-2025 08:50:32</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18-11-2025 09:25:32</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18-11-2025 09:25:32</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18-11-2025 09:48:10</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>2717</v>
+        <v>15556</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6782,6 +6771,9 @@
       <c r="N80" t="n">
         <v>70</v>
       </c>
+      <c r="O80" t="n">
+        <v>406422</v>
+      </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
@@ -6790,19 +6782,19 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="T80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>254652</v>
+        <v>254427</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6815,71 +6807,76 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E81" t="n">
-        <v>28.73333333333333</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>18-11-2025 09:48:10</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18-11-2025 10:18:10</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>18-11-2025 10:18:10</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>18-11-2025 10:46:54</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3448</v>
+        <v>6667</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
         <v>70</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
+      <c r="O81" t="n">
+        <v>406422</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>0</v>
+        <v>-4.590092592592592</v>
       </c>
       <c r="T81" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254756</v>
+        <v>254574</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6888,37 +6885,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E82" t="n">
-        <v>60.625</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>18-11-2025 10:46:54</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18-11-2025 11:36:54</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>18-11-2025 11:36:54</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18-11-2025 12:37:32</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>7275</v>
+        <v>20833</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6927,15 +6924,18 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
         <v>70</v>
       </c>
+      <c r="O82" t="n">
+        <v>406422</v>
+      </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
@@ -6944,11 +6944,11 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-4.526064814814815</v>
+        <v>-7</v>
       </c>
       <c r="T82" t="n">
         <v>7</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>254910</v>
+        <v>254460</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -6965,37 +6965,37 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E83" t="n">
-        <v>73.53333333333333</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>18-11-2025 12:37:32</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18-11-2025 13:32:32</t>
+          <t>17-11-2025 10:13:20</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18-11-2025 13:32:32</t>
+          <t>17-11-2025 10:13:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>18-11-2025 14:46:04</t>
+          <t>17-11-2025 11:00:01</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>8824</v>
+        <v>5602</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -7021,19 +7021,19 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>0</v>
+        <v>-25.45835069444444</v>
       </c>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254101</v>
+        <v>254245</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7042,37 +7042,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>40</v>
       </c>
       <c r="E84" t="n">
-        <v>28.425</v>
+        <v>89.8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>18-11-2025 14:46:04</t>
+          <t>17-11-2025 11:00:01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19-11-2025 07:26:04</t>
+          <t>17-11-2025 11:40:01</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>19-11-2025 07:26:04</t>
+          <t>17-11-2025 11:40:01</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>19-11-2025 07:54:29</t>
+          <t>17-11-2025 13:09:49</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3411</v>
+        <v>10776</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7081,11 +7081,11 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N84" t="n">
         <v>70</v>
@@ -7098,19 +7098,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
-        <v>-26.32950810185185</v>
+        <v>-18.54848958333333</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>254100</v>
+        <v>254356</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7119,37 +7119,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>25</v>
       </c>
       <c r="E85" t="n">
-        <v>28.425</v>
+        <v>179.6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>19-11-2025 07:54:29</t>
+          <t>17-11-2025 13:09:49</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19-11-2025 08:19:29</t>
+          <t>17-11-2025 13:34:49</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>19-11-2025 08:19:29</t>
+          <t>17-11-2025 13:34:49</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>19-11-2025 08:47:55</t>
+          <t>18-11-2025 08:34:25</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>3411</v>
+        <v>21552</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7158,11 +7158,11 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N85" t="n">
         <v>70</v>
@@ -7175,19 +7175,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>-26.3666087962963</v>
+        <v>-10.35723958333333</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>254252</v>
+        <v>253961</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7196,37 +7196,37 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
-        <v>80.51666666666667</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>19-11-2025 08:47:55</t>
+          <t>18-11-2025 08:34:25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>19-11-2025 09:22:55</t>
+          <t>18-11-2025 08:59:25</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>19-11-2025 09:22:55</t>
+          <t>18-11-2025 08:59:25</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>19-11-2025 10:43:26</t>
+          <t>18-11-2025 09:35:20</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>9662</v>
+        <v>4310</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7252,11 +7252,11 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>-26.44682870370371</v>
+        <v>-7.399542824074074</v>
       </c>
       <c r="T86" t="n">
         <v>4</v>
@@ -7264,7 +7264,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>254354</v>
+        <v>252811</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7273,37 +7273,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D87" t="n">
         <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>18.675</v>
+        <v>11.875</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>19-11-2025 10:43:26</t>
+          <t>18-11-2025 09:35:20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19-11-2025 11:13:26</t>
+          <t>18-11-2025 10:05:20</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>19-11-2025 11:13:26</t>
+          <t>18-11-2025 10:05:20</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>19-11-2025 11:32:06</t>
+          <t>18-11-2025 10:17:13</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>2241</v>
+        <v>1425</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7329,19 +7329,19 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>-15.48063078703704</v>
+        <v>-5.428622685185185</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>253906</v>
+        <v>254651</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7350,37 +7350,37 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E88" t="n">
-        <v>45.79166666666666</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>19-11-2025 11:32:06</t>
+          <t>18-11-2025 10:17:13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19-11-2025 12:12:06</t>
+          <t>18-11-2025 10:52:13</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>19-11-2025 12:12:06</t>
+          <t>18-11-2025 10:52:13</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>19-11-2025 12:57:54</t>
+          <t>18-11-2025 11:14:51</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>5495</v>
+        <v>2717</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
         <v>70</v>
@@ -7406,58 +7406,58 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>25-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>254521</v>
+        <v>254586</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E89" t="n">
-        <v>39.68333333333333</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 11:14:51</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 11:49:51</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 11:49:51</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:39:41</t>
+          <t>18-11-2025 12:41:24</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4762</v>
+        <v>6185</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -7483,58 +7483,58 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>254117</v>
+        <v>254893</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E90" t="n">
-        <v>9.166666666666666</v>
+        <v>46.675</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 12:41:24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 13:06:24</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 13:06:24</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14-11-2025 07:09:10</t>
+          <t>18-11-2025 13:53:04</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1100</v>
+        <v>5601</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7543,14 +7543,14 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M90" t="n">
         <v>3</v>
       </c>
       <c r="N90" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7560,11 +7560,11 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
-        <v>-35.2980324074074</v>
+        <v>0</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
@@ -7572,11 +7572,11 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>252980</v>
+        <v>254521</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7588,46 +7588,46 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>17.075</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:09:10</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:09:10</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:09:10</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:26:14</t>
+          <t>12-11-2025 07:39:41</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2049</v>
+        <v>4762</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -7637,14 +7637,168 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
-        <v>-77.3098900462963</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>17.075</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>2049</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>08-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S92" s="1" t="n">
+        <v>-67.30352430555556</v>
+      </c>
+      <c r="T92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>254117</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>07-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:26:14</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>3</v>
+      </c>
+      <c r="N93" t="n">
+        <v>76</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>20-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>-25.3098900462963</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T93"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254129</v>
+        <v>252999</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>44.5</v>
+        <v>325.8416666666666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>08-07-2025 12:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>08-07-2025 12:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>09-07-2025 09:57:50</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5340</v>
+        <v>39101</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,80 +591,75 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>76</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>06-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-0.553125</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>254385</v>
+        <v>252207</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>27-06-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>52.08333333333334</v>
+        <v>51.55</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>08-07-2025 12:27:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>08-07-2025 12:27:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>08-07-2025 13:18:33</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6250</v>
+        <v>6186</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -673,80 +668,75 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>152</v>
-      </c>
-      <c r="O3" t="n">
-        <v>40627</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40627</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>26-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0</v>
+        <v>-12.55454861111111</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254713</v>
+        <v>252723</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>49.96666666666667</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>08-07-2025 13:18:33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>08-07-2025 13:43:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>08-07-2025 13:43:33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>09-07-2025 08:17:30</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5996</v>
+        <v>18475</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -759,76 +749,71 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
       </c>
-      <c r="O4" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>31-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-1.335104166666667</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>243569</v>
+        <v>251231</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E5" t="n">
-        <v>21.675</v>
+        <v>312.3083333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>09-07-2025 08:17:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>09-07-2025 09:03:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>09-07-2025 09:03:30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>09-07-2025 14:15:49</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2601</v>
+        <v>37477</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -837,78 +822,82 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>76</v>
-      </c>
-      <c r="O5" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>40034 (esterno)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>40034</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>03-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-429</v>
+        <v>-6.59431712962963</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>254675</v>
+        <v>252277</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>09-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>153.9583333333333</v>
+        <v>144.925</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>09-07-2025 14:15:49</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:13</t>
+          <t>09-07-2025 14:46:49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:13</t>
+          <t>09-07-2025 14:46:49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:34:11</t>
+          <t>10-07-2025 09:11:44</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18475</v>
+        <v>17391</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,78 +906,82 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>40024 (esterno)</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>40024</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>20-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-4</v>
+        <v>-20.38315393518518</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254546</v>
+        <v>252085</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>109.4083333333333</v>
+        <v>28.55</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:34:11</t>
+          <t>10-07-2025 09:11:44</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:06:11</t>
+          <t>10-07-2025 09:38:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:06:11</t>
+          <t>10-07-2025 09:38:44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:35</t>
+          <t>10-07-2025 10:07:17</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13129</v>
+        <v>3426</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1006,9 +999,6 @@
       <c r="N7" t="n">
         <v>70</v>
       </c>
-      <c r="O7" t="n">
-        <v>406242</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1017,58 +1007,58 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>18-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-7</v>
+        <v>-22.42173032407407</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>244023</v>
+        <v>252298</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>01-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>8.308333333333334</v>
+        <v>70.76666666666667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:35</t>
+          <t>10-07-2025 10:07:17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:14:35</t>
+          <t>10-07-2025 10:51:17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:14:35</t>
+          <t>10-07-2025 10:51:17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:22:54</t>
+          <t>10-07-2025 12:02:03</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>997</v>
+        <v>8492</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1077,17 +1067,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>70</v>
-      </c>
-      <c r="O8" t="n">
-        <v>406062</v>
+        <v>76</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1097,58 +1084,58 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>23-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-417</v>
+        <v>-17.50142939814815</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254256</v>
+        <v>250383</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>50.925</v>
+        <v>24.925</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:22:54</t>
+          <t>10-07-2025 12:02:03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:54</t>
+          <t>10-07-2025 12:29:03</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:54</t>
+          <t>10-07-2025 12:29:03</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:49</t>
+          <t>10-07-2025 12:53:59</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6111</v>
+        <v>2991</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1157,17 +1144,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
-      </c>
-      <c r="O9" t="n">
-        <v>406422</v>
+        <v>76</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1177,58 +1161,58 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>15-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-18</v>
+        <v>-25.53748842592593</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254375</v>
+        <v>252201</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>03-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>45.29166666666666</v>
+        <v>34.10833333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:49</t>
+          <t>10-07-2025 12:53:59</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:51:49</t>
+          <t>10-07-2025 13:22:59</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:51:49</t>
+          <t>10-07-2025 13:22:59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:37:07</t>
+          <t>10-07-2025 13:57:05</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5435</v>
+        <v>4093</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1237,17 +1221,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
-      </c>
-      <c r="O10" t="n">
-        <v>40624</v>
+        <v>76</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1257,11 +1238,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-12</v>
+        <v>-20.58131365740741</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -1269,46 +1250,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254512</v>
+        <v>252364</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>59.55833333333333</v>
+        <v>116.4833333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 08:37:07</t>
+          <t>10-07-2025 13:57:05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:13:07</t>
+          <t>10-07-2025 14:39:05</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:13:07</t>
+          <t>10-07-2025 14:39:05</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:12:40</t>
+          <t>11-07-2025 08:35:34</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7147</v>
+        <v>13978</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1324,10 +1305,7 @@
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>76</v>
-      </c>
-      <c r="O11" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1337,58 +1315,58 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>27-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-6</v>
+        <v>-14.35803819444445</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254188</v>
+        <v>252638</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>09-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>37.44166666666667</v>
+        <v>61.49166666666667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:12:40</t>
+          <t>11-07-2025 08:35:34</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:40</t>
+          <t>11-07-2025 09:02:34</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:40</t>
+          <t>11-07-2025 09:02:34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:07</t>
+          <t>11-07-2025 10:04:04</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4493</v>
+        <v>7379</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1401,14 +1379,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
       </c>
-      <c r="O12" t="n">
-        <v>406372</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1417,58 +1392,58 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>06-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-1</v>
+        <v>-5.41949074074074</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>255039</v>
+        <v>235572</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:07</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:07</t>
+          <t>08-07-2025 12:36:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:07</t>
+          <t>08-07-2025 12:36:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-11-2025 11:52:16</t>
+          <t>08-07-2025 13:58:59</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1098</v>
+        <v>9958</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1477,18 +1452,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
         <v>70</v>
       </c>
-      <c r="O13" t="n">
-        <v>40624</v>
-      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
@@ -1497,58 +1469,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0</v>
+        <v>-610.5826273148148</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254230</v>
+        <v>251849</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>62.475</v>
+        <v>33.38333333333333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17-11-2025 11:52:16</t>
+          <t>08-07-2025 13:58:59</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:16</t>
+          <t>08-07-2025 14:21:59</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:16</t>
+          <t>08-07-2025 14:21:59</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:11:44</t>
+          <t>08-07-2025 14:55:22</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7497</v>
+        <v>4006</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1561,74 +1533,78 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
         <v>70</v>
       </c>
-      <c r="O14" t="n">
-        <v>406552</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>40042 (esterno)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>40042</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>25-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-14</v>
+        <v>-13.62178240740741</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254198</v>
+        <v>250284</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>146.35</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17-11-2025 13:11:44</t>
+          <t>08-07-2025 14:55:22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17-11-2025 13:43:44</t>
+          <t>09-07-2025 07:16:22</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17-11-2025 13:43:44</t>
+          <t>09-07-2025 07:16:22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18-11-2025 09:18:44</t>
+          <t>09-07-2025 09:42:43</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>25800</v>
+        <v>17562</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1641,10 +1617,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1654,62 +1630,62 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-19.3880150462963</v>
+        <v>-119.4046643518518</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254173</v>
+        <v>244023</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>202.5916666666667</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18-11-2025 09:18:44</t>
+          <t>09-07-2025 09:42:43</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18-11-2025 09:52:44</t>
+          <t>09-07-2025 10:01:43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18-11-2025 09:52:44</t>
+          <t>09-07-2025 10:01:43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-11-2025 13:15:20</t>
+          <t>09-07-2025 10:10:01</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24311</v>
+        <v>997</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1718,10 +1694,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1731,58 +1707,58 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-29.55231481481481</v>
+        <v>-282.4236284722222</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254652</v>
+        <v>252220</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>28.73333333333333</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18-11-2025 13:15:20</t>
+          <t>09-07-2025 10:10:01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18-11-2025 13:53:20</t>
+          <t>09-07-2025 10:29:01</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18-11-2025 13:53:20</t>
+          <t>09-07-2025 10:29:01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18-11-2025 14:22:04</t>
+          <t>09-07-2025 11:49:32</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3448</v>
+        <v>9662</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1808,58 +1784,58 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>16-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0</v>
+        <v>-23.49273726851852</v>
       </c>
       <c r="T17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254605</v>
+        <v>252087</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>39.025</v>
+        <v>35.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18-11-2025 14:22:04</t>
+          <t>09-07-2025 11:49:32</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:04</t>
+          <t>09-07-2025 12:06:32</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:04</t>
+          <t>09-07-2025 12:06:32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19-11-2025 07:18:05</t>
+          <t>09-07-2025 12:42:02</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4683</v>
+        <v>4260</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1868,11 +1844,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
         <v>70</v>
@@ -1885,58 +1861,58 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>29-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0</v>
+        <v>-10.52919560185185</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254653</v>
+        <v>245089</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E19" t="n">
-        <v>64.40833333333333</v>
+        <v>1022.208333333333</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19-11-2025 07:18:05</t>
+          <t>09-07-2025 12:42:02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19-11-2025 07:35:05</t>
+          <t>09-07-2025 13:14:02</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19-11-2025 07:35:05</t>
+          <t>09-07-2025 13:14:02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19-11-2025 08:39:30</t>
+          <t>11-07-2025 14:16:15</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7729</v>
+        <v>122665</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1945,14 +1921,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1962,58 +1938,58 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>31-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>254165</v>
+        <v>252209</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>58.31666666666667</v>
+        <v>29.19166666666667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>11-07-2025 14:16:15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>11-07-2025 14:33:15</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>11-07-2025 14:33:15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>14-07-2025 07:02:26</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6998</v>
+        <v>3503</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2022,80 +1998,75 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
         <v>76</v>
       </c>
-      <c r="O20" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P20" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>26-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.3613310185185185</v>
+        <v>-18.29336226851852</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254156</v>
+        <v>252378</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>87.47499999999999</v>
+        <v>37.55833333333333</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>14-07-2025 07:02:26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:19</t>
+          <t>14-07-2025 07:21:26</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:19</t>
+          <t>14-07-2025 07:21:26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-11-2025 10:32:47</t>
+          <t>14-07-2025 07:59:00</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10497</v>
+        <v>4507</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2104,80 +2075,75 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>76</v>
       </c>
-      <c r="O21" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P21" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-0.4394386574074074</v>
+        <v>-10.33263888888889</v>
       </c>
       <c r="T21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>253382</v>
+        <v>252362</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>85.09999999999999</v>
+        <v>39.95</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14-11-2025 10:32:47</t>
+          <t>14-07-2025 07:59:00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14-11-2025 10:59:47</t>
+          <t>14-07-2025 08:14:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-11-2025 10:59:47</t>
+          <t>14-07-2025 08:14:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-11-2025 12:24:53</t>
+          <t>14-07-2025 08:53:57</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10212</v>
+        <v>4794</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2186,18 +2152,15 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
         <v>76</v>
       </c>
-      <c r="O22" t="n">
-        <v>406372</v>
-      </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
@@ -2206,11 +2169,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-12</v>
+        <v>-10.37079861111111</v>
       </c>
       <c r="T22" t="n">
         <v>2</v>
@@ -2218,46 +2181,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254451</v>
+        <v>252814</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>321.1416666666667</v>
+        <v>50.08333333333334</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-11-2025 12:24:53</t>
+          <t>14-07-2025 08:53:57</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-11-2025 13:08:53</t>
+          <t>14-07-2025 09:10:57</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-11-2025 13:08:53</t>
+          <t>14-07-2025 09:10:57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-11-2025 10:30:02</t>
+          <t>14-07-2025 10:01:02</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>38537</v>
+        <v>6010</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2270,10 +2233,10 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2283,58 +2246,58 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>14-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0</v>
+        <v>-0.4173842592592593</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254309</v>
+        <v>243569</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>900.0166666666667</v>
+        <v>21.675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17-11-2025 10:30:02</t>
+          <t>14-07-2025 10:01:02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17-11-2025 11:12:02</t>
+          <t>14-07-2025 10:18:02</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-11-2025 11:12:02</t>
+          <t>14-07-2025 10:18:02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-11-2025 10:12:03</t>
+          <t>14-07-2025 10:39:42</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>108002</v>
+        <v>2601</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2343,14 +2306,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2360,58 +2323,58 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-9.425034722222222</v>
+        <v>-301.4442418981482</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254252</v>
+        <v>251812</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>80.51666666666667</v>
+        <v>33.875</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19-11-2025 10:12:03</t>
+          <t>14-07-2025 10:39:42</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19-11-2025 10:58:03</t>
+          <t>14-07-2025 10:58:42</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19-11-2025 10:58:03</t>
+          <t>14-07-2025 10:58:42</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-11-2025 12:18:34</t>
+          <t>14-07-2025 11:32:35</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9662</v>
+        <v>4065</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2420,14 +2383,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2437,11 +2400,11 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>23-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-16.51289351851852</v>
+        <v>-21.48096064814815</v>
       </c>
       <c r="T25" t="n">
         <v>4</v>
@@ -2449,46 +2412,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254419</v>
+        <v>252426</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>72.34166666666667</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19-11-2025 12:18:34</t>
+          <t>14-07-2025 11:32:35</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19-11-2025 12:49:34</t>
+          <t>14-07-2025 12:04:35</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19-11-2025 12:49:34</t>
+          <t>14-07-2025 12:04:35</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19-11-2025 14:01:54</t>
+          <t>15-07-2025 07:08:52</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8681</v>
+        <v>22114</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2501,7 +2464,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>70</v>
@@ -2514,58 +2477,58 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>02-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-9.584658564814815</v>
+        <v>-13.29782407407407</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>253974</v>
+        <v>252598</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>28.425</v>
+        <v>149.625</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19-11-2025 14:01:54</t>
+          <t>15-07-2025 07:08:52</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19-11-2025 14:30:54</t>
+          <t>15-07-2025 07:23:52</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-11-2025 14:30:54</t>
+          <t>15-07-2025 07:23:52</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-11-2025 14:59:20</t>
+          <t>15-07-2025 09:53:29</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3411</v>
+        <v>17955</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2574,11 +2537,11 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>70</v>
@@ -2591,11 +2554,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>29-10-2025 00:00:00</t>
+          <t>10-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-21.62453703703704</v>
+        <v>-5.412146990740741</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -2603,46 +2566,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254547</v>
+        <v>252547</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E28" t="n">
-        <v>68.55</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19-11-2025 14:59:20</t>
+          <t>15-07-2025 09:53:29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20-11-2025 07:28:20</t>
+          <t>15-07-2025 10:14:29</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>20-11-2025 07:28:20</t>
+          <t>15-07-2025 10:14:29</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20-11-2025 08:36:53</t>
+          <t>15-07-2025 11:35:39</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>8226</v>
+        <v>9740</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2655,7 +2618,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
         <v>70</v>
@@ -2668,58 +2631,58 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-1.358946759259259</v>
+        <v>-11.48309606481481</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>254166</v>
+        <v>252470</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>38.85</v>
+        <v>62.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20-11-2025 08:36:53</t>
+          <t>15-07-2025 11:35:39</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20-11-2025 09:03:53</t>
+          <t>15-07-2025 11:52:39</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20-11-2025 09:03:53</t>
+          <t>15-07-2025 11:52:39</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20-11-2025 09:42:44</t>
+          <t>15-07-2025 12:55:09</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4662</v>
+        <v>7500</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2732,7 +2695,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
@@ -2745,19 +2708,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0</v>
+        <v>-11.53830439814815</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>253380</v>
+        <v>251926</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2766,37 +2729,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>104.275</v>
+        <v>78.91666666666667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>15-07-2025 12:55:09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:00</t>
+          <t>15-07-2025 13:16:09</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:00</t>
+          <t>15-07-2025 13:16:09</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-11-2025 09:30:16</t>
+          <t>15-07-2025 14:35:04</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>12513</v>
+        <v>9470</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2805,41 +2768,36 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
-      <c r="O30" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P30" t="n">
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>09-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-0.3960243055555556</v>
+        <v>-6.607690972222223</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>250284</v>
+        <v>251495</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2848,37 +2806,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>146.35</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14-11-2025 09:30:16</t>
+          <t>15-07-2025 14:35:04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14-11-2025 09:47:16</t>
+          <t>15-07-2025 14:52:04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-11-2025 09:47:16</t>
+          <t>15-07-2025 14:52:04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14-11-2025 12:13:37</t>
+          <t>16-07-2025 08:04:25</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>17562</v>
+        <v>8681</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2891,14 +2849,11 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="O31" t="n">
-        <v>406422</v>
-      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -2907,19 +2862,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>09-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-254</v>
+        <v>-7.336400462962963</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254293</v>
+        <v>252656</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2928,37 +2883,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
-        <v>18.85</v>
+        <v>189.8666666666667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14-11-2025 12:13:37</t>
+          <t>16-07-2025 08:04:25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14-11-2025 12:32:37</t>
+          <t>16-07-2025 08:25:25</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-11-2025 12:32:37</t>
+          <t>16-07-2025 08:25:25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-11-2025 12:51:28</t>
+          <t>16-07-2025 11:35:17</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2262</v>
+        <v>22784</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2967,18 +2922,15 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
       </c>
-      <c r="O32" t="n">
-        <v>40624</v>
-      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
@@ -2987,19 +2939,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>14-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-14</v>
+        <v>-2.482835648148148</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254088</v>
+        <v>252576</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3008,57 +2960,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>425.2166666666666</v>
+        <v>374.0666666666667</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14-11-2025 12:51:28</t>
+          <t>16-07-2025 11:35:17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14-11-2025 13:18:28</t>
+          <t>16-07-2025 11:50:17</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14-11-2025 13:18:28</t>
+          <t>16-07-2025 11:50:17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-11-2025 12:23:41</t>
+          <t>17-07-2025 10:04:21</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>51026</v>
+        <v>44888</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
-      <c r="O33" t="n">
-        <v>406372</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3067,11 +3016,11 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>15-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-30</v>
+        <v>-2.4196875</v>
       </c>
       <c r="T33" t="n">
         <v>2</v>
@@ -3079,7 +3028,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254189</v>
+        <v>252779</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3088,37 +3037,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>15-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>55.875</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17-11-2025 12:23:41</t>
+          <t>17-07-2025 10:04:21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17-11-2025 12:42:41</t>
+          <t>17-07-2025 10:19:21</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17-11-2025 12:42:41</t>
+          <t>17-07-2025 10:19:21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17-11-2025 13:38:34</t>
+          <t>17-07-2025 13:23:38</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6705</v>
+        <v>22114</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3127,7 +3076,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -3136,9 +3085,6 @@
       <c r="N34" t="n">
         <v>70</v>
       </c>
-      <c r="O34" t="n">
-        <v>406552</v>
-      </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
@@ -3147,19 +3093,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>21-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254457</v>
+        <v>252778</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3168,37 +3114,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>16-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>3.925</v>
+        <v>160.9916666666667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17-11-2025 13:38:34</t>
+          <t>17-07-2025 13:23:38</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17-11-2025 13:57:34</t>
+          <t>17-07-2025 13:42:38</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17-11-2025 13:57:34</t>
+          <t>17-07-2025 13:42:38</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17-11-2025 14:01:29</t>
+          <t>18-07-2025 08:23:37</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>471</v>
+        <v>19319</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3216,9 +3162,6 @@
       <c r="N35" t="n">
         <v>70</v>
       </c>
-      <c r="O35" t="n">
-        <v>406372</v>
-      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
@@ -3227,11 +3170,11 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>21-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
@@ -3239,50 +3182,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254428</v>
+        <v>252665</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>48.30833333333333</v>
+        <v>48.875</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17-11-2025 14:01:29</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17-11-2025 14:24:29</t>
+          <t>08-07-2025 12:32:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17-11-2025 14:24:29</t>
+          <t>08-07-2025 12:32:30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18-11-2025 07:12:48</t>
+          <t>08-07-2025 13:21:22</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5797</v>
+        <v>5865</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3291,29 +3234,24 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
       </c>
-      <c r="O36" t="n">
-        <v>40649</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P36" t="n">
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>02-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-8.300555555555556</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>7</v>
@@ -3321,46 +3259,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254107</v>
+        <v>252713</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E37" t="n">
-        <v>175.0583333333333</v>
+        <v>907.7666666666667</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18-11-2025 07:12:48</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18-11-2025 07:35:48</t>
+          <t>08-07-2025 13:05:00</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18-11-2025 07:35:48</t>
+          <t>08-07-2025 13:05:00</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>18-11-2025 10:30:51</t>
+          <t>10-07-2025 12:12:46</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21007</v>
+        <v>108932</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3369,11 +3307,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3386,58 +3324,58 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>18-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-27.43809606481481</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254599</v>
+        <v>252978</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
-        <v>44.9</v>
+        <v>23.3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18-11-2025 10:30:51</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18-11-2025 10:51:51</t>
+          <t>08-07-2025 12:19:00</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>18-11-2025 10:51:51</t>
+          <t>08-07-2025 12:19:00</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18-11-2025 11:36:45</t>
+          <t>08-07-2025 12:42:18</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>5388</v>
+        <v>2796</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3446,17 +3384,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>70</v>
-      </c>
-      <c r="O38" t="n">
-        <v>406372</v>
+        <v>76</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3466,77 +3401,74 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>16-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-2</v>
+        <v>-22.529375</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>254609</v>
+        <v>245623</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>07-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E39" t="n">
-        <v>416.6666666666667</v>
+        <v>220.1583333333333</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18-11-2025 11:36:45</t>
+          <t>08-07-2025 12:42:18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18-11-2025 12:14:45</t>
+          <t>08-07-2025 13:14:18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18-11-2025 12:14:45</t>
+          <t>08-07-2025 13:14:18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19-11-2025 11:11:25</t>
+          <t>09-07-2025 08:54:27</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>50000</v>
+        <v>26419</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>406552</v>
+        <v>152</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3546,58 +3478,58 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>25-01-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>0</v>
+        <v>-165.3711516203704</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254437</v>
+        <v>252686</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>58.05833333333333</v>
+        <v>329.15</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19-11-2025 11:11:25</t>
+          <t>09-07-2025 08:54:27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-11-2025 11:49:25</t>
+          <t>09-07-2025 09:11:27</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19-11-2025 11:49:25</t>
+          <t>09-07-2025 09:11:27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19-11-2025 12:47:29</t>
+          <t>09-07-2025 14:40:36</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>6967</v>
+        <v>39498</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3606,17 +3538,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>70</v>
-      </c>
-      <c r="O40" t="n">
-        <v>406552</v>
+        <v>152</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3626,11 +3555,11 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>21-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
@@ -3638,46 +3567,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>253885</v>
+        <v>252245</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>105.9333333333333</v>
+        <v>489.7583333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>19-11-2025 12:47:29</t>
+          <t>09-07-2025 14:40:36</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 13:04:29</t>
+          <t>09-07-2025 14:57:36</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>19-11-2025 13:04:29</t>
+          <t>09-07-2025 14:57:36</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>19-11-2025 14:50:25</t>
+          <t>11-07-2025 07:07:22</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>12712</v>
+        <v>58771</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3686,14 +3615,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3703,58 +3632,58 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>27-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-5.618344907407407</v>
+        <v>-14.29678240740741</v>
       </c>
       <c r="T41" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254903</v>
+        <v>252210</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E42" t="n">
-        <v>256.6416666666667</v>
+        <v>29.2</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>19-11-2025 14:50:25</t>
+          <t>11-07-2025 07:07:22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20-11-2025 07:09:25</t>
+          <t>11-07-2025 07:39:22</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20-11-2025 07:09:25</t>
+          <t>11-07-2025 07:39:22</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20-11-2025 11:26:03</t>
+          <t>11-07-2025 08:08:34</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>30797</v>
+        <v>3504</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3763,14 +3692,14 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
         <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3780,11 +3709,11 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>26-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0</v>
+        <v>-15.33928240740741</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -3792,46 +3721,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254758</v>
+        <v>251919</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>20-06-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>61.38333333333333</v>
+        <v>140.05</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20-11-2025 11:26:03</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20-11-2025 11:43:03</t>
+          <t>08-07-2025 12:35:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20-11-2025 11:43:03</t>
+          <t>08-07-2025 12:35:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20-11-2025 12:44:26</t>
+          <t>08-07-2025 14:55:03</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>7366</v>
+        <v>16806</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3840,14 +3769,14 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3857,11 +3786,11 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>16-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0</v>
+        <v>-22.6215625</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -3869,46 +3798,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254481</v>
+        <v>252680</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="E44" t="n">
-        <v>81.16666666666667</v>
+        <v>254.7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>08-07-2025 14:55:03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>09-07-2025 07:30:03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>09-07-2025 07:30:03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>09-07-2025 11:44:45</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9740</v>
+        <v>30564</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3917,29 +3846,24 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>70</v>
-      </c>
-      <c r="O44" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>30-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3951,46 +3875,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254762</v>
+        <v>252519</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>34.5</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>31.85833333333333</v>
+        <v>11.475</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>09-07-2025 11:44:45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>09-07-2025 12:14:45</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>09-07-2025 12:14:45</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>09-07-2025 12:26:13</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>3823</v>
+        <v>1377</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3999,33 +3923,28 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
         <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>70</v>
-      </c>
-      <c r="O45" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>-5.518211805555556</v>
       </c>
       <c r="T45" t="n">
         <v>2</v>
@@ -4033,46 +3952,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>253897</v>
+        <v>252476</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>46.5</v>
+        <v>40</v>
       </c>
       <c r="E46" t="n">
-        <v>94.01666666666667</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>09-07-2025 12:26:13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:31</t>
+          <t>09-07-2025 13:06:13</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:31</t>
+          <t>09-07-2025 13:06:13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:32</t>
+          <t>09-07-2025 14:18:34</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>11282</v>
+        <v>8681</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4085,76 +4004,71 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>76</v>
-      </c>
-      <c r="O46" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>07-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-0.3892650462962963</v>
+        <v>-2.596226851851852</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254291</v>
+        <v>252473</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>09-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>40.5</v>
+        <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>18.85</v>
+        <v>189.8666666666667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:32</t>
+          <t>09-07-2025 14:18:34</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14-11-2025 10:01:02</t>
+          <t>09-07-2025 14:48:34</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>14-11-2025 10:01:02</t>
+          <t>09-07-2025 14:48:34</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14-11-2025 10:19:53</t>
+          <t>10-07-2025 09:58:26</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2262</v>
+        <v>22784</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4163,18 +4077,15 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
         <v>70</v>
       </c>
-      <c r="O47" t="n">
-        <v>40624</v>
-      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -4183,58 +4094,58 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>01-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-14</v>
+        <v>-9.415578703703703</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>252061</v>
+        <v>252662</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>09-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.5</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>36.16666666666666</v>
+        <v>189.8666666666667</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14-11-2025 10:19:53</t>
+          <t>10-07-2025 09:58:26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:23</t>
+          <t>10-07-2025 10:23:26</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:23</t>
+          <t>10-07-2025 10:23:26</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14-11-2025 11:28:33</t>
+          <t>10-07-2025 13:33:18</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>4340</v>
+        <v>22784</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4243,29 +4154,24 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>70</v>
       </c>
-      <c r="O48" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P48" t="n">
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>31-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -4277,46 +4183,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>253694</v>
+        <v>252549</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>09-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E49" t="n">
-        <v>121.7583333333333</v>
+        <v>92.59166666666667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>10-07-2025 13:33:18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>10-07-2025 14:03:18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>10-07-2025 14:03:18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>11-07-2025 07:35:53</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>14611</v>
+        <v>11111</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4329,76 +4235,71 @@
         </is>
       </c>
       <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>70</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>20-07-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>4</v>
-      </c>
-      <c r="N49" t="n">
-        <v>76</v>
-      </c>
-      <c r="O49" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>05-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>-0.6158043981481481</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254556</v>
+        <v>252414</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E50" t="n">
-        <v>173.4166666666667</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>11-07-2025 07:35:53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>11-07-2025 08:20:53</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>11-07-2025 08:20:53</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14-11-2025 10:10:10</t>
+          <t>11-07-2025 09:38:03</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>20810</v>
+        <v>9259</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4407,80 +4308,75 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N50" t="n">
-        <v>76</v>
-      </c>
-      <c r="O50" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>30-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-1.423732638888889</v>
+        <v>-11.40142361111111</v>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254283</v>
+        <v>252157</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E51" t="n">
-        <v>95.76666666666667</v>
+        <v>396.825</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:10:10</t>
+          <t>11-07-2025 09:38:03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:55:10</t>
+          <t>11-07-2025 10:13:03</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:55:10</t>
+          <t>11-07-2025 10:13:03</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:56</t>
+          <t>14-07-2025 08:49:52</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>11492</v>
+        <v>47619</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4489,17 +4385,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N51" t="n">
-        <v>76</v>
-      </c>
-      <c r="O51" t="n">
-        <v>406552</v>
+        <v>70</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4509,58 +4402,58 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>18-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-9</v>
+        <v>-26.36796875</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>253865</v>
+        <v>252507</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="E52" t="n">
-        <v>116.7583333333333</v>
+        <v>102.8833333333333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:56</t>
+          <t>14-07-2025 08:49:52</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:56</t>
+          <t>14-07-2025 09:19:52</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:56</t>
+          <t>14-07-2025 09:19:52</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17-11-2025 07:22:42</t>
+          <t>14-07-2025 11:02:45</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>14011</v>
+        <v>12346</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4569,11 +4462,11 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
         <v>70</v>
@@ -4586,58 +4479,58 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>03-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-28.30743055555556</v>
+        <v>-11.46024884259259</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254106</v>
+        <v>252511</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E53" t="n">
-        <v>107.6416666666667</v>
+        <v>87.45</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17-11-2025 07:22:42</t>
+          <t>14-07-2025 11:02:45</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17-11-2025 07:52:42</t>
+          <t>14-07-2025 11:27:45</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17-11-2025 07:52:42</t>
+          <t>14-07-2025 11:27:45</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-11-2025 09:40:20</t>
+          <t>14-07-2025 12:55:12</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>12917</v>
+        <v>10494</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4646,11 +4539,11 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N53" t="n">
         <v>70</v>
@@ -4663,11 +4556,11 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>03-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-31.4030150462963</v>
+        <v>-11.53833912037037</v>
       </c>
       <c r="T53" t="n">
         <v>7</v>
@@ -4675,46 +4568,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>253838</v>
+        <v>252336</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>108.3666666666667</v>
+        <v>120.275</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17-11-2025 09:40:20</t>
+          <t>14-07-2025 12:55:12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17-11-2025 10:10:20</t>
+          <t>14-07-2025 13:45:12</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-11-2025 10:10:20</t>
+          <t>14-07-2025 13:45:12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17-11-2025 11:58:42</t>
+          <t>15-07-2025 07:45:29</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>13004</v>
+        <v>14433</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4740,58 +4633,58 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-11.49910300925926</v>
+        <v>-11.32325231481481</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254237</v>
+        <v>252334</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E55" t="n">
-        <v>184.0916666666667</v>
+        <v>486.5916666666666</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17-11-2025 11:58:42</t>
+          <t>15-07-2025 07:45:29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-11-2025 12:33:42</t>
+          <t>15-07-2025 08:10:29</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-11-2025 12:33:42</t>
+          <t>15-07-2025 08:10:29</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18-11-2025 07:37:48</t>
+          <t>16-07-2025 08:17:04</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>22091</v>
+        <v>58391</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4800,82 +4693,75 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>70</v>
       </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P55" t="n">
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>04-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-8.317916666666667</v>
+        <v>-12.34519097222222</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254824</v>
+        <v>252467</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
-        <v>748.225</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>18-11-2025 07:37:48</t>
+          <t>16-07-2025 08:17:04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37:48</t>
+          <t>16-07-2025 08:42:04</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37:48</t>
+          <t>16-07-2025 08:42:04</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>19-11-2025 13:06:01</t>
+          <t>16-07-2025 10:03:14</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>89787</v>
+        <v>9740</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4888,13 +4774,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>76</v>
-      </c>
-      <c r="O56" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4904,58 +4787,58 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>17-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>253614</v>
+        <v>252790</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E57" t="n">
-        <v>122.45</v>
+        <v>12.10833333333333</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>19-11-2025 13:06:01</t>
+          <t>16-07-2025 10:03:14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19-11-2025 13:46:01</t>
+          <t>16-07-2025 10:28:14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>19-11-2025 13:46:01</t>
+          <t>16-07-2025 10:28:14</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20-11-2025 07:48:28</t>
+          <t>16-07-2025 10:40:21</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>14694</v>
+        <v>1453</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4964,14 +4847,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4981,58 +4864,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>25-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-0.3253298611111111</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254910</v>
+        <v>252755</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E58" t="n">
-        <v>73.53333333333333</v>
+        <v>109.575</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>20-11-2025 07:48:28</t>
+          <t>16-07-2025 10:40:21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20-11-2025 08:28:28</t>
+          <t>16-07-2025 11:10:21</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20-11-2025 08:28:28</t>
+          <t>16-07-2025 11:10:21</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20-11-2025 09:42:00</t>
+          <t>16-07-2025 12:59:55</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>8824</v>
+        <v>13149</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5048,7 +4931,7 @@
         <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5058,58 +4941,58 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>17-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254433</v>
+        <v>252899</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E59" t="n">
-        <v>67.84999999999999</v>
+        <v>180.5666666666667</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20-11-2025 09:42:00</t>
+          <t>16-07-2025 12:59:55</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20-11-2025 10:27:00</t>
+          <t>16-07-2025 13:29:55</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>20-11-2025 10:27:00</t>
+          <t>16-07-2025 13:29:55</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>20-11-2025 11:34:51</t>
+          <t>17-07-2025 08:30:29</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>8142</v>
+        <v>21668</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5122,7 +5005,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
         <v>70</v>
@@ -5135,58 +5018,58 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>24-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-2.482540509259259</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>254339</v>
+        <v>252371</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>01-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>245.9666666666667</v>
+        <v>50.04166666666666</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20-11-2025 11:34:51</t>
+          <t>08-07-2025 12:00:00</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20-11-2025 12:14:51</t>
+          <t>08-07-2025 12:35:00</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20-11-2025 12:14:51</t>
+          <t>08-07-2025 12:35:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>21-11-2025 08:20:49</t>
+          <t>08-07-2025 13:25:02</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>29516</v>
+        <v>6005</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5195,14 +5078,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5212,58 +5095,58 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>30-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-22.34779513888889</v>
+        <v>-8.559056712962963</v>
       </c>
       <c r="T60" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254101</v>
+        <v>252369</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E61" t="n">
-        <v>28.425</v>
+        <v>19.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>21-11-2025 08:20:49</t>
+          <t>08-07-2025 13:25:02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21-11-2025 08:50:49</t>
+          <t>08-07-2025 14:15:02</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>21-11-2025 08:50:49</t>
+          <t>08-07-2025 14:15:02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>21-11-2025 09:19:15</t>
+          <t>08-07-2025 14:34:14</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3411</v>
+        <v>2304</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5272,14 +5155,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N61" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5289,11 +5172,11 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>27-06-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-18.38836805555556</v>
+        <v>-11.60711226851852</v>
       </c>
       <c r="T61" t="n">
         <v>2</v>
@@ -5301,46 +5184,46 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254100</v>
+        <v>252495</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E62" t="n">
-        <v>28.425</v>
+        <v>70.77500000000001</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>21-11-2025 09:19:15</t>
+          <t>08-07-2025 14:34:14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21-11-2025 09:44:15</t>
+          <t>09-07-2025 07:24:14</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>21-11-2025 09:44:15</t>
+          <t>09-07-2025 07:24:14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>21-11-2025 10:12:40</t>
+          <t>09-07-2025 08:35:01</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3411</v>
+        <v>8493</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5349,14 +5232,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5366,58 +5249,58 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>07-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-18.42546875</v>
+        <v>-2.389924768518518</v>
       </c>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254354</v>
+        <v>252890</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>08-07-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
         <v>30</v>
       </c>
       <c r="E63" t="n">
-        <v>18.675</v>
+        <v>51.7</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:12:40</t>
+          <t>09-07-2025 08:35:01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:42:40</t>
+          <t>09-07-2025 09:05:01</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>21-11-2025 10:42:40</t>
+          <t>09-07-2025 09:05:01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>21-11-2025 11:01:21</t>
+          <t>09-07-2025 09:56:43</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2241</v>
+        <v>6204</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5426,14 +5309,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -5443,2359 +5326,14 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>01-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-7.459270833333333</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>254671</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>35</v>
-      </c>
-      <c r="E64" t="n">
-        <v>136.1666666666667</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>21-11-2025 11:01:21</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>21-11-2025 11:36:21</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>21-11-2025 11:36:21</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>21-11-2025 13:52:31</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>16340</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M64" t="n">
         <v>7</v>
-      </c>
-      <c r="N64" t="n">
-        <v>70</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>21-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S64" s="1" t="n">
-        <v>-0.578136574074074</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>H7</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>50</v>
-      </c>
-      <c r="E65" t="n">
-        <v>45.79166666666666</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>21-11-2025 13:52:31</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>21-11-2025 14:42:31</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>21-11-2025 14:42:31</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>24-11-2025 07:28:18</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>5495</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>2</v>
-      </c>
-      <c r="N65" t="n">
-        <v>70</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>25-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>254714</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>19</v>
-      </c>
-      <c r="E66" t="n">
-        <v>91.47499999999999</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:19:00</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:19:00</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:50:28</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>10977</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>76</v>
-      </c>
-      <c r="O66" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>19-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S66" s="1" t="n">
-        <v>-1.368385416666667</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>253650</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>19</v>
-      </c>
-      <c r="E67" t="n">
-        <v>273.1333333333333</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:50:28</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:09:28</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:09:28</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:42:36</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>32776</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>3</v>
-      </c>
-      <c r="N67" t="n">
-        <v>76</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>30-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S67" s="1" t="n">
-        <v>-15.57125578703704</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>254519</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>34</v>
-      </c>
-      <c r="E68" t="n">
-        <v>77.15833333333333</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:42:36</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:16:36</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:16:36</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:33:46</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>9259</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>3</v>
-      </c>
-      <c r="N68" t="n">
-        <v>70</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>17-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S68" s="1" t="n">
-        <v>-0.3151157407407407</v>
-      </c>
-      <c r="T68" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>254365</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>10-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>19</v>
-      </c>
-      <c r="E69" t="n">
-        <v>67.53333333333333</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:33:46</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:52:46</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:52:46</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:00:18</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>8104</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>5</v>
-      </c>
-      <c r="N69" t="n">
-        <v>70</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>14-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S69" s="1" t="n">
-        <v>-3.375208333333333</v>
-      </c>
-      <c r="T69" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>254598</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>04-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>31</v>
-      </c>
-      <c r="E70" t="n">
-        <v>104.2583333333333</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:00:18</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:31:18</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:31:18</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:15:33</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>12511</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
-        <v>13</v>
-      </c>
-      <c r="N70" t="n">
-        <v>70</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>15-12-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>254915</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>37</v>
-      </c>
-      <c r="E71" t="n">
-        <v>48.875</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:15:33</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:52:33</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:52:33</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:41:26</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>5865</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>2</v>
-      </c>
-      <c r="N71" t="n">
-        <v>70</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>12-01-2026 00:00:00</t>
-        </is>
-      </c>
-      <c r="S71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>254941</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>45</v>
-      </c>
-      <c r="E72" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:45:00</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:45:00</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:20:30</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>4260</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>4</v>
-      </c>
-      <c r="N72" t="n">
-        <v>152</v>
-      </c>
-      <c r="O72" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>14-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S72" s="1" t="n">
-        <v>-1.347569444444444</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>254381</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>35</v>
-      </c>
-      <c r="E73" t="n">
-        <v>83.86666666666666</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:20:30</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:55:30</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>14-11-2025 08:55:30</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:19:22</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>10064</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>CASON ;H7 ;R5</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>3</v>
-      </c>
-      <c r="N73" t="n">
-        <v>70</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>07-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S73" s="1" t="n">
-        <v>-7.430115740740741</v>
-      </c>
-      <c r="T73" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>254429</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>30-10-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>35</v>
-      </c>
-      <c r="E74" t="n">
-        <v>240.2416666666667</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:19:22</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:54:22</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:54:22</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:54:36</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>28829</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>5</v>
-      </c>
-      <c r="N74" t="n">
-        <v>70</v>
-      </c>
-      <c r="O74" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S74" s="1" t="n">
-        <v>-9</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>254555</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>35</v>
-      </c>
-      <c r="E75" t="n">
-        <v>172.9833333333333</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:54:36</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:29:36</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>17-11-2025 07:29:36</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:22:35</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>20758</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>4</v>
-      </c>
-      <c r="N75" t="n">
-        <v>76</v>
-      </c>
-      <c r="O75" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>20-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>235572</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>35</v>
-      </c>
-      <c r="E76" t="n">
-        <v>82.98333333333333</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:22:35</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:57:35</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:57:35</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:20:34</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>9958</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>5</v>
-      </c>
-      <c r="N76" t="n">
-        <v>70</v>
-      </c>
-      <c r="O76" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>06-11-2023 00:00:00</t>
-        </is>
-      </c>
-      <c r="S76" s="1" t="n">
-        <v>-744</v>
-      </c>
-      <c r="T76" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>254276</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>30</v>
-      </c>
-      <c r="E77" t="n">
-        <v>37.03333333333333</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:20:34</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:50:34</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>17-11-2025 12:50:34</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:27:36</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>4444</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>4</v>
-      </c>
-      <c r="N77" t="n">
-        <v>70</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S77" s="1" t="n">
-        <v>-14.56083912037037</v>
-      </c>
-      <c r="T77" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>254756</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>50</v>
-      </c>
-      <c r="E78" t="n">
-        <v>60.625</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:27:36</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:17:36</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:17:36</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>18-11-2025 07:18:14</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>7275</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>9</v>
-      </c>
-      <c r="N78" t="n">
-        <v>70</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>24-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>254715</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>35</v>
-      </c>
-      <c r="E79" t="n">
-        <v>134.5416666666667</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:35:00</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:49:32</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>16145</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>4</v>
-      </c>
-      <c r="N79" t="n">
-        <v>76</v>
-      </c>
-      <c r="O79" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>19-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S79" s="1" t="n">
-        <v>-1.409403935185185</v>
-      </c>
-      <c r="T79" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>254287</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>12-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>35</v>
-      </c>
-      <c r="E80" t="n">
-        <v>129.6333333333333</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>14-11-2025 09:49:32</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:24:32</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>14-11-2025 10:24:32</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>14-11-2025 12:34:10</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>15556</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" t="n">
-        <v>70</v>
-      </c>
-      <c r="O80" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="n">
-        <v>-18</v>
-      </c>
-      <c r="T80" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>254427</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>40</v>
-      </c>
-      <c r="E81" t="n">
-        <v>55.55833333333333</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>14-11-2025 12:34:10</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:14:10</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>14-11-2025 13:14:10</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:09:44</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>6667</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>T1 ;T2 ;T8</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>70</v>
-      </c>
-      <c r="O81" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>40649</v>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S81" s="1" t="n">
-        <v>-4.590092592592592</v>
-      </c>
-      <c r="T81" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>254574</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>13-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>40</v>
-      </c>
-      <c r="E82" t="n">
-        <v>173.6083333333333</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:09:44</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:49:44</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:49:44</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:43:20</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>20833</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>3</v>
-      </c>
-      <c r="N82" t="n">
-        <v>70</v>
-      </c>
-      <c r="O82" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>14-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S82" s="1" t="n">
-        <v>-7</v>
-      </c>
-      <c r="T82" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>254460</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>21-10-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>30</v>
-      </c>
-      <c r="E83" t="n">
-        <v>46.68333333333333</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>17-11-2025 09:43:20</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:13:20</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>17-11-2025 10:13:20</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:00:01</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>5602</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>4</v>
-      </c>
-      <c r="N83" t="n">
-        <v>70</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>23-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S83" s="1" t="n">
-        <v>-35.45835069444445</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>254245</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>40</v>
-      </c>
-      <c r="E84" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:00:01</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:40:01</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>17-11-2025 11:40:01</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:09:49</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>10776</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>4</v>
-      </c>
-      <c r="N84" t="n">
-        <v>70</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>30-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S84" s="1" t="n">
-        <v>-18.54848958333333</v>
-      </c>
-      <c r="T84" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>254356</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>25</v>
-      </c>
-      <c r="E85" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:09:49</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:34:49</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>17-11-2025 13:34:49</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:34:25</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>21552</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>4</v>
-      </c>
-      <c r="N85" t="n">
-        <v>70</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>08-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S85" s="1" t="n">
-        <v>-10.35723958333333</v>
-      </c>
-      <c r="T85" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>253961</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>25</v>
-      </c>
-      <c r="E86" t="n">
-        <v>35.91666666666666</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:34:25</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:59:25</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>18-11-2025 08:59:25</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:35:20</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>4310</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>4</v>
-      </c>
-      <c r="N86" t="n">
-        <v>70</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>11-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S86" s="1" t="n">
-        <v>-7.399542824074074</v>
-      </c>
-      <c r="T86" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>252811</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>30</v>
-      </c>
-      <c r="E87" t="n">
-        <v>11.875</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:35:20</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:05:20</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:05:20</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:17:13</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>1425</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>70</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>13-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S87" s="1" t="n">
-        <v>-15.42862268518519</v>
-      </c>
-      <c r="T87" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>254651</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>13-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>35</v>
-      </c>
-      <c r="E88" t="n">
-        <v>22.64166666666667</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:17:13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:52:13</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:52:13</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:14:51</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>2717</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>3</v>
-      </c>
-      <c r="N88" t="n">
-        <v>70</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>21-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S88" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>254586</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>35</v>
-      </c>
-      <c r="E89" t="n">
-        <v>51.54166666666666</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:14:51</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:49:51</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>18-11-2025 11:49:51</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:41:24</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>6185</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
-        <v>3</v>
-      </c>
-      <c r="N89" t="n">
-        <v>70</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>24-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S89" s="1" t="n">
-        <v>-4.52875</v>
-      </c>
-      <c r="T89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>254893</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>14-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>25</v>
-      </c>
-      <c r="E90" t="n">
-        <v>46.675</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>18-11-2025 12:41:24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:06:24</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:06:24</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>18-11-2025 13:53:04</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>5601</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>3</v>
-      </c>
-      <c r="N90" t="n">
-        <v>70</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>04-12-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>254521</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>39.68333333333333</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:39:41</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>4762</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>T1 ;T2 ;T8</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>3</v>
-      </c>
-      <c r="N91" t="n">
-        <v>70</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>15-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>17.075</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>2049</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>08-09-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S92" s="1" t="n">
-        <v>-67.30352430555556</v>
-      </c>
-      <c r="T92" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>254117</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>07-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>9.166666666666666</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:26:14</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>1100</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="M93" t="n">
-        <v>3</v>
-      </c>
-      <c r="N93" t="n">
-        <v>76</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>20-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S93" s="1" t="n">
-        <v>-25.3098900462963</v>
-      </c>
-      <c r="T93" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>252999</v>
+        <v>250891</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>325.8416666666666</v>
+        <v>77.49166666666666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>08-07-2025 12:32:00</t>
+          <t>08-09-2025 07:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>08-07-2025 12:32:00</t>
+          <t>08-09-2025 07:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>09-07-2025 09:57:50</t>
+          <t>08-09-2025 08:49:29</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39101</v>
+        <v>9299</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,15 +591,18 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
         <v>70</v>
       </c>
+      <c r="O2" t="n">
+        <v>40910</v>
+      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -608,58 +611,58 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06-08-2025 00:00:00</t>
+          <t>13-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>252207</v>
+        <v>252216</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>27-06-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>51.55</v>
+        <v>141.8083333333333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>08-09-2025 08:49:29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>08-07-2025 12:27:00</t>
+          <t>08-09-2025 09:14:29</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>08-07-2025 12:27:00</t>
+          <t>08-09-2025 09:14:29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08-07-2025 13:18:33</t>
+          <t>08-09-2025 11:36:18</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6186</v>
+        <v>17017</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -668,14 +671,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O3" t="n">
+        <v>40910</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -685,58 +691,58 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>26-06-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-12.55454861111111</v>
+        <v>-27</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>252723</v>
+        <v>253527</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>153.9583333333333</v>
+        <v>67.48333333333333</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08-07-2025 13:18:33</t>
+          <t>08-09-2025 11:36:18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08-07-2025 13:43:33</t>
+          <t>08-09-2025 12:05:18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>08-07-2025 13:43:33</t>
+          <t>08-09-2025 12:05:18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09-07-2025 08:17:30</t>
+          <t>08-09-2025 13:12:47</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18475</v>
+        <v>8098</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -745,14 +751,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O4" t="n">
+        <v>40910</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -762,11 +771,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>31-07-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -774,46 +783,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>251231</v>
+        <v>253524</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>312.3083333333333</v>
+        <v>58.75833333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09-07-2025 08:17:30</t>
+          <t>08-09-2025 13:12:47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>09-07-2025 09:03:30</t>
+          <t>08-09-2025 13:27:47</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>09-07-2025 09:03:30</t>
+          <t>08-09-2025 13:27:47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09-07-2025 14:15:49</t>
+          <t>08-09-2025 14:26:32</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>37477</v>
+        <v>7051</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -822,35 +831,31 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>70</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>40034 (esterno)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="O5" t="n">
+        <v>40910</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>40034</v>
+        <v>0</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-07-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-6.59431712962963</v>
+        <v>-9</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -858,46 +863,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>252277</v>
+        <v>253528</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>09-07-2025 14:00:00</t>
+          <t>11-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>144.925</v>
+        <v>119.175</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09-07-2025 14:15:49</t>
+          <t>08-09-2025 14:26:32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09-07-2025 14:46:49</t>
+          <t>08-09-2025 14:41:32</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>09-07-2025 14:46:49</t>
+          <t>08-09-2025 14:41:32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10-07-2025 09:11:44</t>
+          <t>09-09-2025 08:40:43</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17391</v>
+        <v>14301</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -915,73 +920,69 @@
       <c r="N6" t="n">
         <v>70</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>40024 (esterno)</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="O6" t="n">
+        <v>40910</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40024</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20-06-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-20.38315393518518</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>252085</v>
+        <v>244023</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>28.55</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10-07-2025 09:11:44</t>
+          <t>09-09-2025 08:40:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10-07-2025 09:38:44</t>
+          <t>09-09-2025 09:01:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10-07-2025 09:38:44</t>
+          <t>09-09-2025 09:01:43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10-07-2025 10:07:17</t>
+          <t>09-09-2025 09:10:01</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3426</v>
+        <v>997</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -994,7 +995,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
@@ -1007,58 +1008,58 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>18-06-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-22.42173032407407</v>
+        <v>-344.3819618055555</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>252298</v>
+        <v>252939</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>70.76666666666667</v>
+        <v>89.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10-07-2025 10:07:17</t>
+          <t>09-09-2025 09:10:01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10-07-2025 10:51:17</t>
+          <t>09-09-2025 09:31:01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10-07-2025 10:51:17</t>
+          <t>09-09-2025 09:31:01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10-07-2025 12:02:03</t>
+          <t>09-09-2025 11:00:49</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8492</v>
+        <v>10776</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1067,14 +1068,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1084,58 +1085,58 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>23-06-2025 00:00:00</t>
+          <t>22-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-17.50142939814815</v>
+        <v>-18.45890625</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>250383</v>
+        <v>252815</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>24.925</v>
+        <v>242.9416666666667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10-07-2025 12:02:03</t>
+          <t>09-09-2025 11:00:49</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10-07-2025 12:29:03</t>
+          <t>09-09-2025 11:40:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10-07-2025 12:29:03</t>
+          <t>09-09-2025 11:40:49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10-07-2025 12:53:59</t>
+          <t>10-09-2025 07:43:46</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2991</v>
+        <v>29153</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1148,7 +1149,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
         <v>76</v>
@@ -1161,19 +1162,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>15-06-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-25.53748842592593</v>
+        <v>-5.322060185185185</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>252201</v>
+        <v>253072</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1182,37 +1183,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>34.10833333333333</v>
+        <v>29.13333333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10-07-2025 12:53:59</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10-07-2025 13:22:59</t>
+          <t>08-09-2025 07:46:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10-07-2025 13:22:59</t>
+          <t>08-09-2025 07:46:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10-07-2025 13:57:05</t>
+          <t>08-09-2025 08:15:08</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4093</v>
+        <v>3496</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1221,14 +1222,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O10" t="n">
+        <v>40904</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1238,11 +1242,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>20-06-2025 00:00:00</t>
+          <t>18-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-20.58131365740741</v>
+        <v>-38</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -1250,7 +1254,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>252364</v>
+        <v>253271</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1259,37 +1263,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>116.4833333333333</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10-07-2025 13:57:05</t>
+          <t>08-09-2025 08:15:08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10-07-2025 14:39:05</t>
+          <t>08-09-2025 08:40:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10-07-2025 14:39:05</t>
+          <t>08-09-2025 08:40:08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-07-2025 08:35:34</t>
+          <t>08-09-2025 09:22:46</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13978</v>
+        <v>5116</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1302,11 +1306,14 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
+      <c r="O11" t="n">
+        <v>40904</v>
+      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1315,19 +1322,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>27-06-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-14.35803819444445</v>
+        <v>-20</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>252638</v>
+        <v>253278</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1336,37 +1343,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>09-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>61.49166666666667</v>
+        <v>28.425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11-07-2025 08:35:34</t>
+          <t>08-09-2025 09:22:46</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11-07-2025 09:02:34</t>
+          <t>08-09-2025 09:47:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11-07-2025 09:02:34</t>
+          <t>08-09-2025 09:47:46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11-07-2025 10:04:04</t>
+          <t>08-09-2025 10:16:11</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7379</v>
+        <v>3411</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1379,11 +1386,14 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
       </c>
+      <c r="O12" t="n">
+        <v>40904</v>
+      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1392,58 +1402,58 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06-07-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-5.41949074074074</v>
+        <v>-13</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>235572</v>
+        <v>253317</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>82.98333333333333</v>
+        <v>102.775</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>08-09-2025 10:16:11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>08-07-2025 12:36:00</t>
+          <t>08-09-2025 11:02:11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>08-07-2025 12:36:00</t>
+          <t>08-09-2025 11:02:11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08-07-2025 13:58:59</t>
+          <t>08-09-2025 12:44:58</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9958</v>
+        <v>12333</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1452,14 +1462,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O13" t="n">
+        <v>40910</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1469,58 +1482,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-610.5826273148148</v>
+        <v>-13</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>251849</v>
+        <v>253318</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>33.38333333333333</v>
+        <v>51.55</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-07-2025 13:58:59</t>
+          <t>08-09-2025 12:44:58</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>08-07-2025 14:21:59</t>
+          <t>08-09-2025 13:09:58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>08-07-2025 14:21:59</t>
+          <t>08-09-2025 13:09:58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08-07-2025 14:55:22</t>
+          <t>08-09-2025 14:01:31</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4006</v>
+        <v>6186</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1529,82 +1542,78 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>70</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>40042 (esterno)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="O14" t="n">
+        <v>40910</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>40042</v>
+        <v>0</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>25-06-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-13.62178240740741</v>
+        <v>-13</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>250284</v>
+        <v>253260</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>146.35</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08-07-2025 14:55:22</t>
+          <t>08-09-2025 14:01:31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>09-07-2025 07:16:22</t>
+          <t>08-09-2025 14:43:31</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>09-07-2025 07:16:22</t>
+          <t>08-09-2025 14:43:31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09-07-2025 09:42:43</t>
+          <t>09-09-2025 08:32:55</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17562</v>
+        <v>13129</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1617,11 +1626,14 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
+      <c r="O15" t="n">
+        <v>40279</v>
+      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -1630,11 +1642,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-119.4046643518518</v>
+        <v>-16</v>
       </c>
       <c r="T15" t="n">
         <v>7</v>
@@ -1642,46 +1654,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>244023</v>
+        <v>253455</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>10-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
-        <v>8.308333333333334</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09-07-2025 09:42:43</t>
+          <t>09-09-2025 08:32:55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09-07-2025 10:01:43</t>
+          <t>09-09-2025 08:57:55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>09-07-2025 10:01:43</t>
+          <t>09-09-2025 08:57:55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09-07-2025 10:10:01</t>
+          <t>09-09-2025 09:53:29</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>997</v>
+        <v>6667</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1694,11 +1706,14 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
         <v>70</v>
       </c>
+      <c r="O16" t="n">
+        <v>40279</v>
+      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -1707,58 +1722,58 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-282.4236284722222</v>
+        <v>-2</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>252220</v>
+        <v>253247</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>80.51666666666667</v>
+        <v>109.575</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09-07-2025 10:10:01</t>
+          <t>09-09-2025 09:53:29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09-07-2025 10:29:01</t>
+          <t>09-09-2025 10:18:29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>09-07-2025 10:29:01</t>
+          <t>09-09-2025 10:18:29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09-07-2025 11:49:32</t>
+          <t>09-09-2025 12:08:03</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9662</v>
+        <v>13149</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1776,6 +1791,9 @@
       <c r="N17" t="n">
         <v>70</v>
       </c>
+      <c r="O17" t="n">
+        <v>40279</v>
+      </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
@@ -1784,58 +1802,58 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>16-06-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-23.49273726851852</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>252087</v>
+        <v>253249</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>28-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>35.5</v>
+        <v>57.75833333333333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09-07-2025 11:49:32</t>
+          <t>09-09-2025 12:08:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09-07-2025 12:06:32</t>
+          <t>09-09-2025 12:50:03</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>09-07-2025 12:06:32</t>
+          <t>09-09-2025 12:50:03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09-07-2025 12:42:02</t>
+          <t>09-09-2025 13:47:49</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4260</v>
+        <v>6931</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1844,14 +1862,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1861,58 +1879,58 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>29-06-2025 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-10.52919560185185</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>245089</v>
+        <v>253706</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>1022.208333333333</v>
+        <v>311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09-07-2025 12:42:02</t>
+          <t>09-09-2025 13:47:49</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09-07-2025 13:14:02</t>
+          <t>09-09-2025 14:22:49</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>09-07-2025 13:14:02</t>
+          <t>09-09-2025 14:22:49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11-07-2025 14:16:15</t>
+          <t>10-09-2025 11:33:49</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>122665</v>
+        <v>37320</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1925,7 +1943,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
         <v>76</v>
@@ -1938,19 +1956,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>31-12-2025 00:00:00</t>
+          <t>30-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>252209</v>
+        <v>252702</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1959,37 +1977,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>29.19166666666667</v>
+        <v>58.38333333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11-07-2025 14:16:15</t>
+          <t>05-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11-07-2025 14:33:15</t>
+          <t>05-09-2025 07:34:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11-07-2025 14:33:15</t>
+          <t>05-09-2025 07:34:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14-07-2025 07:02:26</t>
+          <t>05-09-2025 08:32:23</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3503</v>
+        <v>7006</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1998,36 +2016,41 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>76</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O20" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>26-06-2025 00:00:00</t>
+          <t>04-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-18.29336226851852</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>252378</v>
+        <v>253362</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2036,37 +2059,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>37.55833333333333</v>
+        <v>58.38333333333333</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14-07-2025 07:02:26</t>
+          <t>05-09-2025 08:32:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14-07-2025 07:21:26</t>
+          <t>05-09-2025 08:47:23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-07-2025 07:21:26</t>
+          <t>05-09-2025 08:47:23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-07-2025 07:59:00</t>
+          <t>05-09-2025 09:45:46</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4507</v>
+        <v>7006</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2075,28 +2098,33 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>76</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O21" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>15-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-10.33263888888889</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2104,7 +2132,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>252362</v>
+        <v>252681</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2113,37 +2141,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>39.95</v>
+        <v>115.0166666666667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14-07-2025 07:59:00</t>
+          <t>05-09-2025 09:45:46</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14-07-2025 08:14:00</t>
+          <t>05-09-2025 10:19:46</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-07-2025 08:14:00</t>
+          <t>05-09-2025 10:19:46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-07-2025 08:53:57</t>
+          <t>05-09-2025 12:14:47</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4794</v>
+        <v>13802</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2152,36 +2180,41 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
         <v>76</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
+      <c r="O22" t="n">
+        <v>40279</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>40279</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-10.37079861111111</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>252814</v>
+        <v>253591</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2190,37 +2223,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>50.08333333333334</v>
+        <v>17.41666666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-07-2025 08:53:57</t>
+          <t>05-09-2025 12:14:47</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-07-2025 09:10:57</t>
+          <t>05-09-2025 12:29:47</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-07-2025 09:10:57</t>
+          <t>05-09-2025 12:29:47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-07-2025 10:01:02</t>
+          <t>05-09-2025 12:47:12</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6010</v>
+        <v>2090</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2229,31 +2262,36 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>76</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
+      <c r="O23" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>14-07-2025 00:00:00</t>
+          <t>24-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.4173842592592593</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2271,29 +2309,29 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
         <v>21.675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14-07-2025 10:01:02</t>
+          <t>05-09-2025 12:47:12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14-07-2025 10:18:02</t>
+          <t>05-09-2025 13:06:12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-07-2025 10:18:02</t>
+          <t>05-09-2025 13:06:12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-07-2025 10:39:42</t>
+          <t>05-09-2025 13:27:52</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2315,6 +2353,9 @@
       <c r="N24" t="n">
         <v>76</v>
       </c>
+      <c r="O24" t="n">
+        <v>40904</v>
+      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -2327,7 +2368,7 @@
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-301.4442418981482</v>
+        <v>-374</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -2335,7 +2376,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>251812</v>
+        <v>250284</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2344,37 +2385,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>33.875</v>
+        <v>146.35</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14-07-2025 10:39:42</t>
+          <t>05-09-2025 13:27:52</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14-07-2025 10:58:42</t>
+          <t>05-09-2025 14:07:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-07-2025 10:58:42</t>
+          <t>05-09-2025 14:07:52</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-07-2025 11:32:35</t>
+          <t>08-09-2025 08:34:13</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4065</v>
+        <v>17562</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2383,14 +2424,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O25" t="n">
+        <v>40910</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2400,19 +2444,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>23-06-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-21.48096064814815</v>
+        <v>-193</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>252426</v>
+        <v>252906</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2421,37 +2465,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>184.2833333333333</v>
+        <v>34.725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-07-2025 11:32:35</t>
+          <t>08-09-2025 08:34:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14-07-2025 12:04:35</t>
+          <t>08-09-2025 09:12:13</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-07-2025 12:04:35</t>
+          <t>08-09-2025 09:12:13</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15-07-2025 07:08:52</t>
+          <t>08-09-2025 09:46:57</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>22114</v>
+        <v>4167</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2460,14 +2504,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O26" t="n">
+        <v>40904</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2477,11 +2524,11 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-07-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-13.29782407407407</v>
+        <v>-31</v>
       </c>
       <c r="T26" t="n">
         <v>2</v>
@@ -2489,7 +2536,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>252598</v>
+        <v>253140</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2498,37 +2545,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>149.625</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>15-07-2025 07:08:52</t>
+          <t>08-09-2025 09:46:57</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>15-07-2025 07:23:52</t>
+          <t>08-09-2025 10:03:57</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>15-07-2025 07:23:52</t>
+          <t>08-09-2025 10:03:57</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15-07-2025 09:53:29</t>
+          <t>08-09-2025 10:59:47</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>17955</v>
+        <v>6700</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2537,14 +2584,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O27" t="n">
+        <v>40900</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2554,19 +2604,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-07-2025 00:00:00</t>
+          <t>26-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-5.412146990740741</v>
+        <v>-26</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>252547</v>
+        <v>253100</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2575,37 +2625,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>81.16666666666667</v>
+        <v>47.35</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15-07-2025 09:53:29</t>
+          <t>08-09-2025 10:59:47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15-07-2025 10:14:29</t>
+          <t>08-09-2025 11:31:47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>15-07-2025 10:14:29</t>
+          <t>08-09-2025 11:31:47</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15-07-2025 11:35:39</t>
+          <t>08-09-2025 12:19:08</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>9740</v>
+        <v>5682</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2618,11 +2668,14 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
         <v>70</v>
       </c>
+      <c r="O28" t="n">
+        <v>40900</v>
+      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
@@ -2631,19 +2684,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-11.48309606481481</v>
+        <v>-13</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>252470</v>
+        <v>253246</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2652,37 +2705,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>62.5</v>
+        <v>194.25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15-07-2025 11:35:39</t>
+          <t>08-09-2025 12:19:08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15-07-2025 11:52:39</t>
+          <t>08-09-2025 12:34:08</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15-07-2025 11:52:39</t>
+          <t>08-09-2025 12:34:08</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15-07-2025 12:55:09</t>
+          <t>09-09-2025 07:48:23</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>7500</v>
+        <v>23310</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2700,6 +2753,9 @@
       <c r="N29" t="n">
         <v>70</v>
       </c>
+      <c r="O29" t="n">
+        <v>40900</v>
+      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2708,19 +2764,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-11.53830439814815</v>
+        <v>-11</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>251926</v>
+        <v>253372</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2729,37 +2785,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>78.91666666666667</v>
+        <v>103.775</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15-07-2025 12:55:09</t>
+          <t>09-09-2025 07:48:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15-07-2025 13:16:09</t>
+          <t>09-09-2025 08:07:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15-07-2025 13:16:09</t>
+          <t>09-09-2025 08:07:23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15-07-2025 14:35:04</t>
+          <t>09-09-2025 09:51:09</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9470</v>
+        <v>12453</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2768,15 +2824,18 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
+      <c r="O30" t="n">
+        <v>40904</v>
+      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -2785,19 +2844,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-07-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-6.607690972222223</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>251495</v>
+        <v>253370</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2806,37 +2865,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>72.34166666666667</v>
+        <v>207.5416666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15-07-2025 14:35:04</t>
+          <t>09-09-2025 09:51:09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15-07-2025 14:52:04</t>
+          <t>09-09-2025 10:06:09</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15-07-2025 14:52:04</t>
+          <t>09-09-2025 10:06:09</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16-07-2025 08:04:25</t>
+          <t>09-09-2025 13:33:42</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>8681</v>
+        <v>24905</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2845,15 +2904,18 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
+      <c r="O31" t="n">
+        <v>40904</v>
+      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -2862,19 +2924,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-07-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-7.336400462962963</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>252656</v>
+        <v>253095</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2883,37 +2945,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>189.8666666666667</v>
+        <v>76.31666666666666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16-07-2025 08:04:25</t>
+          <t>09-09-2025 13:33:42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>16-07-2025 08:25:25</t>
+          <t>09-09-2025 13:50:42</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>16-07-2025 08:25:25</t>
+          <t>09-09-2025 13:50:42</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16-07-2025 11:35:17</t>
+          <t>10-09-2025 07:07:01</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>22784</v>
+        <v>9158</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2939,19 +3001,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>14-07-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-2.482835648148148</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>252576</v>
+        <v>253332</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2960,37 +3022,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14-07-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>374.0666666666667</v>
+        <v>184.825</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16-07-2025 11:35:17</t>
+          <t>10-09-2025 07:07:01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>16-07-2025 11:50:17</t>
+          <t>10-09-2025 07:24:01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16-07-2025 11:50:17</t>
+          <t>10-09-2025 07:24:01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-07-2025 10:04:21</t>
+          <t>10-09-2025 10:28:50</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>44888</v>
+        <v>22179</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3016,58 +3078,58 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>15-07-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-2.4196875</v>
+        <v>-0.4366956018518519</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>252779</v>
+        <v>253359</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15-07-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>34.5</v>
       </c>
       <c r="E34" t="n">
-        <v>184.2833333333333</v>
+        <v>134.0166666666667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17-07-2025 10:04:21</t>
+          <t>09-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17-07-2025 10:19:21</t>
+          <t>09-09-2025 07:34:30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17-07-2025 10:19:21</t>
+          <t>09-09-2025 07:34:30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17-07-2025 13:23:38</t>
+          <t>09-09-2025 09:48:31</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>22114</v>
+        <v>16082</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3076,15 +3138,18 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
       </c>
+      <c r="O34" t="n">
+        <v>40904</v>
+      </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
@@ -3093,58 +3158,58 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>21-07-2025 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>252778</v>
+        <v>253223</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>50.5</v>
       </c>
       <c r="E35" t="n">
-        <v>160.9916666666667</v>
+        <v>16.4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17-07-2025 13:23:38</t>
+          <t>09-09-2025 09:48:31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17-07-2025 13:42:38</t>
+          <t>09-09-2025 10:39:01</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17-07-2025 13:42:38</t>
+          <t>09-09-2025 10:39:01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18-07-2025 08:23:37</t>
+          <t>09-09-2025 10:55:25</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>19319</v>
+        <v>1968</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3153,11 +3218,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -3170,19 +3235,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>21-07-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0</v>
+        <v>-8.455150462962964</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>252665</v>
+        <v>253208</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3191,37 +3256,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32.5</v>
+        <v>54.5</v>
       </c>
       <c r="E36" t="n">
-        <v>48.875</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>09-09-2025 10:55:25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>08-07-2025 12:32:30</t>
+          <t>09-09-2025 11:49:55</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>08-07-2025 12:32:30</t>
+          <t>09-09-2025 11:49:55</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>08-07-2025 13:21:22</t>
+          <t>09-09-2025 13:34:10</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5865</v>
+        <v>12511</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3230,11 +3295,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -3247,58 +3312,58 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-09-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0</v>
+        <v>-4.565399305555555</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>252713</v>
+        <v>253210</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>65</v>
+        <v>30.5</v>
       </c>
       <c r="E37" t="n">
-        <v>907.7666666666667</v>
+        <v>94.15833333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>09-09-2025 13:34:10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>08-07-2025 13:05:00</t>
+          <t>09-09-2025 14:04:40</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>08-07-2025 13:05:00</t>
+          <t>09-09-2025 14:04:40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10-07-2025 12:12:46</t>
+          <t>10-09-2025 07:38:50</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>108932</v>
+        <v>11299</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3307,11 +3372,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3324,58 +3389,58 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>18-07-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0</v>
+        <v>-0.3186342592592593</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>252978</v>
+        <v>252601</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>04-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>32.5</v>
       </c>
       <c r="E38" t="n">
-        <v>23.3</v>
+        <v>51.20833333333334</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>10-09-2025 07:38:50</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>08-07-2025 12:19:00</t>
+          <t>10-09-2025 08:11:20</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>08-07-2025 12:19:00</t>
+          <t>10-09-2025 08:11:20</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>08-07-2025 12:42:18</t>
+          <t>10-09-2025 09:02:32</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2796</v>
+        <v>6145</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3384,14 +3449,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3401,58 +3466,58 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>16-06-2025 00:00:00</t>
+          <t>31-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-22.529375</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>245623</v>
+        <v>252002</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>07-07-2025 14:00:00</t>
+          <t>01-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E39" t="n">
-        <v>220.1583333333333</v>
+        <v>55.675</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>08-07-2025 12:42:18</t>
+          <t>04-09-2025 12:00:00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>08-07-2025 13:14:18</t>
+          <t>04-09-2025 12:55:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>08-07-2025 13:14:18</t>
+          <t>04-09-2025 12:55:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09-07-2025 08:54:27</t>
+          <t>04-09-2025 13:50:40</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>26419</v>
+        <v>6681</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3461,75 +3526,82 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>152</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>40307 (esterno)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>40307</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>25-01-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-165.3711516203704</v>
+        <v>-10.57685763888889</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>252686</v>
+        <v>235572</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>329.15</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>09-07-2025 08:54:27</t>
+          <t>04-09-2025 13:50:40</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>09-07-2025 09:11:27</t>
+          <t>04-09-2025 14:20:40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>09-07-2025 09:11:27</t>
+          <t>04-09-2025 14:20:40</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>09-07-2025 14:40:36</t>
+          <t>05-09-2025 07:43:39</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>39498</v>
+        <v>9958</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3538,14 +3610,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="O40" t="n">
+        <v>40904</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3555,58 +3630,58 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>21-07-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>0</v>
+        <v>-689</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>252245</v>
+        <v>252685</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>489.7583333333333</v>
+        <v>74.56666666666666</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>09-07-2025 14:40:36</t>
+          <t>05-09-2025 07:43:39</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>09-07-2025 14:57:36</t>
+          <t>05-09-2025 08:23:39</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>09-07-2025 14:57:36</t>
+          <t>05-09-2025 08:23:39</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11-07-2025 07:07:22</t>
+          <t>05-09-2025 09:38:13</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>58771</v>
+        <v>8948</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3615,75 +3690,80 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>152</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O41" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>27-06-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-14.29678240740741</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>252210</v>
+        <v>252682</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E42" t="n">
-        <v>29.2</v>
+        <v>83.40833333333333</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11-07-2025 07:07:22</t>
+          <t>05-09-2025 09:38:13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11-07-2025 07:39:22</t>
+          <t>05-09-2025 10:18:13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11-07-2025 07:39:22</t>
+          <t>05-09-2025 10:18:13</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>11-07-2025 08:08:34</t>
+          <t>05-09-2025 11:41:38</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3504</v>
+        <v>10009</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3696,71 +3776,76 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>76</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
+      <c r="O42" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>26-06-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-15.33928240740741</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>251919</v>
+        <v>252582</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>20-06-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>140.05</v>
+        <v>46.08333333333334</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>05-09-2025 11:41:38</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>08-07-2025 12:35:00</t>
+          <t>05-09-2025 12:11:38</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>08-07-2025 12:35:00</t>
+          <t>05-09-2025 12:11:38</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>08-07-2025 14:55:03</t>
+          <t>05-09-2025 12:57:43</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>16806</v>
+        <v>5530</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3769,28 +3854,33 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>152</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O43" t="n">
+        <v>40290</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>40290</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-06-2025 00:00:00</t>
+          <t>18-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-22.6215625</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -3798,46 +3888,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>252680</v>
+        <v>253314</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>02-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>254.7</v>
+        <v>43.40833333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>08-07-2025 14:55:03</t>
+          <t>05-09-2025 12:57:43</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>09-07-2025 07:30:03</t>
+          <t>05-09-2025 13:27:43</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>09-07-2025 07:30:03</t>
+          <t>05-09-2025 13:27:43</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>09-07-2025 11:44:45</t>
+          <t>05-09-2025 14:11:07</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>30564</v>
+        <v>5209</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3846,75 +3936,80 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
         <v>76</v>
       </c>
-      <c r="P44" t="n">
-        <v>0</v>
+      <c r="O44" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>30-07-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>252519</v>
+        <v>253036</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>11.475</v>
+        <v>78.73333333333333</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>09-07-2025 11:44:45</t>
+          <t>05-09-2025 14:11:07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>09-07-2025 12:14:45</t>
+          <t>05-09-2025 14:41:07</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>09-07-2025 12:14:45</t>
+          <t>05-09-2025 14:41:07</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>09-07-2025 12:26:13</t>
+          <t>08-09-2025 07:59:51</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1377</v>
+        <v>9448</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3923,7 +4018,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>H7 ;R5</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3932,6 +4027,9 @@
       <c r="N45" t="n">
         <v>76</v>
       </c>
+      <c r="O45" t="n">
+        <v>40910</v>
+      </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
@@ -3940,58 +4038,58 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>22-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-5.518211805555556</v>
+        <v>-30</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>252476</v>
+        <v>253284</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>28-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>72.34166666666667</v>
+        <v>56.99166666666667</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>09-07-2025 12:26:13</t>
+          <t>08-09-2025 07:59:51</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>09-07-2025 13:06:13</t>
+          <t>08-09-2025 08:29:51</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>09-07-2025 13:06:13</t>
+          <t>08-09-2025 08:29:51</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>09-07-2025 14:18:34</t>
+          <t>08-09-2025 09:26:51</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>8681</v>
+        <v>6839</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4000,14 +4098,17 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O46" t="n">
+        <v>40910</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4017,58 +4118,58 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>07-07-2025 00:00:00</t>
+          <t>28-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-2.596226851851852</v>
+        <v>-24</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>252473</v>
+        <v>253313</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>09-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E47" t="n">
-        <v>189.8666666666667</v>
+        <v>100.0083333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>09-07-2025 14:18:34</t>
+          <t>08-09-2025 09:26:51</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>09-07-2025 14:48:34</t>
+          <t>08-09-2025 09:51:51</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>09-07-2025 14:48:34</t>
+          <t>08-09-2025 09:51:51</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10-07-2025 09:58:26</t>
+          <t>08-09-2025 11:31:51</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>22784</v>
+        <v>12001</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4077,14 +4178,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O47" t="n">
+        <v>40910</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4094,58 +4198,58 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>01-07-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-9.415578703703703</v>
+        <v>-16</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>252662</v>
+        <v>252883</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>09-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E48" t="n">
-        <v>189.8666666666667</v>
+        <v>247.3083333333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10-07-2025 09:58:26</t>
+          <t>08-09-2025 11:31:51</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10-07-2025 10:23:26</t>
+          <t>08-09-2025 12:46:51</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>10-07-2025 10:23:26</t>
+          <t>08-09-2025 12:46:51</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10-07-2025 13:33:18</t>
+          <t>09-09-2025 08:54:10</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>22784</v>
+        <v>29677</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4154,15 +4258,18 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N48" t="n">
         <v>70</v>
       </c>
+      <c r="O48" t="n">
+        <v>40900</v>
+      </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
@@ -4171,58 +4278,58 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>31-07-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>252549</v>
+        <v>253710</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>09-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E49" t="n">
-        <v>92.59166666666667</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10-07-2025 13:33:18</t>
+          <t>09-09-2025 08:54:10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10-07-2025 14:03:18</t>
+          <t>09-09-2025 10:04:10</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>10-07-2025 14:03:18</t>
+          <t>09-09-2025 10:04:10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>11-07-2025 07:35:53</t>
+          <t>09-09-2025 10:05:47</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>11111</v>
+        <v>194</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4248,7 +4355,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>20-07-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -4260,46 +4367,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>252414</v>
+        <v>253687</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>01-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E50" t="n">
-        <v>77.15833333333333</v>
+        <v>44.23333333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>11-07-2025 07:35:53</t>
+          <t>09-09-2025 10:05:47</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11-07-2025 08:20:53</t>
+          <t>09-09-2025 10:40:47</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11-07-2025 08:20:53</t>
+          <t>09-09-2025 10:40:47</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11-07-2025 09:38:03</t>
+          <t>09-09-2025 11:25:01</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9259</v>
+        <v>5308</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4308,11 +4415,11 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
         <v>70</v>
@@ -4325,58 +4432,58 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>30-06-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-11.40142361111111</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>252157</v>
+        <v>253267</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>396.825</v>
+        <v>164.3666666666667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>11-07-2025 09:38:03</t>
+          <t>09-09-2025 11:25:01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>11-07-2025 10:13:03</t>
+          <t>09-09-2025 11:55:01</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>11-07-2025 10:13:03</t>
+          <t>09-09-2025 11:55:01</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-07-2025 08:49:52</t>
+          <t>09-09-2025 14:39:23</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>47619</v>
+        <v>19724</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4389,7 +4496,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>70</v>
@@ -4402,58 +4509,58 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-06-2025 00:00:00</t>
+          <t>23-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-26.36796875</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>252507</v>
+        <v>253268</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
-        <v>102.8833333333333</v>
+        <v>78.55833333333334</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-07-2025 08:49:52</t>
+          <t>09-09-2025 14:39:23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-07-2025 09:19:52</t>
+          <t>10-09-2025 07:04:23</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-07-2025 09:19:52</t>
+          <t>10-09-2025 07:04:23</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14-07-2025 11:02:45</t>
+          <t>10-09-2025 08:22:56</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>12346</v>
+        <v>9427</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4462,11 +4569,11 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
         <v>70</v>
@@ -4479,58 +4586,58 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-07-2025 00:00:00</t>
+          <t>23-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-11.46024884259259</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>252511</v>
+        <v>253409</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>27-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>87.45</v>
+        <v>27.18333333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14-07-2025 11:02:45</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14-07-2025 11:27:45</t>
+          <t>08-09-2025 07:19:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14-07-2025 11:27:45</t>
+          <t>08-09-2025 07:19:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14-07-2025 12:55:12</t>
+          <t>08-09-2025 07:46:11</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>10494</v>
+        <v>3262</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4539,14 +4646,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O53" t="n">
+        <v>40910</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4556,58 +4666,58 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>03-07-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-11.53833912037037</v>
+        <v>-23</v>
       </c>
       <c r="T53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>252336</v>
+        <v>253194</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>27-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>120.275</v>
+        <v>199.0833333333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14-07-2025 12:55:12</t>
+          <t>08-09-2025 07:46:11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14-07-2025 13:45:12</t>
+          <t>08-09-2025 08:01:11</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14-07-2025 13:45:12</t>
+          <t>08-09-2025 08:01:11</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15-07-2025 07:45:29</t>
+          <t>08-09-2025 11:20:16</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>14433</v>
+        <v>23890</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4616,14 +4726,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O54" t="n">
+        <v>40910</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4633,58 +4746,58 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>20-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-11.32325231481481</v>
+        <v>-32</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>252334</v>
+        <v>252843</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E55" t="n">
-        <v>486.5916666666666</v>
+        <v>19.2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15-07-2025 07:45:29</t>
+          <t>08-09-2025 11:20:16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>15-07-2025 08:10:29</t>
+          <t>08-09-2025 11:47:16</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>15-07-2025 08:10:29</t>
+          <t>08-09-2025 11:47:16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>16-07-2025 08:17:04</t>
+          <t>08-09-2025 12:06:28</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>58391</v>
+        <v>2304</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4693,14 +4806,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N55" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O55" t="n">
+        <v>40904</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4710,11 +4826,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>04-07-2025 00:00:00</t>
+          <t>30-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-12.34519097222222</v>
+        <v>-57</v>
       </c>
       <c r="T55" t="n">
         <v>2</v>
@@ -4722,46 +4838,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>252467</v>
+        <v>253425</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E56" t="n">
-        <v>81.16666666666667</v>
+        <v>146.35</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>16-07-2025 08:17:04</t>
+          <t>08-09-2025 12:06:28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16-07-2025 08:42:04</t>
+          <t>08-09-2025 12:29:28</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>16-07-2025 08:42:04</t>
+          <t>08-09-2025 12:29:28</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16-07-2025 10:03:14</t>
+          <t>08-09-2025 14:55:49</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>9740</v>
+        <v>17562</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4770,14 +4886,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M56" t="n">
         <v>5</v>
       </c>
       <c r="N56" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4787,58 +4903,58 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>17-07-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0</v>
+        <v>-10.59001157407407</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>252790</v>
+        <v>252569</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>12.10833333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>16-07-2025 10:03:14</t>
+          <t>08-09-2025 14:55:49</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>16-07-2025 10:28:14</t>
+          <t>09-09-2025 07:14:49</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>16-07-2025 10:28:14</t>
+          <t>09-09-2025 07:14:49</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>16-07-2025 10:40:21</t>
+          <t>09-09-2025 07:24:24</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1453</v>
+        <v>1150</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4847,14 +4963,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N57" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4864,58 +4980,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>25-07-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0</v>
+        <v>-7.609861111111111</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>252755</v>
+        <v>252995</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>10-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>109.575</v>
+        <v>68.31666666666666</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>16-07-2025 10:40:21</t>
+          <t>09-09-2025 07:24:24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>16-07-2025 11:10:21</t>
+          <t>09-09-2025 07:43:24</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>16-07-2025 11:10:21</t>
+          <t>09-09-2025 07:43:24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>16-07-2025 12:59:55</t>
+          <t>09-09-2025 08:51:43</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>13149</v>
+        <v>8198</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4924,14 +5040,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -4941,58 +5057,58 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>17-07-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>0</v>
+        <v>-8.337164351851852</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>252899</v>
+        <v>252827</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>180.5666666666667</v>
+        <v>410</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>16-07-2025 12:59:55</t>
+          <t>09-09-2025 08:51:43</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>16-07-2025 13:29:55</t>
+          <t>09-09-2025 09:08:43</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>16-07-2025 13:29:55</t>
+          <t>09-09-2025 09:08:43</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17-07-2025 08:30:29</t>
+          <t>10-09-2025 07:58:43</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>21668</v>
+        <v>49200</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5001,14 +5117,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5018,58 +5134,58 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>24-07-2025 00:00:00</t>
+          <t>04-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>0</v>
+        <v>-6.300358796296297</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>252371</v>
+        <v>253602</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01-07-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E60" t="n">
-        <v>50.04166666666666</v>
+        <v>117.0833333333333</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>08-07-2025 12:00:00</t>
+          <t>10-09-2025 07:58:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>08-07-2025 12:35:00</t>
+          <t>10-09-2025 08:19:43</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>08-07-2025 12:35:00</t>
+          <t>10-09-2025 08:19:43</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>08-07-2025 13:25:02</t>
+          <t>10-09-2025 10:16:48</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>6005</v>
+        <v>14050</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5078,11 +5194,11 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
         <v>76</v>
@@ -5095,58 +5211,58 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>30-06-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-8.559056712962963</v>
+        <v>-0.39625</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>252369</v>
+        <v>253374</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>19.2</v>
+        <v>59.60833333333333</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>08-07-2025 13:25:02</t>
+          <t>09-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>08-07-2025 14:15:02</t>
+          <t>09-09-2025 07:35:00</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>08-07-2025 14:15:02</t>
+          <t>09-09-2025 07:35:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>08-07-2025 14:34:14</t>
+          <t>09-09-2025 08:34:36</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2304</v>
+        <v>7153</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5155,14 +5271,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O61" t="n">
+        <v>40904</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5172,58 +5291,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>27-06-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-11.60711226851852</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>252495</v>
+        <v>253721</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>70.77500000000001</v>
+        <v>39.39166666666667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>08-07-2025 14:34:14</t>
+          <t>09-09-2025 08:34:36</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>09-07-2025 07:24:14</t>
+          <t>09-09-2025 09:04:36</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>09-07-2025 07:24:14</t>
+          <t>09-09-2025 09:04:36</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09-07-2025 08:35:01</t>
+          <t>09-09-2025 09:44:00</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>8493</v>
+        <v>4727</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5232,14 +5351,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O62" t="n">
+        <v>40900</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5249,58 +5371,58 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>07-07-2025 00:00:00</t>
+          <t>08-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-2.389924768518518</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>252890</v>
+        <v>252833</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>08-07-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E63" t="n">
-        <v>51.7</v>
+        <v>74.78333333333333</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09-07-2025 08:35:01</t>
+          <t>09-09-2025 09:44:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>09-07-2025 09:05:01</t>
+          <t>09-09-2025 10:19:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>09-07-2025 09:05:01</t>
+          <t>09-09-2025 10:19:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>09-07-2025 09:56:43</t>
+          <t>09-09-2025 11:33:47</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>6204</v>
+        <v>8974</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5309,30 +5431,1309 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
         <v>3</v>
       </c>
       <c r="N63" t="n">
+        <v>70</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>26-08-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S63" s="1" t="n">
+        <v>-14.48179398148148</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>253659</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>35</v>
+      </c>
+      <c r="E64" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>09-09-2025 11:33:47</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>09-09-2025 12:08:47</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>09-09-2025 12:08:47</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:32:32</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>38850</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>70</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>11-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>253686</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>01-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>25</v>
+      </c>
+      <c r="E65" t="n">
+        <v>44.23333333333333</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:32:32</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:57:32</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:57:32</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10-09-2025 10:41:46</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5308</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>5</v>
+      </c>
+      <c r="N65" t="n">
+        <v>70</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>12-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>253016</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>02-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>30</v>
+      </c>
+      <c r="E66" t="n">
+        <v>73.38333333333334</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:30:00</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>05-09-2025 07:30:00</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>05-09-2025 08:43:23</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8806</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>152</v>
+      </c>
+      <c r="O66" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>40295</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>14-08-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>253259</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>04-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>35</v>
+      </c>
+      <c r="E67" t="n">
+        <v>69.23333333333333</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>05-09-2025 08:43:23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>05-09-2025 09:18:23</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>05-09-2025 09:18:23</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>05-09-2025 10:27:37</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8308</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>2</v>
+      </c>
+      <c r="N67" t="n">
+        <v>70</v>
+      </c>
+      <c r="O67" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>40295</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>25-08-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>252679</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>04-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>45</v>
+      </c>
+      <c r="E68" t="n">
+        <v>60</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>05-09-2025 10:27:37</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>05-09-2025 11:12:37</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>05-09-2025 11:12:37</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:12:37</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>7200</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>5</v>
+      </c>
+      <c r="N68" t="n">
         <v>76</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>01-08-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S63" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
+      <c r="O68" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>40295</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>01-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>252664</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>03-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>45</v>
+      </c>
+      <c r="E69" t="n">
+        <v>365.975</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:12:37</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:57:37</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>05-09-2025 12:57:37</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:03:35</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>43917</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" t="n">
+        <v>70</v>
+      </c>
+      <c r="O69" t="n">
+        <v>40279</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>40279</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>02-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S69" s="1" t="n">
+        <v>-6.460827546296296</v>
+      </c>
+      <c r="T69" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>253361</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>03-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>30</v>
+      </c>
+      <c r="E70" t="n">
+        <v>76.70833333333333</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:03:35</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:33:35</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>08-09-2025 11:33:35</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>08-09-2025 12:50:18</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>9205</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>70</v>
+      </c>
+      <c r="O70" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>11-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S70" s="1" t="n">
+        <v>-14</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>253375</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>04-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+      <c r="E71" t="n">
+        <v>51.88333333333333</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>08-09-2025 12:50:18</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>08-09-2025 13:15:18</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>08-09-2025 13:15:18</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:07:11</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>6226</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" t="n">
+        <v>70</v>
+      </c>
+      <c r="O71" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>25-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>253368</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>09-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" t="n">
+        <v>103.775</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:07:11</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:32:11</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>08-09-2025 14:32:11</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:15:57</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>12453</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>70</v>
+      </c>
+      <c r="O72" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>25-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>253377</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>25</v>
+      </c>
+      <c r="E73" t="n">
+        <v>127.7166666666667</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:15:57</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:40:57</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>09-09-2025 08:40:57</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>09-09-2025 10:48:40</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>15326</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+      <c r="N73" t="n">
+        <v>70</v>
+      </c>
+      <c r="O73" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>25-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>253367</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>11-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>09-09-2025 10:48:40</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>09-09-2025 11:13:40</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>09-09-2025 11:13:40</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:29:22</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>16284</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>70</v>
+      </c>
+      <c r="O74" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>25-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>253371</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>107.7666666666667</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:29:22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:54:22</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>09-09-2025 13:54:22</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:42:08</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>12932</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>70</v>
+      </c>
+      <c r="O75" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>25-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>253525</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>12-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>25</v>
+      </c>
+      <c r="E76" t="n">
+        <v>92.14166666666667</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>10-09-2025 07:42:08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>10-09-2025 08:07:08</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>10-09-2025 08:07:08</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:39:17</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>11057</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>70</v>
+      </c>
+      <c r="O76" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>26-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>253245</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>09-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>35</v>
+      </c>
+      <c r="E77" t="n">
+        <v>150.8333333333333</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>10-09-2025 09:39:17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>10-09-2025 10:14:17</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>10-09-2025 10:14:17</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10-09-2025 12:45:07</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>18100</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>4</v>
+      </c>
+      <c r="N77" t="n">
+        <v>70</v>
+      </c>
+      <c r="O77" t="n">
+        <v>40900</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>10-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S77" s="1" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>253401</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>09-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>30</v>
+      </c>
+      <c r="E78" t="n">
+        <v>22.81666666666667</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>10-09-2025 12:45:07</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>10-09-2025 13:15:07</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>10-09-2025 13:15:07</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10-09-2025 13:37:56</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>2738</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" t="n">
+        <v>70</v>
+      </c>
+      <c r="O78" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>12-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S78" s="1" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>03-09-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>17.075</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>08-09-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>2049</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>08-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>-0.3035243055555555</v>
+      </c>
+      <c r="T79" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:T90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>250891</v>
+        <v>254129</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>77.49166666666666</v>
+        <v>44.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:32:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:32:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08-09-2025 08:49:29</t>
+          <t>13-11-2025 13:16:30</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9299</v>
+        <v>5340</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,39 +591,41 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O2" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>13-08-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-39</v>
+        <v>-0.553125</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>252216</v>
+        <v>254385</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -632,37 +634,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>141.8083333333333</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08-09-2025 08:49:29</t>
+          <t>13-11-2025 13:16:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>08-09-2025 09:14:29</t>
+          <t>13-11-2025 13:48:30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>08-09-2025 09:14:29</t>
+          <t>13-11-2025 13:48:30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08-09-2025 11:36:18</t>
+          <t>13-11-2025 14:40:35</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17017</v>
+        <v>6250</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -671,39 +673,41 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="O3" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
+        <v>40627</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>40627</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>253527</v>
+        <v>254713</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -712,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>67.48333333333333</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08-09-2025 11:36:18</t>
+          <t>13-11-2025 14:40:35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:18</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:18</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>08-09-2025 13:12:47</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8098</v>
+        <v>5996</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -751,39 +755,41 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O4" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-9</v>
+        <v>-1.335104166666667</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>253524</v>
+        <v>243569</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -792,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>58.75833333333333</v>
+        <v>21.675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:12:47</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:27:47</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:27:47</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08-09-2025 14:26:32</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7051</v>
+        <v>2601</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -838,10 +844,10 @@
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -851,19 +857,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-9</v>
+        <v>-429</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>253528</v>
+        <v>254675</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -872,37 +878,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>119.175</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:26:32</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:41:32</t>
+          <t>14-11-2025 09:00:13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:41:32</t>
+          <t>14-11-2025 09:00:13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:43</t>
+          <t>14-11-2025 11:34:11</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14301</v>
+        <v>18475</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -918,10 +924,7 @@
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
-      </c>
-      <c r="O6" t="n">
-        <v>40910</v>
+        <v>76</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -931,11 +934,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0</v>
+        <v>-7.482071759259259</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -943,7 +946,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>244023</v>
+        <v>254512</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -952,37 +955,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>8.308333333333334</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:43</t>
+          <t>14-11-2025 11:34:11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:01:43</t>
+          <t>14-11-2025 11:51:11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:01:43</t>
+          <t>14-11-2025 11:51:11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:10:01</t>
+          <t>14-11-2025 12:50:44</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>997</v>
+        <v>7147</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -991,14 +994,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O7" t="n">
+        <v>406232</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1008,11 +1014,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-344.3819618055555</v>
+        <v>-6</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1020,7 +1026,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>252939</v>
+        <v>255039</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1029,37 +1035,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>89.8</v>
+        <v>9.15</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:10:01</t>
+          <t>14-11-2025 12:50:44</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:31:01</t>
+          <t>14-11-2025 13:22:44</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:31:01</t>
+          <t>14-11-2025 13:22:44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09-09-2025 11:00:49</t>
+          <t>14-11-2025 13:31:53</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10776</v>
+        <v>1098</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1077,6 +1083,9 @@
       <c r="N8" t="n">
         <v>70</v>
       </c>
+      <c r="O8" t="n">
+        <v>40624</v>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1085,11 +1094,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>22-08-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-18.45890625</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>7</v>
@@ -1097,7 +1106,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>252815</v>
+        <v>235572</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1106,37 +1115,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>242.9416666666667</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:00:49</t>
+          <t>14-11-2025 13:31:53</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:40:49</t>
+          <t>14-11-2025 13:50:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:40:49</t>
+          <t>14-11-2025 13:50:53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10-09-2025 07:43:46</t>
+          <t>17-11-2025 07:13:52</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29153</v>
+        <v>9958</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1145,14 +1154,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O9" t="n">
+        <v>406372</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1162,11 +1174,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-5.322060185185185</v>
+        <v>-744</v>
       </c>
       <c r="T9" t="n">
         <v>4</v>
@@ -1174,46 +1186,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>253072</v>
+        <v>255043</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>29.13333333333333</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>17-11-2025 07:13:52</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:00</t>
+          <t>17-11-2025 07:34:52</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:00</t>
+          <t>17-11-2025 07:34:52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>08-09-2025 08:15:08</t>
+          <t>17-11-2025 10:39:09</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3496</v>
+        <v>22114</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1222,17 +1234,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>70</v>
       </c>
       <c r="O10" t="n">
-        <v>40904</v>
+        <v>406552</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1242,11 +1254,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18-08-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -1254,46 +1266,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>253271</v>
+        <v>254457</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>42.63333333333333</v>
+        <v>3.925</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:15:08</t>
+          <t>17-11-2025 10:39:09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:40:08</t>
+          <t>17-11-2025 10:58:09</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:40:08</t>
+          <t>17-11-2025 10:58:09</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>08-09-2025 09:22:46</t>
+          <t>17-11-2025 11:02:05</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5116</v>
+        <v>471</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1306,13 +1318,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
       <c r="O11" t="n">
-        <v>40904</v>
+        <v>406372</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1322,58 +1334,58 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>253278</v>
+        <v>254256</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>28.425</v>
+        <v>50.925</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:22:46</t>
+          <t>17-11-2025 11:02:05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:47:46</t>
+          <t>17-11-2025 11:19:05</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:47:46</t>
+          <t>17-11-2025 11:19:05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08-09-2025 10:16:11</t>
+          <t>17-11-2025 12:10:00</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3411</v>
+        <v>6111</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1382,17 +1394,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
       </c>
       <c r="O12" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1402,58 +1414,58 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-13</v>
+        <v>-18</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>253317</v>
+        <v>254519</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>102.775</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08-09-2025 10:16:11</t>
+          <t>17-11-2025 12:10:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>08-09-2025 11:02:11</t>
+          <t>17-11-2025 12:25:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>08-09-2025 11:02:11</t>
+          <t>17-11-2025 12:25:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08-09-2025 12:44:58</t>
+          <t>17-11-2025 13:42:10</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12333</v>
+        <v>9259</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1462,17 +1474,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>40910</v>
+        <v>406422</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1482,58 +1494,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>253318</v>
+        <v>254189</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>51.55</v>
+        <v>55.875</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-09-2025 12:44:58</t>
+          <t>17-11-2025 13:42:10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>08-09-2025 13:09:58</t>
+          <t>17-11-2025 13:59:10</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>08-09-2025 13:09:58</t>
+          <t>17-11-2025 13:59:10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08-09-2025 14:01:31</t>
+          <t>17-11-2025 14:55:02</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6186</v>
+        <v>6705</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1542,17 +1554,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O14" t="n">
-        <v>40910</v>
+        <v>406552</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1562,11 +1574,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1574,46 +1586,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>253260</v>
+        <v>254309</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>109.4083333333333</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:01:31</t>
+          <t>17-11-2025 14:55:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:43:31</t>
+          <t>18-11-2025 07:29:02</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:43:31</t>
+          <t>18-11-2025 07:29:02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09-09-2025 08:32:55</t>
+          <t>19-11-2025 14:29:03</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13129</v>
+        <v>108002</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1622,17 +1634,14 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M15" t="n">
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>70</v>
-      </c>
-      <c r="O15" t="n">
-        <v>40279</v>
+        <v>152</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1642,19 +1651,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-16</v>
+        <v>-19.60351273148148</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>253455</v>
+        <v>254165</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1663,37 +1672,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>55.55833333333333</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:32:55</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:57:55</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:57:55</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09-09-2025 09:53:29</t>
+          <t>14-11-2025 08:40:19</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6667</v>
+        <v>6998</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1702,39 +1711,41 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O16" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-2</v>
+        <v>-0.3613310185185185</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>253247</v>
+        <v>254156</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1743,37 +1754,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>109.575</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09-09-2025 09:53:29</t>
+          <t>14-11-2025 08:40:19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09-09-2025 10:18:29</t>
+          <t>14-11-2025 09:05:19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>09-09-2025 10:18:29</t>
+          <t>14-11-2025 09:05:19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:03</t>
+          <t>14-11-2025 10:32:47</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13149</v>
+        <v>10497</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1782,39 +1793,41 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O17" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0</v>
+        <v>-0.4394386574074074</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>253249</v>
+        <v>254283</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1823,37 +1836,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28-08-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>57.75833333333333</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:03</t>
+          <t>14-11-2025 10:32:47</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:50:03</t>
+          <t>14-11-2025 10:59:47</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:50:03</t>
+          <t>14-11-2025 10:59:47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09-09-2025 13:47:49</t>
+          <t>14-11-2025 12:35:33</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6931</v>
+        <v>11492</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1866,11 +1879,14 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>76</v>
       </c>
+      <c r="O18" t="n">
+        <v>406552</v>
+      </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
@@ -1879,19 +1895,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>253706</v>
+        <v>253838</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1900,37 +1916,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
-        <v>311</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09-09-2025 13:47:49</t>
+          <t>14-11-2025 12:35:33</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09-09-2025 14:22:49</t>
+          <t>14-11-2025 13:23:33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>09-09-2025 14:22:49</t>
+          <t>14-11-2025 13:23:33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10-09-2025 11:33:49</t>
+          <t>17-11-2025 07:11:55</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>37320</v>
+        <v>13004</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1939,14 +1955,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1956,58 +1972,58 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>30-09-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0</v>
+        <v>-21.59526620370371</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>252702</v>
+        <v>252811</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
-        <v>58.38333333333333</v>
+        <v>11.875</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:00:00</t>
+          <t>17-11-2025 07:11:55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:34:00</t>
+          <t>17-11-2025 07:44:55</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:34:00</t>
+          <t>17-11-2025 07:44:55</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>05-09-2025 08:32:23</t>
+          <t>17-11-2025 07:56:48</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7006</v>
+        <v>1425</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2016,80 +2032,75 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
-        <v>152</v>
-      </c>
-      <c r="O20" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-08-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0</v>
+        <v>-15.29309606481482</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>253362</v>
+        <v>254365</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>58.38333333333333</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:32:23</t>
+          <t>17-11-2025 07:56:48</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:47:23</t>
+          <t>17-11-2025 08:29:48</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:47:23</t>
+          <t>17-11-2025 08:29:48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>05-09-2025 09:45:46</t>
+          <t>17-11-2025 09:37:20</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7006</v>
+        <v>8104</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2098,80 +2109,75 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>152</v>
-      </c>
-      <c r="O21" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>15-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0</v>
+        <v>-4.36291087962963</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>252681</v>
+        <v>254187</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
-        <v>115.0166666666667</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05-09-2025 09:45:46</t>
+          <t>17-11-2025 09:37:20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05-09-2025 10:19:46</t>
+          <t>17-11-2025 10:06:20</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>05-09-2025 10:19:46</t>
+          <t>17-11-2025 10:06:20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>05-09-2025 12:14:47</t>
+          <t>17-11-2025 10:52:43</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13802</v>
+        <v>5567</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2180,80 +2186,75 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
-      </c>
-      <c r="O22" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40279</v>
+        <v>0</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0</v>
+        <v>-10.4152662037037</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>253591</v>
+        <v>254586</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>17.41666666666667</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:14:47</t>
+          <t>17-11-2025 10:52:43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:29:47</t>
+          <t>17-11-2025 11:17:43</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:29:47</t>
+          <t>17-11-2025 11:17:43</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:47:12</t>
+          <t>17-11-2025 12:09:16</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2090</v>
+        <v>6185</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2262,80 +2263,75 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
-      </c>
-      <c r="O23" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>24-09-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0</v>
+        <v>-4.468420138888889</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>243569</v>
+        <v>254893</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>21.675</v>
+        <v>46.675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05-09-2025 12:47:12</t>
+          <t>17-11-2025 12:09:16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:06:12</t>
+          <t>17-11-2025 12:34:16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:06:12</t>
+          <t>17-11-2025 12:34:16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:52</t>
+          <t>17-11-2025 13:20:56</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2601</v>
+        <v>5601</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2344,17 +2340,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>76</v>
-      </c>
-      <c r="O24" t="n">
-        <v>40904</v>
+        <v>70</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2364,58 +2357,58 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-374</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>250284</v>
+        <v>254910</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E25" t="n">
-        <v>146.35</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:52</t>
+          <t>17-11-2025 13:20:56</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05-09-2025 14:07:52</t>
+          <t>17-11-2025 14:02:56</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>05-09-2025 14:07:52</t>
+          <t>17-11-2025 14:02:56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08-09-2025 08:34:13</t>
+          <t>18-11-2025 07:16:28</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17562</v>
+        <v>8824</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2428,13 +2421,10 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
-      </c>
-      <c r="O25" t="n">
-        <v>40910</v>
+        <v>76</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2444,11 +2434,11 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-193</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>7</v>
@@ -2456,46 +2446,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>252906</v>
+        <v>254339</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E26" t="n">
-        <v>34.725</v>
+        <v>245.9666666666667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08-09-2025 08:34:13</t>
+          <t>18-11-2025 07:16:28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:12:13</t>
+          <t>18-11-2025 07:58:28</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:12:13</t>
+          <t>18-11-2025 07:58:28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:46:57</t>
+          <t>18-11-2025 12:04:26</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4167</v>
+        <v>29516</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2504,17 +2494,14 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>76</v>
-      </c>
-      <c r="O26" t="n">
-        <v>40904</v>
+        <v>70</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2524,19 +2511,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-31</v>
+        <v>-30.46506944444445</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>253140</v>
+        <v>254556</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2545,37 +2532,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>55.83333333333334</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08-09-2025 09:46:57</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:03:57</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:03:57</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:59:47</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6700</v>
+        <v>20810</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2588,35 +2575,37 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
         <v>76</v>
       </c>
       <c r="O27" t="n">
-        <v>40900</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>26-08-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-26</v>
+        <v>-1.42806712962963</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>253100</v>
+        <v>254293</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2625,37 +2614,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>47.35</v>
+        <v>18.85</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>08-09-2025 10:59:47</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:47</t>
+          <t>14-11-2025 10:48:25</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:47</t>
+          <t>14-11-2025 10:48:25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>08-09-2025 12:19:08</t>
+          <t>14-11-2025 11:07:16</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>5682</v>
+        <v>2262</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2668,13 +2657,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
         <v>70</v>
       </c>
       <c r="O28" t="n">
-        <v>40900</v>
+        <v>40624</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2684,19 +2673,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>253246</v>
+        <v>252061</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2705,37 +2694,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>194.25</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:19:08</t>
+          <t>14-11-2025 11:07:16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:34:08</t>
+          <t>14-11-2025 11:24:16</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:34:08</t>
+          <t>14-11-2025 11:24:16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>09-09-2025 07:48:23</t>
+          <t>14-11-2025 12:00:26</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23310</v>
+        <v>4340</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2748,27 +2737,29 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
       <c r="O29" t="n">
-        <v>40900</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
+        <v>40628</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
@@ -2776,7 +2767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>253372</v>
+        <v>254291</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2785,37 +2776,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>103.775</v>
+        <v>18.85</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>09-09-2025 07:48:23</t>
+          <t>14-11-2025 12:00:26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>09-09-2025 08:07:23</t>
+          <t>14-11-2025 12:17:26</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>09-09-2025 08:07:23</t>
+          <t>14-11-2025 12:17:26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09-09-2025 09:51:09</t>
+          <t>14-11-2025 12:36:17</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>12453</v>
+        <v>2262</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2824,17 +2815,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
       <c r="O30" t="n">
-        <v>40904</v>
+        <v>40624</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2844,19 +2835,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>253370</v>
+        <v>254375</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2865,37 +2856,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>207.5416666666667</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>09-09-2025 09:51:09</t>
+          <t>14-11-2025 12:36:17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>09-09-2025 10:06:09</t>
+          <t>14-11-2025 12:55:17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>09-09-2025 10:06:09</t>
+          <t>14-11-2025 12:55:17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09-09-2025 13:33:42</t>
+          <t>14-11-2025 13:40:34</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>24905</v>
+        <v>5435</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2904,17 +2895,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
       <c r="O31" t="n">
-        <v>40904</v>
+        <v>40624</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2924,19 +2915,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>253095</v>
+        <v>254188</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2945,37 +2936,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
-        <v>76.31666666666666</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:33:42</t>
+          <t>14-11-2025 13:40:34</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:50:42</t>
+          <t>14-11-2025 14:01:34</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:50:42</t>
+          <t>14-11-2025 14:01:34</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10-09-2025 07:07:01</t>
+          <t>14-11-2025 14:39:01</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9158</v>
+        <v>4493</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2984,15 +2975,18 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
       </c>
+      <c r="O32" t="n">
+        <v>406372</v>
+      </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
@@ -3001,19 +2995,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>253332</v>
+        <v>254276</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3022,37 +3016,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>184.825</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:07:01</t>
+          <t>14-11-2025 14:39:01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:24:01</t>
+          <t>17-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:24:01</t>
+          <t>17-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10-09-2025 10:28:50</t>
+          <t>17-11-2025 07:37:03</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>22179</v>
+        <v>4444</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3061,15 +3055,18 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
+      <c r="O33" t="n">
+        <v>406422</v>
+      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3078,58 +3075,58 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-0.4366956018518519</v>
+        <v>-18</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>253359</v>
+        <v>254546</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34.5</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>134.0166666666667</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:00:00</t>
+          <t>17-11-2025 07:37:03</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:34:30</t>
+          <t>17-11-2025 07:52:03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:34:30</t>
+          <t>17-11-2025 07:52:03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>09-09-2025 09:48:31</t>
+          <t>17-11-2025 09:41:27</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>16082</v>
+        <v>13129</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3142,13 +3139,13 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
       </c>
       <c r="O34" t="n">
-        <v>40904</v>
+        <v>406242</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3158,58 +3155,58 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>253223</v>
+        <v>254555</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>50.5</v>
+        <v>36</v>
       </c>
       <c r="E35" t="n">
-        <v>16.4</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>09-09-2025 09:48:31</t>
+          <t>17-11-2025 09:41:27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>09-09-2025 10:39:01</t>
+          <t>17-11-2025 10:17:27</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>09-09-2025 10:39:01</t>
+          <t>17-11-2025 10:17:27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>09-09-2025 10:55:25</t>
+          <t>17-11-2025 13:10:26</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1968</v>
+        <v>20758</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3218,14 +3215,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O35" t="n">
+        <v>406232</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3235,58 +3235,58 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-8.455150462962964</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>253208</v>
+        <v>254198</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>54.5</v>
+        <v>34</v>
       </c>
       <c r="E36" t="n">
-        <v>104.2583333333333</v>
+        <v>215</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>09-09-2025 10:55:25</t>
+          <t>17-11-2025 13:10:26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>09-09-2025 11:49:55</t>
+          <t>17-11-2025 13:44:26</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>09-09-2025 11:49:55</t>
+          <t>17-11-2025 13:44:26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>09-09-2025 13:34:10</t>
+          <t>18-11-2025 09:19:26</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>12511</v>
+        <v>25800</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3295,14 +3295,14 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3312,58 +3312,58 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-4.565399305555555</v>
+        <v>-18.60680555555556</v>
       </c>
       <c r="T36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>253210</v>
+        <v>253885</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="E37" t="n">
-        <v>94.15833333333333</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>09-09-2025 13:34:10</t>
+          <t>18-11-2025 09:19:26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>09-09-2025 14:04:40</t>
+          <t>18-11-2025 09:51:26</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>09-09-2025 14:04:40</t>
+          <t>18-11-2025 09:51:26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10-09-2025 07:38:50</t>
+          <t>18-11-2025 11:37:22</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>11299</v>
+        <v>12712</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3372,11 +3372,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.3186342592592593</v>
+        <v>-4.369259259259259</v>
       </c>
       <c r="T37" t="n">
         <v>8</v>
@@ -3401,46 +3401,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>252601</v>
+        <v>254451</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>32.5</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
-        <v>51.20833333333334</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10-09-2025 07:38:50</t>
+          <t>18-11-2025 11:37:22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10-09-2025 08:11:20</t>
+          <t>18-11-2025 11:56:22</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10-09-2025 08:11:20</t>
+          <t>18-11-2025 11:56:22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10-09-2025 09:02:32</t>
+          <t>19-11-2025 09:17:31</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6145</v>
+        <v>38537</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
@@ -3466,58 +3466,58 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>31-12-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>0</v>
+        <v>-10.60546875</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>252002</v>
+        <v>254101</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E39" t="n">
-        <v>55.675</v>
+        <v>28.425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>04-09-2025 12:00:00</t>
+          <t>19-11-2025 09:17:31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>04-09-2025 12:55:00</t>
+          <t>19-11-2025 09:38:31</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>04-09-2025 12:55:00</t>
+          <t>19-11-2025 09:38:31</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>04-09-2025 13:50:40</t>
+          <t>19-11-2025 10:06:56</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>6681</v>
+        <v>3411</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3530,78 +3530,71 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>40307 (esterno)</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P39" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>40307</v>
+        <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-10.57685763888889</v>
+        <v>-26.30645833333333</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>235572</v>
+        <v>254100</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>82.98333333333333</v>
+        <v>28.425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>04-09-2025 13:50:40</t>
+          <t>19-11-2025 10:06:56</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>04-09-2025 14:20:40</t>
+          <t>19-11-2025 10:21:56</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>04-09-2025 14:20:40</t>
+          <t>19-11-2025 10:21:56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>05-09-2025 07:43:39</t>
+          <t>19-11-2025 10:50:22</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>9958</v>
+        <v>3411</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3614,14 +3607,11 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
-      <c r="O40" t="n">
-        <v>40904</v>
-      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
@@ -3630,58 +3620,58 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-689</v>
+        <v>-26.33661458333333</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>252685</v>
+        <v>254419</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
-        <v>74.56666666666666</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>05-09-2025 07:43:39</t>
+          <t>19-11-2025 10:50:22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05-09-2025 08:23:39</t>
+          <t>19-11-2025 11:09:22</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>05-09-2025 08:23:39</t>
+          <t>19-11-2025 11:09:22</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>05-09-2025 09:38:13</t>
+          <t>19-11-2025 12:21:42</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>8948</v>
+        <v>8681</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3690,80 +3680,75 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
-      </c>
-      <c r="O41" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0</v>
+        <v>-19.4000462962963</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>252682</v>
+        <v>254166</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>83.40833333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>05-09-2025 09:38:13</t>
+          <t>19-11-2025 12:21:42</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05-09-2025 10:18:13</t>
+          <t>19-11-2025 12:38:42</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>05-09-2025 10:18:13</t>
+          <t>19-11-2025 12:38:42</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>05-09-2025 11:41:38</t>
+          <t>19-11-2025 13:17:33</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10009</v>
+        <v>4662</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3772,80 +3757,75 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>76</v>
-      </c>
-      <c r="O42" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>252582</v>
+        <v>254481</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="E43" t="n">
-        <v>46.08333333333334</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>05-09-2025 11:41:38</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05-09-2025 12:11:38</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>05-09-2025 12:11:38</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:43</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>5530</v>
+        <v>9740</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3854,17 +3834,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O43" t="n">
-        <v>40290</v>
+        <v>40642</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3872,11 +3852,11 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>40290</v>
+        <v>40642</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-09-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3888,46 +3868,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>253314</v>
+        <v>254762</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>34.5</v>
       </c>
       <c r="E44" t="n">
-        <v>43.40833333333333</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:43</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:43</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:43</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>05-09-2025 14:11:07</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>5209</v>
+        <v>3823</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3936,17 +3916,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>40295</v>
+        <v>40623</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3954,62 +3934,62 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>40295</v>
+        <v>40623</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0</v>
+        <v>-1.291684027777778</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>253036</v>
+        <v>253380</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>42.5</v>
       </c>
       <c r="E45" t="n">
-        <v>78.73333333333333</v>
+        <v>104.275</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>05-09-2025 14:11:07</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05-09-2025 14:41:07</t>
+          <t>14-11-2025 07:42:31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>05-09-2025 14:41:07</t>
+          <t>14-11-2025 07:42:31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>08-09-2025 07:59:51</t>
+          <t>14-11-2025 09:26:48</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>9448</v>
+        <v>12513</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4018,31 +3998,33 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>H7 ;R5</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N45" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O45" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>22-08-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-30</v>
+        <v>-0.3936111111111111</v>
       </c>
       <c r="T45" t="n">
         <v>7</v>
@@ -4050,46 +4032,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>253284</v>
+        <v>253865</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>28-08-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>38.5</v>
       </c>
       <c r="E46" t="n">
-        <v>56.99166666666667</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>08-09-2025 07:59:51</t>
+          <t>14-11-2025 09:26:48</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>08-09-2025 08:29:51</t>
+          <t>14-11-2025 10:05:18</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>08-09-2025 08:29:51</t>
+          <t>14-11-2025 10:05:18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08-09-2025 09:26:51</t>
+          <t>14-11-2025 12:02:03</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>6839</v>
+        <v>14011</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4098,17 +4080,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>76</v>
-      </c>
-      <c r="O46" t="n">
-        <v>40910</v>
+        <v>70</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4118,58 +4097,58 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>28-08-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-24</v>
+        <v>-35.50142939814815</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>253313</v>
+        <v>254117</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="E47" t="n">
-        <v>100.0083333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>08-09-2025 09:26:51</t>
+          <t>14-11-2025 12:02:03</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>08-09-2025 09:51:51</t>
+          <t>14-11-2025 12:36:33</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>08-09-2025 09:51:51</t>
+          <t>14-11-2025 12:36:33</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:51</t>
+          <t>14-11-2025 12:45:43</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>12001</v>
+        <v>1100</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4178,18 +4157,15 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
         <v>76</v>
       </c>
-      <c r="O47" t="n">
-        <v>40910</v>
-      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -4198,11 +4174,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-16</v>
+        <v>-35.53175347222222</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -4210,46 +4186,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>252883</v>
+        <v>254824</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>75</v>
+        <v>32.5</v>
       </c>
       <c r="E48" t="n">
-        <v>247.3083333333333</v>
+        <v>748.225</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:51</t>
+          <t>14-11-2025 12:45:43</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08-09-2025 12:46:51</t>
+          <t>14-11-2025 13:18:13</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>08-09-2025 12:46:51</t>
+          <t>14-11-2025 13:18:13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>09-09-2025 08:54:10</t>
+          <t>18-11-2025 09:46:27</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>29677</v>
+        <v>89787</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4258,17 +4234,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O48" t="n">
-        <v>40900</v>
+        <v>406232</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4278,58 +4254,58 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>253710</v>
+        <v>254599</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>70</v>
+        <v>34.5</v>
       </c>
       <c r="E49" t="n">
-        <v>1.616666666666667</v>
+        <v>44.9</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>09-09-2025 08:54:10</t>
+          <t>18-11-2025 09:46:27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>09-09-2025 10:04:10</t>
+          <t>18-11-2025 10:20:57</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>09-09-2025 10:04:10</t>
+          <t>18-11-2025 10:20:57</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>09-09-2025 10:05:47</t>
+          <t>18-11-2025 11:05:51</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>194</v>
+        <v>5388</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4342,11 +4318,14 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
         <v>70</v>
       </c>
+      <c r="O49" t="n">
+        <v>406372</v>
+      </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
@@ -4355,11 +4334,11 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T49" t="n">
         <v>4</v>
@@ -4367,7 +4346,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>253687</v>
+        <v>253694</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4376,37 +4355,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E50" t="n">
-        <v>44.23333333333333</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>09-09-2025 10:05:47</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>09-09-2025 10:40:47</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>09-09-2025 10:40:47</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>09-09-2025 11:25:01</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>5308</v>
+        <v>14611</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4415,36 +4394,41 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>70</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O50" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>0</v>
+        <v>-0.6158043981481481</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>253267</v>
+        <v>254714</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4453,37 +4437,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>164.3666666666667</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>09-09-2025 11:25:01</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>09-09-2025 11:55:01</t>
+          <t>14-11-2025 07:16:45</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>09-09-2025 11:55:01</t>
+          <t>14-11-2025 07:16:45</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>09-09-2025 14:39:23</t>
+          <t>14-11-2025 08:48:14</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>19724</v>
+        <v>10977</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4492,36 +4476,41 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>70</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O51" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-09-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0</v>
+        <v>-1.366828703703704</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>253268</v>
+        <v>254088</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4530,54 +4519,57 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E52" t="n">
-        <v>78.55833333333334</v>
+        <v>425.2166666666666</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>09-09-2025 14:39:23</t>
+          <t>14-11-2025 08:48:14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10-09-2025 07:04:23</t>
+          <t>14-11-2025 09:48:14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>10-09-2025 07:04:23</t>
+          <t>14-11-2025 09:48:14</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10-09-2025 08:22:56</t>
+          <t>17-11-2025 08:53:27</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>9427</v>
+        <v>51026</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
         <v>70</v>
       </c>
+      <c r="O52" t="n">
+        <v>406372</v>
+      </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
@@ -4586,62 +4578,62 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>23-09-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>253409</v>
+        <v>254609</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>27-08-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E53" t="n">
-        <v>27.18333333333333</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>17-11-2025 08:53:27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>08-09-2025 07:19:00</t>
+          <t>17-11-2025 09:23:27</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>08-09-2025 07:19:00</t>
+          <t>17-11-2025 09:23:27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:11</t>
+          <t>18-11-2025 08:20:07</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>3262</v>
+        <v>50000</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4650,13 +4642,13 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>40910</v>
+        <v>406552</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4666,58 +4658,58 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>253194</v>
+        <v>254651</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>27-08-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>199.0833333333333</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:11</t>
+          <t>18-11-2025 08:20:07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>08-09-2025 08:01:11</t>
+          <t>18-11-2025 09:10:07</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>08-09-2025 08:01:11</t>
+          <t>18-11-2025 09:10:07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>08-09-2025 11:20:16</t>
+          <t>18-11-2025 09:32:45</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>23890</v>
+        <v>2717</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4726,17 +4718,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
         <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>76</v>
-      </c>
-      <c r="O54" t="n">
-        <v>40910</v>
+        <v>70</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4746,58 +4735,58 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>20-08-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>252843</v>
+        <v>254653</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E55" t="n">
-        <v>19.2</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>08-09-2025 11:20:16</t>
+          <t>18-11-2025 09:32:45</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>08-09-2025 11:47:16</t>
+          <t>18-11-2025 10:02:45</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>08-09-2025 11:47:16</t>
+          <t>18-11-2025 10:02:45</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>08-09-2025 12:06:28</t>
+          <t>18-11-2025 11:07:10</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>2304</v>
+        <v>7729</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4806,17 +4795,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>76</v>
-      </c>
-      <c r="O55" t="n">
-        <v>40904</v>
+        <v>70</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4826,58 +4812,58 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>30-07-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-57</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>253425</v>
+        <v>254903</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E56" t="n">
-        <v>146.35</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>08-09-2025 12:06:28</t>
+          <t>18-11-2025 11:07:10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>08-09-2025 12:29:28</t>
+          <t>18-11-2025 11:37:10</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>08-09-2025 12:29:28</t>
+          <t>18-11-2025 11:37:10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>08-09-2025 14:55:49</t>
+          <t>19-11-2025 07:53:48</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>17562</v>
+        <v>30797</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4886,14 +4872,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4903,58 +4889,58 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-10.59001157407407</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>252569</v>
+        <v>254354</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E57" t="n">
-        <v>9.583333333333334</v>
+        <v>18.675</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>08-09-2025 14:55:49</t>
+          <t>19-11-2025 07:53:48</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>09-09-2025 07:14:49</t>
+          <t>19-11-2025 08:28:48</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>09-09-2025 07:14:49</t>
+          <t>19-11-2025 08:28:48</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09-09-2025 07:24:24</t>
+          <t>19-11-2025 08:47:29</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1150</v>
+        <v>2241</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4963,14 +4949,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N57" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4980,58 +4966,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-7.609861111111111</v>
+        <v>-15.43277777777778</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>252995</v>
+        <v>254671</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E58" t="n">
-        <v>68.31666666666666</v>
+        <v>136.1666666666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>09-09-2025 07:24:24</t>
+          <t>19-11-2025 08:47:29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>09-09-2025 07:43:24</t>
+          <t>19-11-2025 09:22:29</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>09-09-2025 07:43:24</t>
+          <t>19-11-2025 09:22:29</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>09-09-2025 08:51:43</t>
+          <t>19-11-2025 11:38:39</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>8198</v>
+        <v>16340</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5040,14 +5026,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N58" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5057,19 +5043,19 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-8.337164351851852</v>
+        <v>-8.551643518518519</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>252827</v>
+        <v>254941</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5078,37 +5064,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E59" t="n">
-        <v>410</v>
+        <v>35.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>09-09-2025 08:51:43</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>09-09-2025 09:08:43</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>09-09-2025 09:08:43</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10-09-2025 07:58:43</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>49200</v>
+        <v>4260</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5121,32 +5107,37 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>76</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O59" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>04-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-6.300358796296297</v>
+        <v>-1.338541666666667</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>253602</v>
+        <v>253897</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5155,37 +5146,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E60" t="n">
-        <v>117.0833333333333</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10-09-2025 07:58:43</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10-09-2025 08:19:43</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>10-09-2025 08:19:43</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10-09-2025 10:16:48</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>14050</v>
+        <v>11282</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5198,71 +5189,76 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N60" t="n">
         <v>76</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
+      <c r="O60" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.39625</v>
+        <v>-0.434386574074074</v>
       </c>
       <c r="T60" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>253374</v>
+        <v>254230</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E61" t="n">
-        <v>59.60833333333333</v>
+        <v>62.475</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>09-09-2025 07:00:00</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>09-09-2025 07:35:00</t>
+          <t>14-11-2025 11:13:31</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>09-09-2025 07:35:00</t>
+          <t>14-11-2025 11:13:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>09-09-2025 08:34:36</t>
+          <t>14-11-2025 12:15:59</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>7153</v>
+        <v>7497</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5271,17 +5267,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
       </c>
       <c r="O61" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5291,58 +5287,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>253721</v>
+        <v>254433</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E62" t="n">
-        <v>39.39166666666667</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>09-09-2025 08:34:36</t>
+          <t>14-11-2025 12:15:59</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>09-09-2025 09:04:36</t>
+          <t>14-11-2025 12:30:59</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>09-09-2025 09:04:36</t>
+          <t>14-11-2025 12:30:59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09-09-2025 09:44:00</t>
+          <t>14-11-2025 13:38:50</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4727</v>
+        <v>8142</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5351,17 +5347,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
       </c>
       <c r="O62" t="n">
-        <v>40900</v>
+        <v>406422</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5371,11 +5367,11 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>08-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
@@ -5383,46 +5379,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>252833</v>
+        <v>254106</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>74.78333333333333</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09-09-2025 09:44:00</t>
+          <t>14-11-2025 13:38:50</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>09-09-2025 10:19:00</t>
+          <t>14-11-2025 13:57:50</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>09-09-2025 10:19:00</t>
+          <t>14-11-2025 13:57:50</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>09-09-2025 11:33:47</t>
+          <t>17-11-2025 07:45:29</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>8974</v>
+        <v>12917</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5431,11 +5427,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
@@ -5448,58 +5444,58 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>26-08-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-14.48179398148148</v>
+        <v>-31.32325231481482</v>
       </c>
       <c r="T63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>253659</v>
+        <v>253650</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E64" t="n">
-        <v>323.75</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>09-09-2025 11:33:47</t>
+          <t>17-11-2025 07:45:29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:47</t>
+          <t>17-11-2025 08:17:29</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:47</t>
+          <t>17-11-2025 08:17:29</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>10-09-2025 09:32:32</t>
+          <t>17-11-2025 12:50:37</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>38850</v>
+        <v>32776</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5508,14 +5504,14 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -5525,58 +5521,58 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>0</v>
+        <v>-18.53515046296296</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>253686</v>
+        <v>253614</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E65" t="n">
-        <v>44.23333333333333</v>
+        <v>122.45</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10-09-2025 09:32:32</t>
+          <t>17-11-2025 12:50:37</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>10-09-2025 09:57:32</t>
+          <t>17-11-2025 13:24:37</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>10-09-2025 09:57:32</t>
+          <t>17-11-2025 13:24:37</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10-09-2025 10:41:46</t>
+          <t>18-11-2025 07:27:04</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>5308</v>
+        <v>14694</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5585,14 +5581,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -5602,58 +5598,58 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>253016</v>
+        <v>254915</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>02-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E66" t="n">
-        <v>73.38333333333334</v>
+        <v>48.875</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:00:00</t>
+          <t>18-11-2025 07:27:04</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:30:00</t>
+          <t>18-11-2025 07:59:04</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:30:00</t>
+          <t>18-11-2025 07:59:04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>05-09-2025 08:43:23</t>
+          <t>18-11-2025 08:47:56</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>8806</v>
+        <v>5865</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5669,73 +5665,68 @@
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>152</v>
-      </c>
-      <c r="O66" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>14-08-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>253259</v>
+        <v>254381</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>69.23333333333333</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>05-09-2025 08:43:23</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05-09-2025 09:18:23</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>05-09-2025 09:18:23</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>05-09-2025 10:27:37</t>
+          <t>14-11-2025 08:58:52</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>8308</v>
+        <v>10064</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5744,33 +5735,28 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
       </c>
-      <c r="O67" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P67" t="n">
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>0</v>
+        <v>-17.37421296296296</v>
       </c>
       <c r="T67" t="n">
         <v>7</v>
@@ -5778,46 +5764,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>252679</v>
+        <v>254107</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E68" t="n">
-        <v>60</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>05-09-2025 10:27:37</t>
+          <t>14-11-2025 08:58:52</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05-09-2025 11:12:37</t>
+          <t>14-11-2025 09:28:52</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>05-09-2025 11:12:37</t>
+          <t>14-11-2025 09:28:52</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>05-09-2025 12:12:37</t>
+          <t>14-11-2025 12:23:55</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>7200</v>
+        <v>21007</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5826,80 +5812,75 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>76</v>
-      </c>
-      <c r="O68" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>0</v>
+        <v>-33.51661458333334</v>
       </c>
       <c r="T68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>252664</v>
+        <v>250284</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>45</v>
       </c>
       <c r="E69" t="n">
-        <v>365.975</v>
+        <v>146.35</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:12:37</t>
+          <t>14-11-2025 12:23:55</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:37</t>
+          <t>14-11-2025 13:08:55</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:37</t>
+          <t>14-11-2025 13:08:55</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>08-09-2025 11:03:35</t>
+          <t>17-11-2025 07:35:16</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>43917</v>
+        <v>17562</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5908,33 +5889,31 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
       <c r="O69" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>40279</v>
+        <v>0</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>02-09-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-6.460827546296296</v>
+        <v>-254</v>
       </c>
       <c r="T69" t="n">
         <v>7</v>
@@ -5942,46 +5921,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>253361</v>
+        <v>254237</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>30</v>
       </c>
       <c r="E70" t="n">
-        <v>76.70833333333333</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:03:35</t>
+          <t>17-11-2025 07:35:16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:33:35</t>
+          <t>17-11-2025 08:05:16</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:33:35</t>
+          <t>17-11-2025 08:05:16</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>08-09-2025 12:50:18</t>
+          <t>17-11-2025 11:09:22</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>9205</v>
+        <v>22091</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5990,31 +5969,35 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-14</v>
+        <v>-7.464837962962963</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6022,46 +6005,46 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>253375</v>
+        <v>254429</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E71" t="n">
-        <v>51.88333333333333</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>08-09-2025 12:50:18</t>
+          <t>17-11-2025 11:09:22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08-09-2025 13:15:18</t>
+          <t>17-11-2025 11:44:22</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>08-09-2025 13:15:18</t>
+          <t>17-11-2025 11:44:22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:11</t>
+          <t>18-11-2025 07:44:36</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>6226</v>
+        <v>28829</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6070,17 +6053,17 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
         <v>70</v>
       </c>
       <c r="O71" t="n">
-        <v>40904</v>
+        <v>406372</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -6090,58 +6073,58 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>253368</v>
+        <v>254437</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E72" t="n">
-        <v>103.775</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:11</t>
+          <t>18-11-2025 07:44:36</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:32:11</t>
+          <t>18-11-2025 08:14:36</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:32:11</t>
+          <t>18-11-2025 08:14:36</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>09-09-2025 08:15:57</t>
+          <t>18-11-2025 09:12:40</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>12453</v>
+        <v>6967</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6150,18 +6133,15 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N72" t="n">
         <v>70</v>
       </c>
-      <c r="O72" t="n">
-        <v>40904</v>
-      </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
@@ -6170,11 +6150,11 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>0</v>
+        <v>-10.3837962962963</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
@@ -6182,46 +6162,46 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>253377</v>
+        <v>254605</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E73" t="n">
-        <v>127.7166666666667</v>
+        <v>39.025</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:15:57</t>
+          <t>18-11-2025 09:12:40</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:57</t>
+          <t>18-11-2025 09:42:40</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:57</t>
+          <t>18-11-2025 09:42:40</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>09-09-2025 10:48:40</t>
+          <t>18-11-2025 10:21:41</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>15326</v>
+        <v>4683</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6230,18 +6210,15 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
-      <c r="O73" t="n">
-        <v>40904</v>
-      </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
@@ -6250,11 +6227,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>0</v>
+        <v>-4.431730324074074</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
@@ -6262,46 +6239,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>253367</v>
+        <v>254758</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E74" t="n">
-        <v>135.7</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>09-09-2025 10:48:40</t>
+          <t>18-11-2025 10:21:41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>09-09-2025 11:13:40</t>
+          <t>18-11-2025 10:51:41</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>09-09-2025 11:13:40</t>
+          <t>18-11-2025 10:51:41</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>09-09-2025 13:29:22</t>
+          <t>18-11-2025 11:53:04</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>16284</v>
+        <v>7366</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6310,18 +6287,15 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
-      <c r="O74" t="n">
-        <v>40904</v>
-      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
@@ -6330,11 +6304,11 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>0</v>
+        <v>-1.495190972222222</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
@@ -6342,46 +6316,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>253371</v>
+        <v>253382</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>107.7666666666667</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:29:22</t>
+          <t>18-11-2025 11:53:04</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:54:22</t>
+          <t>18-11-2025 12:28:04</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:54:22</t>
+          <t>18-11-2025 12:28:04</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10-09-2025 07:42:08</t>
+          <t>18-11-2025 13:53:10</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>12932</v>
+        <v>10212</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6390,39 +6364,39 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" t="n">
+        <v>76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>07-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S75" s="1" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T75" t="n">
         <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>70</v>
-      </c>
-      <c r="O75" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>25-09-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>253525</v>
+        <v>254715</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6431,37 +6405,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E76" t="n">
-        <v>92.14166666666667</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10-09-2025 07:42:08</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10-09-2025 08:07:08</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>10-09-2025 08:07:08</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10-09-2025 09:39:17</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>11057</v>
+        <v>16145</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6470,31 +6444,33 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O76" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>26-09-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>0</v>
+        <v>-1.409403935185185</v>
       </c>
       <c r="T76" t="n">
         <v>2</v>
@@ -6502,7 +6478,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>253245</v>
+        <v>254287</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6511,37 +6487,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>150.8333333333333</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10-09-2025 09:39:17</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10-09-2025 10:14:17</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>10-09-2025 10:14:17</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10-09-2025 12:45:07</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>18100</v>
+        <v>15556</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6554,13 +6530,13 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
       </c>
       <c r="O77" t="n">
-        <v>40900</v>
+        <v>406422</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6570,19 +6546,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>253401</v>
+        <v>254427</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6591,70 +6567,72 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E78" t="n">
-        <v>22.81666666666667</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10-09-2025 12:45:07</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:15:07</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:15:07</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:37:56</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>2738</v>
+        <v>6667</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
       <c r="O78" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
+        <v>406422</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-13</v>
+        <v>-4.590092592592592</v>
       </c>
       <c r="T78" t="n">
         <v>7</v>
@@ -6662,78 +6640,928 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
+        <v>254574</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>40</v>
+      </c>
+      <c r="E79" t="n">
+        <v>173.6083333333333</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:09:44</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:49:44</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:49:44</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:43:20</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>20833</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" t="n">
+        <v>70</v>
+      </c>
+      <c r="O79" t="n">
+        <v>406422</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>14-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S79" s="1" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T79" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>254460</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>21-10-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>30</v>
+      </c>
+      <c r="E80" t="n">
+        <v>46.68333333333333</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:43:20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:13:20</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:13:20</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:00:01</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>5602</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>70</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>23-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>-35.45835069444445</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>254245</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:00:01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:40:01</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>17-11-2025 11:40:01</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:09:49</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>10776</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81" t="n">
+        <v>70</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>30-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S81" s="1" t="n">
+        <v>-18.54848958333333</v>
+      </c>
+      <c r="T81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>254356</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:09:49</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:34:49</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>17-11-2025 13:34:49</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:34:25</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>21552</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>4</v>
+      </c>
+      <c r="N82" t="n">
+        <v>70</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>08-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="n">
+        <v>-10.35723958333333</v>
+      </c>
+      <c r="T82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>253961</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="n">
+        <v>35.91666666666666</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:34:25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:59:25</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>18-11-2025 08:59:25</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:35:20</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>4310</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>4</v>
+      </c>
+      <c r="N83" t="n">
+        <v>70</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>11-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S83" s="1" t="n">
+        <v>-7.399542824074074</v>
+      </c>
+      <c r="T83" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>254652</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="n">
+        <v>28.73333333333333</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:35:20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:15:20</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:15:20</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:44:04</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>3448</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>70</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>21-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>254756</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>50</v>
+      </c>
+      <c r="E85" t="n">
+        <v>60.625</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:44:04</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:34:04</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>18-11-2025 11:34:04</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>18-11-2025 12:34:42</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>7275</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>9</v>
+      </c>
+      <c r="N85" t="n">
+        <v>70</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>24-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S85" s="1" t="n">
+        <v>-4.524097222222222</v>
+      </c>
+      <c r="T85" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>254598</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>04-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>45</v>
+      </c>
+      <c r="E86" t="n">
+        <v>104.2583333333333</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>18-11-2025 12:34:42</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:19:42</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:19:42</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:03:57</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>12511</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>13</v>
+      </c>
+      <c r="N86" t="n">
+        <v>70</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>15-12-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>254252</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>70</v>
+      </c>
+      <c r="E87" t="n">
+        <v>80.51666666666667</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:03:57</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>19-11-2025 08:13:57</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>19-11-2025 08:13:57</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>19-11-2025 09:34:28</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>9662</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>4</v>
+      </c>
+      <c r="N87" t="n">
+        <v>70</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S87" s="1" t="n">
+        <v>-26.39894097222222</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>253906</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>35</v>
+      </c>
+      <c r="E88" t="n">
+        <v>45.79166666666666</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>19-11-2025 09:34:28</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>19-11-2025 10:09:28</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>19-11-2025 10:09:28</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>19-11-2025 10:55:16</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>5495</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" t="n">
+        <v>70</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>25-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>254521</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>39.68333333333333</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:39:41</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>4762</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" t="n">
+        <v>70</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>15-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
         <v>252980</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>03-09-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
         <v>17.075</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>08-09-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>08-09-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>08-09-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>08-09-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
         <v>2049</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>foglio</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>08-09-2025 00:00:00</t>
         </is>
       </c>
-      <c r="S79" s="1" t="n">
-        <v>-0.3035243055555555</v>
-      </c>
-      <c r="T79" t="n">
+      <c r="S90" s="1" t="n">
+        <v>-77.30352430555556</v>
+      </c>
+      <c r="T90" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:T91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -869,7 +869,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>254675</v>
+        <v>254156</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -878,14 +878,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>153.9583333333333</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -894,21 +894,21 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:13</t>
+          <t>14-11-2025 08:58:13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:13</t>
+          <t>14-11-2025 08:58:13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:34:11</t>
+          <t>14-11-2025 10:25:42</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18475</v>
+        <v>10497</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,36 +917,41 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
         <v>76</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
+      <c r="O6" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-7.482071759259259</v>
+        <v>-0.4345138888888889</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254512</v>
+        <v>254375</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -955,37 +960,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E7" t="n">
-        <v>59.55833333333333</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:34:11</t>
+          <t>14-11-2025 10:25:42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:51:11</t>
+          <t>14-11-2025 11:01:42</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:51:11</t>
+          <t>14-11-2025 11:01:42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:50:44</t>
+          <t>14-11-2025 11:46:59</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7147</v>
+        <v>5435</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -994,17 +999,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>406232</v>
+        <v>40624</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1014,19 +1019,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>255039</v>
+        <v>254256</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1039,33 +1044,33 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>9.15</v>
+        <v>50.925</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:50:44</t>
+          <t>14-11-2025 11:46:59</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:22:44</t>
+          <t>14-11-2025 12:03:59</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:22:44</t>
+          <t>14-11-2025 12:03:59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:31:53</t>
+          <t>14-11-2025 12:54:55</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1098</v>
+        <v>6111</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1084,7 +1089,7 @@
         <v>70</v>
       </c>
       <c r="O8" t="n">
-        <v>40624</v>
+        <v>406422</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1094,19 +1099,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>235572</v>
+        <v>254519</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1115,37 +1120,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>82.98333333333333</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:31:53</t>
+          <t>14-11-2025 12:54:55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:50:53</t>
+          <t>14-11-2025 13:09:55</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:50:53</t>
+          <t>14-11-2025 13:09:55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:13:52</t>
+          <t>14-11-2025 14:27:04</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9958</v>
+        <v>9259</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1158,13 +1163,13 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1174,11 +1179,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-744</v>
+        <v>-4</v>
       </c>
       <c r="T9" t="n">
         <v>4</v>
@@ -1186,7 +1191,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>255043</v>
+        <v>254237</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1195,37 +1200,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>184.2833333333333</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:13:52</t>
+          <t>14-11-2025 14:27:04</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:52</t>
+          <t>14-11-2025 14:50:04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:52</t>
+          <t>14-11-2025 14:50:04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:09</t>
+          <t>17-11-2025 09:54:10</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>22114</v>
+        <v>22091</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1234,39 +1239,43 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>70</v>
       </c>
-      <c r="O10" t="n">
-        <v>406552</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0</v>
+        <v>-8.327309027777778</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254457</v>
+        <v>255039</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1275,37 +1284,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>3.925</v>
+        <v>9.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:09</t>
+          <t>17-11-2025 09:54:10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:58:09</t>
+          <t>17-11-2025 10:17:10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:58:09</t>
+          <t>17-11-2025 10:17:10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 11:02:05</t>
+          <t>17-11-2025 10:26:19</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>471</v>
+        <v>1098</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1318,13 +1327,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
       <c r="O11" t="n">
-        <v>406372</v>
+        <v>40624</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1334,19 +1343,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254256</v>
+        <v>254824</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1359,33 +1368,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>50.925</v>
+        <v>748.225</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:02:05</t>
+          <t>17-11-2025 10:26:19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:19:05</t>
+          <t>17-11-2025 10:58:19</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:19:05</t>
+          <t>17-11-2025 10:58:19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 12:10:00</t>
+          <t>19-11-2025 07:26:32</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6111</v>
+        <v>89787</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1394,17 +1403,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O12" t="n">
-        <v>406422</v>
+        <v>406232</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1414,19 +1423,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>254519</v>
+        <v>254599</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1435,37 +1444,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E13" t="n">
-        <v>77.15833333333333</v>
+        <v>44.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 12:10:00</t>
+          <t>19-11-2025 07:26:32</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-11-2025 12:25:00</t>
+          <t>19-11-2025 08:00:32</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-11-2025 12:25:00</t>
+          <t>19-11-2025 08:00:32</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:42:10</t>
+          <t>19-11-2025 08:45:26</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9259</v>
+        <v>5388</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1478,13 +1487,13 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
         <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1498,7 +1507,7 @@
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="T13" t="n">
         <v>4</v>
@@ -1506,7 +1515,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254189</v>
+        <v>253961</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1515,37 +1524,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>55.875</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:42:10</t>
+          <t>19-11-2025 08:45:26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:59:10</t>
+          <t>19-11-2025 09:00:26</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:59:10</t>
+          <t>19-11-2025 09:00:26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:02</t>
+          <t>19-11-2025 09:36:21</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6705</v>
+        <v>4310</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1554,17 +1563,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
         <v>70</v>
       </c>
       <c r="O14" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1574,19 +1583,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254309</v>
+        <v>250284</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1595,37 +1604,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E15" t="n">
-        <v>900.0166666666667</v>
+        <v>146.35</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:02</t>
+          <t>19-11-2025 09:36:21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18-11-2025 07:29:02</t>
+          <t>19-11-2025 09:59:21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18-11-2025 07:29:02</t>
+          <t>19-11-2025 09:59:21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19-11-2025 14:29:03</t>
+          <t>19-11-2025 12:25:42</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>108002</v>
+        <v>17562</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1634,14 +1643,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="O15" t="n">
+        <v>406422</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1651,14 +1663,14 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-19.60351273148148</v>
+        <v>-254</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1745,7 +1757,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254156</v>
+        <v>254117</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1754,14 +1766,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>87.47499999999999</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1770,21 +1782,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:19</t>
+          <t>14-11-2025 09:07:19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:19</t>
+          <t>14-11-2025 09:07:19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-11-2025 10:32:47</t>
+          <t>14-11-2025 09:16:29</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10497</v>
+        <v>1100</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1797,37 +1809,32 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>76</v>
       </c>
-      <c r="O17" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P17" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.4394386574074074</v>
+        <v>-35.38644675925926</v>
       </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254283</v>
+        <v>254107</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1836,37 +1843,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>95.76666666666667</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14-11-2025 10:32:47</t>
+          <t>14-11-2025 09:16:29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-11-2025 10:59:47</t>
+          <t>14-11-2025 09:58:29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14-11-2025 10:59:47</t>
+          <t>14-11-2025 09:58:29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:33</t>
+          <t>14-11-2025 12:53:32</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>11492</v>
+        <v>21007</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1875,17 +1882,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>76</v>
-      </c>
-      <c r="O18" t="n">
-        <v>406552</v>
+        <v>70</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1895,19 +1899,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-9</v>
+        <v>-33.53718171296296</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>253838</v>
+        <v>254293</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1916,37 +1920,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>108.3666666666667</v>
+        <v>18.85</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:33</t>
+          <t>14-11-2025 12:53:32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:23:33</t>
+          <t>14-11-2025 13:22:32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:23:33</t>
+          <t>14-11-2025 13:22:32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17-11-2025 07:11:55</t>
+          <t>14-11-2025 13:41:23</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13004</v>
+        <v>2262</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1959,11 +1963,14 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
         <v>70</v>
       </c>
+      <c r="O19" t="n">
+        <v>40624</v>
+      </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
@@ -1972,19 +1979,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-21.59526620370371</v>
+        <v>-14</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>252811</v>
+        <v>253838</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1993,37 +2000,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>11.875</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17-11-2025 07:11:55</t>
+          <t>14-11-2025 13:41:23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17-11-2025 07:44:55</t>
+          <t>14-11-2025 14:08:23</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17-11-2025 07:44:55</t>
+          <t>14-11-2025 14:08:23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:48</t>
+          <t>17-11-2025 07:56:45</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1425</v>
+        <v>13004</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2049,19 +2056,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-15.29309606481482</v>
+        <v>-21.33108217592592</v>
       </c>
       <c r="T20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254365</v>
+        <v>254605</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2070,37 +2077,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>67.53333333333333</v>
+        <v>39.025</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:48</t>
+          <t>17-11-2025 07:56:45</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:48</t>
+          <t>17-11-2025 08:29:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:48</t>
+          <t>17-11-2025 08:29:45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-11-2025 09:37:20</t>
+          <t>17-11-2025 09:08:47</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8104</v>
+        <v>4683</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2109,7 +2116,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2126,19 +2133,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-4.36291087962963</v>
+        <v>-3.381099537037037</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254187</v>
+        <v>254758</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2151,33 +2158,33 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>46.39166666666667</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17-11-2025 09:37:20</t>
+          <t>17-11-2025 09:08:47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:06:20</t>
+          <t>17-11-2025 09:35:47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:06:20</t>
+          <t>17-11-2025 09:35:47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:52:43</t>
+          <t>17-11-2025 10:37:10</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>5567</v>
+        <v>7366</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2190,7 +2197,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>70</v>
@@ -2203,11 +2210,11 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-10.4152662037037</v>
+        <v>-0.4424768518518519</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
@@ -2215,46 +2222,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254586</v>
+        <v>254556</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>51.54166666666666</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17-11-2025 10:52:43</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17-11-2025 11:17:43</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-11-2025 11:17:43</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:16</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6185</v>
+        <v>20810</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2263,75 +2270,80 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O23" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-4.468420138888889</v>
+        <v>-1.42806712962963</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254893</v>
+        <v>254230</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>46.675</v>
+        <v>62.475</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:16</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17-11-2025 12:34:16</t>
+          <t>14-11-2025 10:52:25</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-11-2025 12:34:16</t>
+          <t>14-11-2025 10:52:25</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-11-2025 13:20:56</t>
+          <t>14-11-2025 11:54:53</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5601</v>
+        <v>7497</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2340,15 +2352,18 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
         <v>70</v>
       </c>
+      <c r="O24" t="n">
+        <v>406422</v>
+      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -2357,58 +2372,58 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254910</v>
+        <v>254433</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>73.53333333333333</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17-11-2025 13:20:56</t>
+          <t>14-11-2025 11:54:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17-11-2025 14:02:56</t>
+          <t>14-11-2025 12:09:53</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-11-2025 14:02:56</t>
+          <t>14-11-2025 12:09:53</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18-11-2025 07:16:28</t>
+          <t>14-11-2025 13:17:44</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8824</v>
+        <v>8142</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2417,14 +2432,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O25" t="n">
+        <v>406422</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2434,58 +2452,58 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254339</v>
+        <v>254106</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>245.9666666666667</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>18-11-2025 07:16:28</t>
+          <t>14-11-2025 13:17:44</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>18-11-2025 07:58:28</t>
+          <t>14-11-2025 13:36:44</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18-11-2025 07:58:28</t>
+          <t>14-11-2025 13:36:44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18-11-2025 12:04:26</t>
+          <t>17-11-2025 07:24:23</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>29516</v>
+        <v>12917</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2498,7 +2516,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>70</v>
@@ -2511,11 +2529,11 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-30.46506944444445</v>
+        <v>-31.30859953703704</v>
       </c>
       <c r="T26" t="n">
         <v>7</v>
@@ -2523,7 +2541,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254556</v>
+        <v>254460</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2532,37 +2550,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27" t="n">
-        <v>173.4166666666667</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 07:24:23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>17-11-2025 07:45:23</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>17-11-2025 07:45:23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>17-11-2025 08:32:04</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>20810</v>
+        <v>5602</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2571,41 +2589,36 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>76</v>
-      </c>
-      <c r="O27" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-1.42806712962963</v>
+        <v>-35.35560185185185</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254293</v>
+        <v>254198</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2614,37 +2627,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>18.85</v>
+        <v>215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>17-11-2025 08:32:04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14-11-2025 10:48:25</t>
+          <t>17-11-2025 09:06:04</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14-11-2025 10:48:25</t>
+          <t>17-11-2025 09:06:04</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14-11-2025 11:07:16</t>
+          <t>17-11-2025 12:41:04</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2262</v>
+        <v>25800</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2653,17 +2666,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
-      </c>
-      <c r="O28" t="n">
-        <v>40624</v>
+        <v>152</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2673,19 +2683,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-14</v>
+        <v>-18.52851851851852</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>252061</v>
+        <v>253885</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2698,33 +2708,33 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>36.16666666666666</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14-11-2025 11:07:16</t>
+          <t>17-11-2025 12:41:04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14-11-2025 11:24:16</t>
+          <t>17-11-2025 13:13:04</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>14-11-2025 11:24:16</t>
+          <t>17-11-2025 13:13:04</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:26</t>
+          <t>17-11-2025 14:59:00</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4340</v>
+        <v>12712</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2737,37 +2747,32 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
-      <c r="O29" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P29" t="n">
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>0</v>
+        <v>-3.624305555555555</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254291</v>
+        <v>254451</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2776,37 +2781,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>18.85</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:26</t>
+          <t>17-11-2025 14:59:00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14-11-2025 12:17:26</t>
+          <t>18-11-2025 07:18:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14-11-2025 12:17:26</t>
+          <t>18-11-2025 07:18:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14-11-2025 12:36:17</t>
+          <t>18-11-2025 12:39:08</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2262</v>
+        <v>38537</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2819,14 +2824,11 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
-      <c r="O30" t="n">
-        <v>40624</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -2835,58 +2837,58 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-14</v>
+        <v>-10.52718171296296</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254375</v>
+        <v>254481</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>32.5</v>
       </c>
       <c r="E31" t="n">
-        <v>45.29166666666666</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14-11-2025 12:36:17</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14-11-2025 12:55:17</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14-11-2025 12:55:17</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14-11-2025 13:40:34</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>5435</v>
+        <v>9740</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2899,74 +2901,76 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
       <c r="O31" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
+        <v>40642</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>40642</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254188</v>
+        <v>254762</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>34.5</v>
       </c>
       <c r="E32" t="n">
-        <v>37.44166666666667</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>14-11-2025 13:40:34</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14-11-2025 14:01:34</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14-11-2025 14:01:34</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-11-2025 14:39:01</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4493</v>
+        <v>3823</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2979,74 +2983,76 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
       </c>
       <c r="O32" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-1</v>
+        <v>-1.291684027777778</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254276</v>
+        <v>253865</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>34.5</v>
       </c>
       <c r="E33" t="n">
-        <v>37.03333333333333</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14-11-2025 14:39:01</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17-11-2025 07:00:01</t>
+          <t>14-11-2025 07:34:31</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>17-11-2025 07:00:01</t>
+          <t>14-11-2025 07:34:31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17-11-2025 07:37:03</t>
+          <t>14-11-2025 09:31:17</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4444</v>
+        <v>14011</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3059,14 +3065,11 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
-      <c r="O33" t="n">
-        <v>406422</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3075,58 +3078,58 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-18</v>
+        <v>-38.33299189814815</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254546</v>
+        <v>254245</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15</v>
+        <v>32.5</v>
       </c>
       <c r="E34" t="n">
-        <v>109.4083333333333</v>
+        <v>89.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>17-11-2025 07:37:03</t>
+          <t>14-11-2025 09:31:17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>17-11-2025 07:52:03</t>
+          <t>14-11-2025 10:03:47</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17-11-2025 07:52:03</t>
+          <t>14-11-2025 10:03:47</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17-11-2025 09:41:27</t>
+          <t>14-11-2025 11:33:35</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>13129</v>
+        <v>10776</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3144,9 +3147,6 @@
       <c r="N34" t="n">
         <v>70</v>
       </c>
-      <c r="O34" t="n">
-        <v>406242</v>
-      </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
@@ -3155,23 +3155,23 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-7</v>
+        <v>-18.4179224537037</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254555</v>
+        <v>254356</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3180,33 +3180,33 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>36</v>
+        <v>30.5</v>
       </c>
       <c r="E35" t="n">
-        <v>172.9833333333333</v>
+        <v>179.6</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>17-11-2025 09:41:27</t>
+          <t>14-11-2025 11:33:35</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:27</t>
+          <t>14-11-2025 12:04:05</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:27</t>
+          <t>14-11-2025 12:04:05</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17-11-2025 13:10:26</t>
+          <t>17-11-2025 07:03:41</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>20758</v>
+        <v>21552</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3215,17 +3215,14 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>76</v>
-      </c>
-      <c r="O35" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3235,58 +3232,58 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0</v>
+        <v>-9.563825231481481</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254198</v>
+        <v>254381</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>215</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17-11-2025 13:10:26</t>
+          <t>17-11-2025 07:03:41</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17-11-2025 13:44:26</t>
+          <t>17-11-2025 07:36:11</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17-11-2025 13:44:26</t>
+          <t>17-11-2025 07:36:11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>18-11-2025 09:19:26</t>
+          <t>17-11-2025 09:00:03</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>25800</v>
+        <v>10064</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3295,14 +3292,14 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3312,58 +3309,58 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-18.60680555555556</v>
+        <v>-21.31130208333333</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>253885</v>
+        <v>254652</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="E37" t="n">
-        <v>105.9333333333333</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>18-11-2025 09:19:26</t>
+          <t>17-11-2025 09:00:03</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18-11-2025 09:51:26</t>
+          <t>17-11-2025 09:32:33</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18-11-2025 09:51:26</t>
+          <t>17-11-2025 09:32:33</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:22</t>
+          <t>17-11-2025 10:01:17</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12712</v>
+        <v>3448</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3376,7 +3373,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3389,11 +3386,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-4.369259259259259</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>8</v>
@@ -3401,46 +3398,46 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254451</v>
+        <v>254756</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>40.5</v>
       </c>
       <c r="E38" t="n">
-        <v>321.1416666666667</v>
+        <v>60.625</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:22</t>
+          <t>17-11-2025 10:01:17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56:22</t>
+          <t>17-11-2025 10:41:47</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56:22</t>
+          <t>17-11-2025 10:41:47</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19-11-2025 09:17:31</t>
+          <t>17-11-2025 11:42:24</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>38537</v>
+        <v>7275</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3453,7 +3450,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
@@ -3466,58 +3463,58 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-10.60546875</v>
+        <v>-4.424050925925926</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>254101</v>
+        <v>253694</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="E39" t="n">
-        <v>28.425</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>19-11-2025 09:17:31</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:31</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:31</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19-11-2025 10:06:56</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>3411</v>
+        <v>14611</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3526,28 +3523,33 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>70</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O39" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-26.30645833333333</v>
+        <v>-0.6158043981481481</v>
       </c>
       <c r="T39" t="n">
         <v>2</v>
@@ -3555,46 +3557,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254100</v>
+        <v>253380</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
-        <v>28.425</v>
+        <v>104.275</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19-11-2025 10:06:56</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-11-2025 10:21:56</t>
+          <t>14-11-2025 07:46:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19-11-2025 10:21:56</t>
+          <t>14-11-2025 07:46:45</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>19-11-2025 10:50:22</t>
+          <t>14-11-2025 09:31:02</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3411</v>
+        <v>12513</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3603,75 +3605,80 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
+      <c r="O40" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-26.33661458333333</v>
+        <v>-0.3965509259259259</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254419</v>
+        <v>254598</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E41" t="n">
-        <v>72.34166666666667</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>19-11-2025 10:50:22</t>
+          <t>14-11-2025 09:31:02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>19-11-2025 11:09:22</t>
+          <t>14-11-2025 10:16:02</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>19-11-2025 11:09:22</t>
+          <t>14-11-2025 10:16:02</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>19-11-2025 12:21:42</t>
+          <t>14-11-2025 12:00:17</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>8681</v>
+        <v>12511</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3680,11 +3687,11 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N41" t="n">
         <v>70</v>
@@ -3697,11 +3704,11 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-19.4000462962963</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>7</v>
@@ -3709,46 +3716,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254166</v>
+        <v>252061</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="E42" t="n">
-        <v>38.85</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>19-11-2025 12:21:42</t>
+          <t>14-11-2025 12:00:17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>19-11-2025 12:38:42</t>
+          <t>14-11-2025 13:05:17</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>19-11-2025 12:38:42</t>
+          <t>14-11-2025 13:05:17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>19-11-2025 13:17:33</t>
+          <t>14-11-2025 13:41:27</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>4662</v>
+        <v>4340</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3761,71 +3768,76 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
         <v>70</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
+      <c r="O42" t="n">
+        <v>40628</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254481</v>
+        <v>254546</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>81.16666666666667</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 13:41:27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 14:11:27</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 14:11:27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>17-11-2025 08:00:52</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>9740</v>
+        <v>13129</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3838,76 +3850,74 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
         <v>70</v>
       </c>
       <c r="O43" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406242</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254762</v>
+        <v>235572</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>34.5</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>31.85833333333333</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>17-11-2025 08:00:52</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>17-11-2025 08:30:52</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>17-11-2025 08:30:52</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>17-11-2025 09:53:51</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>3823</v>
+        <v>9958</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3920,76 +3930,74 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
         <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>-744</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>253380</v>
+        <v>254188</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>42.5</v>
+        <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>104.275</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>17-11-2025 09:53:51</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:31</t>
+          <t>17-11-2025 10:23:51</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:31</t>
+          <t>17-11-2025 10:23:51</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14-11-2025 09:26:48</t>
+          <t>17-11-2025 11:01:17</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>12513</v>
+        <v>4493</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3998,80 +4006,78 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
         <v>70</v>
       </c>
       <c r="O45" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-0.3936111111111111</v>
+        <v>-1</v>
       </c>
       <c r="T45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>253865</v>
+        <v>254457</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
-        <v>116.7583333333333</v>
+        <v>3.925</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14-11-2025 09:26:48</t>
+          <t>17-11-2025 11:01:17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14-11-2025 10:05:18</t>
+          <t>17-11-2025 11:26:17</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>14-11-2025 10:05:18</t>
+          <t>17-11-2025 11:26:17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14-11-2025 12:02:03</t>
+          <t>17-11-2025 11:30:13</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>14011</v>
+        <v>471</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4080,15 +4086,18 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
+      <c r="O46" t="n">
+        <v>406372</v>
+      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
@@ -4097,58 +4106,58 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-35.50142939814815</v>
+        <v>-1</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254117</v>
+        <v>254437</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>34.5</v>
+        <v>25</v>
       </c>
       <c r="E47" t="n">
-        <v>9.166666666666666</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>14-11-2025 12:02:03</t>
+          <t>17-11-2025 11:30:13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14-11-2025 12:36:33</t>
+          <t>17-11-2025 11:55:13</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>14-11-2025 12:36:33</t>
+          <t>17-11-2025 11:55:13</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14-11-2025 12:45:43</t>
+          <t>17-11-2025 12:53:16</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1100</v>
+        <v>6967</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4161,10 +4170,13 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O47" t="n">
+        <v>406372</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4174,11 +4186,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-35.53175347222222</v>
+        <v>-1</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -4186,46 +4198,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254824</v>
+        <v>254941</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="E48" t="n">
-        <v>748.225</v>
+        <v>35.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14-11-2025 12:45:43</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 13:18:13</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 13:18:13</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18-11-2025 09:46:27</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>89787</v>
+        <v>4260</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4234,78 +4246,80 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="O48" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>0</v>
+        <v>-1.338541666666667</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254599</v>
+        <v>253897</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>34.5</v>
+        <v>44</v>
       </c>
       <c r="E49" t="n">
-        <v>44.9</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>18-11-2025 09:46:27</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>18-11-2025 10:20:57</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>18-11-2025 10:20:57</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>18-11-2025 11:05:51</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>5388</v>
+        <v>11282</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4314,78 +4328,80 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N49" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O49" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-2</v>
+        <v>-0.434386574074074</v>
       </c>
       <c r="T49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>253694</v>
+        <v>254675</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E50" t="n">
-        <v>121.7583333333333</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>14-11-2025 10:56:31</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>14-11-2025 10:56:31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 13:30:28</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>14611</v>
+        <v>18475</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4398,41 +4414,36 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
         <v>76</v>
       </c>
-      <c r="O50" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P50" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-0.6158043981481481</v>
+        <v>-11.38066550925926</v>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254714</v>
+        <v>254512</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4441,33 +4452,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
-        <v>91.47499999999999</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 13:30:28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>14-11-2025 13:47:28</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:45</t>
+          <t>14-11-2025 13:47:28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:48:14</t>
+          <t>14-11-2025 14:47:02</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>10977</v>
+        <v>7147</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4480,80 +4491,78 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>76</v>
       </c>
       <c r="O51" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406232</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-1.366828703703704</v>
+        <v>-6</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254088</v>
+        <v>253382</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
-        <v>425.2166666666666</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 08:48:14</t>
+          <t>14-11-2025 14:47:02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-11-2025 09:48:14</t>
+          <t>17-11-2025 07:04:02</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-11-2025 09:48:14</t>
+          <t>17-11-2025 07:04:02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17-11-2025 08:53:27</t>
+          <t>17-11-2025 08:29:08</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>51026</v>
+        <v>10212</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4562,10 +4571,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O52" t="n">
         <v>406372</v>
@@ -4578,11 +4587,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-30</v>
+        <v>-12</v>
       </c>
       <c r="T52" t="n">
         <v>2</v>
@@ -4590,11 +4599,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254609</v>
+        <v>254910</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4603,37 +4612,37 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E53" t="n">
-        <v>416.6666666666667</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17-11-2025 08:53:27</t>
+          <t>17-11-2025 08:29:08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17-11-2025 09:23:27</t>
+          <t>17-11-2025 08:46:08</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17-11-2025 09:23:27</t>
+          <t>17-11-2025 08:46:08</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18-11-2025 08:20:07</t>
+          <t>17-11-2025 09:59:40</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>50000</v>
+        <v>8824</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4642,13 +4651,13 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="O53" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4658,58 +4667,58 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254651</v>
+        <v>254283</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>22.64166666666667</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>18-11-2025 08:20:07</t>
+          <t>17-11-2025 09:59:40</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>18-11-2025 09:10:07</t>
+          <t>17-11-2025 10:16:40</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>18-11-2025 09:10:07</t>
+          <t>17-11-2025 10:16:40</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18-11-2025 09:32:45</t>
+          <t>17-11-2025 11:52:26</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>2717</v>
+        <v>11492</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4718,14 +4727,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O54" t="n">
+        <v>406372</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4735,58 +4747,58 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="T54" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254653</v>
+        <v>254555</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E55" t="n">
-        <v>64.40833333333333</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>18-11-2025 09:32:45</t>
+          <t>17-11-2025 11:52:26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>18-11-2025 10:02:45</t>
+          <t>17-11-2025 12:09:26</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>18-11-2025 10:02:45</t>
+          <t>17-11-2025 12:09:26</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18-11-2025 11:07:10</t>
+          <t>18-11-2025 07:02:25</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>7729</v>
+        <v>20758</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4795,14 +4807,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
         <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O55" t="n">
+        <v>406232</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4812,23 +4827,23 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254903</v>
+        <v>253650</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4837,33 +4852,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>256.6416666666667</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>18-11-2025 11:07:10</t>
+          <t>18-11-2025 07:02:25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:10</t>
+          <t>18-11-2025 07:19:25</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18-11-2025 11:37:10</t>
+          <t>18-11-2025 07:19:25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>19-11-2025 07:53:48</t>
+          <t>18-11-2025 11:52:33</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>30797</v>
+        <v>32776</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4872,14 +4887,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M56" t="n">
         <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4889,58 +4904,58 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>0</v>
+        <v>-18.44603009259259</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254354</v>
+        <v>254309</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E57" t="n">
-        <v>18.675</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>19-11-2025 07:53:48</t>
+          <t>18-11-2025 11:52:33</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>19-11-2025 08:28:48</t>
+          <t>18-11-2025 12:24:33</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>19-11-2025 08:28:48</t>
+          <t>18-11-2025 12:24:33</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19-11-2025 08:47:29</t>
+          <t>20-11-2025 11:24:34</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2241</v>
+        <v>108002</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4949,14 +4964,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4966,58 +4981,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-15.43277777777778</v>
+        <v>-19.42659722222222</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254671</v>
+        <v>254714</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E58" t="n">
-        <v>136.1666666666667</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>19-11-2025 08:47:29</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19-11-2025 09:22:29</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>19-11-2025 09:22:29</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>19-11-2025 11:38:39</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>16340</v>
+        <v>10977</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5026,75 +5041,80 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O58" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-8.551643518518519</v>
+        <v>-1.389913194444444</v>
       </c>
       <c r="T58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254941</v>
+        <v>244023</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E59" t="n">
-        <v>35.5</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>14-11-2025 10:04:47</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>4260</v>
+        <v>997</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5103,33 +5123,31 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="O59" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406062</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-1.338541666666667</v>
+        <v>-417</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
@@ -5137,46 +5155,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>253897</v>
+        <v>254429</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E60" t="n">
-        <v>94.01666666666667</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>14-11-2025 10:04:47</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>14-11-2025 10:34:47</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>14-11-2025 10:34:47</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>14-11-2025 14:35:01</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>11282</v>
+        <v>28829</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5185,80 +5203,78 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O60" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-0.434386574074074</v>
+        <v>-9</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254230</v>
+        <v>254291</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E61" t="n">
-        <v>62.475</v>
+        <v>18.85</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>14-11-2025 14:35:01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14-11-2025 11:13:31</t>
+          <t>17-11-2025 07:05:01</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14-11-2025 11:13:31</t>
+          <t>17-11-2025 07:05:01</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>14-11-2025 12:15:59</t>
+          <t>17-11-2025 07:23:52</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>7497</v>
+        <v>2262</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5267,17 +5283,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
       </c>
       <c r="O61" t="n">
-        <v>406422</v>
+        <v>40624</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5287,58 +5303,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254433</v>
+        <v>254276</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E62" t="n">
-        <v>67.84999999999999</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14-11-2025 12:15:59</t>
+          <t>17-11-2025 07:23:52</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:59</t>
+          <t>17-11-2025 07:58:52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14-11-2025 12:30:59</t>
+          <t>17-11-2025 07:58:52</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>14-11-2025 13:38:50</t>
+          <t>17-11-2025 08:35:54</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>8142</v>
+        <v>4444</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5347,11 +5363,11 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
@@ -5367,58 +5383,58 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254106</v>
+        <v>254893</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E63" t="n">
-        <v>107.6416666666667</v>
+        <v>46.675</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14-11-2025 13:38:50</t>
+          <t>17-11-2025 08:35:54</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14-11-2025 13:57:50</t>
+          <t>17-11-2025 09:05:54</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14-11-2025 13:57:50</t>
+          <t>17-11-2025 09:05:54</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:29</t>
+          <t>17-11-2025 09:52:35</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>12917</v>
+        <v>5601</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5427,15 +5443,18 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
       </c>
+      <c r="O63" t="n">
+        <v>406372</v>
+      </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
@@ -5444,58 +5463,58 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-31.32325231481482</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>253650</v>
+        <v>254189</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>273.1333333333333</v>
+        <v>55.875</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:29</t>
+          <t>17-11-2025 09:52:35</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17-11-2025 08:17:29</t>
+          <t>17-11-2025 10:22:35</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17-11-2025 08:17:29</t>
+          <t>17-11-2025 10:22:35</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>17-11-2025 12:50:37</t>
+          <t>17-11-2025 11:18:27</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>32776</v>
+        <v>6705</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5504,14 +5523,17 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O64" t="n">
+        <v>406372</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -5521,58 +5543,58 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-18.53515046296296</v>
+        <v>-1</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>253614</v>
+        <v>255043</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E65" t="n">
-        <v>122.45</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17-11-2025 12:50:37</t>
+          <t>17-11-2025 11:18:27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17-11-2025 13:24:37</t>
+          <t>17-11-2025 11:43:27</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>17-11-2025 13:24:37</t>
+          <t>17-11-2025 11:43:27</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18-11-2025 07:27:04</t>
+          <t>17-11-2025 14:47:44</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>14694</v>
+        <v>22114</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5581,14 +5603,17 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="O65" t="n">
+        <v>406372</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -5598,23 +5623,23 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254915</v>
+        <v>254521</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5623,33 +5648,33 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>48.875</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:27:04</t>
+          <t>17-11-2025 14:47:44</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:59:04</t>
+          <t>18-11-2025 07:17:44</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:59:04</t>
+          <t>18-11-2025 07:17:44</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18-11-2025 08:47:56</t>
+          <t>18-11-2025 07:57:25</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>5865</v>
+        <v>4762</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5658,11 +5683,11 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
         <v>70</v>
@@ -5675,11 +5700,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>0</v>
+        <v>-2.615833333333333</v>
       </c>
       <c r="T66" t="n">
         <v>7</v>
@@ -5687,7 +5712,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>254381</v>
+        <v>252811</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -5696,37 +5721,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>83.86666666666666</v>
+        <v>11.875</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 07:57:25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>18-11-2025 08:32:25</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>18-11-2025 08:32:25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:52</t>
+          <t>18-11-2025 08:44:18</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>10064</v>
+        <v>1425</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5735,11 +5760,11 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
@@ -5752,11 +5777,11 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-17.37421296296296</v>
+        <v>-15.31505208333333</v>
       </c>
       <c r="T67" t="n">
         <v>7</v>
@@ -5764,7 +5789,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254107</v>
+        <v>254651</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -5773,37 +5798,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E68" t="n">
-        <v>175.0583333333333</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:52</t>
+          <t>18-11-2025 08:44:18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14-11-2025 09:28:52</t>
+          <t>18-11-2025 09:19:18</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14-11-2025 09:28:52</t>
+          <t>18-11-2025 09:19:18</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>14-11-2025 12:23:55</t>
+          <t>18-11-2025 09:41:56</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>21007</v>
+        <v>2717</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5816,7 +5841,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>70</v>
@@ -5829,19 +5854,19 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>-33.51661458333334</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>250284</v>
+        <v>254653</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -5850,37 +5875,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
-        <v>146.35</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>14-11-2025 12:23:55</t>
+          <t>18-11-2025 09:41:56</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14-11-2025 13:08:55</t>
+          <t>18-11-2025 10:11:56</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14-11-2025 13:08:55</t>
+          <t>18-11-2025 10:11:56</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:16</t>
+          <t>18-11-2025 11:16:21</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>17562</v>
+        <v>7729</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5889,18 +5914,15 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
-      <c r="O69" t="n">
-        <v>406422</v>
-      </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
@@ -5909,11 +5931,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-254</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>7</v>
@@ -5921,7 +5943,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254237</v>
+        <v>254915</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5930,37 +5952,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>184.0916666666667</v>
+        <v>48.875</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:16</t>
+          <t>18-11-2025 11:16:21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17-11-2025 08:05:16</t>
+          <t>18-11-2025 11:51:21</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>17-11-2025 08:05:16</t>
+          <t>18-11-2025 11:51:21</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17-11-2025 11:09:22</t>
+          <t>18-11-2025 12:40:13</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>22091</v>
+        <v>5865</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5969,82 +5991,75 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P70" t="n">
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-7.464837962962963</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254429</v>
+        <v>254715</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>35</v>
       </c>
       <c r="E71" t="n">
-        <v>240.2416666666667</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17-11-2025 11:09:22</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17-11-2025 11:44:22</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>17-11-2025 11:44:22</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>18-11-2025 07:44:36</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>28829</v>
+        <v>16145</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6053,31 +6068,33 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O71" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-9</v>
+        <v>-1.409403935185185</v>
       </c>
       <c r="T71" t="n">
         <v>2</v>
@@ -6085,46 +6102,46 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254437</v>
+        <v>254287</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E72" t="n">
-        <v>58.05833333333333</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>18-11-2025 07:44:36</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:36</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:36</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>18-11-2025 09:12:40</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>6967</v>
+        <v>15556</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6137,11 +6154,14 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
         <v>70</v>
       </c>
+      <c r="O72" t="n">
+        <v>406422</v>
+      </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
@@ -6150,135 +6170,140 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-10.3837962962963</v>
+        <v>-18</v>
       </c>
       <c r="T72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254605</v>
+        <v>254427</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E73" t="n">
-        <v>39.025</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>18-11-2025 09:12:40</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>18-11-2025 09:42:40</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>18-11-2025 09:42:40</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18-11-2025 10:21:41</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>4683</v>
+        <v>6667</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
+      <c r="O73" t="n">
+        <v>406422</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-4.431730324074074</v>
+        <v>-4.590092592592592</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254758</v>
+        <v>254574</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E74" t="n">
-        <v>61.38333333333333</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>18-11-2025 10:21:41</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18-11-2025 10:51:41</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>18-11-2025 10:51:41</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>18-11-2025 11:53:04</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>7366</v>
+        <v>20833</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6291,11 +6316,14 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
+      <c r="O74" t="n">
+        <v>406422</v>
+      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
@@ -6304,58 +6332,58 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-1.495190972222222</v>
+        <v>-7</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>253382</v>
+        <v>254187</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>85.09999999999999</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>18-11-2025 11:53:04</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18-11-2025 12:28:04</t>
+          <t>17-11-2025 10:18:20</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>18-11-2025 12:28:04</t>
+          <t>17-11-2025 10:18:20</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>18-11-2025 13:53:10</t>
+          <t>17-11-2025 11:04:44</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>10212</v>
+        <v>5567</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6364,14 +6392,14 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
         <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O75" t="n">
         <v>406372</v>
@@ -6384,19 +6412,19 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-12</v>
+        <v>-1</v>
       </c>
       <c r="T75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254715</v>
+        <v>254586</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6405,37 +6433,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>134.5416666666667</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 11:04:44</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>17-11-2025 11:29:44</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>17-11-2025 11:29:44</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>17-11-2025 12:21:16</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>16145</v>
+        <v>6185</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6444,41 +6472,39 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O76" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>-1.409403935185185</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254287</v>
+        <v>254166</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6487,37 +6513,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>129.6333333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>17-11-2025 12:21:16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>17-11-2025 12:46:16</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>17-11-2025 12:46:16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>17-11-2025 13:25:07</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>15556</v>
+        <v>4662</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6536,7 +6562,7 @@
         <v>70</v>
       </c>
       <c r="O77" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6546,19 +6572,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254427</v>
+        <v>254365</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6567,80 +6593,75 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E78" t="n">
-        <v>55.55833333333333</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>17-11-2025 13:25:07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>17-11-2025 14:00:07</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>17-11-2025 14:00:07</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>18-11-2025 07:07:39</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>6667</v>
+        <v>8104</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
-      <c r="O78" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P78" t="n">
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-4.590092592592592</v>
+        <v>-4.296984953703704</v>
       </c>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>254574</v>
+        <v>253614</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6649,37 +6670,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>40</v>
       </c>
       <c r="E79" t="n">
-        <v>173.6083333333333</v>
+        <v>122.45</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>18-11-2025 07:07:39</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>18-11-2025 07:47:39</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>18-11-2025 07:47:39</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>18-11-2025 09:50:06</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>20833</v>
+        <v>14694</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6688,17 +6709,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>70</v>
-      </c>
-      <c r="O79" t="n">
-        <v>406422</v>
+        <v>152</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6708,11 +6726,11 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
         <v>7</v>
@@ -6720,7 +6738,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254460</v>
+        <v>254903</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -6729,37 +6747,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E80" t="n">
-        <v>46.68333333333333</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>18-11-2025 09:50:06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17-11-2025 10:13:20</t>
+          <t>18-11-2025 10:30:06</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>17-11-2025 10:13:20</t>
+          <t>18-11-2025 10:30:06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>17-11-2025 11:00:01</t>
+          <t>18-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>5602</v>
+        <v>30797</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6772,7 +6790,7 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
         <v>70</v>
@@ -6785,11 +6803,11 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>-35.45835069444445</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -6797,7 +6815,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>254245</v>
+        <v>254339</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6806,37 +6824,37 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E81" t="n">
-        <v>89.8</v>
+        <v>245.9666666666667</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>17-11-2025 11:00:01</t>
+          <t>18-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>17-11-2025 11:40:01</t>
+          <t>19-11-2025 07:21:45</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>17-11-2025 11:40:01</t>
+          <t>19-11-2025 07:21:45</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:49</t>
+          <t>19-11-2025 11:27:43</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>10776</v>
+        <v>29516</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6849,7 +6867,7 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N81" t="n">
         <v>70</v>
@@ -6866,15 +6884,15 @@
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-18.54848958333333</v>
+        <v>-30.47758101851852</v>
       </c>
       <c r="T81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254356</v>
+        <v>254101</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6883,37 +6901,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E82" t="n">
-        <v>179.6</v>
+        <v>28.425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:49</t>
+          <t>19-11-2025 11:27:43</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>17-11-2025 13:34:49</t>
+          <t>19-11-2025 11:57:43</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>17-11-2025 13:34:49</t>
+          <t>19-11-2025 11:57:43</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18-11-2025 08:34:25</t>
+          <t>19-11-2025 12:26:08</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>21552</v>
+        <v>3411</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6926,7 +6944,7 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N82" t="n">
         <v>70</v>
@@ -6939,19 +6957,19 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-10.35723958333333</v>
+        <v>-26.51815393518519</v>
       </c>
       <c r="T82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>253961</v>
+        <v>254100</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -6960,37 +6978,37 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>25</v>
       </c>
       <c r="E83" t="n">
-        <v>35.91666666666666</v>
+        <v>28.425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>18-11-2025 08:34:25</t>
+          <t>19-11-2025 12:26:08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>18-11-2025 08:59:25</t>
+          <t>19-11-2025 12:51:08</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18-11-2025 08:59:25</t>
+          <t>19-11-2025 12:51:08</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>18-11-2025 09:35:20</t>
+          <t>19-11-2025 13:19:34</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>4310</v>
+        <v>3411</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7003,7 +7021,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N83" t="n">
         <v>70</v>
@@ -7016,19 +7034,19 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-7.399542824074074</v>
+        <v>-26.55525462962963</v>
       </c>
       <c r="T83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254652</v>
+        <v>254252</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7037,37 +7055,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E84" t="n">
-        <v>28.73333333333333</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>18-11-2025 09:35:20</t>
+          <t>19-11-2025 13:19:34</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>18-11-2025 10:15:20</t>
+          <t>19-11-2025 13:54:34</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>18-11-2025 10:15:20</t>
+          <t>19-11-2025 13:54:34</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>18-11-2025 10:44:04</t>
+          <t>20-11-2025 07:15:05</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3448</v>
+        <v>9662</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7093,19 +7111,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
-        <v>0</v>
+        <v>-27.30214120370371</v>
       </c>
       <c r="T84" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>254756</v>
+        <v>253974</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7114,37 +7132,37 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E85" t="n">
-        <v>60.625</v>
+        <v>28.425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>18-11-2025 10:44:04</t>
+          <t>20-11-2025 07:15:05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18-11-2025 11:34:04</t>
+          <t>20-11-2025 07:50:05</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>18-11-2025 11:34:04</t>
+          <t>20-11-2025 07:50:05</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>18-11-2025 12:34:42</t>
+          <t>20-11-2025 08:18:30</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>7275</v>
+        <v>3411</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7157,7 +7175,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N85" t="n">
         <v>70</v>
@@ -7170,19 +7188,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>29-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>-4.524097222222222</v>
+        <v>-32.3461863425926</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>254598</v>
+        <v>254419</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7191,37 +7209,37 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E86" t="n">
-        <v>104.2583333333333</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>18-11-2025 12:34:42</t>
+          <t>20-11-2025 08:18:30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18-11-2025 13:19:42</t>
+          <t>20-11-2025 08:53:30</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18-11-2025 13:19:42</t>
+          <t>20-11-2025 08:53:30</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>19-11-2025 07:03:57</t>
+          <t>20-11-2025 10:05:51</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12511</v>
+        <v>8681</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7234,7 +7252,7 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N86" t="n">
         <v>70</v>
@@ -7247,11 +7265,11 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>0</v>
+        <v>-20.42072916666667</v>
       </c>
       <c r="T86" t="n">
         <v>7</v>
@@ -7259,7 +7277,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>254252</v>
+        <v>254354</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7272,33 +7290,33 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>80.51666666666667</v>
+        <v>18.675</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>19-11-2025 07:03:57</t>
+          <t>20-11-2025 10:05:51</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>19-11-2025 08:13:57</t>
+          <t>20-11-2025 10:35:51</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>19-11-2025 08:13:57</t>
+          <t>20-11-2025 10:35:51</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>19-11-2025 09:34:28</t>
+          <t>20-11-2025 10:54:31</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>9662</v>
+        <v>2241</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7311,7 +7329,7 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N87" t="n">
         <v>70</v>
@@ -7324,19 +7342,19 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>-26.39894097222222</v>
+        <v>-16.45453125</v>
       </c>
       <c r="T87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>253906</v>
+        <v>254547</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7345,37 +7363,37 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E88" t="n">
-        <v>45.79166666666666</v>
+        <v>68.55</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>19-11-2025 09:34:28</t>
+          <t>20-11-2025 10:54:31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19-11-2025 10:09:28</t>
+          <t>20-11-2025 11:24:31</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>19-11-2025 10:09:28</t>
+          <t>20-11-2025 11:24:31</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>19-11-2025 10:55:16</t>
+          <t>20-11-2025 12:33:04</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>5495</v>
+        <v>8226</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7384,11 +7402,11 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N88" t="n">
         <v>70</v>
@@ -7401,11 +7419,11 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>25-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
-        <v>0</v>
+        <v>-11.52296875</v>
       </c>
       <c r="T88" t="n">
         <v>7</v>
@@ -7413,46 +7431,46 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>254521</v>
+        <v>253906</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E89" t="n">
-        <v>39.68333333333333</v>
+        <v>45.79166666666666</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>20-11-2025 12:33:04</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>20-11-2025 13:08:04</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>20-11-2025 13:08:04</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12-11-2025 07:39:41</t>
+          <t>20-11-2025 13:53:52</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>4762</v>
+        <v>5495</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7461,11 +7479,11 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N89" t="n">
         <v>70</v>
@@ -7478,7 +7496,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>25-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -7490,78 +7508,158 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
+        <v>254609</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>416.6666666666667</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12-11-2025 13:56:40</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>40655</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>20-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
         <v>252980</v>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>11-11-2025 14:00:00</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
         <v>17.075</v>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>14-11-2025 07:00:00</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>14-11-2025 07:17:04</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J91" t="n">
         <v>2049</v>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>foglio</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>08-09-2025 00:00:00</t>
         </is>
       </c>
-      <c r="S90" s="1" t="n">
+      <c r="S91" s="1" t="n">
         <v>-77.30352430555556</v>
       </c>
-      <c r="T90" t="n">
+      <c r="T91" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T91"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254129</v>
+        <v>250891</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>44.5</v>
+        <v>77.49166666666666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>08-09-2025 07:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>08-09-2025 07:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>08-09-2025 08:49:29</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5340</v>
+        <v>9299</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,41 +591,39 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N2" t="n">
+        <v>70</v>
+      </c>
+      <c r="O2" t="n">
+        <v>40910</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13-08-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>-39</v>
+      </c>
+      <c r="T2" t="n">
         <v>4</v>
-      </c>
-      <c r="N2" t="n">
-        <v>76</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>40623</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>30-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>-0.553125</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>254385</v>
+        <v>252216</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -634,37 +632,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>52.08333333333334</v>
+        <v>141.8083333333333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>08-09-2025 08:49:29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>08-09-2025 09:14:29</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>08-09-2025 09:14:29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>08-09-2025 11:36:18</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6250</v>
+        <v>17017</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -673,41 +671,39 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="O3" t="n">
-        <v>40627</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40910</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40627</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254713</v>
+        <v>253527</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,37 +712,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>49.96666666666667</v>
+        <v>67.48333333333333</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>08-09-2025 11:36:18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>08-09-2025 12:05:18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>08-09-2025 12:05:18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>08-09-2025 13:12:47</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5996</v>
+        <v>8098</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -755,41 +751,39 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O4" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40910</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-1.335104166666667</v>
+        <v>-9</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>243569</v>
+        <v>253524</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,37 +792,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>21.675</v>
+        <v>58.75833333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>08-09-2025 13:12:47</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>08-09-2025 13:27:47</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>08-09-2025 13:27:47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>08-09-2025 14:26:32</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2601</v>
+        <v>7051</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -837,17 +831,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O5" t="n">
-        <v>406372</v>
+        <v>40910</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -857,19 +851,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-429</v>
+        <v>-9</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>254156</v>
+        <v>253528</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -878,37 +872,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>87.47499999999999</v>
+        <v>119.175</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>08-09-2025 14:26:32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:13</t>
+          <t>08-09-2025 14:41:32</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:13</t>
+          <t>08-09-2025 14:41:32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:42</t>
+          <t>09-09-2025 08:40:43</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10497</v>
+        <v>14301</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,41 +911,39 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O6" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40910</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-0.4345138888888889</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254375</v>
+        <v>244023</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -960,37 +952,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>45.29166666666666</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:42</t>
+          <t>09-09-2025 08:40:43</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:01:42</t>
+          <t>09-09-2025 09:01:43</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:01:42</t>
+          <t>09-09-2025 09:01:43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 11:46:59</t>
+          <t>09-09-2025 09:10:01</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5435</v>
+        <v>997</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1003,14 +995,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
       </c>
-      <c r="O7" t="n">
-        <v>40624</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1019,19 +1008,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-12</v>
+        <v>-354.3819618055555</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254256</v>
+        <v>252939</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1040,37 +1029,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>50.925</v>
+        <v>89.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 11:46:59</t>
+          <t>09-09-2025 09:10:01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:03:59</t>
+          <t>09-09-2025 09:31:01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:03:59</t>
+          <t>09-09-2025 09:31:01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-11-2025 12:54:55</t>
+          <t>09-09-2025 11:00:49</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6111</v>
+        <v>10776</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1088,9 +1077,6 @@
       <c r="N8" t="n">
         <v>70</v>
       </c>
-      <c r="O8" t="n">
-        <v>406422</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1099,19 +1085,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>22-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-18</v>
+        <v>-28.45890625</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254519</v>
+        <v>252815</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1120,37 +1106,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>77.15833333333333</v>
+        <v>242.9416666666667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14-11-2025 12:54:55</t>
+          <t>09-09-2025 11:00:49</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:09:55</t>
+          <t>09-09-2025 11:40:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14-11-2025 13:09:55</t>
+          <t>09-09-2025 11:40:49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:27:04</t>
+          <t>10-09-2025 07:43:46</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9259</v>
+        <v>29153</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1159,17 +1145,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
-      </c>
-      <c r="O9" t="n">
-        <v>406422</v>
+        <v>76</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1179,11 +1162,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-4</v>
+        <v>-15.32206018518518</v>
       </c>
       <c r="T9" t="n">
         <v>4</v>
@@ -1191,46 +1174,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254237</v>
+        <v>253072</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>184.0916666666667</v>
+        <v>29.13333333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:27:04</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:50:04</t>
+          <t>08-09-2025 07:46:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:50:04</t>
+          <t>08-09-2025 07:46:00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:10</t>
+          <t>08-09-2025 08:15:08</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>22091</v>
+        <v>3496</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1243,78 +1226,74 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
         <v>70</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="O10" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>18-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-8.327309027777778</v>
+        <v>-38</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>255039</v>
+        <v>253271</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>9.15</v>
+        <v>42.63333333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:10</t>
+          <t>08-09-2025 08:15:08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:10</t>
+          <t>08-09-2025 08:40:08</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:10</t>
+          <t>08-09-2025 08:40:08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:26:19</t>
+          <t>08-09-2025 09:22:46</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1098</v>
+        <v>5116</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1327,13 +1306,13 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
       <c r="O11" t="n">
-        <v>40624</v>
+        <v>40904</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1343,58 +1322,58 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="T11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254824</v>
+        <v>253278</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>748.225</v>
+        <v>28.425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:26:19</t>
+          <t>08-09-2025 09:22:46</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:58:19</t>
+          <t>08-09-2025 09:47:46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:58:19</t>
+          <t>08-09-2025 09:47:46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>19-11-2025 07:26:32</t>
+          <t>08-09-2025 10:16:11</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>89787</v>
+        <v>3411</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1403,78 +1382,78 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>70</v>
+      </c>
+      <c r="O12" t="n">
+        <v>40904</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>12-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T12" t="n">
         <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>76</v>
-      </c>
-      <c r="O12" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>16-03-2026 00:00:00</t>
-        </is>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>254599</v>
+        <v>253317</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E13" t="n">
-        <v>44.9</v>
+        <v>102.775</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19-11-2025 07:26:32</t>
+          <t>08-09-2025 10:16:11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19-11-2025 08:00:32</t>
+          <t>08-09-2025 11:02:11</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19-11-2025 08:00:32</t>
+          <t>08-09-2025 11:02:11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19-11-2025 08:45:26</t>
+          <t>08-09-2025 12:44:58</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5388</v>
+        <v>12333</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1483,17 +1462,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O13" t="n">
-        <v>406372</v>
+        <v>40910</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1503,58 +1482,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
       <c r="T13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>253961</v>
+        <v>253318</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>35.91666666666666</v>
+        <v>51.55</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19-11-2025 08:45:26</t>
+          <t>08-09-2025 12:44:58</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19-11-2025 09:00:26</t>
+          <t>08-09-2025 13:09:58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19-11-2025 09:00:26</t>
+          <t>08-09-2025 13:09:58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19-11-2025 09:36:21</t>
+          <t>08-09-2025 14:01:31</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4310</v>
+        <v>6186</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1563,17 +1542,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O14" t="n">
-        <v>406372</v>
+        <v>40910</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1583,58 +1562,58 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>250284</v>
+        <v>253260</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>146.35</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19-11-2025 09:36:21</t>
+          <t>08-09-2025 14:01:31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 09:59:21</t>
+          <t>08-09-2025 14:43:31</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19-11-2025 09:59:21</t>
+          <t>08-09-2025 14:43:31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19-11-2025 12:25:42</t>
+          <t>09-09-2025 08:32:55</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17562</v>
+        <v>13129</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1647,13 +1626,13 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
       <c r="O15" t="n">
-        <v>406422</v>
+        <v>40279</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1663,11 +1642,11 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-254</v>
+        <v>-16</v>
       </c>
       <c r="T15" t="n">
         <v>7</v>
@@ -1675,7 +1654,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254165</v>
+        <v>253455</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1684,37 +1663,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
-        <v>58.31666666666667</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>09-09-2025 08:32:55</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>09-09-2025 08:57:55</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>09-09-2025 08:57:55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>09-09-2025 09:53:29</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6998</v>
+        <v>6667</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1723,41 +1702,39 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O16" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40279</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-0.3613310185185185</v>
+        <v>-2</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254117</v>
+        <v>253247</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1766,37 +1743,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>9.166666666666666</v>
+        <v>109.575</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>09-09-2025 09:53:29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:19</t>
+          <t>09-09-2025 10:18:29</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:19</t>
+          <t>09-09-2025 10:18:29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:16:29</t>
+          <t>09-09-2025 12:08:03</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1100</v>
+        <v>13149</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1805,14 +1782,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O17" t="n">
+        <v>40279</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1822,19 +1802,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-35.38644675925926</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254107</v>
+        <v>253249</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1843,37 +1823,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>28-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>175.0583333333333</v>
+        <v>57.75833333333333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14-11-2025 09:16:29</t>
+          <t>09-09-2025 12:08:03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-11-2025 09:58:29</t>
+          <t>09-09-2025 12:50:03</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14-11-2025 09:58:29</t>
+          <t>09-09-2025 12:50:03</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-11-2025 12:53:32</t>
+          <t>09-09-2025 13:47:49</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>21007</v>
+        <v>6931</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1882,14 +1862,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1899,19 +1879,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-33.53718171296296</v>
+        <v>-8.574872685185186</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254293</v>
+        <v>253706</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1920,37 +1900,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>18.85</v>
+        <v>311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14-11-2025 12:53:32</t>
+          <t>09-09-2025 13:47:49</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:22:32</t>
+          <t>09-09-2025 14:22:49</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:22:32</t>
+          <t>09-09-2025 14:22:49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:23</t>
+          <t>10-09-2025 11:33:49</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2262</v>
+        <v>37320</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1959,17 +1939,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>70</v>
-      </c>
-      <c r="O19" t="n">
-        <v>40624</v>
+        <v>76</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1979,11 +1956,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>30-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>7</v>
@@ -1991,46 +1968,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>253838</v>
+        <v>252702</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>108.3666666666667</v>
+        <v>58.38333333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:23</t>
+          <t>05-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14-11-2025 14:08:23</t>
+          <t>05-09-2025 07:34:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-11-2025 14:08:23</t>
+          <t>05-09-2025 07:34:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:45</t>
+          <t>05-09-2025 08:32:23</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13004</v>
+        <v>7006</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2039,75 +2016,80 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>70</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O20" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>04-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-21.33108217592592</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254605</v>
+        <v>253362</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>39.025</v>
+        <v>58.38333333333333</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:45</t>
+          <t>05-09-2025 08:32:23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:45</t>
+          <t>05-09-2025 08:47:23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:45</t>
+          <t>05-09-2025 08:47:23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:47</t>
+          <t>05-09-2025 09:45:46</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4683</v>
+        <v>7006</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2116,75 +2098,80 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>70</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O21" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>15-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-3.381099537037037</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254758</v>
+        <v>252681</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
-        <v>61.38333333333333</v>
+        <v>115.0166666666667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:47</t>
+          <t>05-09-2025 09:45:46</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17-11-2025 09:35:47</t>
+          <t>05-09-2025 10:19:46</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-11-2025 09:35:47</t>
+          <t>05-09-2025 10:19:46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:37:10</t>
+          <t>05-09-2025 12:14:47</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7366</v>
+        <v>13802</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2193,36 +2180,41 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>76</v>
+      </c>
+      <c r="O22" t="n">
+        <v>40279</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>40279</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>01-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
-      </c>
-      <c r="N22" t="n">
-        <v>70</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>27-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S22" s="1" t="n">
-        <v>-0.4424768518518519</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254556</v>
+        <v>253591</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2231,37 +2223,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>173.4166666666667</v>
+        <v>17.41666666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>05-09-2025 12:14:47</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>05-09-2025 12:29:47</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>05-09-2025 12:29:47</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>05-09-2025 12:47:12</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>20810</v>
+        <v>2090</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2270,17 +2262,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>76</v>
       </c>
       <c r="O23" t="n">
-        <v>40623</v>
+        <v>40295</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2288,23 +2280,23 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>40623</v>
+        <v>40295</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>24-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-1.42806712962963</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254230</v>
+        <v>243569</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2313,37 +2305,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
-        <v>62.475</v>
+        <v>21.675</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>05-09-2025 12:47:12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:25</t>
+          <t>05-09-2025 13:06:12</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:25</t>
+          <t>05-09-2025 13:06:12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-11-2025 11:54:53</t>
+          <t>05-09-2025 13:27:52</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7497</v>
+        <v>2601</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2352,17 +2344,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O24" t="n">
-        <v>406422</v>
+        <v>40904</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2372,11 +2364,11 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-15</v>
+        <v>-374</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -2384,7 +2376,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254433</v>
+        <v>250284</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2393,37 +2385,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>67.84999999999999</v>
+        <v>146.35</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14-11-2025 11:54:53</t>
+          <t>05-09-2025 13:27:52</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:53</t>
+          <t>05-09-2025 14:07:52</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:53</t>
+          <t>05-09-2025 14:07:52</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-11-2025 13:17:44</t>
+          <t>08-09-2025 08:34:13</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8142</v>
+        <v>17562</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2432,17 +2424,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N25" t="n">
         <v>70</v>
       </c>
       <c r="O25" t="n">
-        <v>406422</v>
+        <v>40910</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2452,19 +2444,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-3</v>
+        <v>-193</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254106</v>
+        <v>252906</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2473,37 +2465,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>107.6416666666667</v>
+        <v>34.725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-11-2025 13:17:44</t>
+          <t>08-09-2025 08:34:13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14-11-2025 13:36:44</t>
+          <t>08-09-2025 09:12:13</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-11-2025 13:36:44</t>
+          <t>08-09-2025 09:12:13</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:23</t>
+          <t>08-09-2025 09:46:57</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>12917</v>
+        <v>4167</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2512,14 +2504,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O26" t="n">
+        <v>40904</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2529,19 +2524,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-31.30859953703704</v>
+        <v>-31</v>
       </c>
       <c r="T26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254460</v>
+        <v>253140</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2550,37 +2545,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>46.68333333333333</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:23</t>
+          <t>08-09-2025 09:46:57</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:23</t>
+          <t>08-09-2025 10:03:57</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:23</t>
+          <t>08-09-2025 10:03:57</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:04</t>
+          <t>08-09-2025 10:59:47</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>5602</v>
+        <v>6700</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2589,14 +2584,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O27" t="n">
+        <v>40900</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2606,11 +2604,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>26-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-35.35560185185185</v>
+        <v>-26</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -2618,7 +2616,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254198</v>
+        <v>253100</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2627,37 +2625,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>215</v>
+        <v>47.35</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:04</t>
+          <t>08-09-2025 10:59:47</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:04</t>
+          <t>08-09-2025 11:31:47</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:04</t>
+          <t>08-09-2025 11:31:47</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:04</t>
+          <t>08-09-2025 12:19:08</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>25800</v>
+        <v>5682</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2666,14 +2664,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="O28" t="n">
+        <v>40900</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2683,19 +2684,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-18.52851851851852</v>
+        <v>-13</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>253885</v>
+        <v>253246</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2704,37 +2705,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>105.9333333333333</v>
+        <v>194.25</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:04</t>
+          <t>08-09-2025 12:19:08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:04</t>
+          <t>08-09-2025 12:34:08</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:04</t>
+          <t>08-09-2025 12:34:08</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17-11-2025 14:59:00</t>
+          <t>09-09-2025 07:48:23</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>12712</v>
+        <v>23310</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2747,11 +2748,14 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
+      <c r="O29" t="n">
+        <v>40900</v>
+      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2760,19 +2764,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-3.624305555555555</v>
+        <v>-11</v>
       </c>
       <c r="T29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254451</v>
+        <v>253372</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2781,37 +2785,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
         <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>321.1416666666667</v>
+        <v>103.775</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17-11-2025 14:59:00</t>
+          <t>09-09-2025 07:48:23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18-11-2025 07:18:00</t>
+          <t>09-09-2025 08:07:23</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18-11-2025 07:18:00</t>
+          <t>09-09-2025 08:07:23</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-11-2025 12:39:08</t>
+          <t>09-09-2025 09:51:09</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>38537</v>
+        <v>12453</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2820,15 +2824,18 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
+      <c r="O30" t="n">
+        <v>40904</v>
+      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -2837,11 +2844,11 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-10.52718171296296</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
@@ -2849,46 +2856,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254481</v>
+        <v>253370</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32.5</v>
+        <v>15</v>
       </c>
       <c r="E31" t="n">
-        <v>81.16666666666667</v>
+        <v>207.5416666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>09-09-2025 09:51:09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>09-09-2025 10:06:09</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>09-09-2025 10:06:09</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>09-09-2025 13:33:42</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>9740</v>
+        <v>24905</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2897,29 +2904,27 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
       <c r="O31" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40904</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2931,46 +2936,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254762</v>
+        <v>253095</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>34.5</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>31.85833333333333</v>
+        <v>76.31666666666666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>09-09-2025 13:33:42</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>09-09-2025 13:50:42</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>09-09-2025 13:50:42</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>10-09-2025 07:07:01</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3823</v>
+        <v>9158</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2979,80 +2984,75 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
       </c>
-      <c r="O32" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P32" t="n">
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>-8.296539351851852</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>253865</v>
+        <v>253332</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>34.5</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>116.7583333333333</v>
+        <v>184.825</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>10-09-2025 07:07:01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:31</t>
+          <t>10-09-2025 07:24:01</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:31</t>
+          <t>10-09-2025 07:24:01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:17</t>
+          <t>10-09-2025 10:28:50</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>14011</v>
+        <v>22179</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3061,11 +3061,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
@@ -3078,19 +3078,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-38.33299189814815</v>
+        <v>-10.43669560185185</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254245</v>
+        <v>252833</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3099,37 +3099,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="E34" t="n">
-        <v>89.8</v>
+        <v>74.78333333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:17</t>
+          <t>09-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:47</t>
+          <t>09-09-2025 07:34:30</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:47</t>
+          <t>09-09-2025 07:34:30</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:35</t>
+          <t>09-09-2025 08:49:17</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>10776</v>
+        <v>8974</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
@@ -3155,11 +3155,11 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>26-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-18.4179224537037</v>
+        <v>-24.36755787037037</v>
       </c>
       <c r="T34" t="n">
         <v>4</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254356</v>
+        <v>253223</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3176,37 +3176,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30.5</v>
+        <v>50.5</v>
       </c>
       <c r="E35" t="n">
-        <v>179.6</v>
+        <v>16.4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:35</t>
+          <t>09-09-2025 08:49:17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:05</t>
+          <t>09-09-2025 09:39:47</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:05</t>
+          <t>09-09-2025 09:39:47</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:41</t>
+          <t>09-09-2025 09:56:11</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>21552</v>
+        <v>1968</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3215,11 +3215,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -3232,19 +3232,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-9.563825231481481</v>
+        <v>-18.4140162037037</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254381</v>
+        <v>252601</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3253,37 +3253,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>83.86666666666666</v>
+        <v>51.20833333333334</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:41</t>
+          <t>09-09-2025 09:56:11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:11</t>
+          <t>09-09-2025 10:28:41</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:11</t>
+          <t>09-09-2025 10:28:41</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:03</t>
+          <t>09-09-2025 11:19:53</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>10064</v>
+        <v>6145</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3292,11 +3292,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -3309,11 +3309,11 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>31-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-21.31130208333333</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>7</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254652</v>
+        <v>253208</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3330,37 +3330,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>32.5</v>
       </c>
       <c r="E37" t="n">
-        <v>28.73333333333333</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:03</t>
+          <t>09-09-2025 11:19:53</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>17-11-2025 09:32:33</t>
+          <t>09-09-2025 11:52:23</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>17-11-2025 09:32:33</t>
+          <t>09-09-2025 11:52:23</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:17</t>
+          <t>09-09-2025 13:36:39</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>3448</v>
+        <v>12511</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3369,11 +3369,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3386,11 +3386,11 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0</v>
+        <v>-14.56711805555556</v>
       </c>
       <c r="T37" t="n">
         <v>8</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254756</v>
+        <v>253210</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3407,37 +3407,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>40.5</v>
+        <v>30.5</v>
       </c>
       <c r="E38" t="n">
-        <v>60.625</v>
+        <v>94.15833333333333</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:17</t>
+          <t>09-09-2025 13:36:39</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17-11-2025 10:41:47</t>
+          <t>09-09-2025 14:07:09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17-11-2025 10:41:47</t>
+          <t>09-09-2025 14:07:09</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-11-2025 11:42:24</t>
+          <t>10-09-2025 07:41:18</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>7275</v>
+        <v>11299</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3446,11 +3446,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
@@ -3463,58 +3463,58 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-4.424050925925926</v>
+        <v>-10.32035300925926</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>253694</v>
+        <v>252883</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>45</v>
+        <v>32.5</v>
       </c>
       <c r="E39" t="n">
-        <v>121.7583333333333</v>
+        <v>247.3083333333333</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>10-09-2025 07:41:18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>10-09-2025 08:13:48</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>10-09-2025 08:13:48</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>10-09-2025 12:21:07</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>14611</v>
+        <v>29677</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3523,41 +3523,39 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O39" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40900</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.6158043981481481</v>
+        <v>-23</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>253380</v>
+        <v>252002</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3566,37 +3564,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>01-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E40" t="n">
-        <v>104.275</v>
+        <v>55.675</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>04-09-2025 12:00:00</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:45</t>
+          <t>04-09-2025 12:55:00</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:45</t>
+          <t>04-09-2025 12:55:00</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:02</t>
+          <t>04-09-2025 13:50:40</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>12513</v>
+        <v>6681</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3605,17 +3603,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
-      <c r="O40" t="n">
-        <v>40606</v>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>40307 (esterno)</t>
+        </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3623,23 +3623,23 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>40606</v>
+        <v>40307</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-0.3965509259259259</v>
+        <v>-10.57685763888889</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254598</v>
+        <v>253314</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3648,37 +3648,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>02-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>104.2583333333333</v>
+        <v>43.40833333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:02</t>
+          <t>04-09-2025 13:50:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:02</t>
+          <t>04-09-2025 14:40:40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:02</t>
+          <t>04-09-2025 14:40:40</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:17</t>
+          <t>05-09-2025 07:24:05</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>12511</v>
+        <v>5209</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3687,36 +3687,41 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>70</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O41" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>252061</v>
+        <v>252569</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3725,37 +3730,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E42" t="n">
-        <v>36.16666666666666</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:17</t>
+          <t>05-09-2025 07:24:05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14-11-2025 13:05:17</t>
+          <t>05-09-2025 07:54:05</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14-11-2025 13:05:17</t>
+          <t>05-09-2025 07:54:05</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:27</t>
+          <t>05-09-2025 08:03:40</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>4340</v>
+        <v>1150</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3764,41 +3769,36 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>70</v>
-      </c>
-      <c r="O42" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>0</v>
+        <v>-14.33587962962963</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254546</v>
+        <v>252685</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3807,37 +3807,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>109.4083333333333</v>
+        <v>74.56666666666666</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:27</t>
+          <t>05-09-2025 08:03:40</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14-11-2025 14:11:27</t>
+          <t>05-09-2025 08:33:40</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>14-11-2025 14:11:27</t>
+          <t>05-09-2025 08:33:40</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:52</t>
+          <t>05-09-2025 09:48:14</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>13129</v>
+        <v>8948</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3846,39 +3846,41 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
         <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O43" t="n">
-        <v>406242</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
+        <v>40295</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>235572</v>
+        <v>252682</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3887,37 +3889,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E44" t="n">
-        <v>82.98333333333333</v>
+        <v>83.40833333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:52</t>
+          <t>05-09-2025 09:48:14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>17-11-2025 08:30:52</t>
+          <t>05-09-2025 10:28:14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17-11-2025 08:30:52</t>
+          <t>05-09-2025 10:28:14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17-11-2025 09:53:51</t>
+          <t>05-09-2025 11:51:38</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9958</v>
+        <v>10009</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3926,31 +3928,33 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O44" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
+        <v>40295</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-744</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>4</v>
@@ -3958,7 +3962,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254188</v>
+        <v>252582</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3967,37 +3971,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>37.44166666666667</v>
+        <v>46.08333333333334</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17-11-2025 09:53:51</t>
+          <t>05-09-2025 11:51:38</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:51</t>
+          <t>05-09-2025 12:21:38</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:51</t>
+          <t>05-09-2025 12:21:38</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17-11-2025 11:01:17</t>
+          <t>05-09-2025 13:07:43</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>4493</v>
+        <v>5530</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4006,31 +4010,33 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O45" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
+        <v>40290</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>40290</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>18-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -4038,7 +4044,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254457</v>
+        <v>235572</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4047,37 +4053,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E46" t="n">
-        <v>3.925</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17-11-2025 11:01:17</t>
+          <t>05-09-2025 13:07:43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:17</t>
+          <t>05-09-2025 13:52:43</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>17-11-2025 11:26:17</t>
+          <t>05-09-2025 13:52:43</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17-11-2025 11:30:13</t>
+          <t>08-09-2025 07:15:42</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>471</v>
+        <v>9958</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4090,13 +4096,13 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>406372</v>
+        <v>40904</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4106,19 +4112,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-1</v>
+        <v>-689</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254437</v>
+        <v>253374</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4127,37 +4133,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>58.05833333333333</v>
+        <v>59.60833333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17-11-2025 11:30:13</t>
+          <t>08-09-2025 07:15:42</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:13</t>
+          <t>08-09-2025 07:45:42</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17-11-2025 11:55:13</t>
+          <t>08-09-2025 07:45:42</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17-11-2025 12:53:16</t>
+          <t>08-09-2025 08:45:19</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6967</v>
+        <v>7153</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4176,7 +4182,7 @@
         <v>70</v>
       </c>
       <c r="O47" t="n">
-        <v>406372</v>
+        <v>40904</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -4186,11 +4192,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -4198,46 +4204,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254941</v>
+        <v>253036</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>35.5</v>
+        <v>78.73333333333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>08-09-2025 08:45:19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>08-09-2025 09:25:19</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>08-09-2025 09:25:19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>08-09-2025 10:44:03</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>4260</v>
+        <v>9448</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4246,80 +4252,78 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>H7 ;R5</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="O48" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40910</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>22-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-1.338541666666667</v>
+        <v>-30</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>253897</v>
+        <v>253710</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E49" t="n">
-        <v>94.01666666666667</v>
+        <v>1.616666666666667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>08-09-2025 10:44:03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>08-09-2025 11:29:03</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>08-09-2025 11:29:03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>08-09-2025 11:30:40</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>11282</v>
+        <v>194</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4328,80 +4332,75 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>76</v>
-      </c>
-      <c r="O49" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.434386574074074</v>
+        <v>-8.479629629629629</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254675</v>
+        <v>253687</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>01-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E50" t="n">
-        <v>153.9583333333333</v>
+        <v>44.23333333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>08-09-2025 11:30:40</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 10:56:31</t>
+          <t>08-09-2025 12:05:40</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 10:56:31</t>
+          <t>08-09-2025 12:05:40</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14-11-2025 13:30:28</t>
+          <t>08-09-2025 12:49:54</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>18475</v>
+        <v>5308</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4410,14 +4409,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -4427,11 +4426,11 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-11.38066550925926</v>
+        <v>-6.534652777777778</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
@@ -4439,46 +4438,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254512</v>
+        <v>253267</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E51" t="n">
-        <v>59.55833333333333</v>
+        <v>164.3666666666667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14-11-2025 13:30:28</t>
+          <t>08-09-2025 12:49:54</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 13:47:28</t>
+          <t>08-09-2025 13:19:54</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 13:47:28</t>
+          <t>08-09-2025 13:19:54</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 14:47:02</t>
+          <t>09-09-2025 08:04:16</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>7147</v>
+        <v>19724</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4487,17 +4486,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
         <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>76</v>
-      </c>
-      <c r="O51" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4507,58 +4503,58 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>23-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>253382</v>
+        <v>253268</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
-        <v>85.09999999999999</v>
+        <v>78.55833333333334</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 14:47:02</t>
+          <t>09-09-2025 08:04:16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:02</t>
+          <t>09-09-2025 08:29:16</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:02</t>
+          <t>09-09-2025 08:29:16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:08</t>
+          <t>09-09-2025 09:47:49</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>10212</v>
+        <v>9427</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4567,17 +4563,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>76</v>
-      </c>
-      <c r="O52" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4587,58 +4580,58 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>23-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254910</v>
+        <v>253359</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E53" t="n">
-        <v>73.53333333333333</v>
+        <v>134.0166666666667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:08</t>
+          <t>09-09-2025 09:47:49</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17-11-2025 08:46:08</t>
+          <t>09-09-2025 10:17:49</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17-11-2025 08:46:08</t>
+          <t>09-09-2025 10:17:49</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-11-2025 09:59:40</t>
+          <t>09-09-2025 12:31:50</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>8824</v>
+        <v>16082</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4647,17 +4640,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O53" t="n">
-        <v>406372</v>
+        <v>40904</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4667,19 +4660,19 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254283</v>
+        <v>252827</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4688,37 +4681,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>95.76666666666667</v>
+        <v>410</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17-11-2025 09:59:40</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17-11-2025 10:16:40</t>
+          <t>08-09-2025 07:17:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-11-2025 10:16:40</t>
+          <t>08-09-2025 07:17:00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17-11-2025 11:52:26</t>
+          <t>08-09-2025 14:07:00</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11492</v>
+        <v>49200</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4727,18 +4720,15 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N54" t="n">
         <v>76</v>
       </c>
-      <c r="O54" t="n">
-        <v>406372</v>
-      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
@@ -4747,19 +4737,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>04-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-8</v>
+        <v>-14.58819444444444</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254555</v>
+        <v>253409</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4768,37 +4758,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>27-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>17</v>
       </c>
       <c r="E55" t="n">
-        <v>172.9833333333333</v>
+        <v>27.18333333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17-11-2025 11:52:26</t>
+          <t>08-09-2025 14:07:00</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:26</t>
+          <t>08-09-2025 14:24:00</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-11-2025 12:09:26</t>
+          <t>08-09-2025 14:24:00</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18-11-2025 07:02:25</t>
+          <t>08-09-2025 14:51:11</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20758</v>
+        <v>3262</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4811,13 +4801,13 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
         <v>76</v>
       </c>
       <c r="O55" t="n">
-        <v>406232</v>
+        <v>40910</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4827,19 +4817,19 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>253650</v>
+        <v>253194</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4848,37 +4838,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>27-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
-        <v>273.1333333333333</v>
+        <v>199.0833333333333</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>18-11-2025 07:02:25</t>
+          <t>08-09-2025 14:51:11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18-11-2025 07:19:25</t>
+          <t>09-09-2025 07:06:11</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18-11-2025 07:19:25</t>
+          <t>09-09-2025 07:06:11</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18-11-2025 11:52:33</t>
+          <t>09-09-2025 10:25:16</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>32776</v>
+        <v>23890</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4896,6 +4886,9 @@
       <c r="N56" t="n">
         <v>76</v>
       </c>
+      <c r="O56" t="n">
+        <v>40910</v>
+      </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
@@ -4904,19 +4897,19 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>20-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-18.44603009259259</v>
+        <v>-32</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254309</v>
+        <v>252843</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4925,37 +4918,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E57" t="n">
-        <v>900.0166666666667</v>
+        <v>19.2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>18-11-2025 11:52:33</t>
+          <t>09-09-2025 10:25:16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18-11-2025 12:24:33</t>
+          <t>09-09-2025 10:52:16</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>18-11-2025 12:24:33</t>
+          <t>09-09-2025 10:52:16</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20-11-2025 11:24:34</t>
+          <t>09-09-2025 11:11:28</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>108002</v>
+        <v>2304</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4964,14 +4957,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N57" t="n">
-        <v>152</v>
+        <v>76</v>
+      </c>
+      <c r="O57" t="n">
+        <v>40904</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4981,58 +4977,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>30-07-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-19.42659722222222</v>
+        <v>-57</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254714</v>
+        <v>253425</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>05-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="E58" t="n">
-        <v>91.47499999999999</v>
+        <v>146.35</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>09-09-2025 11:11:28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>09-09-2025 11:34:28</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>09-09-2025 11:34:28</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>09-09-2025 14:00:49</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>10977</v>
+        <v>17562</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5050,24 +5046,19 @@
       <c r="N58" t="n">
         <v>76</v>
       </c>
-      <c r="O58" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P58" t="n">
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>29-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-1.389913194444444</v>
+        <v>-21.58390046296296</v>
       </c>
       <c r="T58" t="n">
         <v>2</v>
@@ -5075,46 +5066,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>244023</v>
+        <v>253313</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>8.308333333333334</v>
+        <v>100.0083333333333</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>09-09-2025 14:00:49</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>09-09-2025 14:17:49</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>09-09-2025 14:17:49</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>14-11-2025 10:04:47</t>
+          <t>10-09-2025 07:57:49</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>997</v>
+        <v>12001</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5123,17 +5114,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O59" t="n">
-        <v>406062</v>
+        <v>40910</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5143,11 +5134,11 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-417</v>
+        <v>-16</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
@@ -5155,46 +5146,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>254429</v>
+        <v>252995</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
-        <v>240.2416666666667</v>
+        <v>68.31666666666666</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14-11-2025 10:04:47</t>
+          <t>10-09-2025 07:57:49</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-11-2025 10:34:47</t>
+          <t>10-09-2025 08:14:49</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14-11-2025 10:34:47</t>
+          <t>10-09-2025 08:14:49</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14-11-2025 14:35:01</t>
+          <t>10-09-2025 09:23:08</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>28829</v>
+        <v>8198</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5203,17 +5194,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>70</v>
-      </c>
-      <c r="O60" t="n">
-        <v>406372</v>
+        <v>76</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5223,58 +5211,58 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-9</v>
+        <v>-19.39107060185185</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254291</v>
+        <v>253284</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>28-08-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E61" t="n">
-        <v>18.85</v>
+        <v>56.99166666666667</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14-11-2025 14:35:01</t>
+          <t>10-09-2025 09:23:08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17-11-2025 07:05:01</t>
+          <t>10-09-2025 09:40:08</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>17-11-2025 07:05:01</t>
+          <t>10-09-2025 09:40:08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17-11-2025 07:23:52</t>
+          <t>10-09-2025 10:37:08</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2262</v>
+        <v>6839</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5283,17 +5271,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O61" t="n">
-        <v>40624</v>
+        <v>40910</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5303,58 +5291,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>28-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="T61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254276</v>
+        <v>253602</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E62" t="n">
-        <v>37.03333333333333</v>
+        <v>117.0833333333333</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17-11-2025 07:23:52</t>
+          <t>10-09-2025 10:37:08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17-11-2025 07:58:52</t>
+          <t>10-09-2025 10:54:08</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17-11-2025 07:58:52</t>
+          <t>10-09-2025 10:54:08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>17-11-2025 08:35:54</t>
+          <t>10-09-2025 12:51:13</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4444</v>
+        <v>14050</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5363,17 +5351,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N62" t="n">
-        <v>70</v>
-      </c>
-      <c r="O62" t="n">
-        <v>406422</v>
+        <v>76</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5383,19 +5368,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-18</v>
+        <v>-10.53556712962963</v>
       </c>
       <c r="T62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254893</v>
+        <v>253721</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5404,37 +5389,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E63" t="n">
-        <v>46.675</v>
+        <v>39.39166666666667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17-11-2025 08:35:54</t>
+          <t>09-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17-11-2025 09:05:54</t>
+          <t>09-09-2025 07:40:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17-11-2025 09:05:54</t>
+          <t>09-09-2025 07:40:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>17-11-2025 09:52:35</t>
+          <t>09-09-2025 08:19:23</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>5601</v>
+        <v>4727</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5453,7 +5438,7 @@
         <v>70</v>
       </c>
       <c r="O63" t="n">
-        <v>406372</v>
+        <v>40900</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -5463,7 +5448,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>08-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -5475,7 +5460,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254189</v>
+        <v>253686</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5484,37 +5469,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>01-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E64" t="n">
-        <v>55.875</v>
+        <v>44.23333333333333</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>17-11-2025 09:52:35</t>
+          <t>09-09-2025 08:19:23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17-11-2025 10:22:35</t>
+          <t>09-09-2025 08:54:23</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17-11-2025 10:22:35</t>
+          <t>09-09-2025 08:54:23</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>17-11-2025 11:18:27</t>
+          <t>09-09-2025 09:38:37</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>6705</v>
+        <v>5308</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5523,18 +5508,15 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
       </c>
-      <c r="O64" t="n">
-        <v>406372</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -5543,11 +5525,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-1</v>
+        <v>-7.401822916666666</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
@@ -5555,7 +5537,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>255043</v>
+        <v>253659</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5564,37 +5546,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>08-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>25</v>
       </c>
       <c r="E65" t="n">
-        <v>184.2833333333333</v>
+        <v>323.75</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:18:27</t>
+          <t>09-09-2025 09:38:37</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:27</t>
+          <t>09-09-2025 10:03:37</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:43:27</t>
+          <t>09-09-2025 10:03:37</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>17-11-2025 14:47:44</t>
+          <t>10-09-2025 07:27:22</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>22114</v>
+        <v>38850</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5603,18 +5585,15 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N65" t="n">
         <v>70</v>
       </c>
-      <c r="O65" t="n">
-        <v>406372</v>
-      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -5623,58 +5602,58 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>0</v>
+        <v>-9.310677083333333</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254521</v>
+        <v>253016</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>02-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>39.68333333333333</v>
+        <v>73.38333333333334</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>17-11-2025 14:47:44</t>
+          <t>05-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:17:44</t>
+          <t>05-09-2025 07:30:00</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:17:44</t>
+          <t>05-09-2025 07:30:00</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:57:25</t>
+          <t>05-09-2025 08:43:23</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>4762</v>
+        <v>8806</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5683,75 +5662,80 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>70</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O66" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>14-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-2.615833333333333</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>252811</v>
+        <v>253259</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>11.875</v>
+        <v>69.23333333333333</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18-11-2025 07:57:25</t>
+          <t>05-09-2025 08:43:23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:32:25</t>
+          <t>05-09-2025 09:18:23</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:32:25</t>
+          <t>05-09-2025 09:18:23</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:44:18</t>
+          <t>05-09-2025 10:27:37</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1425</v>
+        <v>8308</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5760,28 +5744,33 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
       </c>
-      <c r="P67" t="n">
-        <v>0</v>
+      <c r="O67" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>25-08-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-15.31505208333333</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
         <v>7</v>
@@ -5789,46 +5778,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254651</v>
+        <v>252679</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E68" t="n">
-        <v>22.64166666666667</v>
+        <v>60</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>18-11-2025 08:44:18</t>
+          <t>05-09-2025 10:27:37</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:19:18</t>
+          <t>05-09-2025 11:12:37</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:19:18</t>
+          <t>05-09-2025 11:12:37</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:41:56</t>
+          <t>05-09-2025 12:12:37</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>2717</v>
+        <v>7200</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5837,75 +5826,80 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
-        <v>70</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O68" t="n">
+        <v>40295</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>40295</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>01-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254653</v>
+        <v>252664</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E69" t="n">
-        <v>64.40833333333333</v>
+        <v>365.975</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18-11-2025 09:41:56</t>
+          <t>05-09-2025 12:12:37</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18-11-2025 10:11:56</t>
+          <t>05-09-2025 12:57:37</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>18-11-2025 10:11:56</t>
+          <t>05-09-2025 12:57:37</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18-11-2025 11:16:21</t>
+          <t>08-09-2025 11:03:35</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>7729</v>
+        <v>43917</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5914,28 +5908,33 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
+      <c r="O69" t="n">
+        <v>40279</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>40279</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>02-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>0</v>
+        <v>-6.460827546296296</v>
       </c>
       <c r="T69" t="n">
         <v>7</v>
@@ -5943,46 +5942,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254915</v>
+        <v>253361</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E70" t="n">
-        <v>48.875</v>
+        <v>76.70833333333333</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:16:21</t>
+          <t>08-09-2025 11:03:35</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:21</t>
+          <t>08-09-2025 11:33:35</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:21</t>
+          <t>08-09-2025 11:33:35</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>18-11-2025 12:40:13</t>
+          <t>08-09-2025 12:50:18</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>5865</v>
+        <v>9205</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6000,6 +5999,9 @@
       <c r="N70" t="n">
         <v>70</v>
       </c>
+      <c r="O70" t="n">
+        <v>40904</v>
+      </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
@@ -6008,19 +6010,19 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>11-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T70" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254715</v>
+        <v>253375</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6029,37 +6031,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E71" t="n">
-        <v>134.5416666666667</v>
+        <v>51.88333333333333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>08-09-2025 12:50:18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>08-09-2025 13:15:18</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>08-09-2025 13:15:18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>08-09-2025 14:07:11</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>16145</v>
+        <v>6226</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6068,41 +6070,39 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O71" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40904</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-1.409403935185185</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254287</v>
+        <v>253368</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6111,37 +6111,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E72" t="n">
-        <v>129.6333333333333</v>
+        <v>103.775</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>08-09-2025 14:07:11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>08-09-2025 14:32:11</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>08-09-2025 14:32:11</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>09-09-2025 08:15:57</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>15556</v>
+        <v>12453</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6150,17 +6150,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72" t="n">
         <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>406422</v>
+        <v>40904</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6170,19 +6170,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254427</v>
+        <v>253377</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6191,80 +6191,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>10-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>55.55833333333333</v>
+        <v>127.7166666666667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>09-09-2025 08:15:57</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>09-09-2025 08:40:57</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>09-09-2025 08:40:57</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>09-09-2025 10:48:40</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>6667</v>
+        <v>15326</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
       <c r="O73" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40904</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-4.590092592592592</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254574</v>
+        <v>253367</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6273,37 +6271,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E74" t="n">
-        <v>173.6083333333333</v>
+        <v>135.7</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>09-09-2025 10:48:40</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>09-09-2025 11:13:40</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>09-09-2025 11:13:40</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>09-09-2025 13:29:22</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>20833</v>
+        <v>16284</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6312,17 +6310,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
       <c r="O74" t="n">
-        <v>406422</v>
+        <v>40904</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -6332,19 +6330,19 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254187</v>
+        <v>253371</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6353,37 +6351,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>10-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E75" t="n">
-        <v>46.39166666666667</v>
+        <v>107.7666666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>09-09-2025 13:29:22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:20</t>
+          <t>09-09-2025 13:54:22</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:20</t>
+          <t>09-09-2025 13:54:22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>17-11-2025 11:04:44</t>
+          <t>10-09-2025 07:42:08</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5567</v>
+        <v>12932</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6392,17 +6390,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
         <v>70</v>
       </c>
       <c r="O75" t="n">
-        <v>406372</v>
+        <v>40904</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6412,11 +6410,11 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>25-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6424,7 +6422,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254586</v>
+        <v>253525</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6433,37 +6431,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>51.54166666666666</v>
+        <v>92.14166666666667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:04:44</t>
+          <t>10-09-2025 07:42:08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:29:44</t>
+          <t>10-09-2025 08:07:08</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:29:44</t>
+          <t>10-09-2025 08:07:08</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:16</t>
+          <t>10-09-2025 09:39:17</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>6185</v>
+        <v>11057</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6472,17 +6470,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76" t="n">
         <v>70</v>
       </c>
       <c r="O76" t="n">
-        <v>406372</v>
+        <v>40904</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -6492,19 +6490,19 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>26-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254166</v>
+        <v>253245</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6513,37 +6511,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>38.85</v>
+        <v>150.8333333333333</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:16</t>
+          <t>10-09-2025 09:39:17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:16</t>
+          <t>10-09-2025 10:14:17</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:16</t>
+          <t>10-09-2025 10:14:17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>17-11-2025 13:25:07</t>
+          <t>10-09-2025 12:45:07</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>4662</v>
+        <v>18100</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6556,13 +6554,13 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
       </c>
       <c r="O77" t="n">
-        <v>406372</v>
+        <v>40900</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6572,19 +6570,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>10-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254365</v>
+        <v>253401</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6593,37 +6591,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>09-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>67.53333333333333</v>
+        <v>22.81666666666667</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17-11-2025 13:25:07</t>
+          <t>10-09-2025 12:45:07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:07</t>
+          <t>10-09-2025 13:15:07</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:07</t>
+          <t>10-09-2025 13:15:07</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:39</t>
+          <t>10-09-2025 13:37:56</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>8104</v>
+        <v>2738</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6636,11 +6634,14 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
+      <c r="O78" t="n">
+        <v>40904</v>
+      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
@@ -6649,74 +6650,74 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>12-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-4.296984953703704</v>
+        <v>-13</v>
       </c>
       <c r="T78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>253614</v>
+        <v>252980</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>03-09-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>122.45</v>
+        <v>17.075</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:39</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:47:39</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:47:39</t>
+          <t>08-09-2025 07:00:00</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 09:50:06</t>
+          <t>08-09-2025 07:17:04</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>14694</v>
+        <v>2049</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6726,940 +6727,13 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>0</v>
+        <v>-10.30352430555556</v>
       </c>
       <c r="T79" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>254903</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>40</v>
-      </c>
-      <c r="E80" t="n">
-        <v>256.6416666666667</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:50:06</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:30:06</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>18-11-2025 10:30:06</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:46:45</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>30797</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" t="n">
-        <v>70</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>12-01-2026 00:00:00</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>254339</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>35</v>
-      </c>
-      <c r="E81" t="n">
-        <v>245.9666666666667</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:46:45</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:21:45</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>19-11-2025 07:21:45</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:27:43</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>29516</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>5</v>
-      </c>
-      <c r="N81" t="n">
-        <v>70</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>30-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S81" s="1" t="n">
-        <v>-30.47758101851852</v>
-      </c>
-      <c r="T81" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>254101</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>30</v>
-      </c>
-      <c r="E82" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:27:43</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:57:43</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:57:43</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:26:08</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>6</v>
-      </c>
-      <c r="N82" t="n">
-        <v>70</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S82" s="1" t="n">
-        <v>-26.51815393518519</v>
-      </c>
-      <c r="T82" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>254100</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>25</v>
-      </c>
-      <c r="E83" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:26:08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:51:08</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:51:08</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:19:34</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>6</v>
-      </c>
-      <c r="N83" t="n">
-        <v>70</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S83" s="1" t="n">
-        <v>-26.55525462962963</v>
-      </c>
-      <c r="T83" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>254252</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>35</v>
-      </c>
-      <c r="E84" t="n">
-        <v>80.51666666666667</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:19:34</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:54:34</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:54:34</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:15:05</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>9662</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>4</v>
-      </c>
-      <c r="N84" t="n">
-        <v>70</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S84" s="1" t="n">
-        <v>-27.30214120370371</v>
-      </c>
-      <c r="T84" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>253974</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>35</v>
-      </c>
-      <c r="E85" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:15:05</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:50:05</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:50:05</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:18:30</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>6</v>
-      </c>
-      <c r="N85" t="n">
-        <v>70</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>29-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S85" s="1" t="n">
-        <v>-32.3461863425926</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>254419</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>35</v>
-      </c>
-      <c r="E86" t="n">
-        <v>72.34166666666667</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:18:30</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:53:30</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:53:30</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>8681</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>4</v>
-      </c>
-      <c r="N86" t="n">
-        <v>70</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S86" s="1" t="n">
-        <v>-20.42072916666667</v>
-      </c>
-      <c r="T86" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>254354</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>30</v>
-      </c>
-      <c r="E87" t="n">
-        <v>18.675</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:35:51</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:35:51</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:54:31</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>2241</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>70</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>14-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S87" s="1" t="n">
-        <v>-16.45453125</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>254547</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>30</v>
-      </c>
-      <c r="E88" t="n">
-        <v>68.55</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:54:31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>20-11-2025 11:24:31</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>20-11-2025 11:24:31</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>20-11-2025 12:33:04</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>8226</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>4</v>
-      </c>
-      <c r="N88" t="n">
-        <v>70</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>19-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S88" s="1" t="n">
-        <v>-11.52296875</v>
-      </c>
-      <c r="T88" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>35</v>
-      </c>
-      <c r="E89" t="n">
-        <v>45.79166666666666</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>20-11-2025 12:33:04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:08:04</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:08:04</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:53:52</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>5495</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" t="n">
-        <v>70</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>25-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>416.6666666666667</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>12-11-2025 13:56:40</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>T1 ;T2 ;T8</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>40655</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>20-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>17.075</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>2049</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>08-09-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S91" s="1" t="n">
-        <v>-77.30352430555556</v>
-      </c>
-      <c r="T91" t="n">
         <v>7</v>
       </c>
     </row>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>250891</v>
+        <v>254129</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -552,37 +552,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>77.49166666666666</v>
+        <v>44.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:32:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>08-09-2025 07:32:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08-09-2025 08:49:29</t>
+          <t>13-11-2025 13:16:30</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9299</v>
+        <v>5340</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,39 +591,41 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O2" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>13-08-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-39</v>
+        <v>-0.553125</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>252216</v>
+        <v>254385</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -632,37 +634,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>141.8083333333333</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>08-09-2025 08:49:29</t>
+          <t>13-11-2025 13:16:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>08-09-2025 09:14:29</t>
+          <t>13-11-2025 13:48:30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>08-09-2025 09:14:29</t>
+          <t>13-11-2025 13:48:30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08-09-2025 11:36:18</t>
+          <t>13-11-2025 14:40:35</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17017</v>
+        <v>6250</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -671,39 +673,41 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="O3" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
+        <v>40627</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>40627</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>253527</v>
+        <v>254713</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -712,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>67.48333333333333</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08-09-2025 11:36:18</t>
+          <t>13-11-2025 14:40:35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:18</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:18</t>
+          <t>14-11-2025 07:12:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>08-09-2025 13:12:47</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8098</v>
+        <v>5996</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -751,39 +755,41 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O4" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-9</v>
+        <v>-1.335104166666667</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>253524</v>
+        <v>243569</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -792,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>58.75833333333333</v>
+        <v>21.675</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:12:47</t>
+          <t>14-11-2025 08:02:33</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:27:47</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>08-09-2025 13:27:47</t>
+          <t>14-11-2025 08:19:33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08-09-2025 14:26:32</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7051</v>
+        <v>2601</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -831,17 +837,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -851,19 +857,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-9</v>
+        <v>-429</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>253528</v>
+        <v>254156</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -872,37 +878,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>119.175</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:26:32</t>
+          <t>14-11-2025 08:41:13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:41:32</t>
+          <t>14-11-2025 08:58:13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>08-09-2025 14:41:32</t>
+          <t>14-11-2025 08:58:13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:43</t>
+          <t>14-11-2025 10:25:42</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14301</v>
+        <v>10497</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -911,39 +917,41 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O6" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0</v>
+        <v>-0.4345138888888889</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>244023</v>
+        <v>254675</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -952,37 +960,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>8.308333333333334</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:43</t>
+          <t>14-11-2025 10:25:42</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:01:43</t>
+          <t>14-11-2025 10:42:42</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:01:43</t>
+          <t>14-11-2025 10:42:42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09-09-2025 09:10:01</t>
+          <t>14-11-2025 13:16:39</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>997</v>
+        <v>18475</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -991,14 +999,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1008,11 +1016,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-354.3819618055555</v>
+        <v>-7.553234953703703</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1020,7 +1028,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>252939</v>
+        <v>254519</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1029,37 +1037,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>89.8</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:10:01</t>
+          <t>14-11-2025 13:16:39</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:31:01</t>
+          <t>14-11-2025 13:50:39</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>09-09-2025 09:31:01</t>
+          <t>14-11-2025 13:50:39</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09-09-2025 11:00:49</t>
+          <t>17-11-2025 07:07:49</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10776</v>
+        <v>9259</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1077,6 +1085,9 @@
       <c r="N8" t="n">
         <v>70</v>
       </c>
+      <c r="O8" t="n">
+        <v>406422</v>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1085,19 +1096,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>22-08-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-28.45890625</v>
+        <v>-4</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>252815</v>
+        <v>254375</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1106,37 +1117,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>242.9416666666667</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:00:49</t>
+          <t>17-11-2025 07:07:49</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:40:49</t>
+          <t>17-11-2025 07:24:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>09-09-2025 11:40:49</t>
+          <t>17-11-2025 07:24:49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10-09-2025 07:43:46</t>
+          <t>17-11-2025 08:10:06</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>29153</v>
+        <v>5435</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1145,14 +1156,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O9" t="n">
+        <v>40624</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1162,58 +1176,58 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-15.32206018518518</v>
+        <v>-12</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>253072</v>
+        <v>254256</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>29.13333333333333</v>
+        <v>50.925</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>17-11-2025 08:10:06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:00</t>
+          <t>17-11-2025 08:27:06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>08-09-2025 07:46:00</t>
+          <t>17-11-2025 08:27:06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>08-09-2025 08:15:08</t>
+          <t>17-11-2025 09:18:02</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3496</v>
+        <v>6111</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1226,13 +1240,13 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>70</v>
       </c>
       <c r="O10" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1242,58 +1256,58 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>18-08-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-38</v>
+        <v>-18</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>253271</v>
+        <v>244023</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>42.63333333333333</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:15:08</t>
+          <t>17-11-2025 09:18:02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:40:08</t>
+          <t>17-11-2025 09:39:02</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>08-09-2025 08:40:08</t>
+          <t>17-11-2025 09:39:02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>08-09-2025 09:22:46</t>
+          <t>17-11-2025 09:47:20</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5116</v>
+        <v>997</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1312,7 +1326,7 @@
         <v>70</v>
       </c>
       <c r="O11" t="n">
-        <v>40904</v>
+        <v>406062</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1322,58 +1336,58 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-20</v>
+        <v>-417</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>253278</v>
+        <v>254237</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>28.425</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:22:46</t>
+          <t>17-11-2025 09:47:20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:47:46</t>
+          <t>17-11-2025 10:04:20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>08-09-2025 09:47:46</t>
+          <t>17-11-2025 10:04:20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08-09-2025 10:16:11</t>
+          <t>17-11-2025 13:08:26</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3411</v>
+        <v>22091</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1386,74 +1400,78 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
       </c>
-      <c r="O12" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-13</v>
+        <v>-7.547523148148148</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>253317</v>
+        <v>255039</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>102.775</v>
+        <v>9.15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>08-09-2025 10:16:11</t>
+          <t>17-11-2025 13:08:26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>08-09-2025 11:02:11</t>
+          <t>17-11-2025 13:31:26</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>08-09-2025 11:02:11</t>
+          <t>17-11-2025 13:31:26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08-09-2025 12:44:58</t>
+          <t>17-11-2025 13:40:35</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12333</v>
+        <v>1098</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1462,17 +1480,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O13" t="n">
-        <v>40910</v>
+        <v>40624</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1482,58 +1500,58 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>253318</v>
+        <v>254824</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>51.55</v>
+        <v>748.225</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-09-2025 12:44:58</t>
+          <t>17-11-2025 13:40:35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>08-09-2025 13:09:58</t>
+          <t>17-11-2025 14:12:35</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>08-09-2025 13:09:58</t>
+          <t>17-11-2025 14:12:35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>08-09-2025 14:01:31</t>
+          <t>19-11-2025 10:40:48</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6186</v>
+        <v>89787</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1542,17 +1560,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>76</v>
       </c>
       <c r="O14" t="n">
-        <v>40910</v>
+        <v>406232</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1562,58 +1580,58 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>253260</v>
+        <v>254599</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>109.4083333333333</v>
+        <v>44.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:01:31</t>
+          <t>19-11-2025 10:40:48</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:43:31</t>
+          <t>19-11-2025 11:14:48</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>08-09-2025 14:43:31</t>
+          <t>19-11-2025 11:14:48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09-09-2025 08:32:55</t>
+          <t>19-11-2025 11:59:42</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13129</v>
+        <v>5388</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1632,7 +1650,7 @@
         <v>70</v>
       </c>
       <c r="O15" t="n">
-        <v>40279</v>
+        <v>406552</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1642,58 +1660,58 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>253455</v>
+        <v>253961</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>55.55833333333333</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:32:55</t>
+          <t>19-11-2025 11:59:42</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:57:55</t>
+          <t>19-11-2025 12:14:42</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>09-09-2025 08:57:55</t>
+          <t>19-11-2025 12:14:42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09-09-2025 09:53:29</t>
+          <t>19-11-2025 12:50:37</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6667</v>
+        <v>4310</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1711,9 +1729,6 @@
       <c r="N16" t="n">
         <v>70</v>
       </c>
-      <c r="O16" t="n">
-        <v>40279</v>
-      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -1722,11 +1737,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-2</v>
+        <v>-18.53515625</v>
       </c>
       <c r="T16" t="n">
         <v>4</v>
@@ -1734,46 +1749,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>253247</v>
+        <v>250284</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>109.575</v>
+        <v>146.35</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09-09-2025 09:53:29</t>
+          <t>19-11-2025 12:50:37</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09-09-2025 10:18:29</t>
+          <t>19-11-2025 13:13:37</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>09-09-2025 10:18:29</t>
+          <t>19-11-2025 13:13:37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:03</t>
+          <t>20-11-2025 07:39:58</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13149</v>
+        <v>17562</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1786,13 +1801,13 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
         <v>70</v>
       </c>
       <c r="O17" t="n">
-        <v>40279</v>
+        <v>406422</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1802,19 +1817,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>0</v>
+        <v>-254</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>253249</v>
+        <v>254165</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1823,37 +1838,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28-08-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>57.75833333333333</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:08:03</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:50:03</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>09-09-2025 12:50:03</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09-09-2025 13:47:49</t>
+          <t>14-11-2025 08:40:19</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6931</v>
+        <v>6998</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1862,36 +1877,41 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>76</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
+      <c r="O18" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-8.574872685185186</v>
+        <v>-0.3613310185185185</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>253706</v>
+        <v>253650</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1900,37 +1920,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>311</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>09-09-2025 13:47:49</t>
+          <t>14-11-2025 08:40:19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09-09-2025 14:22:49</t>
+          <t>14-11-2025 09:07:19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>09-09-2025 14:22:49</t>
+          <t>14-11-2025 09:07:19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10-09-2025 11:33:49</t>
+          <t>14-11-2025 13:40:27</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>37320</v>
+        <v>32776</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1939,11 +1959,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
         <v>76</v>
@@ -1956,58 +1976,58 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>30-09-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0</v>
+        <v>-25.56975694444445</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>252702</v>
+        <v>254107</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>58.38333333333333</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:00:00</t>
+          <t>14-11-2025 13:40:27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:34:00</t>
+          <t>14-11-2025 14:22:27</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>05-09-2025 07:34:00</t>
+          <t>14-11-2025 14:22:27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>05-09-2025 08:32:23</t>
+          <t>17-11-2025 09:17:30</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7006</v>
+        <v>21007</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2016,80 +2036,75 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>152</v>
-      </c>
-      <c r="O20" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-08-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0</v>
+        <v>-36.38715856481482</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>253362</v>
+        <v>254293</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>58.38333333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:32:23</t>
+          <t>17-11-2025 09:17:30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:47:23</t>
+          <t>17-11-2025 09:46:30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>05-09-2025 08:47:23</t>
+          <t>17-11-2025 09:46:30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>05-09-2025 09:45:46</t>
+          <t>17-11-2025 10:05:21</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7006</v>
+        <v>2262</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2098,80 +2113,78 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="O21" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>15-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>252681</v>
+        <v>254188</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
-        <v>115.0166666666667</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>05-09-2025 09:45:46</t>
+          <t>17-11-2025 10:05:21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05-09-2025 10:19:46</t>
+          <t>17-11-2025 10:34:21</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>05-09-2025 10:19:46</t>
+          <t>17-11-2025 10:34:21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>05-09-2025 12:14:47</t>
+          <t>17-11-2025 11:11:48</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>13802</v>
+        <v>4493</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2180,80 +2193,78 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O22" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40279</v>
+        <v>0</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>253591</v>
+        <v>253838</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>17.41666666666667</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:14:47</t>
+          <t>17-11-2025 11:11:48</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:29:47</t>
+          <t>17-11-2025 11:38:48</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:29:47</t>
+          <t>17-11-2025 11:38:48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>05-09-2025 12:47:12</t>
+          <t>17-11-2025 13:27:10</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2090</v>
+        <v>13004</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2262,33 +2273,28 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
-      </c>
-      <c r="O23" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>24-09-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>0</v>
+        <v>-21.56053240740741</v>
       </c>
       <c r="T23" t="n">
         <v>4</v>
@@ -2296,46 +2302,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>243569</v>
+        <v>254758</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>21.675</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>05-09-2025 12:47:12</t>
+          <t>17-11-2025 13:27:10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:06:12</t>
+          <t>17-11-2025 13:54:10</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:06:12</t>
+          <t>17-11-2025 13:54:10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:52</t>
+          <t>17-11-2025 14:55:33</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2601</v>
+        <v>7366</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2344,17 +2350,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>76</v>
-      </c>
-      <c r="O24" t="n">
-        <v>40904</v>
+        <v>70</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2364,19 +2367,19 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-374</v>
+        <v>-0.6219097222222222</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>250284</v>
+        <v>254556</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2385,37 +2388,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>146.35</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>05-09-2025 13:27:52</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05-09-2025 14:07:52</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>05-09-2025 14:07:52</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08-09-2025 08:34:13</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17562</v>
+        <v>20810</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2424,39 +2427,41 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O25" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-193</v>
+        <v>-1.42806712962963</v>
       </c>
       <c r="T25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>252906</v>
+        <v>254230</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2465,37 +2470,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>34.725</v>
+        <v>62.475</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>08-09-2025 08:34:13</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:12:13</t>
+          <t>14-11-2025 10:52:25</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:12:13</t>
+          <t>14-11-2025 10:52:25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08-09-2025 09:46:57</t>
+          <t>14-11-2025 11:54:53</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4167</v>
+        <v>7497</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2504,17 +2509,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O26" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2524,11 +2529,11 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-31</v>
+        <v>-15</v>
       </c>
       <c r="T26" t="n">
         <v>2</v>
@@ -2536,7 +2541,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>253140</v>
+        <v>254433</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2545,37 +2550,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>55.83333333333334</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>08-09-2025 09:46:57</t>
+          <t>14-11-2025 11:54:53</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:03:57</t>
+          <t>14-11-2025 12:09:53</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:03:57</t>
+          <t>14-11-2025 12:09:53</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08-09-2025 10:59:47</t>
+          <t>14-11-2025 13:17:44</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>6700</v>
+        <v>8142</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2584,17 +2589,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>40900</v>
+        <v>406422</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2604,11 +2609,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>26-08-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-26</v>
+        <v>-3</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -2616,7 +2621,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>253100</v>
+        <v>254106</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2625,37 +2630,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>47.35</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>08-09-2025 10:59:47</t>
+          <t>14-11-2025 13:17:44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:47</t>
+          <t>14-11-2025 13:36:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>08-09-2025 11:31:47</t>
+          <t>14-11-2025 13:36:44</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>08-09-2025 12:19:08</t>
+          <t>17-11-2025 07:24:23</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>5682</v>
+        <v>12917</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2673,9 +2678,6 @@
       <c r="N28" t="n">
         <v>70</v>
       </c>
-      <c r="O28" t="n">
-        <v>40900</v>
-      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
@@ -2684,19 +2686,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-13</v>
+        <v>-41.30859953703704</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>253246</v>
+        <v>254460</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2705,37 +2707,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>194.25</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:19:08</t>
+          <t>17-11-2025 07:24:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:34:08</t>
+          <t>17-11-2025 07:45:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>08-09-2025 12:34:08</t>
+          <t>17-11-2025 07:45:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>09-09-2025 07:48:23</t>
+          <t>17-11-2025 08:32:04</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23310</v>
+        <v>5602</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2753,9 +2755,6 @@
       <c r="N29" t="n">
         <v>70</v>
       </c>
-      <c r="O29" t="n">
-        <v>40900</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2764,19 +2763,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-11</v>
+        <v>-35.35560185185185</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>253372</v>
+        <v>254198</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2785,37 +2784,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>103.775</v>
+        <v>215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>09-09-2025 07:48:23</t>
+          <t>17-11-2025 08:32:04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>09-09-2025 08:07:23</t>
+          <t>17-11-2025 09:06:04</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>09-09-2025 08:07:23</t>
+          <t>17-11-2025 09:06:04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09-09-2025 09:51:09</t>
+          <t>17-11-2025 12:41:04</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>12453</v>
+        <v>25800</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2824,17 +2823,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>70</v>
-      </c>
-      <c r="O30" t="n">
-        <v>40904</v>
+        <v>152</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2844,19 +2840,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0</v>
+        <v>-28.52851851851852</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>253370</v>
+        <v>253885</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2865,37 +2861,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>207.5416666666667</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>09-09-2025 09:51:09</t>
+          <t>17-11-2025 12:41:04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>09-09-2025 10:06:09</t>
+          <t>17-11-2025 13:13:04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>09-09-2025 10:06:09</t>
+          <t>17-11-2025 13:13:04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09-09-2025 13:33:42</t>
+          <t>17-11-2025 14:59:00</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>24905</v>
+        <v>12712</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2904,18 +2900,15 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="O31" t="n">
-        <v>40904</v>
-      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -2924,19 +2917,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>0</v>
+        <v>-13.62430555555556</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>253095</v>
+        <v>254451</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2945,37 +2938,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>76.31666666666666</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:33:42</t>
+          <t>17-11-2025 14:59:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:50:42</t>
+          <t>18-11-2025 07:18:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>09-09-2025 13:50:42</t>
+          <t>18-11-2025 07:18:00</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10-09-2025 07:07:01</t>
+          <t>18-11-2025 12:39:08</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9158</v>
+        <v>38537</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2984,11 +2977,11 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -3001,58 +2994,58 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-8.296539351851852</v>
+        <v>-10.52718171296296</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>253332</v>
+        <v>254481</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="E33" t="n">
-        <v>184.825</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:07:01</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:24:01</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10-09-2025 07:24:01</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10-09-2025 10:28:50</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>22179</v>
+        <v>9740</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3061,36 +3054,41 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
+      <c r="O33" t="n">
+        <v>40642</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>40642</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-10.43669560185185</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>252833</v>
+        <v>254762</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3099,37 +3097,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>34.5</v>
       </c>
       <c r="E34" t="n">
-        <v>74.78333333333333</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:00:00</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:34:30</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>09-09-2025 07:34:30</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>09-09-2025 08:49:17</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>8974</v>
+        <v>3823</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3147,27 +3145,32 @@
       <c r="N34" t="n">
         <v>70</v>
       </c>
-      <c r="P34" t="n">
-        <v>0</v>
+      <c r="O34" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>26-08-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-24.36755787037037</v>
+        <v>-1.291684027777778</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>253223</v>
+        <v>253865</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3176,37 +3179,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>50.5</v>
+        <v>34.5</v>
       </c>
       <c r="E35" t="n">
-        <v>16.4</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>09-09-2025 08:49:17</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>09-09-2025 09:39:47</t>
+          <t>14-11-2025 07:34:31</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>09-09-2025 09:39:47</t>
+          <t>14-11-2025 07:34:31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>09-09-2025 09:56:11</t>
+          <t>14-11-2025 09:31:17</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1968</v>
+        <v>14011</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3215,11 +3218,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -3232,19 +3235,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-18.4140162037037</v>
+        <v>-38.33299189814815</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>252601</v>
+        <v>254245</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3253,37 +3256,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>51.20833333333334</v>
+        <v>89.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>09-09-2025 09:56:11</t>
+          <t>14-11-2025 09:31:17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>09-09-2025 10:28:41</t>
+          <t>14-11-2025 10:03:47</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>09-09-2025 10:28:41</t>
+          <t>14-11-2025 10:03:47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>09-09-2025 11:19:53</t>
+          <t>14-11-2025 11:33:35</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>6145</v>
+        <v>10776</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3292,11 +3295,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
@@ -3309,19 +3312,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>31-12-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0</v>
+        <v>-28.4179224537037</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>253208</v>
+        <v>254356</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3330,37 +3333,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="E37" t="n">
-        <v>104.2583333333333</v>
+        <v>179.6</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>09-09-2025 11:19:53</t>
+          <t>14-11-2025 11:33:35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>09-09-2025 11:52:23</t>
+          <t>14-11-2025 12:04:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>09-09-2025 11:52:23</t>
+          <t>14-11-2025 12:04:05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>09-09-2025 13:36:39</t>
+          <t>17-11-2025 07:03:41</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12511</v>
+        <v>21552</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3369,11 +3372,11 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3386,19 +3389,19 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-14.56711805555556</v>
+        <v>-19.56382523148148</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>253210</v>
+        <v>254381</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3407,37 +3410,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="E38" t="n">
-        <v>94.15833333333333</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>09-09-2025 13:36:39</t>
+          <t>17-11-2025 07:03:41</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>09-09-2025 14:07:09</t>
+          <t>17-11-2025 07:36:11</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>09-09-2025 14:07:09</t>
+          <t>17-11-2025 07:36:11</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10-09-2025 07:41:18</t>
+          <t>17-11-2025 09:00:03</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>11299</v>
+        <v>10064</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3446,11 +3449,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
@@ -3463,19 +3466,19 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-10.32035300925926</v>
+        <v>-21.31130208333333</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>252883</v>
+        <v>254652</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3484,37 +3487,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>32.5</v>
       </c>
       <c r="E39" t="n">
-        <v>247.3083333333333</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10-09-2025 07:41:18</t>
+          <t>17-11-2025 09:00:03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10-09-2025 08:13:48</t>
+          <t>17-11-2025 09:32:33</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10-09-2025 08:13:48</t>
+          <t>17-11-2025 09:32:33</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10-09-2025 12:21:07</t>
+          <t>17-11-2025 10:01:17</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>29677</v>
+        <v>3448</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3523,18 +3526,15 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
-      <c r="O39" t="n">
-        <v>40900</v>
-      </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
@@ -3543,58 +3543,58 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-23</v>
+        <v>-7.353825231481482</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>252002</v>
+        <v>254756</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>55</v>
+        <v>40.5</v>
       </c>
       <c r="E40" t="n">
-        <v>55.675</v>
+        <v>60.625</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>04-09-2025 12:00:00</t>
+          <t>17-11-2025 10:01:17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>04-09-2025 12:55:00</t>
+          <t>17-11-2025 10:41:47</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>04-09-2025 12:55:00</t>
+          <t>17-11-2025 10:41:47</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>04-09-2025 13:50:40</t>
+          <t>17-11-2025 11:42:24</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>6681</v>
+        <v>7275</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3607,39 +3607,32 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>40307 (esterno)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P40" t="n">
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>40307</v>
+        <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-10.57685763888889</v>
+        <v>-4.424050925925926</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>253314</v>
+        <v>253694</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3648,37 +3641,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E41" t="n">
-        <v>43.40833333333333</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>04-09-2025 13:50:40</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>04-09-2025 14:40:40</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>04-09-2025 14:40:40</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>05-09-2025 07:24:05</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5209</v>
+        <v>14611</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3697,7 +3690,7 @@
         <v>76</v>
       </c>
       <c r="O41" t="n">
-        <v>40295</v>
+        <v>40623</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -3705,23 +3698,23 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>40295</v>
+        <v>40623</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0</v>
+        <v>-0.6158043981481481</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>252569</v>
+        <v>253380</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3730,37 +3723,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
-        <v>9.583333333333334</v>
+        <v>104.275</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>05-09-2025 07:24:05</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>05-09-2025 07:54:05</t>
+          <t>14-11-2025 07:46:45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>05-09-2025 07:54:05</t>
+          <t>14-11-2025 07:46:45</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>05-09-2025 08:03:40</t>
+          <t>14-11-2025 09:31:02</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1150</v>
+        <v>12513</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3769,36 +3762,41 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>76</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O42" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-14.33587962962963</v>
+        <v>-0.3965509259259259</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>252685</v>
+        <v>252061</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3807,37 +3805,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E43" t="n">
-        <v>74.56666666666666</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>05-09-2025 08:03:40</t>
+          <t>14-11-2025 09:31:02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>05-09-2025 08:33:40</t>
+          <t>14-11-2025 10:16:02</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>05-09-2025 08:33:40</t>
+          <t>14-11-2025 10:16:02</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>05-09-2025 09:48:14</t>
+          <t>14-11-2025 10:52:12</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>8948</v>
+        <v>4340</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3846,17 +3844,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N43" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O43" t="n">
-        <v>40295</v>
+        <v>40628</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -3864,23 +3862,23 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>40295</v>
+        <v>40628</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>252682</v>
+        <v>254546</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3889,37 +3887,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>83.40833333333333</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>05-09-2025 09:48:14</t>
+          <t>14-11-2025 10:52:12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>05-09-2025 10:28:14</t>
+          <t>14-11-2025 11:22:12</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>05-09-2025 10:28:14</t>
+          <t>14-11-2025 11:22:12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>05-09-2025 11:51:38</t>
+          <t>14-11-2025 13:11:36</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>10009</v>
+        <v>13129</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3928,41 +3926,39 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
         <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406242</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>252582</v>
+        <v>235572</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3971,37 +3967,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>30</v>
       </c>
       <c r="E45" t="n">
-        <v>46.08333333333334</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>05-09-2025 11:51:38</t>
+          <t>14-11-2025 13:11:36</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>05-09-2025 12:21:38</t>
+          <t>14-11-2025 13:41:36</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>05-09-2025 12:21:38</t>
+          <t>14-11-2025 13:41:36</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>05-09-2025 13:07:43</t>
+          <t>17-11-2025 07:04:35</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>5530</v>
+        <v>9958</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4010,41 +4006,39 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O45" t="n">
-        <v>40290</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40290</v>
+        <v>0</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-09-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0</v>
+        <v>-744</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>235572</v>
+        <v>254457</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4053,37 +4047,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E46" t="n">
-        <v>82.98333333333333</v>
+        <v>3.925</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>05-09-2025 13:07:43</t>
+          <t>17-11-2025 07:04:35</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05-09-2025 13:52:43</t>
+          <t>17-11-2025 07:34:35</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>05-09-2025 13:52:43</t>
+          <t>17-11-2025 07:34:35</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08-09-2025 07:15:42</t>
+          <t>17-11-2025 07:38:31</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9958</v>
+        <v>471</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4096,13 +4090,13 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
       <c r="O46" t="n">
-        <v>40904</v>
+        <v>406372</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4112,19 +4106,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-689</v>
+        <v>-1</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>253374</v>
+        <v>254605</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4133,37 +4127,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>30</v>
       </c>
       <c r="E47" t="n">
-        <v>59.60833333333333</v>
+        <v>39.025</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>08-09-2025 07:15:42</t>
+          <t>17-11-2025 07:38:31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>08-09-2025 07:45:42</t>
+          <t>17-11-2025 08:08:31</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>08-09-2025 07:45:42</t>
+          <t>17-11-2025 08:08:31</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08-09-2025 08:45:19</t>
+          <t>17-11-2025 08:47:32</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>7153</v>
+        <v>4683</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4176,14 +4170,11 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N47" t="n">
         <v>70</v>
       </c>
-      <c r="O47" t="n">
-        <v>40904</v>
-      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -4192,11 +4183,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>0</v>
+        <v>-3.36634837962963</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
@@ -4204,7 +4195,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>253036</v>
+        <v>254437</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4213,37 +4204,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E48" t="n">
-        <v>78.73333333333333</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>08-09-2025 08:45:19</t>
+          <t>17-11-2025 08:47:32</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08-09-2025 09:25:19</t>
+          <t>17-11-2025 09:17:32</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>08-09-2025 09:25:19</t>
+          <t>17-11-2025 09:17:32</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08-09-2025 10:44:03</t>
+          <t>17-11-2025 10:15:36</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>9448</v>
+        <v>6967</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4252,17 +4243,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O48" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4272,19 +4263,19 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>22-08-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>253710</v>
+        <v>254598</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4293,37 +4284,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E49" t="n">
-        <v>1.616666666666667</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>08-09-2025 10:44:03</t>
+          <t>17-11-2025 10:15:36</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>08-09-2025 11:29:03</t>
+          <t>17-11-2025 11:25:36</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>08-09-2025 11:29:03</t>
+          <t>17-11-2025 11:25:36</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>08-09-2025 11:30:40</t>
+          <t>17-11-2025 13:09:51</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>194</v>
+        <v>12511</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4332,11 +4323,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N49" t="n">
         <v>70</v>
@@ -4349,58 +4340,58 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-8.479629629629629</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>253687</v>
+        <v>254941</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E50" t="n">
-        <v>44.23333333333333</v>
+        <v>35.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>08-09-2025 11:30:40</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:40</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>08-09-2025 12:05:40</t>
+          <t>14-11-2025 07:32:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>08-09-2025 12:49:54</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>5308</v>
+        <v>4260</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4409,28 +4400,33 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>70</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O50" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-6.534652777777778</v>
+        <v>-1.338541666666667</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
@@ -4438,46 +4434,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>253267</v>
+        <v>253897</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E51" t="n">
-        <v>164.3666666666667</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>08-09-2025 12:49:54</t>
+          <t>14-11-2025 08:07:30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>08-09-2025 13:19:54</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>08-09-2025 13:19:54</t>
+          <t>14-11-2025 08:51:30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>09-09-2025 08:04:16</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>19724</v>
+        <v>11282</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4486,75 +4482,80 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N51" t="n">
-        <v>70</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O51" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-09-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>0</v>
+        <v>-0.434386574074074</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>253268</v>
+        <v>254117</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E52" t="n">
-        <v>78.55833333333334</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>09-09-2025 08:04:16</t>
+          <t>14-11-2025 10:25:31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>09-09-2025 08:29:16</t>
+          <t>14-11-2025 10:56:31</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>09-09-2025 08:29:16</t>
+          <t>14-11-2025 10:56:31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09-09-2025 09:47:49</t>
+          <t>14-11-2025 11:05:41</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>9427</v>
+        <v>1100</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4563,14 +4564,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4580,58 +4581,58 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>23-09-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>0</v>
+        <v>-35.46228009259259</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>253359</v>
+        <v>254512</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E53" t="n">
-        <v>134.0166666666667</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>09-09-2025 09:47:49</t>
+          <t>14-11-2025 11:05:41</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>09-09-2025 10:17:49</t>
+          <t>14-11-2025 11:22:41</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>09-09-2025 10:17:49</t>
+          <t>14-11-2025 11:22:41</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>09-09-2025 12:31:50</t>
+          <t>14-11-2025 12:22:14</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>16082</v>
+        <v>7147</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4640,17 +4641,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O53" t="n">
-        <v>40904</v>
+        <v>406232</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4660,11 +4661,11 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
@@ -4672,7 +4673,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>252827</v>
+        <v>253382</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4681,37 +4682,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>410</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>14-11-2025 12:22:14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>08-09-2025 07:17:00</t>
+          <t>14-11-2025 12:39:14</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>08-09-2025 07:17:00</t>
+          <t>14-11-2025 12:39:14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:00</t>
+          <t>14-11-2025 14:04:20</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>49200</v>
+        <v>10212</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4720,15 +4721,18 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
         <v>76</v>
       </c>
+      <c r="O54" t="n">
+        <v>406372</v>
+      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
@@ -4737,19 +4741,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>04-09-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-14.58819444444444</v>
+        <v>-12</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>253409</v>
+        <v>254910</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4758,37 +4762,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>27-08-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>17</v>
       </c>
       <c r="E55" t="n">
-        <v>27.18333333333333</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:00</t>
+          <t>14-11-2025 14:04:20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>08-09-2025 14:24:00</t>
+          <t>14-11-2025 14:21:20</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>08-09-2025 14:24:00</t>
+          <t>14-11-2025 14:21:20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>08-09-2025 14:51:11</t>
+          <t>17-11-2025 07:34:52</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3262</v>
+        <v>8824</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4801,13 +4805,13 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
         <v>76</v>
       </c>
       <c r="O55" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4817,19 +4821,19 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>253194</v>
+        <v>254283</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4838,37 +4842,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>27-08-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>199.0833333333333</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>08-09-2025 14:51:11</t>
+          <t>17-11-2025 07:34:52</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>09-09-2025 07:06:11</t>
+          <t>17-11-2025 07:51:52</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>09-09-2025 07:06:11</t>
+          <t>17-11-2025 07:51:52</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>09-09-2025 10:25:16</t>
+          <t>17-11-2025 09:27:38</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>23890</v>
+        <v>11492</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4881,13 +4885,13 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>76</v>
       </c>
       <c r="O56" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4897,19 +4901,19 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>20-08-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-32</v>
+        <v>-8</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>252843</v>
+        <v>254555</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4918,37 +4922,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E57" t="n">
-        <v>19.2</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>09-09-2025 10:25:16</t>
+          <t>17-11-2025 09:27:38</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>09-09-2025 10:52:16</t>
+          <t>17-11-2025 09:44:38</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>09-09-2025 10:52:16</t>
+          <t>17-11-2025 09:44:38</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09-09-2025 11:11:28</t>
+          <t>17-11-2025 12:37:37</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2304</v>
+        <v>20758</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4961,13 +4965,13 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
         <v>76</v>
       </c>
       <c r="O57" t="n">
-        <v>40904</v>
+        <v>406232</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4977,11 +4981,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>30-07-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-57</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -4989,7 +4993,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>253425</v>
+        <v>254309</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4998,37 +5002,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>05-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E58" t="n">
-        <v>146.35</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>09-09-2025 11:11:28</t>
+          <t>17-11-2025 12:37:37</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>09-09-2025 11:34:28</t>
+          <t>17-11-2025 13:13:37</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>09-09-2025 11:34:28</t>
+          <t>17-11-2025 13:13:37</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:49</t>
+          <t>19-11-2025 12:13:38</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>17562</v>
+        <v>108002</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5037,14 +5041,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5054,58 +5058,58 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>29-08-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-21.58390046296296</v>
+        <v>-19.50947337962963</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>253313</v>
+        <v>254714</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E59" t="n">
-        <v>100.0083333333333</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:49</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>09-09-2025 14:17:49</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>09-09-2025 14:17:49</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10-09-2025 07:57:49</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>12001</v>
+        <v>10977</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5118,74 +5122,76 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N59" t="n">
         <v>76</v>
       </c>
       <c r="O59" t="n">
-        <v>40910</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-16</v>
+        <v>-1.389913194444444</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>252995</v>
+        <v>254291</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E60" t="n">
-        <v>68.31666666666666</v>
+        <v>18.85</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>10-09-2025 07:57:49</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10-09-2025 08:14:49</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>10-09-2025 08:14:49</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10-09-2025 09:23:08</t>
+          <t>14-11-2025 10:15:19</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>8198</v>
+        <v>2262</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5194,14 +5200,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O60" t="n">
+        <v>40624</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5211,11 +5220,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-19.39107060185185</v>
+        <v>-14</v>
       </c>
       <c r="T60" t="n">
         <v>7</v>
@@ -5223,46 +5232,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>253284</v>
+        <v>254429</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>28-08-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E61" t="n">
-        <v>56.99166666666667</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>10-09-2025 09:23:08</t>
+          <t>14-11-2025 10:15:19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10-09-2025 09:40:08</t>
+          <t>14-11-2025 10:45:19</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>10-09-2025 09:40:08</t>
+          <t>14-11-2025 10:45:19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10-09-2025 10:37:08</t>
+          <t>14-11-2025 14:45:34</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>6839</v>
+        <v>28829</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5271,17 +5280,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O61" t="n">
-        <v>40910</v>
+        <v>406372</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5291,58 +5300,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>28-08-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-24</v>
+        <v>-9</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>253602</v>
+        <v>254653</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>117.0833333333333</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10-09-2025 10:37:08</t>
+          <t>14-11-2025 14:45:34</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10-09-2025 10:54:08</t>
+          <t>17-11-2025 07:15:34</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>10-09-2025 10:54:08</t>
+          <t>17-11-2025 07:15:34</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10-09-2025 12:51:13</t>
+          <t>17-11-2025 08:19:58</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>14050</v>
+        <v>7729</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5351,14 +5360,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5368,11 +5377,11 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-10.53556712962963</v>
+        <v>-3.347204861111111</v>
       </c>
       <c r="T62" t="n">
         <v>7</v>
@@ -5380,7 +5389,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>253721</v>
+        <v>254893</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5389,37 +5398,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E63" t="n">
-        <v>39.39166666666667</v>
+        <v>46.675</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>09-09-2025 07:00:00</t>
+          <t>17-11-2025 08:19:58</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>09-09-2025 07:40:00</t>
+          <t>17-11-2025 08:49:58</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>09-09-2025 07:40:00</t>
+          <t>17-11-2025 08:49:58</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>09-09-2025 08:19:23</t>
+          <t>17-11-2025 09:36:39</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>4727</v>
+        <v>5601</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5438,7 +5447,7 @@
         <v>70</v>
       </c>
       <c r="O63" t="n">
-        <v>40900</v>
+        <v>406372</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -5448,7 +5457,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>08-10-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -5460,7 +5469,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>253686</v>
+        <v>254189</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5469,37 +5478,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>01-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>44.23333333333333</v>
+        <v>55.875</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>09-09-2025 08:19:23</t>
+          <t>17-11-2025 09:36:39</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09-09-2025 08:54:23</t>
+          <t>17-11-2025 10:06:39</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>09-09-2025 08:54:23</t>
+          <t>17-11-2025 10:06:39</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>09-09-2025 09:38:37</t>
+          <t>17-11-2025 11:02:31</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>5308</v>
+        <v>6705</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5508,15 +5517,18 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
       </c>
+      <c r="O64" t="n">
+        <v>406372</v>
+      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -5525,11 +5537,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-7.401822916666666</v>
+        <v>-1</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
@@ -5537,7 +5549,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>253659</v>
+        <v>255043</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5546,37 +5558,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>08-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>25</v>
       </c>
       <c r="E65" t="n">
-        <v>323.75</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>09-09-2025 09:38:37</t>
+          <t>17-11-2025 11:02:31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09-09-2025 10:03:37</t>
+          <t>17-11-2025 11:27:31</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>09-09-2025 10:03:37</t>
+          <t>17-11-2025 11:27:31</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10-09-2025 07:27:22</t>
+          <t>17-11-2025 14:31:48</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>38850</v>
+        <v>22114</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5585,15 +5597,18 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N65" t="n">
         <v>70</v>
       </c>
+      <c r="O65" t="n">
+        <v>406372</v>
+      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -5602,58 +5617,58 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>-9.310677083333333</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>253016</v>
+        <v>254521</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>02-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>73.38333333333334</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:00:00</t>
+          <t>17-11-2025 14:31:48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:30:00</t>
+          <t>18-11-2025 07:01:48</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>05-09-2025 07:30:00</t>
+          <t>18-11-2025 07:01:48</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>05-09-2025 08:43:23</t>
+          <t>18-11-2025 07:41:29</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>8806</v>
+        <v>4762</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5662,80 +5677,75 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>152</v>
-      </c>
-      <c r="O66" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>14-08-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>0</v>
+        <v>-13.32048032407407</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>253259</v>
+        <v>252811</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>69.23333333333333</v>
+        <v>11.875</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>05-09-2025 08:43:23</t>
+          <t>18-11-2025 07:41:29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>05-09-2025 09:18:23</t>
+          <t>18-11-2025 08:16:29</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>05-09-2025 09:18:23</t>
+          <t>18-11-2025 08:16:29</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>05-09-2025 10:27:37</t>
+          <t>18-11-2025 08:28:22</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>8308</v>
+        <v>1425</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5744,33 +5754,28 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
       </c>
-      <c r="O67" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P67" t="n">
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>25-08-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>0</v>
+        <v>-15.35303240740741</v>
       </c>
       <c r="T67" t="n">
         <v>7</v>
@@ -5778,46 +5783,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>252679</v>
+        <v>254651</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E68" t="n">
-        <v>60</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>05-09-2025 10:27:37</t>
+          <t>18-11-2025 08:28:22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>05-09-2025 11:12:37</t>
+          <t>18-11-2025 09:03:22</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>05-09-2025 11:12:37</t>
+          <t>18-11-2025 09:03:22</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>05-09-2025 12:12:37</t>
+          <t>18-11-2025 09:26:00</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>7200</v>
+        <v>2717</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5826,80 +5831,75 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>76</v>
-      </c>
-      <c r="O68" t="n">
-        <v>40295</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>40295</v>
+        <v>0</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>01-09-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>0</v>
+        <v>-7.393061342592593</v>
       </c>
       <c r="T68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>252664</v>
+        <v>254276</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
-        <v>365.975</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:12:37</t>
+          <t>18-11-2025 09:26:00</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:37</t>
+          <t>18-11-2025 09:56:00</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>05-09-2025 12:57:37</t>
+          <t>18-11-2025 09:56:00</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>08-09-2025 11:03:35</t>
+          <t>18-11-2025 10:33:02</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>43917</v>
+        <v>4444</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5908,80 +5908,78 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
       <c r="O69" t="n">
-        <v>40279</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>40279</v>
+        <v>0</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>02-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-6.460827546296296</v>
+        <v>-18</v>
       </c>
       <c r="T69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>253361</v>
+        <v>254915</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>76.70833333333333</v>
+        <v>48.875</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:03:35</t>
+          <t>18-11-2025 10:33:02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:33:35</t>
+          <t>18-11-2025 11:08:02</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>08-09-2025 11:33:35</t>
+          <t>18-11-2025 11:08:02</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>08-09-2025 12:50:18</t>
+          <t>18-11-2025 11:56:55</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>9205</v>
+        <v>5865</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5999,9 +5997,6 @@
       <c r="N70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" t="n">
-        <v>40904</v>
-      </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
@@ -6010,19 +6005,19 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>11-09-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>253375</v>
+        <v>254715</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6031,37 +6026,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>04-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E71" t="n">
-        <v>51.88333333333333</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>08-09-2025 12:50:18</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08-09-2025 13:15:18</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>08-09-2025 13:15:18</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:11</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>6226</v>
+        <v>16145</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6070,39 +6065,41 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>76</v>
+      </c>
+      <c r="O71" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>40623</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>19-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S71" s="1" t="n">
+        <v>-1.409403935185185</v>
+      </c>
+      <c r="T71" t="n">
         <v>2</v>
-      </c>
-      <c r="N71" t="n">
-        <v>70</v>
-      </c>
-      <c r="O71" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>25-09-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>253368</v>
+        <v>254287</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6111,37 +6108,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E72" t="n">
-        <v>103.775</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:07:11</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:32:11</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>08-09-2025 14:32:11</t>
+          <t>14-11-2025 10:24:32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>09-09-2025 08:15:57</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>12453</v>
+        <v>15556</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6150,17 +6147,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
         <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6170,19 +6167,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="T72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>253377</v>
+        <v>254427</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6191,78 +6188,80 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E73" t="n">
-        <v>127.7166666666667</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:15:57</t>
+          <t>14-11-2025 12:34:10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:57</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>09-09-2025 08:40:57</t>
+          <t>14-11-2025 13:14:10</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>09-09-2025 10:48:40</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>15326</v>
+        <v>6667</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
       <c r="O73" t="n">
-        <v>40904</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
+        <v>406422</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>0</v>
+        <v>-4.590092592592592</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>253367</v>
+        <v>254574</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6271,37 +6270,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>11-09-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E74" t="n">
-        <v>135.7</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>09-09-2025 10:48:40</t>
+          <t>14-11-2025 14:09:44</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>09-09-2025 11:13:40</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>09-09-2025 11:13:40</t>
+          <t>14-11-2025 14:49:44</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>09-09-2025 13:29:22</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>16284</v>
+        <v>20833</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6310,17 +6309,17 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
       <c r="O74" t="n">
-        <v>40904</v>
+        <v>406422</v>
       </c>
       <c r="P74" t="n">
         <v>0</v>
@@ -6330,19 +6329,19 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>253371</v>
+        <v>254187</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6351,37 +6350,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>10-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>107.7666666666667</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:29:22</t>
+          <t>17-11-2025 09:43:20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:54:22</t>
+          <t>17-11-2025 10:18:20</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>09-09-2025 13:54:22</t>
+          <t>17-11-2025 10:18:20</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10-09-2025 07:42:08</t>
+          <t>17-11-2025 11:04:44</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>12932</v>
+        <v>5567</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6390,17 +6389,17 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
         <v>70</v>
       </c>
       <c r="O75" t="n">
-        <v>40904</v>
+        <v>406372</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6410,11 +6409,11 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>25-09-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6422,7 +6421,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>253525</v>
+        <v>254586</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6431,37 +6430,37 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>12-09-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>92.14166666666667</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>10-09-2025 07:42:08</t>
+          <t>17-11-2025 11:04:44</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10-09-2025 08:07:08</t>
+          <t>17-11-2025 11:29:44</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>10-09-2025 08:07:08</t>
+          <t>17-11-2025 11:29:44</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10-09-2025 09:39:17</t>
+          <t>17-11-2025 12:21:16</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>11057</v>
+        <v>6185</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6470,17 +6469,17 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
         <v>70</v>
       </c>
       <c r="O76" t="n">
-        <v>40904</v>
+        <v>406372</v>
       </c>
       <c r="P76" t="n">
         <v>0</v>
@@ -6490,19 +6489,19 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>26-09-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>253245</v>
+        <v>254166</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6511,37 +6510,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>150.8333333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>10-09-2025 09:39:17</t>
+          <t>17-11-2025 12:21:16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>10-09-2025 10:14:17</t>
+          <t>17-11-2025 12:46:16</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>10-09-2025 10:14:17</t>
+          <t>17-11-2025 12:46:16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10-09-2025 12:45:07</t>
+          <t>17-11-2025 13:25:07</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>18100</v>
+        <v>4662</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6554,13 +6553,13 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
       </c>
       <c r="O77" t="n">
-        <v>40900</v>
+        <v>406372</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6570,19 +6569,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10-09-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>253401</v>
+        <v>254365</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6591,37 +6590,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>09-09-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E78" t="n">
-        <v>22.81666666666667</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10-09-2025 12:45:07</t>
+          <t>17-11-2025 13:25:07</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:15:07</t>
+          <t>17-11-2025 14:00:07</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:15:07</t>
+          <t>17-11-2025 14:00:07</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10-09-2025 13:37:56</t>
+          <t>18-11-2025 07:07:39</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>2738</v>
+        <v>8104</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6634,14 +6633,11 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
-      <c r="O78" t="n">
-        <v>40904</v>
-      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
@@ -6650,74 +6646,74 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>12-09-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-13</v>
+        <v>-14.2969849537037</v>
       </c>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>252980</v>
+        <v>253614</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>03-09-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E79" t="n">
-        <v>17.075</v>
+        <v>122.45</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>18-11-2025 07:07:39</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>18-11-2025 07:47:39</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>08-09-2025 07:00:00</t>
+          <t>18-11-2025 07:47:39</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>08-09-2025 07:17:04</t>
+          <t>18-11-2025 09:50:06</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>2049</v>
+        <v>14694</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6727,14 +6723,1254 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-10.30352430555556</v>
+        <v>-8.409797453703703</v>
       </c>
       <c r="T79" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>254903</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E80" t="n">
+        <v>256.6416666666667</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:50:06</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:30:06</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>18-11-2025 10:30:06</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:46:45</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>30797</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>70</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>12-01-2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="S80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>254339</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>35</v>
+      </c>
+      <c r="E81" t="n">
+        <v>245.9666666666667</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:46:45</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:21:45</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>19-11-2025 07:21:45</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>19-11-2025 11:27:43</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>29516</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>70</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>30-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S81" s="1" t="n">
+        <v>-30.47758101851852</v>
+      </c>
+      <c r="T81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>254101</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>30</v>
+      </c>
+      <c r="E82" t="n">
+        <v>28.425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>19-11-2025 11:27:43</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>19-11-2025 11:57:43</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>19-11-2025 11:57:43</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>19-11-2025 12:26:08</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3411</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>6</v>
+      </c>
+      <c r="N82" t="n">
+        <v>70</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="n">
+        <v>-26.51815393518519</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>254100</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="n">
+        <v>28.425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>19-11-2025 12:26:08</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>19-11-2025 12:51:08</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>19-11-2025 12:51:08</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>19-11-2025 13:19:34</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>3411</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>6</v>
+      </c>
+      <c r="N83" t="n">
+        <v>70</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S83" s="1" t="n">
+        <v>-26.55525462962963</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>254252</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>35</v>
+      </c>
+      <c r="E84" t="n">
+        <v>80.51666666666667</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>19-11-2025 13:19:34</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>19-11-2025 13:54:34</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>19-11-2025 13:54:34</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>20-11-2025 07:15:05</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>9662</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>70</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S84" s="1" t="n">
+        <v>-27.30214120370371</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>253974</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>19-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>35</v>
+      </c>
+      <c r="E85" t="n">
+        <v>28.425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>20-11-2025 07:15:05</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20-11-2025 07:50:05</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>20-11-2025 07:50:05</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20-11-2025 08:18:30</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>3411</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>6</v>
+      </c>
+      <c r="N85" t="n">
+        <v>70</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>29-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S85" s="1" t="n">
+        <v>-32.3461863425926</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>254419</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>35</v>
+      </c>
+      <c r="E86" t="n">
+        <v>72.34166666666667</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>20-11-2025 08:18:30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20-11-2025 08:53:30</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>20-11-2025 08:53:30</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:05:51</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8681</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
+      <c r="N86" t="n">
+        <v>70</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>10-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="n">
+        <v>-20.42072916666667</v>
+      </c>
+      <c r="T86" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>254354</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>30</v>
+      </c>
+      <c r="E87" t="n">
+        <v>18.675</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:05:51</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:35:51</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:35:51</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:54:31</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>2241</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>70</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>14-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S87" s="1" t="n">
+        <v>-16.45453125</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>254547</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>19-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>30</v>
+      </c>
+      <c r="E88" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>20-11-2025 10:54:31</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20-11-2025 11:24:31</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>20-11-2025 11:24:31</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>20-11-2025 12:33:04</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>8226</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>4</v>
+      </c>
+      <c r="N88" t="n">
+        <v>70</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>19-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S88" s="1" t="n">
+        <v>-11.52296875</v>
+      </c>
+      <c r="T88" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>253906</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>35</v>
+      </c>
+      <c r="E89" t="n">
+        <v>45.79166666666666</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>20-11-2025 12:33:04</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20-11-2025 13:08:04</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>20-11-2025 13:08:04</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20-11-2025 13:53:52</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>5495</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="N89" t="n">
+        <v>70</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>25-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S89" s="1" t="n">
+        <v>-5.579074074074074</v>
+      </c>
+      <c r="T89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>254609</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>416.6666666666667</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12-11-2025 13:56:40</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>40655</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>20-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>17.075</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>2049</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>08-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S91" s="1" t="n">
+        <v>-77.30352430555556</v>
+      </c>
+      <c r="T91" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>254428</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>48.30833333333333</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:48:18</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>5797</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>70</v>
+      </c>
+      <c r="O92" t="n">
+        <v>40649</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>40649</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>10-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S92" s="1" t="n">
+        <v>-7.616880787037037</v>
+      </c>
+      <c r="T92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>254173</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>15-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>202.5916666666667</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:22:35</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>24311</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>20-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>-39.39068865740741</v>
+      </c>
+      <c r="T93" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>254967</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BIMEC 5</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>19</v>
+      </c>
+      <c r="E94" t="n">
+        <v>260.4166666666667</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:19:00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>20-11-2025 14:19:00</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>21-11-2025 10:39:25</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>31250</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
+      <c r="N94" t="n">
+        <v>70</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>05-12-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>254671</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CASON</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>136.1666666666667</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:34:30</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:34:30</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>19-11-2025 08:50:40</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>16340</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>CASON ;H7 ;R5</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>7</v>
+      </c>
+      <c r="N95" t="n">
+        <v>70</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>21-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S95" s="1" t="n">
+        <v>-8.368518518518519</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254129</v>
+        <v>254762</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>44.5</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -568,21 +568,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>13-11-2025 12:34:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>13-11-2025 12:34:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>13-11-2025 13:05:51</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5340</v>
+        <v>3823</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,14 +591,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O2" t="n">
         <v>40623</v>
@@ -613,11 +613,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-0.553125</v>
+        <v>-0.5457349537037037</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>254385</v>
+        <v>254941</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -641,30 +641,30 @@
         <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>52.08333333333334</v>
+        <v>35.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:16:30</t>
+          <t>13-11-2025 13:05:51</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>13-11-2025 13:37:51</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:48:30</t>
+          <t>13-11-2025 13:37:51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>13-11-2025 14:13:21</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6250</v>
+        <v>4260</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>152</v>
       </c>
       <c r="O3" t="n">
-        <v>40627</v>
+        <v>40623</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>40627</v>
+        <v>40623</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0</v>
+        <v>-0.5926099537037037</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254713</v>
+        <v>253897</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>49.96666666666667</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:40:35</t>
+          <t>13-11-2025 14:13:21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>13-11-2025 14:57:21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:12:35</t>
+          <t>13-11-2025 14:57:21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>14-11-2025 08:31:22</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5996</v>
+        <v>11282</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
       </c>
       <c r="O4" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -773,23 +773,23 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-1.335104166666667</v>
+        <v>-0.3551215277777778</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>243569</v>
+        <v>253865</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>21.675</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:02:33</t>
+          <t>14-11-2025 08:31:22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>14-11-2025 09:13:22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:33</t>
+          <t>14-11-2025 09:13:22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>14-11-2025 11:10:08</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2601</v>
+        <v>14011</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -837,17 +837,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>76</v>
-      </c>
-      <c r="O5" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -857,11 +854,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-429</v>
+        <v>-35.46537037037037</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -869,7 +866,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>254156</v>
+        <v>252061</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -878,37 +875,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>87.47499999999999</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:41:13</t>
+          <t>14-11-2025 11:10:08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:13</t>
+          <t>14-11-2025 11:33:08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:13</t>
+          <t>14-11-2025 11:33:08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:42</t>
+          <t>14-11-2025 12:09:18</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10497</v>
+        <v>4340</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,17 +914,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O6" t="n">
-        <v>40606</v>
+        <v>40628</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -935,7 +932,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>40606</v>
+        <v>40628</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -943,15 +940,15 @@
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-0.4345138888888889</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254675</v>
+        <v>235572</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -964,33 +961,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>153.9583333333333</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:42</t>
+          <t>14-11-2025 12:09:18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:42:42</t>
+          <t>14-11-2025 12:32:18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 10:42:42</t>
+          <t>14-11-2025 12:32:18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:16:39</t>
+          <t>14-11-2025 13:55:17</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18475</v>
+        <v>9958</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -999,14 +996,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O7" t="n">
+        <v>406372</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1016,19 +1016,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-7.553234953703703</v>
+        <v>-744</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254519</v>
+        <v>254605</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1037,37 +1037,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>77.15833333333333</v>
+        <v>39.025</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:16:39</t>
+          <t>14-11-2025 13:55:17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:50:39</t>
+          <t>14-11-2025 14:18:17</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:50:39</t>
+          <t>14-11-2025 14:18:17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:07:49</t>
+          <t>14-11-2025 14:57:18</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9259</v>
+        <v>4683</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1080,14 +1080,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
         <v>70</v>
       </c>
-      <c r="O8" t="n">
-        <v>406422</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1096,19 +1093,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-4</v>
+        <v>-0.6231307870370371</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254375</v>
+        <v>254758</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1117,37 +1114,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>45.29166666666666</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:07:49</t>
+          <t>14-11-2025 14:57:18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:49</t>
+          <t>17-11-2025 07:14:18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:49</t>
+          <t>17-11-2025 07:14:18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:06</t>
+          <t>17-11-2025 08:15:41</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5435</v>
+        <v>7366</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1165,9 +1162,6 @@
       <c r="N9" t="n">
         <v>70</v>
       </c>
-      <c r="O9" t="n">
-        <v>40624</v>
-      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1176,19 +1170,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-12</v>
+        <v>-0.3442303240740741</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254256</v>
+        <v>254903</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1204,30 +1198,30 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>50.925</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:06</t>
+          <t>17-11-2025 08:15:41</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:27:06</t>
+          <t>17-11-2025 08:32:41</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:27:06</t>
+          <t>17-11-2025 08:32:41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:18:02</t>
+          <t>17-11-2025 12:49:20</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6111</v>
+        <v>30797</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1245,9 +1239,6 @@
       <c r="N10" t="n">
         <v>70</v>
       </c>
-      <c r="O10" t="n">
-        <v>406422</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1256,19 +1247,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>244023</v>
+        <v>254107</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1277,37 +1268,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>8.308333333333334</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:18:02</t>
+          <t>17-11-2025 12:49:20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:39:02</t>
+          <t>17-11-2025 13:06:20</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:39:02</t>
+          <t>17-11-2025 13:06:20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:47:20</t>
+          <t>18-11-2025 08:01:23</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>997</v>
+        <v>21007</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1320,14 +1311,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
         <v>70</v>
       </c>
-      <c r="O11" t="n">
-        <v>406062</v>
-      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1336,19 +1324,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-417</v>
+        <v>-37.33429976851852</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254237</v>
+        <v>254309</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1357,37 +1345,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>184.0916666666667</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 09:47:20</t>
+          <t>18-11-2025 08:01:23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:04:20</t>
+          <t>18-11-2025 08:37:23</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 10:04:20</t>
+          <t>18-11-2025 08:37:23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 13:08:26</t>
+          <t>20-11-2025 07:37:24</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22091</v>
+        <v>108002</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1396,27 +1384,20 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>70</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1424,7 +1405,7 @@
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-7.547523148148148</v>
+        <v>-20.31764467592593</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1432,46 +1413,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>255039</v>
+        <v>254556</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:08:26</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:31:26</t>
+          <t>14-11-2025 07:48:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:31:26</t>
+          <t>14-11-2025 07:48:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:40:35</t>
+          <t>14-11-2025 10:41:25</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1098</v>
+        <v>20810</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1480,78 +1461,80 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O13" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0</v>
+        <v>-1.445428240740741</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254824</v>
+        <v>243569</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>748.225</v>
+        <v>21.675</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:40:35</t>
+          <t>14-11-2025 10:41:25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:12:35</t>
+          <t>14-11-2025 11:10:25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:12:35</t>
+          <t>14-11-2025 11:10:25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19-11-2025 10:40:48</t>
+          <t>14-11-2025 11:32:05</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>89787</v>
+        <v>2601</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1564,13 +1547,13 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
         <v>76</v>
       </c>
       <c r="O14" t="n">
-        <v>406232</v>
+        <v>406372</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1580,58 +1563,58 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>0</v>
+        <v>-429</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254599</v>
+        <v>254460</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>44.9</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19-11-2025 10:40:48</t>
+          <t>14-11-2025 11:32:05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19-11-2025 11:14:48</t>
+          <t>14-11-2025 12:14:05</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>19-11-2025 11:14:48</t>
+          <t>14-11-2025 12:14:05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>19-11-2025 11:59:42</t>
+          <t>14-11-2025 13:00:46</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5388</v>
+        <v>5602</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1649,9 +1632,6 @@
       <c r="N15" t="n">
         <v>70</v>
       </c>
-      <c r="O15" t="n">
-        <v>406552</v>
-      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -1660,58 +1640,58 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-3</v>
+        <v>-32.54220486111111</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>253961</v>
+        <v>254519</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>35.91666666666666</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19-11-2025 11:59:42</t>
+          <t>14-11-2025 13:00:46</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19-11-2025 12:14:42</t>
+          <t>14-11-2025 13:27:46</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19-11-2025 12:14:42</t>
+          <t>14-11-2025 13:27:46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19-11-2025 12:50:37</t>
+          <t>14-11-2025 14:44:56</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4310</v>
+        <v>9259</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1724,11 +1704,14 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
         <v>70</v>
       </c>
+      <c r="O16" t="n">
+        <v>406422</v>
+      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -1737,11 +1720,11 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-18.53515625</v>
+        <v>-4</v>
       </c>
       <c r="T16" t="n">
         <v>4</v>
@@ -1749,46 +1732,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>250284</v>
+        <v>254237</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
-        <v>146.35</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19-11-2025 12:50:37</t>
+          <t>14-11-2025 14:44:56</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19-11-2025 13:13:37</t>
+          <t>17-11-2025 07:17:56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19-11-2025 13:13:37</t>
+          <t>17-11-2025 07:17:56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20-11-2025 07:39:58</t>
+          <t>17-11-2025 10:22:01</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17562</v>
+        <v>22091</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1801,35 +1784,39 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" t="n">
         <v>70</v>
       </c>
-      <c r="O17" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-254</v>
+        <v>-7.431961805555556</v>
       </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254165</v>
+        <v>254287</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1842,33 +1829,33 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
-        <v>58.31666666666667</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 10:22:01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>17-11-2025 10:55:01</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>17-11-2025 10:55:01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>17-11-2025 13:04:39</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6998</v>
+        <v>15556</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1877,41 +1864,36 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="n">
+        <v>70</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="n">
+        <v>-24.54490162037037</v>
+      </c>
+      <c r="T18" t="n">
         <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>76</v>
-      </c>
-      <c r="O18" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>40606</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>07-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S18" s="1" t="n">
-        <v>-0.3613310185185185</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>253650</v>
+        <v>254574</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1920,37 +1902,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>273.1333333333333</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14-11-2025 08:40:19</t>
+          <t>17-11-2025 13:04:39</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:19</t>
+          <t>17-11-2025 13:29:39</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:19</t>
+          <t>17-11-2025 13:29:39</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-11-2025 13:40:27</t>
+          <t>18-11-2025 08:23:16</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32776</v>
+        <v>20833</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1959,14 +1941,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1976,19 +1958,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-25.56975694444445</v>
+        <v>-14.34949074074074</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>254107</v>
+        <v>252811</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1997,37 +1979,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E20" t="n">
-        <v>175.0583333333333</v>
+        <v>11.875</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14-11-2025 13:40:27</t>
+          <t>18-11-2025 08:23:16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14-11-2025 14:22:27</t>
+          <t>18-11-2025 08:52:16</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-11-2025 14:22:27</t>
+          <t>18-11-2025 08:52:16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:30</t>
+          <t>18-11-2025 09:04:08</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21007</v>
+        <v>1425</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2040,7 +2022,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>70</v>
@@ -2053,11 +2035,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-36.38715856481482</v>
+        <v>-15.37787615740741</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -2065,7 +2047,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254293</v>
+        <v>254106</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2074,37 +2056,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>18.85</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:30</t>
+          <t>18-11-2025 09:04:08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17-11-2025 09:46:30</t>
+          <t>18-11-2025 09:31:08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>17-11-2025 09:46:30</t>
+          <t>18-11-2025 09:31:08</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>17-11-2025 10:05:21</t>
+          <t>18-11-2025 11:18:47</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2262</v>
+        <v>12917</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2117,14 +2099,11 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>70</v>
       </c>
-      <c r="O21" t="n">
-        <v>40624</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -2133,11 +2112,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-14</v>
+        <v>-42.47137731481482</v>
       </c>
       <c r="T21" t="n">
         <v>7</v>
@@ -2145,7 +2124,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254188</v>
+        <v>253650</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2154,37 +2133,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
-        <v>37.44166666666667</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:05:21</t>
+          <t>18-11-2025 11:18:47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:34:21</t>
+          <t>18-11-2025 12:00:47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>17-11-2025 10:34:21</t>
+          <t>18-11-2025 12:00:47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17-11-2025 11:11:48</t>
+          <t>19-11-2025 08:33:55</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4493</v>
+        <v>32776</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2193,17 +2172,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>70</v>
-      </c>
-      <c r="O22" t="n">
-        <v>406372</v>
+        <v>76</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2213,58 +2189,58 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-1</v>
+        <v>-30.35688657407407</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>253838</v>
+        <v>254385</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>108.3666666666667</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17-11-2025 11:11:48</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17-11-2025 11:38:48</t>
+          <t>14-11-2025 07:34:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17-11-2025 11:38:48</t>
+          <t>14-11-2025 07:34:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-11-2025 13:27:10</t>
+          <t>14-11-2025 08:26:05</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>13004</v>
+        <v>6250</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2273,20 +2249,25 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O23" t="n">
+        <v>40627</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>40627</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2294,54 +2275,54 @@
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-21.56053240740741</v>
+        <v>-0.3514467592592593</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254758</v>
+        <v>254165</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>61.38333333333333</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17-11-2025 13:27:10</t>
+          <t>14-11-2025 08:26:05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17-11-2025 13:54:10</t>
+          <t>14-11-2025 08:58:05</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-11-2025 13:54:10</t>
+          <t>14-11-2025 08:58:05</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:33</t>
+          <t>14-11-2025 09:56:24</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7366</v>
+        <v>6998</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2350,36 +2331,41 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O24" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.6219097222222222</v>
+        <v>-0.4141666666666667</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254556</v>
+        <v>254117</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2388,37 +2374,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>173.4166666666667</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 09:56:24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>14-11-2025 10:13:24</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>14-11-2025 10:13:24</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>14-11-2025 10:22:34</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>20810</v>
+        <v>1100</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2427,41 +2413,36 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
         <v>76</v>
       </c>
-      <c r="O25" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P25" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-1.42806712962963</v>
+        <v>-35.43233796296296</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254230</v>
+        <v>254512</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2470,37 +2451,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>62.475</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>14-11-2025 10:22:34</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:25</t>
+          <t>14-11-2025 10:39:34</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:25</t>
+          <t>14-11-2025 10:39:34</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14-11-2025 11:54:53</t>
+          <t>14-11-2025 11:39:07</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7497</v>
+        <v>7147</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2509,17 +2490,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O26" t="n">
-        <v>406422</v>
+        <v>406232</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2529,19 +2510,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254433</v>
+        <v>254824</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2550,37 +2531,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>67.84999999999999</v>
+        <v>748.225</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14-11-2025 11:54:53</t>
+          <t>14-11-2025 11:39:07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:53</t>
+          <t>14-11-2025 11:58:07</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:53</t>
+          <t>14-11-2025 11:58:07</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14-11-2025 13:17:44</t>
+          <t>18-11-2025 08:26:21</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>8142</v>
+        <v>89787</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2589,17 +2570,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O27" t="n">
-        <v>406422</v>
+        <v>406232</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2609,19 +2590,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254106</v>
+        <v>254555</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2630,37 +2611,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>107.6416666666667</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>14-11-2025 13:17:44</t>
+          <t>18-11-2025 08:26:21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14-11-2025 13:36:44</t>
+          <t>18-11-2025 08:45:21</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14-11-2025 13:36:44</t>
+          <t>18-11-2025 08:45:21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:23</t>
+          <t>18-11-2025 11:38:20</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>12917</v>
+        <v>20758</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2669,14 +2650,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O28" t="n">
+        <v>406232</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2686,19 +2670,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-41.30859953703704</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>254460</v>
+        <v>244023</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2707,37 +2691,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>46.68333333333333</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>17-11-2025 07:24:23</t>
+          <t>18-11-2025 11:38:20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:23</t>
+          <t>18-11-2025 12:12:20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17-11-2025 07:45:23</t>
+          <t>18-11-2025 12:12:20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:04</t>
+          <t>18-11-2025 12:20:38</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5602</v>
+        <v>997</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2750,11 +2734,14 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
+      <c r="O29" t="n">
+        <v>406062</v>
+      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2763,11 +2750,11 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-35.35560185185185</v>
+        <v>-417</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -2775,7 +2762,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254198</v>
+        <v>254457</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2784,37 +2771,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>215</v>
+        <v>3.925</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:04</t>
+          <t>18-11-2025 12:20:38</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:04</t>
+          <t>18-11-2025 12:39:38</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:04</t>
+          <t>18-11-2025 12:39:38</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:04</t>
+          <t>18-11-2025 12:43:34</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25800</v>
+        <v>471</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2823,14 +2810,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>152</v>
+        <v>70</v>
+      </c>
+      <c r="O30" t="n">
+        <v>406372</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2840,19 +2830,19 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-28.52851851851852</v>
+        <v>-1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>253885</v>
+        <v>254245</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2861,37 +2851,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E31" t="n">
-        <v>105.9333333333333</v>
+        <v>89.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17-11-2025 12:41:04</t>
+          <t>18-11-2025 12:43:34</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:04</t>
+          <t>18-11-2025 13:04:34</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:04</t>
+          <t>18-11-2025 13:04:34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17-11-2025 14:59:00</t>
+          <t>18-11-2025 14:34:22</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>12712</v>
+        <v>10776</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2904,11 +2894,14 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
+      <c r="O31" t="n">
+        <v>406372</v>
+      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -2917,19 +2910,19 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-13.62430555555556</v>
+        <v>-20</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254451</v>
+        <v>253961</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2938,37 +2931,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>321.1416666666667</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>17-11-2025 14:59:00</t>
+          <t>18-11-2025 14:34:22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18-11-2025 07:18:00</t>
+          <t>18-11-2025 14:49:22</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18-11-2025 07:18:00</t>
+          <t>18-11-2025 14:49:22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18-11-2025 12:39:08</t>
+          <t>19-11-2025 07:25:17</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>38537</v>
+        <v>4310</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2981,7 +2974,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -2994,58 +2987,58 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-10.52718171296296</v>
+        <v>-18.30922453703704</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254481</v>
+        <v>254599</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>32.5</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>81.16666666666667</v>
+        <v>44.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>19-11-2025 07:25:17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>19-11-2025 07:40:17</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>19-11-2025 07:40:17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>19-11-2025 08:25:11</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>9740</v>
+        <v>5388</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3058,76 +3051,74 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
       <c r="O33" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406552</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254762</v>
+        <v>254166</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>34.5</v>
+        <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>31.85833333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>19-11-2025 08:25:11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>19-11-2025 08:42:11</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>19-11-2025 08:42:11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>19-11-2025 09:21:02</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3823</v>
+        <v>4662</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3145,71 +3136,66 @@
       <c r="N34" t="n">
         <v>70</v>
       </c>
-      <c r="O34" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P34" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>253865</v>
+        <v>254546</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>34.5</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>116.7583333333333</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>19-11-2025 09:21:02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:31</t>
+          <t>19-11-2025 09:38:02</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:31</t>
+          <t>19-11-2025 09:38:02</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:17</t>
+          <t>19-11-2025 11:27:26</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>14011</v>
+        <v>13129</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3222,11 +3208,14 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
       </c>
+      <c r="O35" t="n">
+        <v>406242</v>
+      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
@@ -3235,19 +3224,19 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-38.33299189814815</v>
+        <v>-7</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254245</v>
+        <v>254481</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3256,37 +3245,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>89.8</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:17</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:47</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:47</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:35</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>10776</v>
+        <v>9740</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3299,32 +3288,37 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36" t="n">
         <v>70</v>
       </c>
-      <c r="P36" t="n">
-        <v>0</v>
+      <c r="O36" t="n">
+        <v>40642</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>40642</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-28.4179224537037</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254356</v>
+        <v>253380</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3333,37 +3327,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>30.5</v>
+        <v>38.5</v>
       </c>
       <c r="E37" t="n">
-        <v>179.6</v>
+        <v>104.275</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:35</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:05</t>
+          <t>13-11-2025 14:32:10</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14-11-2025 12:04:05</t>
+          <t>13-11-2025 14:32:10</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:41</t>
+          <t>14-11-2025 08:16:26</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>21552</v>
+        <v>12513</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3372,36 +3366,41 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
+      <c r="O37" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-19.56382523148148</v>
+        <v>-0.3447511574074074</v>
       </c>
       <c r="T37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254381</v>
+        <v>255043</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3410,37 +3409,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>32.5</v>
+        <v>44.5</v>
       </c>
       <c r="E38" t="n">
-        <v>83.86666666666666</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:41</t>
+          <t>14-11-2025 08:16:26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:11</t>
+          <t>14-11-2025 09:00:56</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17-11-2025 07:36:11</t>
+          <t>14-11-2025 09:00:56</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:03</t>
+          <t>14-11-2025 12:05:13</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10064</v>
+        <v>22114</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3449,15 +3448,18 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
       </c>
+      <c r="O38" t="n">
+        <v>406422</v>
+      </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
@@ -3466,19 +3468,19 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-21.31130208333333</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>254652</v>
+        <v>254189</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3487,37 +3489,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="E39" t="n">
-        <v>28.73333333333333</v>
+        <v>55.875</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>17-11-2025 09:00:03</t>
+          <t>14-11-2025 12:05:13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17-11-2025 09:32:33</t>
+          <t>14-11-2025 12:35:43</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>17-11-2025 09:32:33</t>
+          <t>14-11-2025 12:35:43</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:17</t>
+          <t>14-11-2025 13:31:36</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>3448</v>
+        <v>6705</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3526,15 +3528,18 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
+      <c r="O39" t="n">
+        <v>406422</v>
+      </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
@@ -3543,19 +3548,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-7.353825231481482</v>
+        <v>-3</v>
       </c>
       <c r="T39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254756</v>
+        <v>254230</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3564,37 +3569,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.5</v>
+        <v>30.5</v>
       </c>
       <c r="E40" t="n">
-        <v>60.625</v>
+        <v>62.475</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>17-11-2025 10:01:17</t>
+          <t>14-11-2025 13:31:36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17-11-2025 10:41:47</t>
+          <t>14-11-2025 14:02:06</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>17-11-2025 10:41:47</t>
+          <t>14-11-2025 14:02:06</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17-11-2025 11:42:24</t>
+          <t>17-11-2025 07:04:34</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>7275</v>
+        <v>7497</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3603,15 +3608,18 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
+      <c r="O40" t="n">
+        <v>406422</v>
+      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
@@ -3620,58 +3628,58 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-4.424050925925926</v>
+        <v>-15</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>253694</v>
+        <v>254433</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>30.5</v>
       </c>
       <c r="E41" t="n">
-        <v>121.7583333333333</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>17-11-2025 07:04:34</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>17-11-2025 07:35:04</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>17-11-2025 07:35:04</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>17-11-2025 08:42:55</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>14611</v>
+        <v>8142</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3680,80 +3688,78 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O41" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-0.6158043981481481</v>
+        <v>-3</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>253380</v>
+        <v>254276</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>34.5</v>
       </c>
       <c r="E42" t="n">
-        <v>104.275</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>17-11-2025 08:42:55</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:45</t>
+          <t>17-11-2025 09:17:25</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14-11-2025 07:46:45</t>
+          <t>17-11-2025 09:17:25</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:02</t>
+          <t>17-11-2025 09:54:27</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>12513</v>
+        <v>4444</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3762,80 +3768,78 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
         <v>70</v>
       </c>
       <c r="O42" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-0.3965509259259259</v>
+        <v>-18</v>
       </c>
       <c r="T42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>252061</v>
+        <v>254451</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>45</v>
+        <v>32.5</v>
       </c>
       <c r="E43" t="n">
-        <v>36.16666666666666</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:02</t>
+          <t>17-11-2025 09:54:27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:02</t>
+          <t>17-11-2025 10:26:57</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:02</t>
+          <t>17-11-2025 10:26:57</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:12</t>
+          <t>18-11-2025 07:48:06</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>4340</v>
+        <v>38537</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3848,76 +3852,71 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
         <v>70</v>
       </c>
-      <c r="O43" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P43" t="n">
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>0</v>
+        <v>-10.32506944444444</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254546</v>
+        <v>254521</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30</v>
+        <v>34.5</v>
       </c>
       <c r="E44" t="n">
-        <v>109.4083333333333</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>14-11-2025 10:52:12</t>
+          <t>18-11-2025 07:48:06</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14-11-2025 11:22:12</t>
+          <t>18-11-2025 08:22:36</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>14-11-2025 11:22:12</t>
+          <t>18-11-2025 08:22:36</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>14-11-2025 13:11:36</t>
+          <t>18-11-2025 09:02:17</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>13129</v>
+        <v>4762</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3930,14 +3929,11 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
         <v>70</v>
       </c>
-      <c r="O44" t="n">
-        <v>406242</v>
-      </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
@@ -3946,11 +3942,11 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-7</v>
+        <v>-13.37658564814815</v>
       </c>
       <c r="T44" t="n">
         <v>7</v>
@@ -3958,46 +3954,46 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>235572</v>
+        <v>254653</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="E45" t="n">
-        <v>82.98333333333333</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>14-11-2025 13:11:36</t>
+          <t>18-11-2025 09:02:17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:36</t>
+          <t>18-11-2025 09:34:47</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14-11-2025 13:41:36</t>
+          <t>18-11-2025 09:34:47</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:35</t>
+          <t>18-11-2025 10:39:11</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>9958</v>
+        <v>7729</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4010,14 +4006,11 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
         <v>70</v>
       </c>
-      <c r="O45" t="n">
-        <v>406372</v>
-      </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
@@ -4026,58 +4019,58 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-744</v>
+        <v>-4.443883101851852</v>
       </c>
       <c r="T45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254457</v>
+        <v>253885</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="E46" t="n">
-        <v>3.925</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:35</t>
+          <t>18-11-2025 10:39:11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:35</t>
+          <t>18-11-2025 11:11:41</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:35</t>
+          <t>18-11-2025 11:11:41</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17-11-2025 07:38:31</t>
+          <t>18-11-2025 12:57:37</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>471</v>
+        <v>12712</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4090,14 +4083,11 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
-      <c r="O46" t="n">
-        <v>406372</v>
-      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
@@ -4106,19 +4096,19 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-1</v>
+        <v>-14.54001736111111</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254605</v>
+        <v>253694</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4127,37 +4117,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>39.025</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17-11-2025 07:38:31</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>17-11-2025 08:08:31</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17-11-2025 08:08:31</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17-11-2025 08:47:32</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>4683</v>
+        <v>14611</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4166,36 +4156,41 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>70</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O47" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-3.36634837962963</v>
+        <v>-0.6158043981481481</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254437</v>
+        <v>254129</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4204,37 +4199,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>58.05833333333333</v>
+        <v>44.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>17-11-2025 08:47:32</t>
+          <t>13-11-2025 14:46:45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:32</t>
+          <t>14-11-2025 07:26:45</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:32</t>
+          <t>14-11-2025 07:26:45</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>17-11-2025 10:15:36</t>
+          <t>14-11-2025 08:11:15</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>6967</v>
+        <v>5340</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4243,34 +4238,36 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
         <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O48" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-1</v>
+        <v>-1.34115162037037</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4288,29 +4285,29 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E49" t="n">
         <v>104.2583333333333</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>17-11-2025 10:15:36</t>
+          <t>14-11-2025 08:11:15</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:36</t>
+          <t>14-11-2025 09:31:15</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:36</t>
+          <t>14-11-2025 09:31:15</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:51</t>
+          <t>14-11-2025 11:15:31</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -4352,7 +4349,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254941</v>
+        <v>254714</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4365,10 +4362,10 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
-        <v>35.5</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4377,21 +4374,21 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:32:00</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>14-11-2025 08:50:28</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4260</v>
+        <v>10977</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4400,14 +4397,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="O50" t="n">
         <v>40623</v>
@@ -4422,19 +4419,19 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-1.338541666666667</v>
+        <v>-1.368385416666667</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>253897</v>
+        <v>254156</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4443,37 +4440,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E51" t="n">
-        <v>94.01666666666667</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:30</t>
+          <t>14-11-2025 08:50:28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>14-11-2025 09:07:28</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:51:30</t>
+          <t>14-11-2025 09:07:28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>14-11-2025 10:34:57</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>11282</v>
+        <v>10497</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4482,11 +4479,11 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>76</v>
@@ -4504,19 +4501,19 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.434386574074074</v>
+        <v>-0.4409375</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254117</v>
+        <v>254675</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4525,37 +4522,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E52" t="n">
-        <v>9.166666666666666</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:25:31</t>
+          <t>14-11-2025 10:34:57</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:56:31</t>
+          <t>14-11-2025 10:51:57</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:56:31</t>
+          <t>14-11-2025 10:51:57</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14-11-2025 11:05:41</t>
+          <t>14-11-2025 13:25:54</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1100</v>
+        <v>18475</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4564,7 +4561,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -4573,6 +4570,9 @@
       <c r="N52" t="n">
         <v>76</v>
       </c>
+      <c r="O52" t="n">
+        <v>406422</v>
+      </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
@@ -4581,11 +4581,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-35.46228009259259</v>
+        <v>-4</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254512</v>
+        <v>254283</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4606,33 +4606,33 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>59.55833333333333</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14-11-2025 11:05:41</t>
+          <t>14-11-2025 13:25:54</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14-11-2025 11:22:41</t>
+          <t>14-11-2025 13:44:54</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14-11-2025 11:22:41</t>
+          <t>14-11-2025 13:44:54</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14-11-2025 12:22:14</t>
+          <t>17-11-2025 07:20:40</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>7147</v>
+        <v>11492</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
         <v>76</v>
       </c>
       <c r="O53" t="n">
-        <v>406232</v>
+        <v>406372</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4661,19 +4661,19 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>253382</v>
+        <v>254910</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4682,37 +4682,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>85.09999999999999</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>14-11-2025 12:22:14</t>
+          <t>17-11-2025 07:20:40</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14-11-2025 12:39:14</t>
+          <t>17-11-2025 07:37:40</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14-11-2025 12:39:14</t>
+          <t>17-11-2025 07:37:40</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14-11-2025 14:04:20</t>
+          <t>17-11-2025 08:51:12</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>10212</v>
+        <v>8824</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>76</v>
@@ -4741,19 +4741,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254910</v>
+        <v>253614</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4766,33 +4766,33 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E55" t="n">
-        <v>73.53333333333333</v>
+        <v>122.45</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:04:20</t>
+          <t>17-11-2025 08:51:12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:21:20</t>
+          <t>17-11-2025 09:23:12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:21:20</t>
+          <t>17-11-2025 09:23:12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:52</t>
+          <t>17-11-2025 11:25:39</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>8824</v>
+        <v>14694</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4801,17 +4801,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>76</v>
-      </c>
-      <c r="O55" t="n">
-        <v>406372</v>
+        <v>152</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4821,11 +4818,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>0</v>
+        <v>-7.47615162037037</v>
       </c>
       <c r="T55" t="n">
         <v>7</v>
@@ -4833,11 +4830,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254283</v>
+        <v>254713</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4846,33 +4843,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E56" t="n">
-        <v>95.76666666666667</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17-11-2025 07:34:52</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17-11-2025 07:51:52</t>
+          <t>14-11-2025 07:45:00</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>17-11-2025 07:51:52</t>
+          <t>14-11-2025 07:45:00</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>17-11-2025 09:27:38</t>
+          <t>14-11-2025 08:34:58</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>11492</v>
+        <v>5996</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4885,27 +4882,29 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
         <v>76</v>
       </c>
       <c r="O56" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-8</v>
+        <v>-1.357615740740741</v>
       </c>
       <c r="T56" t="n">
         <v>2</v>
@@ -4913,46 +4912,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254555</v>
+        <v>254198</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E57" t="n">
-        <v>172.9833333333333</v>
+        <v>215</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17-11-2025 09:27:38</t>
+          <t>14-11-2025 08:34:58</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17-11-2025 09:44:38</t>
+          <t>14-11-2025 09:14:58</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>17-11-2025 09:44:38</t>
+          <t>14-11-2025 09:14:58</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>17-11-2025 12:37:37</t>
+          <t>14-11-2025 12:49:58</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>20758</v>
+        <v>25800</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4961,17 +4960,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>76</v>
-      </c>
-      <c r="O57" t="n">
-        <v>406232</v>
+        <v>152</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4981,11 +4977,11 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>0</v>
+        <v>-25.53469907407407</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -4993,46 +4989,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254309</v>
+        <v>254256</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E58" t="n">
-        <v>900.0166666666667</v>
+        <v>50.925</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17-11-2025 12:37:37</t>
+          <t>14-11-2025 12:49:58</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:37</t>
+          <t>14-11-2025 13:24:58</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>17-11-2025 13:13:37</t>
+          <t>14-11-2025 13:24:58</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>19-11-2025 12:13:38</t>
+          <t>14-11-2025 14:15:53</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>108002</v>
+        <v>6111</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5041,36 +5037,39 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>70</v>
+      </c>
+      <c r="O58" t="n">
+        <v>406422</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>03-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S58" s="1" t="n">
+        <v>-18</v>
+      </c>
+      <c r="T58" t="n">
         <v>4</v>
-      </c>
-      <c r="N58" t="n">
-        <v>152</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S58" s="1" t="n">
-        <v>-19.50947337962963</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254714</v>
+        <v>254375</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5079,37 +5078,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E59" t="n">
-        <v>91.47499999999999</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 14:15:53</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>14-11-2025 14:45:53</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>14-11-2025 14:45:53</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>17-11-2025 07:31:11</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>10977</v>
+        <v>5435</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5118,33 +5117,31 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O59" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-1.389913194444444</v>
+        <v>-12</v>
       </c>
       <c r="T59" t="n">
         <v>2</v>
@@ -5152,7 +5149,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>254291</v>
+        <v>255039</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5161,37 +5158,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E60" t="n">
-        <v>18.85</v>
+        <v>9.15</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>17-11-2025 07:31:11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>17-11-2025 08:01:11</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>17-11-2025 08:01:11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14-11-2025 10:15:19</t>
+          <t>17-11-2025 08:10:20</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2262</v>
+        <v>1098</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5204,7 +5201,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N60" t="n">
         <v>70</v>
@@ -5220,11 +5217,11 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>7</v>
@@ -5232,7 +5229,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254429</v>
+        <v>254381</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5241,37 +5238,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>240.2416666666667</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14-11-2025 10:15:19</t>
+          <t>17-11-2025 08:10:20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14-11-2025 10:45:19</t>
+          <t>17-11-2025 08:45:20</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14-11-2025 10:45:19</t>
+          <t>17-11-2025 08:45:20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>14-11-2025 14:45:34</t>
+          <t>17-11-2025 10:09:12</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>28829</v>
+        <v>10064</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5280,17 +5277,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
         <v>70</v>
       </c>
       <c r="O61" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5300,19 +5297,19 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254653</v>
+        <v>254188</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5321,37 +5318,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>64.40833333333333</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>14-11-2025 14:45:34</t>
+          <t>17-11-2025 10:09:12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17-11-2025 07:15:34</t>
+          <t>17-11-2025 10:39:12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17-11-2025 07:15:34</t>
+          <t>17-11-2025 10:39:12</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>17-11-2025 08:19:58</t>
+          <t>17-11-2025 11:16:38</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>7729</v>
+        <v>4493</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5369,6 +5366,9 @@
       <c r="N62" t="n">
         <v>70</v>
       </c>
+      <c r="O62" t="n">
+        <v>406372</v>
+      </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
@@ -5377,19 +5377,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-3.347204861111111</v>
+        <v>-1</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254893</v>
+        <v>254437</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5402,33 +5402,33 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E63" t="n">
-        <v>46.675</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17-11-2025 08:19:58</t>
+          <t>17-11-2025 11:16:38</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17-11-2025 08:49:58</t>
+          <t>17-11-2025 11:41:38</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17-11-2025 08:49:58</t>
+          <t>17-11-2025 11:41:38</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:39</t>
+          <t>17-11-2025 12:39:42</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>5601</v>
+        <v>6967</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
@@ -5457,11 +5457,11 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254189</v>
+        <v>253838</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5478,37 +5478,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>55.875</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:39</t>
+          <t>17-11-2025 12:39:42</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17-11-2025 10:06:39</t>
+          <t>17-11-2025 13:09:42</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17-11-2025 10:06:39</t>
+          <t>17-11-2025 13:09:42</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>17-11-2025 11:02:31</t>
+          <t>17-11-2025 14:58:04</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>6705</v>
+        <v>13004</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5517,18 +5517,15 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
       </c>
-      <c r="O64" t="n">
-        <v>406372</v>
-      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -5537,19 +5534,19 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-1</v>
+        <v>-21.62365740740741</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>255043</v>
+        <v>250284</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5558,37 +5555,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E65" t="n">
-        <v>184.2833333333333</v>
+        <v>146.35</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:02:31</t>
+          <t>17-11-2025 14:58:04</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:27:31</t>
+          <t>18-11-2025 07:38:04</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>17-11-2025 11:27:31</t>
+          <t>18-11-2025 07:38:04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>17-11-2025 14:31:48</t>
+          <t>18-11-2025 10:04:25</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>22114</v>
+        <v>17562</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5597,18 +5594,15 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N65" t="n">
         <v>70</v>
       </c>
-      <c r="O65" t="n">
-        <v>406372</v>
-      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -5617,19 +5611,19 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>0</v>
+        <v>-261.4197337962963</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254521</v>
+        <v>254756</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -5638,37 +5632,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>39.68333333333333</v>
+        <v>60.625</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>17-11-2025 14:31:48</t>
+          <t>18-11-2025 10:04:25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:01:48</t>
+          <t>18-11-2025 10:34:25</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:01:48</t>
+          <t>18-11-2025 10:34:25</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18-11-2025 07:41:29</t>
+          <t>18-11-2025 11:35:02</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>4762</v>
+        <v>7275</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5681,7 +5675,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N66" t="n">
         <v>70</v>
@@ -5694,11 +5688,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-13.32048032407407</v>
+        <v>-4.482667824074074</v>
       </c>
       <c r="T66" t="n">
         <v>7</v>
@@ -5706,7 +5700,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>252811</v>
+        <v>254365</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -5715,37 +5709,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E67" t="n">
-        <v>11.875</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18-11-2025 07:41:29</t>
+          <t>18-11-2025 11:35:02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:16:29</t>
+          <t>18-11-2025 12:20:02</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:16:29</t>
+          <t>18-11-2025 12:20:02</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18-11-2025 08:28:22</t>
+          <t>18-11-2025 13:27:34</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1425</v>
+        <v>8104</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5771,19 +5765,19 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-15.35303240740741</v>
+        <v>-14.56081597222222</v>
       </c>
       <c r="T67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254651</v>
+        <v>254652</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -5792,37 +5786,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E68" t="n">
-        <v>22.64166666666667</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>18-11-2025 08:28:22</t>
+          <t>18-11-2025 13:27:34</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:03:22</t>
+          <t>18-11-2025 13:57:34</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:03:22</t>
+          <t>18-11-2025 13:57:34</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18-11-2025 09:26:00</t>
+          <t>18-11-2025 14:26:18</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>2717</v>
+        <v>3448</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5835,7 +5829,7 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N68" t="n">
         <v>70</v>
@@ -5852,7 +5846,7 @@
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>-7.393061342592593</v>
+        <v>-7.601603009259259</v>
       </c>
       <c r="T68" t="n">
         <v>8</v>
@@ -5860,7 +5854,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254276</v>
+        <v>254429</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -5869,37 +5863,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>30</v>
       </c>
       <c r="E69" t="n">
-        <v>37.03333333333333</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18-11-2025 09:26:00</t>
+          <t>18-11-2025 14:26:18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18-11-2025 09:56:00</t>
+          <t>18-11-2025 14:56:18</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>18-11-2025 09:56:00</t>
+          <t>18-11-2025 14:56:18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>18-11-2025 10:33:02</t>
+          <t>19-11-2025 10:56:33</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>4444</v>
+        <v>28829</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5912,13 +5906,13 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
       <c r="O69" t="n">
-        <v>406422</v>
+        <v>406552</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -5928,58 +5922,58 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="T69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254915</v>
+        <v>254715</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>48.875</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18-11-2025 10:33:02</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:08:02</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:08:02</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>18-11-2025 11:56:55</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>5865</v>
+        <v>16145</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5988,36 +5982,41 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
+        <v>4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>76</v>
+      </c>
+      <c r="O70" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>40623</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>19-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S70" s="1" t="n">
+        <v>-1.409403935185185</v>
+      </c>
+      <c r="T70" t="n">
         <v>2</v>
-      </c>
-      <c r="N70" t="n">
-        <v>70</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>12-01-2026 00:00:00</t>
-        </is>
-      </c>
-      <c r="S70" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254715</v>
+        <v>253382</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6026,37 +6025,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E71" t="n">
-        <v>134.5416666666667</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 09:49:32</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 10:19:32</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 10:19:32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 11:44:38</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>16145</v>
+        <v>10212</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6069,29 +6068,27 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>76</v>
       </c>
       <c r="O71" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-1.409403935185185</v>
+        <v>-12</v>
       </c>
       <c r="T71" t="n">
         <v>2</v>
@@ -6099,7 +6096,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254287</v>
+        <v>254293</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6108,37 +6105,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E72" t="n">
-        <v>129.6333333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 11:44:38</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>14-11-2025 12:29:38</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:32</t>
+          <t>14-11-2025 12:29:38</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>14-11-2025 12:48:29</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>15556</v>
+        <v>2262</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6151,13 +6148,13 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N72" t="n">
         <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>406422</v>
+        <v>40624</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6167,19 +6164,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254427</v>
+        <v>254291</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6188,72 +6185,70 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>55.55833333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:10</t>
+          <t>14-11-2025 12:48:29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>14-11-2025 13:13:29</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:14:10</t>
+          <t>14-11-2025 13:13:29</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>14-11-2025 13:32:20</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>6667</v>
+        <v>2262</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
       <c r="O73" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-4.590092592592592</v>
+        <v>-14</v>
       </c>
       <c r="T73" t="n">
         <v>7</v>
@@ -6261,7 +6256,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254574</v>
+        <v>254356</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6270,37 +6265,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E74" t="n">
-        <v>173.6083333333333</v>
+        <v>179.6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:44</t>
+          <t>14-11-2025 13:32:20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>14-11-2025 14:07:20</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:49:44</t>
+          <t>14-11-2025 14:07:20</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>17-11-2025 09:06:56</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>20833</v>
+        <v>21552</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6313,14 +6308,11 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
-      <c r="O74" t="n">
-        <v>406422</v>
-      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
@@ -6329,14 +6321,14 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-7</v>
+        <v>-19.37982060185185</v>
       </c>
       <c r="T74" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -6354,29 +6346,29 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E75" t="n">
         <v>46.39166666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:43:20</t>
+          <t>17-11-2025 09:06:56</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:20</t>
+          <t>17-11-2025 09:36:56</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:20</t>
+          <t>17-11-2025 09:36:56</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>17-11-2025 11:04:44</t>
+          <t>17-11-2025 10:23:20</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -6421,7 +6413,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254586</v>
+        <v>254893</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6437,30 +6429,30 @@
         <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>51.54166666666666</v>
+        <v>46.675</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:04:44</t>
+          <t>17-11-2025 10:23:20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:29:44</t>
+          <t>17-11-2025 10:48:20</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:29:44</t>
+          <t>17-11-2025 10:48:20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:16</t>
+          <t>17-11-2025 11:35:00</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>6185</v>
+        <v>5601</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6489,7 +6481,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -6501,7 +6493,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254166</v>
+        <v>254586</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6510,37 +6502,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>25</v>
       </c>
       <c r="E77" t="n">
-        <v>38.85</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:16</t>
+          <t>17-11-2025 11:35:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:16</t>
+          <t>17-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:16</t>
+          <t>17-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>17-11-2025 13:25:07</t>
+          <t>17-11-2025 12:51:33</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>4662</v>
+        <v>6185</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6569,19 +6561,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254365</v>
+        <v>254915</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6590,37 +6582,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>67.53333333333333</v>
+        <v>48.875</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17-11-2025 13:25:07</t>
+          <t>17-11-2025 12:51:33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:07</t>
+          <t>17-11-2025 13:21:33</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:07</t>
+          <t>17-11-2025 13:21:33</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:39</t>
+          <t>17-11-2025 14:10:25</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>8104</v>
+        <v>5865</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6629,11 +6621,11 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
@@ -6646,19 +6638,19 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-14.2969849537037</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>253614</v>
+        <v>254651</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6667,37 +6659,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>122.45</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:07:39</t>
+          <t>17-11-2025 14:10:25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:47:39</t>
+          <t>17-11-2025 14:40:25</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:47:39</t>
+          <t>17-11-2025 14:40:25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 09:50:06</t>
+          <t>18-11-2025 07:03:04</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>14694</v>
+        <v>2717</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6706,14 +6698,14 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6723,23 +6715,23 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-8.409797453703703</v>
+        <v>-7.293796296296296</v>
       </c>
       <c r="T79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254903</v>
+        <v>254609</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6748,49 +6740,52 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>256.6416666666667</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18-11-2025 09:50:06</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18-11-2025 10:30:06</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18-11-2025 10:30:06</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18-11-2025 14:46:45</t>
+          <t>12-11-2025 13:56:40</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>30797</v>
+        <v>50000</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>40655</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -6800,74 +6795,74 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>254339</v>
+        <v>252980</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>245.9666666666667</v>
+        <v>17.075</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>18-11-2025 14:46:45</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>19-11-2025 07:21:45</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>19-11-2025 07:21:45</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>19-11-2025 11:27:43</t>
+          <t>14-11-2025 07:17:04</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>29516</v>
+        <v>2049</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -6877,1100 +6872,14 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-30.47758101851852</v>
+        <v>-77.30352430555556</v>
       </c>
       <c r="T81" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>254101</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>30</v>
-      </c>
-      <c r="E82" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:27:43</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:57:43</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>19-11-2025 11:57:43</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:26:08</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>6</v>
-      </c>
-      <c r="N82" t="n">
-        <v>70</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S82" s="1" t="n">
-        <v>-26.51815393518519</v>
-      </c>
-      <c r="T82" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>254100</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>25</v>
-      </c>
-      <c r="E83" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:26:08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:51:08</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>19-11-2025 12:51:08</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:19:34</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>6</v>
-      </c>
-      <c r="N83" t="n">
-        <v>70</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S83" s="1" t="n">
-        <v>-26.55525462962963</v>
-      </c>
-      <c r="T83" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>254252</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>35</v>
-      </c>
-      <c r="E84" t="n">
-        <v>80.51666666666667</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:19:34</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:54:34</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>19-11-2025 13:54:34</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:15:05</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>9662</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>4</v>
-      </c>
-      <c r="N84" t="n">
-        <v>70</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>03-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S84" s="1" t="n">
-        <v>-27.30214120370371</v>
-      </c>
-      <c r="T84" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>253974</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>35</v>
-      </c>
-      <c r="E85" t="n">
-        <v>28.425</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:15:05</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:50:05</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>20-11-2025 07:50:05</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:18:30</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>3411</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>6</v>
-      </c>
-      <c r="N85" t="n">
-        <v>70</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>29-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S85" s="1" t="n">
-        <v>-32.3461863425926</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>254419</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>35</v>
-      </c>
-      <c r="E86" t="n">
-        <v>72.34166666666667</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:18:30</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:53:30</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>20-11-2025 08:53:30</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>8681</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>4</v>
-      </c>
-      <c r="N86" t="n">
-        <v>70</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S86" s="1" t="n">
-        <v>-20.42072916666667</v>
-      </c>
-      <c r="T86" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>254354</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>30</v>
-      </c>
-      <c r="E87" t="n">
-        <v>18.675</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:05:51</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:35:51</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:35:51</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:54:31</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>2241</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>70</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>14-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S87" s="1" t="n">
-        <v>-16.45453125</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>254547</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>19-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>30</v>
-      </c>
-      <c r="E88" t="n">
-        <v>68.55</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>20-11-2025 10:54:31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>20-11-2025 11:24:31</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>20-11-2025 11:24:31</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>20-11-2025 12:33:04</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>8226</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>4</v>
-      </c>
-      <c r="N88" t="n">
-        <v>70</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>19-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S88" s="1" t="n">
-        <v>-11.52296875</v>
-      </c>
-      <c r="T88" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>253906</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>35</v>
-      </c>
-      <c r="E89" t="n">
-        <v>45.79166666666666</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>20-11-2025 12:33:04</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:08:04</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:08:04</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20-11-2025 13:53:52</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>5495</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M89" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" t="n">
-        <v>70</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>25-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S89" s="1" t="n">
-        <v>-5.579074074074074</v>
-      </c>
-      <c r="T89" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>254609</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>416.6666666666667</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>12-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>12-11-2025 13:56:40</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>T1 ;T2 ;T8</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>40655</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>20-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S90" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>252980</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>11-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>17.075</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:00:00</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>14-11-2025 07:17:04</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>2049</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>08-09-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S91" s="1" t="n">
-        <v>-77.30352430555556</v>
-      </c>
-      <c r="T91" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>254428</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>48.30833333333333</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:48:18</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>5797</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>T1 ;T2 ;T8</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>70</v>
-      </c>
-      <c r="O92" t="n">
-        <v>40649</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>40649</v>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S92" s="1" t="n">
-        <v>-7.616880787037037</v>
-      </c>
-      <c r="T92" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>254173</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>15-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>202.5916666666667</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>17-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>18-11-2025 09:22:35</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>24311</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>foglio</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>20-10-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S93" s="1" t="n">
-        <v>-39.39068865740741</v>
-      </c>
-      <c r="T93" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>254967</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>BIMEC 5</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>19</v>
-      </c>
-      <c r="E94" t="n">
-        <v>260.4166666666667</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:19:00</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>20-11-2025 14:19:00</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>21-11-2025 10:39:25</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>31250</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
-        </is>
-      </c>
-      <c r="M94" t="n">
-        <v>4</v>
-      </c>
-      <c r="N94" t="n">
-        <v>70</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>05-12-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>254671</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>CASON</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E95" t="n">
-        <v>136.1666666666667</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:00:00</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:34:30</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>18-11-2025 14:34:30</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>19-11-2025 08:50:40</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>16340</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>bobina</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>CASON ;H7 ;R5</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
-        <v>7</v>
-      </c>
-      <c r="N95" t="n">
-        <v>70</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>21-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S95" s="1" t="n">
-        <v>-8.368518518518519</v>
-      </c>
-      <c r="T95" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254762</v>
+        <v>254715</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>31.85833333333333</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -568,21 +568,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:34:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:34:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:05:51</t>
+          <t>13-11-2025 14:46:32</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3823</v>
+        <v>16145</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,14 +591,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O2" t="n">
         <v>40623</v>
@@ -613,11 +613,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-0.5457349537037037</v>
+        <v>-0.6156539351851852</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>254941</v>
+        <v>253897</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -634,37 +634,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
-        <v>35.5</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:05:51</t>
+          <t>13-11-2025 14:46:32</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:37:51</t>
+          <t>14-11-2025 07:15:32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:37:51</t>
+          <t>14-11-2025 07:15:32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:13:21</t>
+          <t>14-11-2025 08:49:33</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4260</v>
+        <v>11282</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="O3" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-0.5926099537037037</v>
+        <v>-0.3677488425925926</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>253897</v>
+        <v>254117</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>94.01666666666667</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:13:21</t>
+          <t>14-11-2025 08:49:33</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:57:21</t>
+          <t>14-11-2025 09:20:33</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-11-2025 14:57:21</t>
+          <t>14-11-2025 09:20:33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:31:22</t>
+          <t>14-11-2025 09:29:43</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11282</v>
+        <v>1100</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -755,33 +755,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
       </c>
-      <c r="O4" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-0.3551215277777778</v>
+        <v>-35.39564236111111</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -789,7 +784,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>253865</v>
+        <v>253885</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,37 +793,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>116.7583333333333</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:31:22</t>
+          <t>14-11-2025 09:29:43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:13:22</t>
+          <t>14-11-2025 10:03:43</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:13:22</t>
+          <t>14-11-2025 10:03:43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:08</t>
+          <t>14-11-2025 11:49:39</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14011</v>
+        <v>12712</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -841,7 +836,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>70</v>
@@ -854,19 +849,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-35.46537037037037</v>
+        <v>-10.49281828703704</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>252061</v>
+        <v>255039</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -875,37 +870,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>36.16666666666666</v>
+        <v>9.15</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:08</t>
+          <t>14-11-2025 11:49:39</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:08</t>
+          <t>14-11-2025 12:08:39</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:33:08</t>
+          <t>14-11-2025 12:08:39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:18</t>
+          <t>14-11-2025 12:17:48</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4340</v>
+        <v>1098</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -918,37 +913,35 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>70</v>
       </c>
       <c r="O6" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>235572</v>
+        <v>255043</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -957,37 +950,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>82.98333333333333</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:09:18</t>
+          <t>14-11-2025 12:17:48</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:32:18</t>
+          <t>14-11-2025 12:34:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:32:18</t>
+          <t>14-11-2025 12:34:48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:17</t>
+          <t>17-11-2025 07:39:05</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9958</v>
+        <v>22114</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -996,17 +989,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1016,19 +1009,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-744</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254605</v>
+        <v>254230</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1037,37 +1030,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>39.025</v>
+        <v>62.475</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:17</t>
+          <t>17-11-2025 07:39:05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:18:17</t>
+          <t>17-11-2025 07:54:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:18:17</t>
+          <t>17-11-2025 07:54:05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:57:18</t>
+          <t>17-11-2025 08:56:34</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4683</v>
+        <v>7497</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1076,15 +1069,18 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>70</v>
       </c>
+      <c r="O8" t="n">
+        <v>406422</v>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1093,19 +1089,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-0.6231307870370371</v>
+        <v>-15</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254758</v>
+        <v>254605</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1118,33 +1114,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>61.38333333333333</v>
+        <v>39.025</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:57:18</t>
+          <t>17-11-2025 08:56:34</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:14:18</t>
+          <t>17-11-2025 09:17:34</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:14:18</t>
+          <t>17-11-2025 09:17:34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:15:41</t>
+          <t>17-11-2025 09:56:35</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7366</v>
+        <v>4683</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1157,7 +1153,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
@@ -1170,11 +1166,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-0.3442303240740741</v>
+        <v>-3.414299768518518</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1182,7 +1178,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254903</v>
+        <v>254555</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1191,37 +1187,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>256.6416666666667</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:15:41</t>
+          <t>17-11-2025 09:56:35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:41</t>
+          <t>17-11-2025 10:28:35</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:32:41</t>
+          <t>17-11-2025 10:28:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 12:49:20</t>
+          <t>17-11-2025 13:21:34</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30797</v>
+        <v>20758</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1230,14 +1226,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O10" t="n">
+        <v>406232</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1247,19 +1246,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254107</v>
+        <v>254276</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1268,37 +1267,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>175.0583333333333</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 12:49:20</t>
+          <t>17-11-2025 13:21:34</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 13:06:20</t>
+          <t>17-11-2025 13:57:34</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 13:06:20</t>
+          <t>17-11-2025 13:57:34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>18-11-2025 08:01:23</t>
+          <t>17-11-2025 14:34:36</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>21007</v>
+        <v>4444</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1324,19 +1323,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-37.33429976851852</v>
+        <v>-24.60736689814815</v>
       </c>
       <c r="T11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254309</v>
+        <v>254356</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1345,37 +1344,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>900.0166666666667</v>
+        <v>179.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18-11-2025 08:01:23</t>
+          <t>17-11-2025 14:34:36</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37:23</t>
+          <t>17-11-2025 14:55:36</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>18-11-2025 08:37:23</t>
+          <t>17-11-2025 14:55:36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20-11-2025 07:37:24</t>
+          <t>18-11-2025 09:55:12</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>108002</v>
+        <v>21552</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1384,14 +1383,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M12" t="n">
         <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1401,58 +1400,58 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-20.31764467592593</v>
+        <v>-20.41333912037037</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>254556</v>
+        <v>243569</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>173.4166666666667</v>
+        <v>21.675</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 09:55:12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14-11-2025 07:48:00</t>
+          <t>18-11-2025 10:27:12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14-11-2025 07:48:00</t>
+          <t>18-11-2025 10:27:12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14-11-2025 10:41:25</t>
+          <t>18-11-2025 10:48:53</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20810</v>
+        <v>2601</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1461,33 +1460,31 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>76</v>
       </c>
       <c r="O13" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-1.445428240740741</v>
+        <v>-429</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -1495,46 +1492,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>243569</v>
+        <v>235572</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>21.675</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14-11-2025 10:41:25</t>
+          <t>18-11-2025 10:48:53</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:25</t>
+          <t>18-11-2025 11:22:53</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>14-11-2025 11:10:25</t>
+          <t>18-11-2025 11:22:53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14-11-2025 11:32:05</t>
+          <t>18-11-2025 12:45:52</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2601</v>
+        <v>9958</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1543,14 +1540,14 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O14" t="n">
         <v>406372</v>
@@ -1563,19 +1560,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-429</v>
+        <v>-744</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254460</v>
+        <v>254293</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1584,37 +1581,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>46.68333333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14-11-2025 11:32:05</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14-11-2025 12:14:05</t>
+          <t>14-11-2025 07:27:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-11-2025 12:14:05</t>
+          <t>14-11-2025 07:27:00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14-11-2025 13:00:46</t>
+          <t>14-11-2025 07:45:51</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5602</v>
+        <v>2262</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1627,11 +1624,14 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
+      <c r="O15" t="n">
+        <v>40624</v>
+      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -1640,19 +1640,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-32.54220486111111</v>
+        <v>-14</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254519</v>
+        <v>254941</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1665,33 +1665,33 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>77.15833333333333</v>
+        <v>35.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14-11-2025 13:00:46</t>
+          <t>14-11-2025 07:45:51</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-11-2025 13:27:46</t>
+          <t>14-11-2025 08:29:51</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-11-2025 13:27:46</t>
+          <t>14-11-2025 08:29:51</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-11-2025 14:44:56</t>
+          <t>14-11-2025 09:05:21</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9259</v>
+        <v>4260</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1700,39 +1700,41 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="O16" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-4</v>
+        <v>-1.378715277777778</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254237</v>
+        <v>254375</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1741,37 +1743,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>184.0916666666667</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14-11-2025 14:44:56</t>
+          <t>14-11-2025 09:05:21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17-11-2025 07:17:56</t>
+          <t>14-11-2025 09:51:21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17-11-2025 07:17:56</t>
+          <t>14-11-2025 09:51:21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17-11-2025 10:22:01</t>
+          <t>14-11-2025 10:36:38</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>22091</v>
+        <v>5435</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1784,39 +1786,35 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
         <v>70</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="O17" t="n">
+        <v>40624</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-7.431961805555556</v>
+        <v>-12</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254287</v>
+        <v>252061</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1825,37 +1823,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>129.6333333333333</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17-11-2025 10:22:01</t>
+          <t>14-11-2025 10:36:38</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>17-11-2025 10:55:01</t>
+          <t>14-11-2025 11:03:38</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17-11-2025 10:55:01</t>
+          <t>14-11-2025 11:03:38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17-11-2025 13:04:39</t>
+          <t>14-11-2025 11:39:48</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>15556</v>
+        <v>4340</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1868,32 +1866,37 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>70</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
+      <c r="O18" t="n">
+        <v>40628</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-24.54490162037037</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254574</v>
+        <v>254291</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1906,33 +1909,33 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>173.6083333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17-11-2025 13:04:39</t>
+          <t>14-11-2025 11:39:48</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17-11-2025 13:29:39</t>
+          <t>14-11-2025 12:06:48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-11-2025 13:29:39</t>
+          <t>14-11-2025 12:06:48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-11-2025 08:23:16</t>
+          <t>14-11-2025 12:25:39</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>20833</v>
+        <v>2262</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1945,11 +1948,14 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
         <v>70</v>
       </c>
+      <c r="O19" t="n">
+        <v>40624</v>
+      </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
@@ -1958,11 +1964,11 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-14.34949074074074</v>
+        <v>-14</v>
       </c>
       <c r="T19" t="n">
         <v>7</v>
@@ -1970,7 +1976,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>252811</v>
+        <v>254824</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1979,37 +1985,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E20" t="n">
-        <v>11.875</v>
+        <v>748.225</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18-11-2025 08:23:16</t>
+          <t>14-11-2025 12:25:39</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18-11-2025 08:52:16</t>
+          <t>14-11-2025 13:13:39</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18-11-2025 08:52:16</t>
+          <t>14-11-2025 13:13:39</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-11-2025 09:04:08</t>
+          <t>18-11-2025 09:41:53</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1425</v>
+        <v>89787</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2018,14 +2024,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O20" t="n">
+        <v>406232</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2035,11 +2044,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-15.37787615740741</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -2047,7 +2056,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254106</v>
+        <v>254599</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2056,37 +2065,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>107.6416666666667</v>
+        <v>44.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18-11-2025 09:04:08</t>
+          <t>18-11-2025 09:41:53</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18-11-2025 09:31:08</t>
+          <t>18-11-2025 10:25:53</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18-11-2025 09:31:08</t>
+          <t>18-11-2025 10:25:53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-11-2025 11:18:47</t>
+          <t>18-11-2025 11:10:47</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>12917</v>
+        <v>5388</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2104,6 +2113,9 @@
       <c r="N21" t="n">
         <v>70</v>
       </c>
+      <c r="O21" t="n">
+        <v>406372</v>
+      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -2112,19 +2124,19 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-42.47137731481482</v>
+        <v>-2</v>
       </c>
       <c r="T21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>253650</v>
+        <v>254245</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2133,37 +2145,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>273.1333333333333</v>
+        <v>89.8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18-11-2025 11:18:47</t>
+          <t>18-11-2025 11:10:47</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18-11-2025 12:00:47</t>
+          <t>18-11-2025 11:35:47</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18-11-2025 12:00:47</t>
+          <t>18-11-2025 11:35:47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19-11-2025 08:33:55</t>
+          <t>18-11-2025 13:05:35</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>32776</v>
+        <v>10776</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2172,14 +2184,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O22" t="n">
+        <v>406372</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2193,54 +2208,54 @@
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-30.35688657407407</v>
+        <v>-20</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254385</v>
+        <v>253961</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>52.08333333333334</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 13:05:35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:00</t>
+          <t>18-11-2025 13:30:35</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:00</t>
+          <t>18-11-2025 13:30:35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:05</t>
+          <t>18-11-2025 14:06:30</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>6250</v>
+        <v>4310</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2249,80 +2264,78 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="O23" t="n">
-        <v>40627</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40627</v>
+        <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-0.3514467592592593</v>
+        <v>-8</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254165</v>
+        <v>254101</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>58.31666666666667</v>
+        <v>28.425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:05</t>
+          <t>18-11-2025 14:06:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:05</t>
+          <t>18-11-2025 14:35:30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:58:05</t>
+          <t>18-11-2025 14:35:30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:24</t>
+          <t>19-11-2025 07:03:55</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6998</v>
+        <v>3411</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2331,80 +2344,78 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O24" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406552</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-0.4141666666666667</v>
+        <v>-17</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254117</v>
+        <v>254100</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>9.166666666666666</v>
+        <v>28.425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:24</t>
+          <t>19-11-2025 07:03:55</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14-11-2025 10:13:24</t>
+          <t>19-11-2025 07:28:55</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14-11-2025 10:13:24</t>
+          <t>19-11-2025 07:28:55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>14-11-2025 10:22:34</t>
+          <t>19-11-2025 07:57:21</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1100</v>
+        <v>3411</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2413,14 +2424,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="O25" t="n">
+        <v>406552</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2430,58 +2444,58 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-35.43233796296296</v>
+        <v>-17</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254512</v>
+        <v>254433</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
-        <v>59.55833333333333</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:22:34</t>
+          <t>19-11-2025 07:57:21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:39:34</t>
+          <t>19-11-2025 08:30:21</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14-11-2025 10:39:34</t>
+          <t>19-11-2025 08:30:21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14-11-2025 11:39:07</t>
+          <t>19-11-2025 09:38:12</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7147</v>
+        <v>8142</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2490,17 +2504,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O26" t="n">
-        <v>406232</v>
+        <v>406552</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2510,11 +2524,11 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2522,46 +2536,46 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254824</v>
+        <v>254354</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
-        <v>748.225</v>
+        <v>18.675</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14-11-2025 11:39:07</t>
+          <t>19-11-2025 09:38:12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14-11-2025 11:58:07</t>
+          <t>19-11-2025 10:09:12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14-11-2025 11:58:07</t>
+          <t>19-11-2025 10:09:12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-11-2025 08:26:21</t>
+          <t>19-11-2025 10:27:52</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>89787</v>
+        <v>2241</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2570,78 +2584,75 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
+        <v>5</v>
+      </c>
+      <c r="N27" t="n">
+        <v>70</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>14-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>-15.43602430555556</v>
+      </c>
+      <c r="T27" t="n">
         <v>2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>76</v>
-      </c>
-      <c r="O27" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>16-03-2026 00:00:00</t>
-        </is>
-      </c>
-      <c r="S27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254555</v>
+        <v>254252</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>172.9833333333333</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18-11-2025 08:26:21</t>
+          <t>19-11-2025 10:27:52</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18-11-2025 08:45:21</t>
+          <t>19-11-2025 10:54:52</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18-11-2025 08:45:21</t>
+          <t>19-11-2025 10:54:52</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18-11-2025 11:38:20</t>
+          <t>19-11-2025 12:15:23</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>20758</v>
+        <v>9662</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2650,17 +2661,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
         <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>76</v>
-      </c>
-      <c r="O28" t="n">
-        <v>406232</v>
+        <v>70</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2670,58 +2678,58 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>0</v>
+        <v>-26.51068865740741</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>244023</v>
+        <v>253906</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E29" t="n">
-        <v>8.308333333333334</v>
+        <v>45.79166666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18-11-2025 11:38:20</t>
+          <t>19-11-2025 12:15:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18-11-2025 12:12:20</t>
+          <t>19-11-2025 12:44:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-11-2025 12:12:20</t>
+          <t>19-11-2025 12:44:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:38</t>
+          <t>19-11-2025 13:30:11</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>997</v>
+        <v>5495</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2730,18 +2738,15 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
-      <c r="O29" t="n">
-        <v>406062</v>
-      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2750,58 +2755,58 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>25-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-417</v>
+        <v>-4.562627314814815</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254457</v>
+        <v>253974</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E30" t="n">
-        <v>3.925</v>
+        <v>28.425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:38</t>
+          <t>19-11-2025 13:30:11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18-11-2025 12:39:38</t>
+          <t>19-11-2025 14:03:11</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18-11-2025 12:39:38</t>
+          <t>19-11-2025 14:03:11</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-11-2025 12:43:34</t>
+          <t>19-11-2025 14:31:36</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>471</v>
+        <v>3411</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2814,13 +2819,13 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
       <c r="O30" t="n">
-        <v>406372</v>
+        <v>406552</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2830,58 +2835,58 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>29-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-1</v>
+        <v>-22</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254245</v>
+        <v>254419</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>89.8</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18-11-2025 12:43:34</t>
+          <t>19-11-2025 14:31:36</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18-11-2025 13:04:34</t>
+          <t>20-11-2025 07:00:36</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18-11-2025 13:04:34</t>
+          <t>20-11-2025 07:00:36</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18-11-2025 14:34:22</t>
+          <t>20-11-2025 08:12:57</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>10776</v>
+        <v>8681</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2899,9 +2904,6 @@
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="O31" t="n">
-        <v>406372</v>
-      </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
@@ -2910,58 +2912,58 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-20</v>
+        <v>-20.34232638888889</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>253961</v>
+        <v>254339</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E32" t="n">
-        <v>35.91666666666666</v>
+        <v>245.9666666666667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18-11-2025 14:34:22</t>
+          <t>20-11-2025 08:12:57</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18-11-2025 14:49:22</t>
+          <t>20-11-2025 08:39:57</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18-11-2025 14:49:22</t>
+          <t>20-11-2025 08:39:57</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>19-11-2025 07:25:17</t>
+          <t>20-11-2025 12:45:55</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4310</v>
+        <v>29516</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2974,7 +2976,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -2987,58 +2989,58 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-18.30922453703704</v>
+        <v>-31.53188657407408</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254599</v>
+        <v>254547</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>44.9</v>
+        <v>68.55</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>19-11-2025 07:25:17</t>
+          <t>20-11-2025 12:45:55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>19-11-2025 07:40:17</t>
+          <t>20-11-2025 13:12:55</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19-11-2025 07:40:17</t>
+          <t>20-11-2025 13:12:55</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19-11-2025 08:25:11</t>
+          <t>20-11-2025 14:21:28</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5388</v>
+        <v>8226</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3056,9 +3058,6 @@
       <c r="N33" t="n">
         <v>70</v>
       </c>
-      <c r="O33" t="n">
-        <v>406552</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3067,58 +3066,58 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-3</v>
+        <v>-11.59824074074074</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254166</v>
+        <v>254967</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>20-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>38.85</v>
+        <v>260.4166666666667</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>19-11-2025 08:25:11</t>
+          <t>20-11-2025 14:21:28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19-11-2025 08:42:11</t>
+          <t>20-11-2025 14:52:28</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>19-11-2025 08:42:11</t>
+          <t>20-11-2025 14:52:28</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>19-11-2025 09:21:02</t>
+          <t>21-11-2025 11:12:53</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4662</v>
+        <v>31250</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3131,7 +3130,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
@@ -3144,19 +3143,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254546</v>
+        <v>254556</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3169,33 +3168,33 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E35" t="n">
-        <v>109.4083333333333</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19-11-2025 09:21:02</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:02</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:02</t>
+          <t>14-11-2025 07:23:00</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19-11-2025 11:27:26</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>13129</v>
+        <v>20810</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3204,78 +3203,80 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O35" t="n">
-        <v>406242</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-7</v>
+        <v>-1.42806712962963</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254481</v>
+        <v>253382</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32.5</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>81.16666666666667</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 10:16:25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 10:35:25</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 10:35:25</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 12:00:31</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9740</v>
+        <v>10212</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3284,80 +3285,78 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O36" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>253380</v>
+        <v>253865</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>38.5</v>
+        <v>34</v>
       </c>
       <c r="E37" t="n">
-        <v>104.275</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>14-11-2025 12:00:31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13-11-2025 14:32:10</t>
+          <t>14-11-2025 12:34:31</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>13-11-2025 14:32:10</t>
+          <t>14-11-2025 12:34:31</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:26</t>
+          <t>14-11-2025 14:31:16</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12513</v>
+        <v>14011</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3366,80 +3365,75 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
       </c>
-      <c r="O37" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P37" t="n">
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-0.3447511574074074</v>
+        <v>-35.60505208333333</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>255043</v>
+        <v>254758</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>44.5</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>184.2833333333333</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:26</t>
+          <t>14-11-2025 14:31:16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:56</t>
+          <t>14-11-2025 14:48:16</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14-11-2025 09:00:56</t>
+          <t>14-11-2025 14:48:16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>14-11-2025 12:05:13</t>
+          <t>17-11-2025 07:49:39</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>22114</v>
+        <v>7366</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3448,18 +3442,15 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
       </c>
-      <c r="O38" t="n">
-        <v>406422</v>
-      </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
@@ -3468,23 +3459,23 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>0</v>
+        <v>-0.3261516203703704</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>254189</v>
+        <v>254237</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3493,33 +3484,33 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30.5</v>
+        <v>21</v>
       </c>
       <c r="E39" t="n">
-        <v>55.875</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14-11-2025 12:05:13</t>
+          <t>17-11-2025 07:49:39</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:43</t>
+          <t>17-11-2025 08:10:39</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:43</t>
+          <t>17-11-2025 08:10:39</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14-11-2025 13:31:36</t>
+          <t>17-11-2025 11:14:45</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>6705</v>
+        <v>22091</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3528,31 +3519,35 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
-      <c r="O39" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-3</v>
+        <v>-7.468576388888889</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -3560,46 +3555,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254230</v>
+        <v>254457</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.5</v>
+        <v>21</v>
       </c>
       <c r="E40" t="n">
-        <v>62.475</v>
+        <v>3.925</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14-11-2025 13:31:36</t>
+          <t>17-11-2025 11:14:45</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14-11-2025 14:02:06</t>
+          <t>17-11-2025 11:35:45</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14-11-2025 14:02:06</t>
+          <t>17-11-2025 11:35:45</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:34</t>
+          <t>17-11-2025 11:39:40</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>7497</v>
+        <v>471</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3608,17 +3603,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
       <c r="O40" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3628,58 +3623,58 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254433</v>
+        <v>254283</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
       <c r="E41" t="n">
-        <v>67.84999999999999</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17-11-2025 07:04:34</t>
+          <t>17-11-2025 11:39:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:04</t>
+          <t>17-11-2025 12:11:40</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17-11-2025 07:35:04</t>
+          <t>17-11-2025 12:11:40</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17-11-2025 08:42:55</t>
+          <t>17-11-2025 13:47:26</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>8142</v>
+        <v>11492</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3688,78 +3683,78 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" t="n">
+        <v>76</v>
+      </c>
+      <c r="O41" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>11-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S41" s="1" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T41" t="n">
         <v>2</v>
-      </c>
-      <c r="N41" t="n">
-        <v>70</v>
-      </c>
-      <c r="O41" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>18-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S41" s="1" t="n">
-        <v>-3</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254276</v>
+        <v>254256</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>34.5</v>
+        <v>34</v>
       </c>
       <c r="E42" t="n">
-        <v>37.03333333333333</v>
+        <v>50.925</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>17-11-2025 08:42:55</t>
+          <t>17-11-2025 13:47:26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:25</t>
+          <t>17-11-2025 14:21:26</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:25</t>
+          <t>17-11-2025 14:21:26</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:27</t>
+          <t>18-11-2025 07:12:22</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>4444</v>
+        <v>6111</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3772,14 +3767,11 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
         <v>70</v>
       </c>
-      <c r="O42" t="n">
-        <v>406422</v>
-      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
@@ -3792,7 +3784,7 @@
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-18</v>
+        <v>-25.30025462962963</v>
       </c>
       <c r="T42" t="n">
         <v>4</v>
@@ -3800,46 +3792,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254451</v>
+        <v>254189</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>32.5</v>
+        <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>321.1416666666667</v>
+        <v>55.875</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:27</t>
+          <t>18-11-2025 07:12:22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17-11-2025 10:26:57</t>
+          <t>18-11-2025 07:29:22</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>17-11-2025 10:26:57</t>
+          <t>18-11-2025 07:29:22</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18-11-2025 07:48:06</t>
+          <t>18-11-2025 08:25:14</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>38537</v>
+        <v>6705</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3848,15 +3840,18 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
         <v>70</v>
       </c>
+      <c r="O43" t="n">
+        <v>406422</v>
+      </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
@@ -3869,7 +3864,7 @@
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-10.32506944444444</v>
+        <v>-3</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -3877,46 +3872,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254521</v>
+        <v>254519</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>34.5</v>
+        <v>17</v>
       </c>
       <c r="E44" t="n">
-        <v>39.68333333333333</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>18-11-2025 07:48:06</t>
+          <t>18-11-2025 08:25:14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18-11-2025 08:22:36</t>
+          <t>18-11-2025 08:42:14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18-11-2025 08:22:36</t>
+          <t>18-11-2025 08:42:14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>18-11-2025 09:02:17</t>
+          <t>18-11-2025 09:59:24</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>4762</v>
+        <v>9259</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3942,14 +3937,14 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-13.37658564814815</v>
+        <v>-11.41625</v>
       </c>
       <c r="T44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -3958,7 +3953,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3967,29 +3962,29 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>32.5</v>
+        <v>17</v>
       </c>
       <c r="E45" t="n">
         <v>64.40833333333333</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18-11-2025 09:02:17</t>
+          <t>18-11-2025 09:59:24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18-11-2025 09:34:47</t>
+          <t>18-11-2025 10:16:24</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18-11-2025 09:34:47</t>
+          <t>18-11-2025 10:16:24</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18-11-2025 10:39:11</t>
+          <t>18-11-2025 11:20:48</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -4023,7 +4018,7 @@
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-4.443883101851852</v>
+        <v>-4.472783564814815</v>
       </c>
       <c r="T45" t="n">
         <v>7</v>
@@ -4031,7 +4026,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>253885</v>
+        <v>254481</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4040,37 +4035,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>32.5</v>
       </c>
       <c r="E46" t="n">
-        <v>105.9333333333333</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>18-11-2025 10:39:11</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18-11-2025 11:11:41</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18-11-2025 11:11:41</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18-11-2025 12:57:37</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>12712</v>
+        <v>9740</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4083,36 +4078,41 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
+      <c r="O46" t="n">
+        <v>40642</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>40642</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-14.54001736111111</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>253694</v>
+        <v>254762</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4121,33 +4121,33 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>45</v>
+        <v>34.5</v>
       </c>
       <c r="E47" t="n">
-        <v>121.7583333333333</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>13-11-2025 13:53:40</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>13-11-2025 14:28:10</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>14611</v>
+        <v>3823</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4156,14 +4156,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O47" t="n">
         <v>40623</v>
@@ -4178,11 +4178,11 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-0.6158043981481481</v>
+        <v>-1.291684027777778</v>
       </c>
       <c r="T47" t="n">
         <v>2</v>
@@ -4190,11 +4190,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254129</v>
+        <v>253380</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4203,33 +4203,33 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E48" t="n">
-        <v>44.5</v>
+        <v>104.275</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:45</t>
+          <t>14-11-2025 07:00:01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:26:45</t>
+          <t>14-11-2025 07:42:31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:26:45</t>
+          <t>14-11-2025 07:42:31</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14-11-2025 08:11:15</t>
+          <t>14-11-2025 09:26:48</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>5340</v>
+        <v>12513</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4238,17 +4238,17 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O48" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4256,62 +4256,62 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-1.34115162037037</v>
+        <v>-0.3936111111111111</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254598</v>
+        <v>254460</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>80</v>
+        <v>40.5</v>
       </c>
       <c r="E49" t="n">
-        <v>104.2583333333333</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14-11-2025 08:11:15</t>
+          <t>14-11-2025 09:26:48</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:15</t>
+          <t>14-11-2025 10:07:18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>14-11-2025 09:31:15</t>
+          <t>14-11-2025 10:07:18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>14-11-2025 11:15:31</t>
+          <t>14-11-2025 10:53:59</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>12511</v>
+        <v>5602</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4320,11 +4320,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
         <v>70</v>
@@ -4337,58 +4337,58 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>0</v>
+        <v>-32.45415509259259</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254714</v>
+        <v>254429</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>32.5</v>
       </c>
       <c r="E50" t="n">
-        <v>91.47499999999999</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 10:53:59</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>14-11-2025 11:26:29</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>14-11-2025 11:26:29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:28</t>
+          <t>17-11-2025 07:26:43</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10977</v>
+        <v>28829</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4397,33 +4397,31 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
         <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O50" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-1.368385416666667</v>
+        <v>-9</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -4431,46 +4429,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254156</v>
+        <v>254188</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="E51" t="n">
-        <v>87.47499999999999</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:28</t>
+          <t>17-11-2025 07:26:43</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:28</t>
+          <t>17-11-2025 07:59:13</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 09:07:28</t>
+          <t>17-11-2025 07:59:13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:34:57</t>
+          <t>17-11-2025 08:36:40</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>10497</v>
+        <v>4493</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4479,80 +4477,78 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
         <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O51" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406372</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.4409375</v>
+        <v>-1</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254675</v>
+        <v>254437</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>30.5</v>
       </c>
       <c r="E52" t="n">
-        <v>153.9583333333333</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:34:57</t>
+          <t>17-11-2025 08:36:40</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:51:57</t>
+          <t>17-11-2025 09:07:10</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:51:57</t>
+          <t>17-11-2025 09:07:10</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:54</t>
+          <t>17-11-2025 10:05:13</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>18475</v>
+        <v>6967</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4561,17 +4557,17 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N52" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O52" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4581,11 +4577,11 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
@@ -4593,46 +4589,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254283</v>
+        <v>244023</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>34.5</v>
       </c>
       <c r="E53" t="n">
-        <v>95.76666666666667</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:54</t>
+          <t>17-11-2025 10:05:13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14-11-2025 13:44:54</t>
+          <t>17-11-2025 10:39:43</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14-11-2025 13:44:54</t>
+          <t>17-11-2025 10:39:43</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-11-2025 07:20:40</t>
+          <t>17-11-2025 10:48:02</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>11492</v>
+        <v>997</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4641,17 +4637,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N53" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O53" t="n">
-        <v>406372</v>
+        <v>406062</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4661,23 +4657,23 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-8</v>
+        <v>-417</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254910</v>
+        <v>253838</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4686,33 +4682,33 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="E54" t="n">
-        <v>73.53333333333333</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17-11-2025 07:20:40</t>
+          <t>17-11-2025 10:48:02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17-11-2025 07:37:40</t>
+          <t>17-11-2025 11:20:32</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-11-2025 07:37:40</t>
+          <t>17-11-2025 11:20:32</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17-11-2025 08:51:12</t>
+          <t>17-11-2025 13:08:54</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>8824</v>
+        <v>13004</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4721,78 +4717,75 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M54" t="n">
+        <v>5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>70</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>06-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S54" s="1" t="n">
+        <v>-21.54784722222222</v>
+      </c>
+      <c r="T54" t="n">
         <v>4</v>
-      </c>
-      <c r="N54" t="n">
-        <v>76</v>
-      </c>
-      <c r="O54" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>05-12-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>253614</v>
+        <v>254107</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="E55" t="n">
-        <v>122.45</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17-11-2025 08:51:12</t>
+          <t>17-11-2025 13:08:54</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-11-2025 09:23:12</t>
+          <t>17-11-2025 13:41:24</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-11-2025 09:23:12</t>
+          <t>17-11-2025 13:41:24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17-11-2025 11:25:39</t>
+          <t>18-11-2025 08:36:27</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>14694</v>
+        <v>21007</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4801,14 +4794,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -4818,11 +4811,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-7.47615162037037</v>
+        <v>-37.35865162037037</v>
       </c>
       <c r="T55" t="n">
         <v>7</v>
@@ -4830,11 +4823,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254713</v>
+        <v>254381</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4843,33 +4836,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>45</v>
+        <v>32.5</v>
       </c>
       <c r="E56" t="n">
-        <v>49.96666666666667</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 08:36:27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:00</t>
+          <t>18-11-2025 09:08:57</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:00</t>
+          <t>18-11-2025 09:08:57</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>14-11-2025 08:34:58</t>
+          <t>18-11-2025 10:32:49</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>5996</v>
+        <v>10064</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4878,80 +4871,75 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
-        <v>76</v>
-      </c>
-      <c r="O56" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-1.357615740740741</v>
+        <v>-21.43946180555556</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254198</v>
+        <v>254756</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E57" t="n">
-        <v>215</v>
+        <v>60.625</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14-11-2025 08:34:58</t>
+          <t>18-11-2025 10:32:49</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14-11-2025 09:14:58</t>
+          <t>18-11-2025 11:15:19</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>14-11-2025 09:14:58</t>
+          <t>18-11-2025 11:15:19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>14-11-2025 12:49:58</t>
+          <t>18-11-2025 12:15:57</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>25800</v>
+        <v>7275</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4960,14 +4948,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N57" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4977,58 +4965,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-25.53469907407407</v>
+        <v>-4.511076388888889</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254256</v>
+        <v>254713</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E58" t="n">
-        <v>50.925</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14-11-2025 12:49:58</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14-11-2025 13:24:58</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14-11-2025 13:24:58</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>14-11-2025 14:15:53</t>
+          <t>13-11-2025 13:34:58</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6111</v>
+        <v>5996</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5037,78 +5025,80 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O58" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-18</v>
+        <v>-0.565949074074074</v>
       </c>
       <c r="T58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254375</v>
+        <v>253694</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E59" t="n">
-        <v>45.29166666666666</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>14-11-2025 14:15:53</t>
+          <t>13-11-2025 13:34:58</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-11-2025 14:45:53</t>
+          <t>13-11-2025 14:14:58</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14-11-2025 14:45:53</t>
+          <t>13-11-2025 14:14:58</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17-11-2025 07:31:11</t>
+          <t>14-11-2025 08:16:43</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5435</v>
+        <v>14611</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5117,31 +5107,33 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
         <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O59" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-12</v>
+        <v>-1.344947916666667</v>
       </c>
       <c r="T59" t="n">
         <v>2</v>
@@ -5149,11 +5141,11 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>255039</v>
+        <v>253650</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5165,30 +5157,30 @@
         <v>30</v>
       </c>
       <c r="E60" t="n">
-        <v>9.15</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17-11-2025 07:31:11</t>
+          <t>14-11-2025 08:16:43</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>17-11-2025 08:01:11</t>
+          <t>14-11-2025 08:46:43</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>17-11-2025 08:01:11</t>
+          <t>14-11-2025 08:46:43</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:20</t>
+          <t>14-11-2025 13:19:51</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1098</v>
+        <v>32776</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5197,17 +5189,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
         <v>3</v>
       </c>
       <c r="N60" t="n">
-        <v>70</v>
-      </c>
-      <c r="O60" t="n">
-        <v>40624</v>
+        <v>76</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5217,58 +5206,58 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0</v>
+        <v>-25.55545717592593</v>
       </c>
       <c r="T60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254381</v>
+        <v>254675</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>35</v>
       </c>
       <c r="E61" t="n">
-        <v>83.86666666666666</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:20</t>
+          <t>14-11-2025 13:19:51</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17-11-2025 08:45:20</t>
+          <t>14-11-2025 13:54:51</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>17-11-2025 08:45:20</t>
+          <t>14-11-2025 13:54:51</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17-11-2025 10:09:12</t>
+          <t>17-11-2025 08:28:49</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>10064</v>
+        <v>18475</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5277,14 +5266,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
         <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O61" t="n">
         <v>406422</v>
@@ -5297,58 +5286,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="T61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254188</v>
+        <v>254910</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>37.44166666666667</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17-11-2025 10:09:12</t>
+          <t>17-11-2025 08:28:49</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:12</t>
+          <t>17-11-2025 08:58:49</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:12</t>
+          <t>17-11-2025 08:58:49</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>17-11-2025 11:16:38</t>
+          <t>17-11-2025 10:12:21</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4493</v>
+        <v>8824</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5357,14 +5346,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
         <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O62" t="n">
         <v>406372</v>
@@ -5377,58 +5366,58 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254437</v>
+        <v>254451</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E63" t="n">
-        <v>58.05833333333333</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17-11-2025 11:16:38</t>
+          <t>17-11-2025 10:12:21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17-11-2025 11:41:38</t>
+          <t>17-11-2025 10:52:21</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17-11-2025 11:41:38</t>
+          <t>17-11-2025 10:52:21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>17-11-2025 12:39:42</t>
+          <t>18-11-2025 08:13:29</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>6967</v>
+        <v>38537</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5441,14 +5430,11 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
       </c>
-      <c r="O63" t="n">
-        <v>406372</v>
-      </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
@@ -5461,7 +5447,7 @@
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-1</v>
+        <v>-10.3427025462963</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -5469,46 +5455,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>253838</v>
+        <v>254652</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>108.3666666666667</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>17-11-2025 12:39:42</t>
+          <t>18-11-2025 08:13:29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:42</t>
+          <t>18-11-2025 08:43:29</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17-11-2025 13:09:42</t>
+          <t>18-11-2025 08:43:29</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>17-11-2025 14:58:04</t>
+          <t>18-11-2025 09:12:13</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>13004</v>
+        <v>3448</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5521,7 +5507,7 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
@@ -5534,58 +5520,58 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-21.62365740740741</v>
+        <v>-7.383489583333334</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>250284</v>
+        <v>254598</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E65" t="n">
-        <v>146.35</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17-11-2025 14:58:04</t>
+          <t>18-11-2025 09:12:13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18-11-2025 07:38:04</t>
+          <t>18-11-2025 10:22:13</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>18-11-2025 07:38:04</t>
+          <t>18-11-2025 10:22:13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18-11-2025 10:04:25</t>
+          <t>18-11-2025 12:06:29</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>17562</v>
+        <v>12511</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5594,11 +5580,11 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N65" t="n">
         <v>70</v>
@@ -5611,11 +5597,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>-261.4197337962963</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>7</v>
@@ -5623,46 +5609,46 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254756</v>
+        <v>254651</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E66" t="n">
-        <v>60.625</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18-11-2025 10:04:25</t>
+          <t>18-11-2025 12:06:29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18-11-2025 10:34:25</t>
+          <t>18-11-2025 13:21:29</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18-11-2025 10:34:25</t>
+          <t>18-11-2025 13:21:29</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18-11-2025 11:35:02</t>
+          <t>18-11-2025 13:44:07</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>7275</v>
+        <v>2717</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5675,7 +5661,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
         <v>70</v>
@@ -5688,58 +5674,58 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-4.482667824074074</v>
+        <v>-7.572309027777778</v>
       </c>
       <c r="T66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>254365</v>
+        <v>254166</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>67.53333333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18-11-2025 11:35:02</t>
+          <t>18-11-2025 13:44:07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:02</t>
+          <t>18-11-2025 14:19:07</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:02</t>
+          <t>18-11-2025 14:19:07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18-11-2025 13:27:34</t>
+          <t>18-11-2025 14:57:58</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>8104</v>
+        <v>4662</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5752,11 +5738,14 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
         <v>70</v>
       </c>
+      <c r="O67" t="n">
+        <v>406372</v>
+      </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
@@ -5765,58 +5754,58 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-14.56081597222222</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254652</v>
+        <v>254385</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E68" t="n">
-        <v>28.73333333333333</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>18-11-2025 13:27:34</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>18-11-2025 13:57:34</t>
+          <t>14-11-2025 07:34:00</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>18-11-2025 13:57:34</t>
+          <t>14-11-2025 07:34:00</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>18-11-2025 14:26:18</t>
+          <t>14-11-2025 08:26:05</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3448</v>
+        <v>6250</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5825,75 +5814,80 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>70</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
+        <v>152</v>
+      </c>
+      <c r="O68" t="n">
+        <v>40627</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>40627</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>-7.601603009259259</v>
+        <v>-0.3514467592592593</v>
       </c>
       <c r="T68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254429</v>
+        <v>254198</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E69" t="n">
-        <v>240.2416666666667</v>
+        <v>215</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18-11-2025 14:26:18</t>
+          <t>14-11-2025 08:26:05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>18-11-2025 14:56:18</t>
+          <t>14-11-2025 08:43:05</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>18-11-2025 14:56:18</t>
+          <t>14-11-2025 08:43:05</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>19-11-2025 10:56:33</t>
+          <t>14-11-2025 12:18:05</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>28829</v>
+        <v>25800</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5902,17 +5896,14 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
-        <v>70</v>
-      </c>
-      <c r="O69" t="n">
-        <v>406552</v>
+        <v>152</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
@@ -5922,11 +5913,11 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-10</v>
+        <v>-25.51255787037037</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
@@ -5934,46 +5925,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254715</v>
+        <v>253614</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E70" t="n">
-        <v>134.5416666666667</v>
+        <v>122.45</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 12:18:05</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 12:35:05</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 12:35:05</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 14:37:32</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>16145</v>
+        <v>14694</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5982,80 +5973,75 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>76</v>
-      </c>
-      <c r="O70" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-1.409403935185185</v>
+        <v>-4.609398148148149</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>253382</v>
+        <v>254309</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E71" t="n">
-        <v>85.09999999999999</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14-11-2025 09:49:32</t>
+          <t>14-11-2025 14:37:32</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14-11-2025 10:19:32</t>
+          <t>14-11-2025 14:54:32</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>14-11-2025 10:19:32</t>
+          <t>14-11-2025 14:54:32</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:38</t>
+          <t>18-11-2025 13:54:33</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>10212</v>
+        <v>108002</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6064,17 +6050,14 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
-        <v>76</v>
-      </c>
-      <c r="O71" t="n">
-        <v>406372</v>
+        <v>152</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -6084,58 +6067,58 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-12</v>
+        <v>-18.57954861111111</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254293</v>
+        <v>254714</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E72" t="n">
-        <v>18.85</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:38</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14-11-2025 12:29:38</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14-11-2025 12:29:38</t>
+          <t>14-11-2025 07:50:00</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14-11-2025 12:48:29</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>2262</v>
+        <v>10977</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6144,78 +6127,80 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O72" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-14</v>
+        <v>-1.389913194444444</v>
       </c>
       <c r="T72" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254291</v>
+        <v>254106</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>18.85</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-11-2025 12:48:29</t>
+          <t>14-11-2025 09:21:28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:13:29</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:13:29</t>
+          <t>14-11-2025 09:56:28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14-11-2025 13:32:20</t>
+          <t>14-11-2025 11:44:07</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2262</v>
+        <v>12917</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6228,14 +6213,11 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N73" t="n">
         <v>70</v>
       </c>
-      <c r="O73" t="n">
-        <v>40624</v>
-      </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
@@ -6244,11 +6226,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-14</v>
+        <v>-38.48896990740741</v>
       </c>
       <c r="T73" t="n">
         <v>7</v>
@@ -6256,46 +6238,46 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254356</v>
+        <v>254287</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E74" t="n">
-        <v>179.6</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14-11-2025 13:32:20</t>
+          <t>14-11-2025 11:44:07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:07:20</t>
+          <t>14-11-2025 12:14:07</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:07:20</t>
+          <t>14-11-2025 12:14:07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:56</t>
+          <t>14-11-2025 14:23:45</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>21552</v>
+        <v>15556</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6308,11 +6290,14 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
+      <c r="O74" t="n">
+        <v>406422</v>
+      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
@@ -6321,11 +6306,11 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-19.37982060185185</v>
+        <v>-18</v>
       </c>
       <c r="T74" t="n">
         <v>4</v>
@@ -6333,46 +6318,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254187</v>
+        <v>254574</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E75" t="n">
-        <v>46.39166666666667</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:06:56</t>
+          <t>14-11-2025 14:23:45</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:56</t>
+          <t>14-11-2025 14:48:45</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:36:56</t>
+          <t>14-11-2025 14:48:45</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:20</t>
+          <t>17-11-2025 09:42:21</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5567</v>
+        <v>20833</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6391,7 +6376,7 @@
         <v>70</v>
       </c>
       <c r="O75" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6401,58 +6386,58 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254893</v>
+        <v>254903</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E76" t="n">
-        <v>46.675</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:23:20</t>
+          <t>17-11-2025 09:42:21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:20</t>
+          <t>17-11-2025 10:17:21</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:20</t>
+          <t>17-11-2025 10:17:21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17-11-2025 11:35:00</t>
+          <t>17-11-2025 14:34:00</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5601</v>
+        <v>30797</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6470,9 +6455,6 @@
       <c r="N76" t="n">
         <v>70</v>
       </c>
-      <c r="O76" t="n">
-        <v>406372</v>
-      </c>
       <c r="P76" t="n">
         <v>0</v>
       </c>
@@ -6481,7 +6463,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -6493,46 +6475,46 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254586</v>
+        <v>252811</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>51.54166666666666</v>
+        <v>11.875</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17-11-2025 11:35:00</t>
+          <t>17-11-2025 14:34:00</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:00:00</t>
+          <t>18-11-2025 07:09:00</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:00:00</t>
+          <t>18-11-2025 07:09:00</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>17-11-2025 12:51:33</t>
+          <t>18-11-2025 07:20:52</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>6185</v>
+        <v>1425</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6545,14 +6527,11 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
       </c>
-      <c r="O77" t="n">
-        <v>406372</v>
-      </c>
       <c r="P77" t="n">
         <v>0</v>
       </c>
@@ -6561,58 +6540,58 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>0</v>
+        <v>-15.30616319444444</v>
       </c>
       <c r="T77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254915</v>
+        <v>254586</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E78" t="n">
-        <v>48.875</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17-11-2025 12:51:33</t>
+          <t>18-11-2025 07:20:52</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:33</t>
+          <t>18-11-2025 07:55:52</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:33</t>
+          <t>18-11-2025 07:55:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:10:25</t>
+          <t>18-11-2025 08:47:25</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>5865</v>
+        <v>6185</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6621,15 +6600,18 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
+      <c r="O78" t="n">
+        <v>406372</v>
+      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
@@ -6638,58 +6620,58 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>254651</v>
+        <v>254915</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
         <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>22.64166666666667</v>
+        <v>48.875</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>17-11-2025 14:10:25</t>
+          <t>18-11-2025 08:47:25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17-11-2025 14:40:25</t>
+          <t>18-11-2025 09:17:25</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>17-11-2025 14:40:25</t>
+          <t>18-11-2025 09:17:25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 07:03:04</t>
+          <t>18-11-2025 10:06:17</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>2717</v>
+        <v>5865</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6698,11 +6680,11 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
         <v>70</v>
@@ -6715,77 +6697,77 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-7.293796296296296</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254609</v>
+        <v>254512</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E80" t="n">
-        <v>416.6666666666667</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 10:06:17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 10:46:17</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 10:46:17</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>12-11-2025 13:56:40</t>
+          <t>18-11-2025 11:45:51</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>50000</v>
+        <v>7147</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="O80" t="n">
-        <v>40655</v>
+        <v>406232</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -6795,23 +6777,23 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="T80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>252980</v>
+        <v>254521</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6820,49 +6802,49 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E81" t="n">
-        <v>17.075</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 11:45:51</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 12:20:51</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 12:20:51</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>14-11-2025 07:17:04</t>
+          <t>18-11-2025 13:00:32</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>2049</v>
+        <v>4762</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -6872,14 +6854,1129 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-77.30352430555556</v>
+        <v>-13.54203703703704</v>
       </c>
       <c r="T81" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>254365</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>10-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>35</v>
+      </c>
+      <c r="E82" t="n">
+        <v>67.53333333333333</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:00:32</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:35:32</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>18-11-2025 13:35:32</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:43:04</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8104</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>5</v>
+      </c>
+      <c r="N82" t="n">
+        <v>70</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>14-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S82" s="1" t="n">
+        <v>-14.61324074074074</v>
+      </c>
+      <c r="T82" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>254129</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>12-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>35</v>
+      </c>
+      <c r="E83" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:35:00</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:19:30</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5340</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>4</v>
+      </c>
+      <c r="N83" t="n">
+        <v>76</v>
+      </c>
+      <c r="O83" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>40623</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>30-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S83" s="1" t="n">
+        <v>-1.346875</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>254156</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>12-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E84" t="n">
+        <v>87.47499999999999</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:19:30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:59:30</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>14-11-2025 08:59:30</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:26:58</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>10497</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>76</v>
+      </c>
+      <c r="O84" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>40606</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>07-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S84" s="1" t="n">
+        <v>-0.4353993055555556</v>
+      </c>
+      <c r="T84" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>254165</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>12-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>25</v>
+      </c>
+      <c r="E85" t="n">
+        <v>58.31666666666667</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:26:58</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:51:58</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>14-11-2025 10:51:58</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:50:17</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>6998</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
+      <c r="N85" t="n">
+        <v>76</v>
+      </c>
+      <c r="O85" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>40606</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>07-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S85" s="1" t="n">
+        <v>-0.4932581018518519</v>
+      </c>
+      <c r="T85" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>250284</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>17-03-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>50</v>
+      </c>
+      <c r="E86" t="n">
+        <v>146.35</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>14-11-2025 11:50:17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:40:17</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>14-11-2025 12:40:17</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:06:38</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>17562</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>8</v>
+      </c>
+      <c r="N86" t="n">
+        <v>70</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>12-03-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S86" s="1" t="n">
+        <v>-260.2962789351852</v>
+      </c>
+      <c r="T86" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>254187</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>50</v>
+      </c>
+      <c r="E87" t="n">
+        <v>46.39166666666667</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:06:38</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:56:38</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>17-11-2025 07:56:38</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:43:02</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>5567</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" t="n">
+        <v>70</v>
+      </c>
+      <c r="O87" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>18-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S87" s="1" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>254893</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>14-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>25</v>
+      </c>
+      <c r="E88" t="n">
+        <v>46.675</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>17-11-2025 08:43:02</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:08:02</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:08:02</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:54:42</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>5601</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>3</v>
+      </c>
+      <c r="N88" t="n">
+        <v>70</v>
+      </c>
+      <c r="O88" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>04-12-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>254546</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>13-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>30</v>
+      </c>
+      <c r="E89" t="n">
+        <v>109.4083333333333</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>17-11-2025 09:54:42</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:24:42</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>17-11-2025 10:24:42</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>17-11-2025 12:14:07</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>13129</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>70</v>
+      </c>
+      <c r="O89" t="n">
+        <v>406242</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>19-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S89" s="1" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T89" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>254609</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>416.6666666666667</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>12-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>12-11-2025 13:56:40</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>40655</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>20-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>252980</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>11-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>17.075</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:00:00</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>14-11-2025 07:17:04</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>2049</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>08-09-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S91" s="1" t="n">
+        <v>-77.30352430555556</v>
+      </c>
+      <c r="T91" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>254428</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>48.30833333333333</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:48:18</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>5797</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>70</v>
+      </c>
+      <c r="O92" t="n">
+        <v>40649</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>40649</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>10-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S92" s="1" t="n">
+        <v>-7.616880787037037</v>
+      </c>
+      <c r="T92" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>254427</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>55.55833333333333</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:55:33</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>6667</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>T1 ;T2 ;T8</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>70</v>
+      </c>
+      <c r="O93" t="n">
+        <v>40649</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>40649</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>10-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S93" s="1" t="n">
+        <v>-7.621915509259259</v>
+      </c>
+      <c r="T93" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>254173</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>15-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>202.5916666666667</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>17-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>18-11-2025 09:22:35</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>24311</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>foglio</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>20-10-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S94" s="1" t="n">
+        <v>-39.39068865740741</v>
+      </c>
+      <c r="T94" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>254671</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>55</v>
+      </c>
+      <c r="E95" t="n">
+        <v>136.1666666666667</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:00:00</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:55:00</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>18-11-2025 14:55:00</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>19-11-2025 09:11:10</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>16340</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>bobina</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>CASON ;H7 ;R5</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>7</v>
+      </c>
+      <c r="N95" t="n">
+        <v>70</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>21-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S95" s="1" t="n">
+        <v>-8.38275462962963</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254715</v>
+        <v>254481</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>134.5416666666667</v>
+        <v>81.16666666666667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -568,21 +568,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>13-11-2025 12:34:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:00</t>
+          <t>13-11-2025 12:34:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:32</t>
+          <t>13-11-2025 13:55:10</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16145</v>
+        <v>9740</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,17 +591,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O2" t="n">
-        <v>40623</v>
+        <v>40642</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>40623</v>
+        <v>40642</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>04-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>-0.6156539351851852</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>253897</v>
+        <v>254941</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -634,37 +634,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>94.01666666666667</v>
+        <v>35.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:46:32</t>
+          <t>13-11-2025 13:55:10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:15:32</t>
+          <t>13-11-2025 14:27:10</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:15:32</t>
+          <t>13-11-2025 14:27:10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14-11-2025 08:49:33</t>
+          <t>14-11-2025 07:02:40</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11282</v>
+        <v>4260</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -673,17 +673,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="O3" t="n">
-        <v>40606</v>
+        <v>40623</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>40606</v>
+        <v>40623</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-0.3677488425925926</v>
+        <v>-1.293518518518519</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254117</v>
+        <v>254713</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>9.166666666666666</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:49:33</t>
+          <t>14-11-2025 07:02:40</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:33</t>
+          <t>14-11-2025 07:38:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:20:33</t>
+          <t>14-11-2025 07:38:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:29:43</t>
+          <t>14-11-2025 08:28:38</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1100</v>
+        <v>5996</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -755,36 +755,41 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
+      <c r="O4" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-35.39564236111111</v>
+        <v>-1.353217592592593</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>253885</v>
+        <v>254675</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>105.9333333333333</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:29:43</t>
+          <t>14-11-2025 08:28:38</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:43</t>
+          <t>14-11-2025 08:45:38</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 10:03:43</t>
+          <t>14-11-2025 08:45:38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:49:39</t>
+          <t>14-11-2025 11:19:35</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12712</v>
+        <v>18475</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -832,14 +837,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O5" t="n">
+        <v>406422</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -849,14 +857,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-10.49281828703704</v>
+        <v>-4</v>
       </c>
       <c r="T5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -874,29 +882,29 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
         <v>9.15</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:49:39</t>
+          <t>14-11-2025 11:19:35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:08:39</t>
+          <t>14-11-2025 11:53:35</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:08:39</t>
+          <t>14-11-2025 11:53:35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:17:48</t>
+          <t>14-11-2025 12:02:44</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -941,7 +949,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>255043</v>
+        <v>254546</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -957,30 +965,30 @@
         <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>184.2833333333333</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:17:48</t>
+          <t>14-11-2025 12:02:44</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:48</t>
+          <t>14-11-2025 12:19:44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:48</t>
+          <t>14-11-2025 12:19:44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17-11-2025 07:39:05</t>
+          <t>14-11-2025 14:09:09</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22114</v>
+        <v>13129</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -989,17 +997,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>406422</v>
+        <v>406242</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1009,19 +1017,19 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254230</v>
+        <v>254893</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1030,37 +1038,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>62.475</v>
+        <v>46.675</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:39:05</t>
+          <t>14-11-2025 14:09:09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:54:05</t>
+          <t>14-11-2025 14:26:09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:54:05</t>
+          <t>14-11-2025 14:26:09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17-11-2025 08:56:34</t>
+          <t>17-11-2025 07:12:49</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7497</v>
+        <v>5601</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1069,17 +1077,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>70</v>
       </c>
       <c r="O8" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1089,19 +1097,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254605</v>
+        <v>254187</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1114,33 +1122,33 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>39.025</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:56:34</t>
+          <t>17-11-2025 07:12:49</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:34</t>
+          <t>17-11-2025 07:27:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-11-2025 09:17:34</t>
+          <t>17-11-2025 07:27:49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 09:56:35</t>
+          <t>17-11-2025 08:14:13</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4683</v>
+        <v>5567</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1153,11 +1161,14 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
       </c>
+      <c r="O9" t="n">
+        <v>406372</v>
+      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1166,11 +1177,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-3.414299768518518</v>
+        <v>-1</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1178,7 +1189,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254555</v>
+        <v>254166</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1187,37 +1198,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>172.9833333333333</v>
+        <v>38.85</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:56:35</t>
+          <t>17-11-2025 08:14:13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 10:28:35</t>
+          <t>17-11-2025 08:29:13</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 10:28:35</t>
+          <t>17-11-2025 08:29:13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:34</t>
+          <t>17-11-2025 09:08:04</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>20758</v>
+        <v>4662</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1226,17 +1237,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O10" t="n">
-        <v>406232</v>
+        <v>406372</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1246,19 +1257,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254276</v>
+        <v>254555</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1271,33 +1282,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>37.03333333333333</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 13:21:34</t>
+          <t>17-11-2025 09:08:04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 13:57:34</t>
+          <t>17-11-2025 09:40:04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 13:57:34</t>
+          <t>17-11-2025 09:40:04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:36</t>
+          <t>17-11-2025 12:33:03</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4444</v>
+        <v>20758</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1306,14 +1317,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O11" t="n">
+        <v>406232</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1323,19 +1337,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-24.60736689814815</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254356</v>
+        <v>253838</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1344,37 +1358,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>179.6</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:36</t>
+          <t>17-11-2025 12:33:03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:36</t>
+          <t>17-11-2025 13:05:03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:36</t>
+          <t>17-11-2025 13:05:03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18-11-2025 09:55:12</t>
+          <t>17-11-2025 14:53:25</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>21552</v>
+        <v>13004</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1387,7 +1401,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
@@ -1400,11 +1414,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-20.41333912037037</v>
+        <v>-21.62042824074074</v>
       </c>
       <c r="T12" t="n">
         <v>4</v>
@@ -1412,7 +1426,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>243569</v>
+        <v>250284</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1421,37 +1435,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>21.675</v>
+        <v>146.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18-11-2025 09:55:12</t>
+          <t>17-11-2025 14:53:25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18-11-2025 10:27:12</t>
+          <t>18-11-2025 07:14:25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18-11-2025 10:27:12</t>
+          <t>18-11-2025 07:14:25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18-11-2025 10:48:53</t>
+          <t>18-11-2025 09:40:46</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2601</v>
+        <v>17562</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1460,17 +1474,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>76</v>
-      </c>
-      <c r="O13" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1480,19 +1491,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-429</v>
+        <v>-60</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>235572</v>
+        <v>254106</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1505,33 +1516,33 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>82.98333333333333</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18-11-2025 10:48:53</t>
+          <t>18-11-2025 09:40:46</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18-11-2025 11:22:53</t>
+          <t>18-11-2025 10:03:46</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18-11-2025 11:22:53</t>
+          <t>18-11-2025 10:03:46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18-11-2025 12:45:52</t>
+          <t>18-11-2025 11:51:24</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9958</v>
+        <v>12917</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1544,14 +1555,11 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
         <v>70</v>
       </c>
-      <c r="O14" t="n">
-        <v>406372</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
@@ -1560,23 +1568,23 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-744</v>
+        <v>-42.49403356481481</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254293</v>
+        <v>253885</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1585,33 +1593,33 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>18.85</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 11:51:24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14-11-2025 07:27:00</t>
+          <t>18-11-2025 12:08:24</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>14-11-2025 07:27:00</t>
+          <t>18-11-2025 12:08:24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:51</t>
+          <t>18-11-2025 13:54:20</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2262</v>
+        <v>12712</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1624,14 +1632,11 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
-      <c r="O15" t="n">
-        <v>40624</v>
-      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -1640,19 +1645,19 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-14</v>
+        <v>-14.57940393518519</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254941</v>
+        <v>254129</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1665,33 +1670,33 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>35.5</v>
+        <v>44.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:45:51</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-11-2025 08:29:51</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-11-2025 08:29:51</t>
+          <t>14-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:21</t>
+          <t>14-11-2025 08:26:30</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4260</v>
+        <v>5340</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1700,14 +1705,14 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="O16" t="n">
         <v>40623</v>
@@ -1722,19 +1727,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-1.378715277777778</v>
+        <v>-1.351736111111111</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254375</v>
+        <v>254156</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1743,37 +1748,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>45.29166666666666</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:05:21</t>
+          <t>14-11-2025 08:26:30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:51:21</t>
+          <t>14-11-2025 08:57:30</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14-11-2025 09:51:21</t>
+          <t>14-11-2025 08:57:30</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:38</t>
+          <t>14-11-2025 10:24:58</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5435</v>
+        <v>10497</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1782,23 +1787,25 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M17" t="n">
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O17" t="n">
-        <v>40624</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1806,15 +1813,15 @@
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-12</v>
+        <v>-0.4340104166666667</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>252061</v>
+        <v>254198</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1823,37 +1830,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>36.16666666666666</v>
+        <v>215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:38</t>
+          <t>14-11-2025 10:24:58</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-11-2025 11:03:38</t>
+          <t>14-11-2025 11:08:58</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14-11-2025 11:03:38</t>
+          <t>14-11-2025 11:08:58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-11-2025 11:39:48</t>
+          <t>14-11-2025 14:43:58</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4340</v>
+        <v>25800</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1862,33 +1869,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
-      </c>
-      <c r="O18" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0</v>
+        <v>-25.61387152777778</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
@@ -1896,7 +1898,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254291</v>
+        <v>254309</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1905,37 +1907,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>18.85</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14-11-2025 11:39:48</t>
+          <t>14-11-2025 14:43:58</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14-11-2025 12:06:48</t>
+          <t>17-11-2025 07:12:58</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14-11-2025 12:06:48</t>
+          <t>17-11-2025 07:12:58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>14-11-2025 12:25:39</t>
+          <t>18-11-2025 14:12:59</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2262</v>
+        <v>108002</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1944,17 +1946,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>70</v>
-      </c>
-      <c r="O19" t="n">
-        <v>40624</v>
+        <v>152</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1964,19 +1963,19 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-14</v>
+        <v>-18.59235532407407</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>254824</v>
+        <v>253614</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1989,33 +1988,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>748.225</v>
+        <v>122.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14-11-2025 12:25:39</t>
+          <t>18-11-2025 14:12:59</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14-11-2025 13:13:39</t>
+          <t>18-11-2025 14:39:59</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>14-11-2025 13:13:39</t>
+          <t>18-11-2025 14:39:59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18-11-2025 09:41:53</t>
+          <t>19-11-2025 08:42:26</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>89787</v>
+        <v>14694</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2028,13 +2027,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>76</v>
-      </c>
-      <c r="O20" t="n">
-        <v>406232</v>
+        <v>152</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2044,11 +2040,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>0</v>
+        <v>-9.362806712962962</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -2056,46 +2052,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254599</v>
+        <v>254715</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>44.9</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18-11-2025 09:41:53</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>18-11-2025 10:25:53</t>
+          <t>14-11-2025 07:21:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18-11-2025 10:25:53</t>
+          <t>14-11-2025 07:21:00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-11-2025 11:10:47</t>
+          <t>14-11-2025 09:35:32</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5388</v>
+        <v>16145</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2104,78 +2100,80 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O21" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-2</v>
+        <v>-1.399681712962963</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254245</v>
+        <v>253650</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>89.8</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18-11-2025 11:10:47</t>
+          <t>14-11-2025 09:35:32</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>18-11-2025 11:35:47</t>
+          <t>14-11-2025 09:52:32</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18-11-2025 11:35:47</t>
+          <t>14-11-2025 09:52:32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18-11-2025 13:05:35</t>
+          <t>14-11-2025 14:25:40</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10776</v>
+        <v>32776</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2184,17 +2182,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>70</v>
-      </c>
-      <c r="O22" t="n">
-        <v>406372</v>
+        <v>76</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2208,54 +2203,54 @@
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-20</v>
+        <v>-25.60116319444445</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>253961</v>
+        <v>243569</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
-        <v>35.91666666666666</v>
+        <v>21.675</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18-11-2025 13:05:35</t>
+          <t>14-11-2025 14:25:40</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>18-11-2025 13:30:35</t>
+          <t>14-11-2025 14:44:40</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18-11-2025 13:30:35</t>
+          <t>14-11-2025 14:44:40</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18-11-2025 14:06:30</t>
+          <t>17-11-2025 07:06:21</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4310</v>
+        <v>2601</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2264,14 +2259,14 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O23" t="n">
         <v>406372</v>
@@ -2284,58 +2279,58 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-8</v>
+        <v>-60</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254101</v>
+        <v>254910</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>28.425</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18-11-2025 14:06:30</t>
+          <t>17-11-2025 07:06:21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:30</t>
+          <t>17-11-2025 07:23:21</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:30</t>
+          <t>17-11-2025 07:23:21</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19-11-2025 07:03:55</t>
+          <t>17-11-2025 08:36:53</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3411</v>
+        <v>8824</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2344,17 +2339,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O24" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2364,58 +2359,58 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254100</v>
+        <v>253382</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>28.425</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19-11-2025 07:03:55</t>
+          <t>17-11-2025 08:36:53</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19-11-2025 07:28:55</t>
+          <t>17-11-2025 08:53:53</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19-11-2025 07:28:55</t>
+          <t>17-11-2025 08:53:53</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19-11-2025 07:57:21</t>
+          <t>17-11-2025 10:18:59</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3411</v>
+        <v>10212</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2424,17 +2419,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O25" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2444,11 +2439,11 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="T25" t="n">
         <v>2</v>
@@ -2456,46 +2451,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254433</v>
+        <v>254276</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>67.84999999999999</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19-11-2025 07:57:21</t>
+          <t>17-11-2025 10:18:59</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19-11-2025 08:30:21</t>
+          <t>17-11-2025 10:50:59</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19-11-2025 08:30:21</t>
+          <t>17-11-2025 10:50:59</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:12</t>
+          <t>17-11-2025 11:28:01</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8142</v>
+        <v>4444</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2504,18 +2499,15 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
         <v>70</v>
       </c>
-      <c r="O26" t="n">
-        <v>406552</v>
-      </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
@@ -2524,58 +2516,58 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-2</v>
+        <v>-24.47778935185185</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254354</v>
+        <v>254429</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E27" t="n">
-        <v>18.675</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19-11-2025 09:38:12</t>
+          <t>17-11-2025 11:28:01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19-11-2025 10:09:12</t>
+          <t>17-11-2025 11:45:01</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>19-11-2025 10:09:12</t>
+          <t>17-11-2025 11:45:01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>19-11-2025 10:27:52</t>
+          <t>18-11-2025 07:45:15</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2241</v>
+        <v>28829</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2593,6 +2585,9 @@
       <c r="N27" t="n">
         <v>70</v>
       </c>
+      <c r="O27" t="n">
+        <v>406372</v>
+      </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
@@ -2601,11 +2596,11 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-15.43602430555556</v>
+        <v>-9</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -2613,46 +2608,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254252</v>
+        <v>235572</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>80.51666666666667</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19-11-2025 10:27:52</t>
+          <t>18-11-2025 07:45:15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19-11-2025 10:54:52</t>
+          <t>18-11-2025 08:00:15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>19-11-2025 10:54:52</t>
+          <t>18-11-2025 08:00:15</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>19-11-2025 12:15:23</t>
+          <t>18-11-2025 09:23:14</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>9662</v>
+        <v>9958</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2665,11 +2660,14 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
         <v>70</v>
       </c>
+      <c r="O28" t="n">
+        <v>406372</v>
+      </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
@@ -2678,11 +2676,11 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-26.51068865740741</v>
+        <v>-60</v>
       </c>
       <c r="T28" t="n">
         <v>4</v>
@@ -2690,46 +2688,46 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>253906</v>
+        <v>254375</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E29" t="n">
-        <v>45.79166666666666</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19-11-2025 12:15:23</t>
+          <t>18-11-2025 09:23:14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-11-2025 12:44:23</t>
+          <t>18-11-2025 09:40:14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19-11-2025 12:44:23</t>
+          <t>18-11-2025 09:40:14</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19-11-2025 13:30:11</t>
+          <t>18-11-2025 10:25:32</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5495</v>
+        <v>5435</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2738,15 +2736,18 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
+      <c r="O29" t="n">
+        <v>40624</v>
+      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2755,58 +2756,58 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>25-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-4.562627314814815</v>
+        <v>-12</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>253974</v>
+        <v>254586</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>28.425</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19-11-2025 13:30:11</t>
+          <t>18-11-2025 10:25:32</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-11-2025 14:03:11</t>
+          <t>18-11-2025 10:42:32</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>19-11-2025 14:03:11</t>
+          <t>18-11-2025 10:42:32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19-11-2025 14:31:36</t>
+          <t>18-11-2025 11:34:04</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3411</v>
+        <v>6185</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2819,13 +2820,13 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
       <c r="O30" t="n">
-        <v>406552</v>
+        <v>406372</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2835,58 +2836,58 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>29-10-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254419</v>
+        <v>254460</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>72.34166666666667</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19-11-2025 14:31:36</t>
+          <t>18-11-2025 11:34:04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20-11-2025 07:00:36</t>
+          <t>18-11-2025 11:51:04</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20-11-2025 07:00:36</t>
+          <t>18-11-2025 11:51:04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20-11-2025 08:12:57</t>
+          <t>18-11-2025 12:37:45</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>8681</v>
+        <v>5602</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2912,58 +2913,58 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-20.34232638888889</v>
+        <v>-36.52622106481481</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254339</v>
+        <v>254521</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E32" t="n">
-        <v>245.9666666666667</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20-11-2025 08:12:57</t>
+          <t>18-11-2025 12:37:45</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20-11-2025 08:39:57</t>
+          <t>18-11-2025 12:54:45</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20-11-2025 08:39:57</t>
+          <t>18-11-2025 12:54:45</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20-11-2025 12:45:55</t>
+          <t>18-11-2025 13:34:26</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>29516</v>
+        <v>4762</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2976,7 +2977,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -2989,11 +2990,11 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-31.53188657407408</v>
+        <v>-13.56558449074074</v>
       </c>
       <c r="T32" t="n">
         <v>7</v>
@@ -3001,46 +3002,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254547</v>
+        <v>254293</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>68.55</v>
+        <v>18.85</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20-11-2025 12:45:55</t>
+          <t>18-11-2025 13:34:26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20-11-2025 13:12:55</t>
+          <t>18-11-2025 13:55:26</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20-11-2025 13:12:55</t>
+          <t>18-11-2025 13:55:26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20-11-2025 14:21:28</t>
+          <t>18-11-2025 14:14:17</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>8226</v>
+        <v>2262</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3053,11 +3054,14 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
+      <c r="O33" t="n">
+        <v>40624</v>
+      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3066,11 +3070,11 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-11.59824074074074</v>
+        <v>-14</v>
       </c>
       <c r="T33" t="n">
         <v>7</v>
@@ -3078,46 +3082,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254967</v>
+        <v>254756</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E34" t="n">
-        <v>260.4166666666667</v>
+        <v>60.625</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>20-11-2025 14:21:28</t>
+          <t>18-11-2025 14:14:17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20-11-2025 14:52:28</t>
+          <t>18-11-2025 14:35:17</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20-11-2025 14:52:28</t>
+          <t>18-11-2025 14:35:17</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21-11-2025 11:12:53</t>
+          <t>19-11-2025 07:35:55</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>31250</v>
+        <v>7275</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3130,7 +3134,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
@@ -3143,19 +3147,19 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0</v>
+        <v>-5.316608796296296</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254556</v>
+        <v>254915</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3164,37 +3168,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E35" t="n">
-        <v>173.4166666666667</v>
+        <v>48.875</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>19-11-2025 07:35:55</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>19-11-2025 08:04:55</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14-11-2025 07:23:00</t>
+          <t>19-11-2025 08:04:55</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>19-11-2025 08:53:47</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>20810</v>
+        <v>5865</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3203,41 +3207,36 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>76</v>
-      </c>
-      <c r="O35" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>-1.42806712962963</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>253382</v>
+        <v>254574</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3250,33 +3249,33 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>85.09999999999999</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14-11-2025 10:16:25</t>
+          <t>19-11-2025 08:53:47</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14-11-2025 10:35:25</t>
+          <t>19-11-2025 09:10:47</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14-11-2025 10:35:25</t>
+          <t>19-11-2025 09:10:47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:31</t>
+          <t>19-11-2025 12:04:24</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>10212</v>
+        <v>20833</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3285,17 +3284,14 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M36" t="n">
         <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>76</v>
-      </c>
-      <c r="O36" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3305,19 +3301,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-12</v>
+        <v>-15.50305555555556</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>253865</v>
+        <v>254652</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3326,37 +3322,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E37" t="n">
-        <v>116.7583333333333</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>14-11-2025 12:00:31</t>
+          <t>19-11-2025 12:04:24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:31</t>
+          <t>19-11-2025 12:21:24</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14-11-2025 12:34:31</t>
+          <t>19-11-2025 12:21:24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14-11-2025 14:31:16</t>
+          <t>19-11-2025 12:50:08</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>14011</v>
+        <v>3448</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3369,7 +3365,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
@@ -3382,58 +3378,58 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-35.60505208333333</v>
+        <v>-8.534814814814816</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254758</v>
+        <v>254762</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="E38" t="n">
-        <v>61.38333333333333</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14-11-2025 14:31:16</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14-11-2025 14:48:16</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14-11-2025 14:48:16</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17-11-2025 07:49:39</t>
+          <t>13-11-2025 13:04:21</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>7366</v>
+        <v>3823</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3446,71 +3442,76 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
       </c>
-      <c r="P38" t="n">
-        <v>0</v>
+      <c r="O38" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.3261516203703704</v>
+        <v>-0.544693287037037</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>254237</v>
+        <v>253380</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>21</v>
+        <v>42.5</v>
       </c>
       <c r="E39" t="n">
-        <v>184.0916666666667</v>
+        <v>104.275</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>17-11-2025 07:49:39</t>
+          <t>13-11-2025 13:04:21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:39</t>
+          <t>13-11-2025 13:46:51</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>17-11-2025 08:10:39</t>
+          <t>13-11-2025 13:46:51</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>17-11-2025 11:14:45</t>
+          <t>14-11-2025 07:31:08</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>22091</v>
+        <v>12513</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3519,19 +3520,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
+      <c r="O39" t="n">
+        <v>40606</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3539,62 +3538,62 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>40651</v>
+        <v>40606</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-7.468576388888889</v>
+        <v>-0.313287037037037</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254457</v>
+        <v>244023</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>21</v>
+        <v>36.5</v>
       </c>
       <c r="E40" t="n">
-        <v>3.925</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>17-11-2025 11:14:45</t>
+          <t>14-11-2025 07:31:08</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17-11-2025 11:35:45</t>
+          <t>14-11-2025 08:07:38</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>17-11-2025 11:35:45</t>
+          <t>14-11-2025 08:07:38</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>17-11-2025 11:39:40</t>
+          <t>14-11-2025 08:15:56</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>471</v>
+        <v>997</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3607,13 +3606,13 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
       <c r="O40" t="n">
-        <v>406372</v>
+        <v>406062</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3623,11 +3622,11 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-1</v>
+        <v>-60</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
@@ -3635,46 +3634,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254283</v>
+        <v>255043</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>38.5</v>
       </c>
       <c r="E41" t="n">
-        <v>95.76666666666667</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17-11-2025 11:39:40</t>
+          <t>14-11-2025 08:15:56</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>17-11-2025 12:11:40</t>
+          <t>14-11-2025 08:54:26</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17-11-2025 12:11:40</t>
+          <t>14-11-2025 08:54:26</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17-11-2025 13:47:26</t>
+          <t>14-11-2025 11:58:43</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>11492</v>
+        <v>22114</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3683,17 +3682,17 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O41" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3703,11 +3702,11 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
@@ -3715,46 +3714,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254256</v>
+        <v>254189</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>30.5</v>
       </c>
       <c r="E42" t="n">
-        <v>50.925</v>
+        <v>55.875</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>17-11-2025 13:47:26</t>
+          <t>14-11-2025 11:58:43</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17-11-2025 14:21:26</t>
+          <t>14-11-2025 12:29:13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>17-11-2025 14:21:26</t>
+          <t>14-11-2025 12:29:13</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18-11-2025 07:12:22</t>
+          <t>14-11-2025 13:25:06</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>6111</v>
+        <v>6705</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3763,15 +3762,18 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
         <v>70</v>
       </c>
+      <c r="O42" t="n">
+        <v>406422</v>
+      </c>
       <c r="P42" t="n">
         <v>0</v>
       </c>
@@ -3780,58 +3782,58 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-25.30025462962963</v>
+        <v>-3</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254189</v>
+        <v>254433</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>30.5</v>
       </c>
       <c r="E43" t="n">
-        <v>55.875</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>18-11-2025 07:12:22</t>
+          <t>14-11-2025 13:25:06</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18-11-2025 07:29:22</t>
+          <t>14-11-2025 13:55:36</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18-11-2025 07:29:22</t>
+          <t>14-11-2025 13:55:36</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18-11-2025 08:25:14</t>
+          <t>17-11-2025 07:03:27</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>6705</v>
+        <v>8142</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3872,46 +3874,46 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254519</v>
+        <v>254230</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17</v>
+        <v>30.5</v>
       </c>
       <c r="E44" t="n">
-        <v>77.15833333333333</v>
+        <v>62.475</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>18-11-2025 08:25:14</t>
+          <t>17-11-2025 07:03:27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>18-11-2025 08:42:14</t>
+          <t>17-11-2025 07:33:57</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18-11-2025 08:42:14</t>
+          <t>17-11-2025 07:33:57</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>18-11-2025 09:59:24</t>
+          <t>17-11-2025 08:36:25</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9259</v>
+        <v>7497</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3920,15 +3922,18 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>70</v>
       </c>
+      <c r="O44" t="n">
+        <v>406422</v>
+      </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
@@ -3937,58 +3942,58 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-11.41625</v>
+        <v>-15</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254653</v>
+        <v>254188</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>34.5</v>
       </c>
       <c r="E45" t="n">
-        <v>64.40833333333333</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18-11-2025 09:59:24</t>
+          <t>17-11-2025 08:36:25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18-11-2025 10:16:24</t>
+          <t>17-11-2025 09:10:55</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18-11-2025 10:16:24</t>
+          <t>17-11-2025 09:10:55</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18-11-2025 11:20:48</t>
+          <t>17-11-2025 09:48:22</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>7729</v>
+        <v>4493</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4006,6 +4011,9 @@
       <c r="N45" t="n">
         <v>70</v>
       </c>
+      <c r="O45" t="n">
+        <v>406372</v>
+      </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
@@ -4014,19 +4022,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-4.472783564814815</v>
+        <v>-1</v>
       </c>
       <c r="T45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254481</v>
+        <v>254451</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4042,30 +4050,30 @@
         <v>32.5</v>
       </c>
       <c r="E46" t="n">
-        <v>81.16666666666667</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>17-11-2025 09:48:22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>17-11-2025 10:20:52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>17-11-2025 10:20:52</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>18-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9740</v>
+        <v>38537</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4078,29 +4086,24 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
         <v>70</v>
       </c>
-      <c r="O46" t="n">
-        <v>40642</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P46" t="n">
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40642</v>
+        <v>0</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>0</v>
+        <v>-10.32083912037037</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254762</v>
+        <v>254107</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4117,37 +4120,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="E47" t="n">
-        <v>31.85833333333333</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>13-11-2025 13:53:40</t>
+          <t>18-11-2025 07:42:00</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>18-11-2025 08:14:30</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13-11-2025 14:28:10</t>
+          <t>18-11-2025 08:14:30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>18-11-2025 11:09:34</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3823</v>
+        <v>21007</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4160,37 +4163,32 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
         <v>70</v>
       </c>
-      <c r="O47" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P47" t="n">
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-1.291684027777778</v>
+        <v>-37.46497685185185</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>253380</v>
+        <v>254381</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4203,33 +4201,33 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>42.5</v>
+        <v>32.5</v>
       </c>
       <c r="E48" t="n">
-        <v>104.275</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:01</t>
+          <t>18-11-2025 11:09:34</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:31</t>
+          <t>18-11-2025 11:42:04</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:31</t>
+          <t>18-11-2025 11:42:04</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>14-11-2025 09:26:48</t>
+          <t>18-11-2025 13:05:56</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>12513</v>
+        <v>10064</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4242,29 +4240,24 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
         <v>70</v>
       </c>
-      <c r="O48" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P48" t="n">
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-0.3936111111111111</v>
+        <v>-21.54578703703704</v>
       </c>
       <c r="T48" t="n">
         <v>7</v>
@@ -4272,46 +4265,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254460</v>
+        <v>254714</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="E49" t="n">
-        <v>46.68333333333333</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>14-11-2025 09:26:48</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14-11-2025 10:07:18</t>
+          <t>13-11-2025 12:50:00</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>14-11-2025 10:07:18</t>
+          <t>13-11-2025 12:50:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>14-11-2025 10:53:59</t>
+          <t>13-11-2025 14:21:28</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>5602</v>
+        <v>10977</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4320,75 +4313,80 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>70</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O49" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-32.45415509259259</v>
+        <v>-0.5982465277777778</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254429</v>
+        <v>253897</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>32.5</v>
+        <v>55</v>
       </c>
       <c r="E50" t="n">
-        <v>240.2416666666667</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14-11-2025 10:53:59</t>
+          <t>13-11-2025 14:21:28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 11:26:29</t>
+          <t>14-11-2025 07:16:28</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 11:26:29</t>
+          <t>14-11-2025 07:16:28</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>17-11-2025 07:26:43</t>
+          <t>14-11-2025 08:50:29</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>28829</v>
+        <v>11282</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4397,78 +4395,80 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N50" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O50" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-9</v>
+        <v>-0.3683969907407407</v>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254188</v>
+        <v>254512</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>32.5</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
-        <v>37.44166666666667</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>17-11-2025 07:26:43</t>
+          <t>14-11-2025 08:50:29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>17-11-2025 07:59:13</t>
+          <t>14-11-2025 09:50:29</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>17-11-2025 07:59:13</t>
+          <t>14-11-2025 09:50:29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:40</t>
+          <t>14-11-2025 10:50:03</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4493</v>
+        <v>7147</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4477,17 +4477,17 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M51" t="n">
         <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O51" t="n">
-        <v>406372</v>
+        <v>406232</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
@@ -4509,46 +4509,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254437</v>
+        <v>254287</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30.5</v>
+        <v>40</v>
       </c>
       <c r="E52" t="n">
-        <v>58.05833333333333</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:40</t>
+          <t>14-11-2025 10:50:03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17-11-2025 09:07:10</t>
+          <t>14-11-2025 11:30:03</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>17-11-2025 09:07:10</t>
+          <t>14-11-2025 11:30:03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17-11-2025 10:05:13</t>
+          <t>14-11-2025 13:39:41</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>6967</v>
+        <v>15556</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4561,13 +4561,13 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
         <v>70</v>
       </c>
       <c r="O52" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4577,138 +4577,140 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>244023</v>
+        <v>254427</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>34.5</v>
+        <v>40</v>
       </c>
       <c r="E53" t="n">
-        <v>8.308333333333334</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17-11-2025 10:05:13</t>
+          <t>14-11-2025 13:39:41</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:43</t>
+          <t>14-11-2025 14:19:41</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17-11-2025 10:39:43</t>
+          <t>14-11-2025 14:19:41</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:02</t>
+          <t>17-11-2025 07:15:14</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>997</v>
+        <v>6667</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>70</v>
       </c>
       <c r="O53" t="n">
-        <v>406062</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
+        <v>406422</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-417</v>
+        <v>-7.302251157407407</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>253838</v>
+        <v>254457</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.5</v>
+        <v>45</v>
       </c>
       <c r="E54" t="n">
-        <v>108.3666666666667</v>
+        <v>3.925</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17-11-2025 10:48:02</t>
+          <t>17-11-2025 07:15:14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17-11-2025 11:20:32</t>
+          <t>17-11-2025 08:00:14</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-11-2025 11:20:32</t>
+          <t>17-11-2025 08:00:14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17-11-2025 13:08:54</t>
+          <t>17-11-2025 08:04:10</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>13004</v>
+        <v>471</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4721,11 +4723,14 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>70</v>
       </c>
+      <c r="O54" t="n">
+        <v>406372</v>
+      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
@@ -4734,58 +4739,58 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-21.54784722222222</v>
+        <v>-1</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254107</v>
+        <v>254437</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>32.5</v>
+        <v>25</v>
       </c>
       <c r="E55" t="n">
-        <v>175.0583333333333</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17-11-2025 13:08:54</t>
+          <t>17-11-2025 08:04:10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-11-2025 13:41:24</t>
+          <t>17-11-2025 08:29:10</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-11-2025 13:41:24</t>
+          <t>17-11-2025 08:29:10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>18-11-2025 08:36:27</t>
+          <t>17-11-2025 09:27:13</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>21007</v>
+        <v>6967</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4803,6 +4808,9 @@
       <c r="N55" t="n">
         <v>70</v>
       </c>
+      <c r="O55" t="n">
+        <v>406372</v>
+      </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
@@ -4811,58 +4819,58 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-37.35865162037037</v>
+        <v>-1</v>
       </c>
       <c r="T55" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254381</v>
+        <v>254605</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="E56" t="n">
-        <v>83.86666666666666</v>
+        <v>39.025</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>18-11-2025 08:36:27</t>
+          <t>17-11-2025 09:27:13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>18-11-2025 09:08:57</t>
+          <t>17-11-2025 09:57:13</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18-11-2025 09:08:57</t>
+          <t>17-11-2025 09:57:13</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18-11-2025 10:32:49</t>
+          <t>17-11-2025 10:36:15</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>10064</v>
+        <v>4683</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4871,11 +4879,11 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>70</v>
@@ -4888,58 +4896,58 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-21.43946180555556</v>
+        <v>-3.441840277777778</v>
       </c>
       <c r="T56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254756</v>
+        <v>254758</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>42.5</v>
+        <v>30</v>
       </c>
       <c r="E57" t="n">
-        <v>60.625</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>18-11-2025 10:32:49</t>
+          <t>17-11-2025 10:36:15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18-11-2025 11:15:19</t>
+          <t>17-11-2025 11:06:15</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>18-11-2025 11:15:19</t>
+          <t>17-11-2025 11:06:15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>18-11-2025 12:15:57</t>
+          <t>17-11-2025 12:07:38</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>7275</v>
+        <v>7366</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4952,7 +4960,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
         <v>70</v>
@@ -4965,19 +4973,19 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-4.511076388888889</v>
+        <v>-0.5053009259259259</v>
       </c>
       <c r="T57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254713</v>
+        <v>253865</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4986,37 +4994,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E58" t="n">
-        <v>49.96666666666667</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>17-11-2025 12:07:38</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>17-11-2025 12:37:38</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>13-11-2025 12:45:00</t>
+          <t>17-11-2025 12:37:38</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>13-11-2025 13:34:58</t>
+          <t>17-11-2025 14:34:23</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>5996</v>
+        <v>14011</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5025,33 +5033,28 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>76</v>
-      </c>
-      <c r="O58" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-0.565949074074074</v>
+        <v>-38.60721643518519</v>
       </c>
       <c r="T58" t="n">
         <v>2</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>253694</v>
+        <v>254245</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5068,37 +5071,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E59" t="n">
-        <v>121.7583333333333</v>
+        <v>89.8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>13-11-2025 13:34:58</t>
+          <t>17-11-2025 14:34:23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>13-11-2025 14:14:58</t>
+          <t>18-11-2025 07:04:23</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>13-11-2025 14:14:58</t>
+          <t>18-11-2025 07:04:23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:43</t>
+          <t>18-11-2025 08:34:11</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>14611</v>
+        <v>10776</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5107,41 +5110,36 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
         <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>76</v>
-      </c>
-      <c r="O59" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-1.344947916666667</v>
+        <v>-29.3570775462963</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>253650</v>
+        <v>253961</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5150,37 +5148,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E60" t="n">
-        <v>273.1333333333333</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:16:43</t>
+          <t>18-11-2025 08:34:11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:46:43</t>
+          <t>18-11-2025 08:59:11</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14-11-2025 08:46:43</t>
+          <t>18-11-2025 08:59:11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14-11-2025 13:19:51</t>
+          <t>18-11-2025 09:35:06</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>32776</v>
+        <v>4310</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5189,14 +5187,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5206,19 +5204,19 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-25.55545717592593</v>
+        <v>-17.39938078703704</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>254675</v>
+        <v>252811</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5227,37 +5225,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E61" t="n">
-        <v>153.9583333333333</v>
+        <v>11.875</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14-11-2025 13:19:51</t>
+          <t>18-11-2025 09:35:06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14-11-2025 13:54:51</t>
+          <t>18-11-2025 10:05:06</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14-11-2025 13:54:51</t>
+          <t>18-11-2025 10:05:06</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17-11-2025 08:28:49</t>
+          <t>18-11-2025 10:16:59</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>18475</v>
+        <v>1425</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5266,17 +5264,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
-        <v>76</v>
-      </c>
-      <c r="O61" t="n">
-        <v>406422</v>
+        <v>70</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5286,19 +5281,19 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-4</v>
+        <v>-15.42846064814815</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254910</v>
+        <v>254598</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5307,37 +5302,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E62" t="n">
-        <v>73.53333333333333</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>17-11-2025 08:28:49</t>
+          <t>18-11-2025 10:16:59</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17-11-2025 08:58:49</t>
+          <t>18-11-2025 11:21:59</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>17-11-2025 08:58:49</t>
+          <t>18-11-2025 11:21:59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>17-11-2025 10:12:21</t>
+          <t>18-11-2025 13:06:14</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>8824</v>
+        <v>12511</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5346,17 +5341,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N62" t="n">
-        <v>76</v>
-      </c>
-      <c r="O62" t="n">
-        <v>406372</v>
+        <v>70</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5366,7 +5358,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -5378,46 +5370,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254451</v>
+        <v>254556</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E63" t="n">
-        <v>321.1416666666667</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>17-11-2025 10:12:21</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>17-11-2025 10:52:21</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17-11-2025 10:52:21</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>18-11-2025 08:13:29</t>
+          <t>14-11-2025 10:12:25</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>38537</v>
+        <v>20810</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5426,75 +5418,80 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>70</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O63" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-10.3427025462963</v>
+        <v>-1.425289351851852</v>
       </c>
       <c r="T63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254652</v>
+        <v>254165</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>28.73333333333333</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>18-11-2025 08:13:29</t>
+          <t>14-11-2025 10:12:25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18-11-2025 08:43:29</t>
+          <t>14-11-2025 10:29:25</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>18-11-2025 08:43:29</t>
+          <t>14-11-2025 10:29:25</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>18-11-2025 09:12:13</t>
+          <t>14-11-2025 11:27:44</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>3448</v>
+        <v>6998</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5503,75 +5500,80 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
         <v>4</v>
       </c>
       <c r="N64" t="n">
-        <v>70</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O64" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-7.383489583333334</v>
+        <v>-0.4775925925925926</v>
       </c>
       <c r="T64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>254598</v>
+        <v>254117</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="E65" t="n">
-        <v>104.2583333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>18-11-2025 09:12:13</t>
+          <t>14-11-2025 11:27:44</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>18-11-2025 10:22:13</t>
+          <t>14-11-2025 11:44:44</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>18-11-2025 10:22:13</t>
+          <t>14-11-2025 11:44:44</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>18-11-2025 12:06:29</t>
+          <t>14-11-2025 11:53:54</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>12511</v>
+        <v>1100</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5580,14 +5582,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -5597,58 +5599,58 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>0</v>
+        <v>-35.49576388888889</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254651</v>
+        <v>254283</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>22.64166666666667</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18-11-2025 12:06:29</t>
+          <t>14-11-2025 11:53:54</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>18-11-2025 13:21:29</t>
+          <t>14-11-2025 12:12:54</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18-11-2025 13:21:29</t>
+          <t>14-11-2025 12:12:54</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>18-11-2025 13:44:07</t>
+          <t>14-11-2025 13:48:40</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>2717</v>
+        <v>11492</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5657,14 +5659,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O66" t="n">
+        <v>406372</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -5674,58 +5679,58 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-7.572309027777778</v>
+        <v>-8</v>
       </c>
       <c r="T66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>254166</v>
+        <v>254385</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E67" t="n">
-        <v>38.85</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18-11-2025 13:44:07</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18-11-2025 14:19:07</t>
+          <t>14-11-2025 07:40:00</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>18-11-2025 14:19:07</t>
+          <t>14-11-2025 07:40:00</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18-11-2025 14:57:58</t>
+          <t>14-11-2025 08:32:05</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>4662</v>
+        <v>6250</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5734,78 +5739,80 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="O67" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
+        <v>40627</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>40627</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>0</v>
+        <v>-0.3556134259259259</v>
       </c>
       <c r="T67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254385</v>
+        <v>254903</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E68" t="n">
-        <v>52.08333333333334</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 08:32:05</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:00</t>
+          <t>14-11-2025 09:12:05</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:00</t>
+          <t>14-11-2025 09:12:05</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:05</t>
+          <t>14-11-2025 13:28:43</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>6250</v>
+        <v>30797</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5814,80 +5821,75 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
         <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>152</v>
-      </c>
-      <c r="O68" t="n">
-        <v>40627</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>40627</v>
+        <v>0</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>-0.3514467592592593</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254198</v>
+        <v>252061</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E69" t="n">
-        <v>215</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:05</t>
+          <t>14-11-2025 13:28:43</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14-11-2025 08:43:05</t>
+          <t>14-11-2025 14:03:43</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14-11-2025 08:43:05</t>
+          <t>14-11-2025 14:03:43</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>14-11-2025 12:18:05</t>
+          <t>14-11-2025 14:39:53</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>25800</v>
+        <v>4340</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5896,28 +5898,33 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>152</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O69" t="n">
+        <v>40628</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>-25.51255787037037</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
@@ -5925,46 +5932,46 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>253614</v>
+        <v>254237</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>122.45</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14-11-2025 12:18:05</t>
+          <t>14-11-2025 14:39:53</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:05</t>
+          <t>17-11-2025 07:14:53</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14-11-2025 12:35:05</t>
+          <t>17-11-2025 07:14:53</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>14-11-2025 14:37:32</t>
+          <t>17-11-2025 10:18:59</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>14694</v>
+        <v>22091</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5973,40 +5980,47 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N70" t="n">
-        <v>152</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-4.609398148148149</v>
+        <v>-7.429849537037037</v>
       </c>
       <c r="T70" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254309</v>
+        <v>254519</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6015,33 +6029,33 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E71" t="n">
-        <v>900.0166666666667</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14-11-2025 14:37:32</t>
+          <t>17-11-2025 10:18:59</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14-11-2025 14:54:32</t>
+          <t>17-11-2025 11:03:59</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>14-11-2025 14:54:32</t>
+          <t>17-11-2025 11:03:59</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>18-11-2025 13:54:33</t>
+          <t>17-11-2025 12:21:08</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>108002</v>
+        <v>9259</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6050,36 +6064,36 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>70</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>17-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S71" s="1" t="n">
+        <v>-10.51468171296296</v>
+      </c>
+      <c r="T71" t="n">
         <v>4</v>
-      </c>
-      <c r="N71" t="n">
-        <v>152</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>10-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S71" s="1" t="n">
-        <v>-18.57954861111111</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254714</v>
+        <v>254256</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6088,37 +6102,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E72" t="n">
-        <v>91.47499999999999</v>
+        <v>50.925</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 12:21:08</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>17-11-2025 12:46:08</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14-11-2025 07:50:00</t>
+          <t>17-11-2025 12:46:08</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>17-11-2025 13:37:04</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>10977</v>
+        <v>6111</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6127,41 +6141,39 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-1.389913194444444</v>
+        <v>-18</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254106</v>
+        <v>254653</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6170,37 +6182,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E73" t="n">
-        <v>107.6416666666667</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>14-11-2025 09:21:28</t>
+          <t>17-11-2025 13:37:04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>17-11-2025 14:07:04</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14-11-2025 09:56:28</t>
+          <t>17-11-2025 14:07:04</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:07</t>
+          <t>18-11-2025 07:11:28</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>12917</v>
+        <v>7729</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6226,11 +6238,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-38.48896990740741</v>
+        <v>-4.299635416666667</v>
       </c>
       <c r="T73" t="n">
         <v>7</v>
@@ -6238,7 +6250,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254287</v>
+        <v>254365</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6247,37 +6259,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>30</v>
       </c>
       <c r="E74" t="n">
-        <v>129.6333333333333</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:07</t>
+          <t>18-11-2025 07:11:28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14-11-2025 12:14:07</t>
+          <t>18-11-2025 07:41:28</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14-11-2025 12:14:07</t>
+          <t>18-11-2025 07:41:28</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>14-11-2025 14:23:45</t>
+          <t>18-11-2025 08:49:00</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>15556</v>
+        <v>8104</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6290,14 +6302,11 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
       </c>
-      <c r="O74" t="n">
-        <v>406422</v>
-      </c>
       <c r="P74" t="n">
         <v>0</v>
       </c>
@@ -6306,19 +6315,19 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-18</v>
+        <v>-14.36736689814815</v>
       </c>
       <c r="T74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254574</v>
+        <v>254651</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6331,33 +6340,33 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>173.6083333333333</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:23:45</t>
+          <t>18-11-2025 08:49:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:48:45</t>
+          <t>18-11-2025 09:24:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>14-11-2025 14:48:45</t>
+          <t>18-11-2025 09:24:00</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>17-11-2025 09:42:21</t>
+          <t>18-11-2025 09:46:39</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>20833</v>
+        <v>2717</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6375,9 +6384,6 @@
       <c r="N75" t="n">
         <v>70</v>
       </c>
-      <c r="O75" t="n">
-        <v>406422</v>
-      </c>
       <c r="P75" t="n">
         <v>0</v>
       </c>
@@ -6386,58 +6392,58 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-7</v>
+        <v>-7.407395833333333</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254903</v>
+        <v>253694</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>35</v>
       </c>
       <c r="E76" t="n">
-        <v>256.6416666666667</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>17-11-2025 09:42:21</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:21</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>17-11-2025 10:17:21</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:00</t>
+          <t>14-11-2025 09:36:45</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>30797</v>
+        <v>14611</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6446,75 +6452,80 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76" t="n">
-        <v>70</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O76" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>0</v>
+        <v>-1.40052662037037</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>252811</v>
+        <v>254824</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>11.875</v>
+        <v>748.225</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:00</t>
+          <t>14-11-2025 09:36:45</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>18-11-2025 07:09:00</t>
+          <t>14-11-2025 10:11:45</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>18-11-2025 07:09:00</t>
+          <t>14-11-2025 10:11:45</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>18-11-2025 07:20:52</t>
+          <t>17-11-2025 14:39:59</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>1425</v>
+        <v>89787</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6523,14 +6534,17 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O77" t="n">
+        <v>406232</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6540,11 +6554,11 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>-15.30616319444444</v>
+        <v>0</v>
       </c>
       <c r="T77" t="n">
         <v>7</v>
@@ -6552,46 +6566,46 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254586</v>
+        <v>254599</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E78" t="n">
-        <v>51.54166666666666</v>
+        <v>44.9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:20:52</t>
+          <t>17-11-2025 14:39:59</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:55:52</t>
+          <t>18-11-2025 07:19:59</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:55:52</t>
+          <t>18-11-2025 07:19:59</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18-11-2025 08:47:25</t>
+          <t>18-11-2025 08:04:53</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>6185</v>
+        <v>5388</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6604,7 +6618,7 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
@@ -6620,58 +6634,58 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>254915</v>
+        <v>254356</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E79" t="n">
-        <v>48.875</v>
+        <v>179.6</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:47:25</t>
+          <t>18-11-2025 08:04:53</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18-11-2025 09:17:25</t>
+          <t>18-11-2025 08:29:53</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18-11-2025 09:17:25</t>
+          <t>18-11-2025 08:29:53</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 10:06:17</t>
+          <t>18-11-2025 11:29:29</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>5865</v>
+        <v>21552</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6680,15 +6694,18 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
         <v>70</v>
       </c>
+      <c r="O79" t="n">
+        <v>406372</v>
+      </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
@@ -6697,58 +6714,58 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="T79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254512</v>
+        <v>254291</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E80" t="n">
-        <v>59.55833333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18-11-2025 10:06:17</t>
+          <t>18-11-2025 11:29:29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18-11-2025 10:46:17</t>
+          <t>18-11-2025 12:04:29</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18-11-2025 10:46:17</t>
+          <t>18-11-2025 12:04:29</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18-11-2025 11:45:51</t>
+          <t>18-11-2025 12:23:20</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>7147</v>
+        <v>2262</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6757,17 +6774,17 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O80" t="n">
-        <v>406232</v>
+        <v>40624</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -6777,23 +6794,23 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>254521</v>
+        <v>254609</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6802,49 +6819,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>39.68333333333333</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>18-11-2025 11:45:51</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:51</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>18-11-2025 12:20:51</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>18-11-2025 13:00:32</t>
+          <t>12-11-2025 13:56:40</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>4762</v>
+        <v>50000</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>40655</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -6854,74 +6874,74 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-13.54203703703704</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254365</v>
+        <v>252980</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>67.53333333333333</v>
+        <v>17.075</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>18-11-2025 13:00:32</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18-11-2025 13:35:32</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>18-11-2025 13:35:32</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18-11-2025 14:43:04</t>
+          <t>14-11-2025 07:17:04</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>8104</v>
+        <v>2049</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6931,77 +6951,77 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-14.61324074074074</v>
+        <v>-60</v>
       </c>
       <c r="T82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>254129</v>
+        <v>254428</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>44.5</v>
+        <v>48.30833333333333</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:30</t>
+          <t>17-11-2025 14:48:18</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>5340</v>
+        <v>5797</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O83" t="n">
-        <v>40623</v>
+        <v>40649</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -7009,97 +7029,92 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>40623</v>
+        <v>40649</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-1.346875</v>
+        <v>-7.616880787037037</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254156</v>
+        <v>254173</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>15-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>87.47499999999999</v>
+        <v>202.5916666666667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>14-11-2025 08:19:30</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14-11-2025 08:59:30</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>14-11-2025 08:59:30</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>14-11-2025 10:26:58</t>
+          <t>18-11-2025 09:22:35</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>10497</v>
+        <v>24311</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>76</v>
-      </c>
-      <c r="O84" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
-        <v>-0.4353993055555556</v>
+        <v>-39.39068865740741</v>
       </c>
       <c r="T84" t="n">
         <v>7</v>
@@ -7107,46 +7122,46 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>254165</v>
+        <v>254671</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E85" t="n">
-        <v>58.31666666666667</v>
+        <v>136.1666666666667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>14-11-2025 10:26:58</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14-11-2025 10:51:58</t>
+          <t>18-11-2025 14:45:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>14-11-2025 10:51:58</t>
+          <t>18-11-2025 14:45:00</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>14-11-2025 11:50:17</t>
+          <t>19-11-2025 09:01:10</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>6998</v>
+        <v>16340</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7155,80 +7170,75 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N85" t="n">
-        <v>76</v>
-      </c>
-      <c r="O85" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>-0.4932581018518519</v>
+        <v>-8.375810185185186</v>
       </c>
       <c r="T85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>250284</v>
+        <v>254967</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>20-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E86" t="n">
-        <v>146.35</v>
+        <v>260.4166666666667</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>14-11-2025 11:50:17</t>
+          <t>20-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14-11-2025 12:40:17</t>
+          <t>20-11-2025 14:29:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>14-11-2025 12:40:17</t>
+          <t>20-11-2025 14:29:00</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>17-11-2025 07:06:38</t>
+          <t>21-11-2025 10:49:25</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>17562</v>
+        <v>31250</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7241,7 +7251,7 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N86" t="n">
         <v>70</v>
@@ -7254,58 +7264,58 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>-260.2962789351852</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>254187</v>
+        <v>254101</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E87" t="n">
-        <v>46.39166666666667</v>
+        <v>28.425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>17-11-2025 07:06:38</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:38</t>
+          <t>18-11-2025 14:35:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>17-11-2025 07:56:38</t>
+          <t>18-11-2025 14:35:00</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>17-11-2025 08:43:02</t>
+          <t>19-11-2025 07:03:25</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>5567</v>
+        <v>3411</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7318,14 +7328,11 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N87" t="n">
         <v>70</v>
       </c>
-      <c r="O87" t="n">
-        <v>406372</v>
-      </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
@@ -7334,58 +7341,58 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>-1</v>
+        <v>-26.29404513888889</v>
       </c>
       <c r="T87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>254893</v>
+        <v>253974</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D88" t="n">
         <v>25</v>
       </c>
       <c r="E88" t="n">
-        <v>46.675</v>
+        <v>28.425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>17-11-2025 08:43:02</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:02</t>
+          <t>19-11-2025 14:25:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:02</t>
+          <t>19-11-2025 14:25:00</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:42</t>
+          <t>19-11-2025 14:53:25</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>5601</v>
+        <v>3411</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7398,14 +7405,11 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N88" t="n">
         <v>70</v>
       </c>
-      <c r="O88" t="n">
-        <v>406372</v>
-      </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
@@ -7414,58 +7418,58 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>29-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
-        <v>0</v>
+        <v>-31.62043402777778</v>
       </c>
       <c r="T88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>254546</v>
+        <v>254100</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E89" t="n">
-        <v>109.4083333333333</v>
+        <v>28.425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>17-11-2025 09:54:42</t>
+          <t>19-11-2025 14:53:25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>17-11-2025 10:24:42</t>
+          <t>20-11-2025 07:18:25</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>17-11-2025 10:24:42</t>
+          <t>20-11-2025 07:18:25</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>17-11-2025 12:14:07</t>
+          <t>20-11-2025 07:46:51</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>13129</v>
+        <v>3411</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7478,14 +7482,11 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N89" t="n">
         <v>70</v>
       </c>
-      <c r="O89" t="n">
-        <v>406242</v>
-      </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
@@ -7494,77 +7495,74 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
-        <v>-7</v>
+        <v>-27.32420138888889</v>
       </c>
       <c r="T89" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>254609</v>
+        <v>254354</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
-        <v>416.6666666666667</v>
+        <v>18.675</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>18-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>12-11-2025 13:56:40</t>
+          <t>18-11-2025 14:37:40</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>50000</v>
+        <v>2241</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>40655</v>
+        <v>70</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7574,74 +7572,74 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
-        <v>0</v>
+        <v>-14.60949652777778</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>252980</v>
+        <v>254252</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="E91" t="n">
-        <v>17.075</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 14:36:30</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 14:36:30</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14-11-2025 07:17:04</t>
+          <t>19-11-2025 07:57:01</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>2049</v>
+        <v>9662</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -7651,93 +7649,88 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
-        <v>-77.30352430555556</v>
+        <v>-26.33126157407407</v>
       </c>
       <c r="T91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>254428</v>
+        <v>254339</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E92" t="n">
-        <v>48.30833333333333</v>
+        <v>245.9666666666667</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:32:00</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:32:00</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>17-11-2025 14:48:18</t>
+          <t>19-11-2025 10:37:58</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>5797</v>
+        <v>29516</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N92" t="n">
         <v>70</v>
       </c>
-      <c r="O92" t="n">
-        <v>40649</v>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P92" t="n">
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
-        <v>-7.616880787037037</v>
+        <v>-30.44303240740741</v>
       </c>
       <c r="T92" t="n">
         <v>7</v>
@@ -7745,73 +7738,68 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>254427</v>
+        <v>254419</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E93" t="n">
-        <v>55.55833333333333</v>
+        <v>72.34166666666667</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>17-11-2025 14:55:33</t>
+          <t>19-11-2025 07:52:20</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>6667</v>
+        <v>8681</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N93" t="n">
         <v>70</v>
       </c>
-      <c r="O93" t="n">
-        <v>40649</v>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P93" t="n">
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -7819,7 +7807,7 @@
         </is>
       </c>
       <c r="S93" s="1" t="n">
-        <v>-7.621915509259259</v>
+        <v>-19.3280150462963</v>
       </c>
       <c r="T93" t="n">
         <v>7</v>
@@ -7827,62 +7815,62 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>254173</v>
+        <v>254547</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>15-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E94" t="n">
-        <v>202.5916666666667</v>
+        <v>68.55</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>19-11-2025 14:17:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>19-11-2025 14:17:00</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>18-11-2025 09:22:35</t>
+          <t>20-11-2025 07:25:33</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>24311</v>
+        <v>8226</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
@@ -7892,11 +7880,11 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
-        <v>-39.39068865740741</v>
+        <v>-11.30940972222222</v>
       </c>
       <c r="T94" t="n">
         <v>7</v>
@@ -7904,11 +7892,11 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>254671</v>
+        <v>253906</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7917,33 +7905,33 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E95" t="n">
-        <v>136.1666666666667</v>
+        <v>45.79166666666666</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>19-11-2025 07:52:20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>18-11-2025 14:55:00</t>
+          <t>19-11-2025 08:27:20</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>18-11-2025 14:55:00</t>
+          <t>19-11-2025 08:27:20</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>19-11-2025 09:11:10</t>
+          <t>19-11-2025 09:13:08</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>16340</v>
+        <v>5495</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7952,11 +7940,11 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N95" t="n">
         <v>70</v>
@@ -7969,14 +7957,14 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>25-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
-        <v>-8.38275462962963</v>
+        <v>-4.38412037037037</v>
       </c>
       <c r="T95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -707,7 +707,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254713</v>
+        <v>254714</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>49.96666666666667</v>
+        <v>91.47499999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -732,21 +732,21 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:38:40</t>
+          <t>14-11-2025 07:34:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:38:40</t>
+          <t>14-11-2025 07:34:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 08:28:38</t>
+          <t>14-11-2025 09:06:08</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5996</v>
+        <v>10977</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
@@ -777,11 +777,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-1.353217592592593</v>
+        <v>-1.379265046296296</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
@@ -789,7 +789,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>254675</v>
+        <v>254910</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -805,30 +805,30 @@
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>153.9583333333333</v>
+        <v>73.53333333333333</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:28:38</t>
+          <t>14-11-2025 09:06:08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:45:38</t>
+          <t>14-11-2025 09:23:08</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 08:45:38</t>
+          <t>14-11-2025 09:23:08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 11:19:35</t>
+          <t>14-11-2025 10:36:40</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18475</v>
+        <v>8824</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
         <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -857,19 +857,19 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>255039</v>
+        <v>254675</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -882,33 +882,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>9.15</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:19:35</t>
+          <t>14-11-2025 10:36:40</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:53:35</t>
+          <t>14-11-2025 10:53:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 11:53:35</t>
+          <t>14-11-2025 10:53:40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 12:02:44</t>
+          <t>14-11-2025 13:27:38</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1098</v>
+        <v>18475</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,17 +917,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O6" t="n">
-        <v>40624</v>
+        <v>406422</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -937,19 +937,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254546</v>
+        <v>252061</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -962,33 +962,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>109.4083333333333</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:02:44</t>
+          <t>14-11-2025 13:27:38</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:19:44</t>
+          <t>14-11-2025 14:01:38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 12:19:44</t>
+          <t>14-11-2025 14:01:38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:09</t>
+          <t>14-11-2025 14:37:48</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13129</v>
+        <v>4340</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1001,35 +1001,37 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
         <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>406242</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
+        <v>40628</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254893</v>
+        <v>254460</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1038,37 +1040,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>46.675</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:09:09</t>
+          <t>14-11-2025 14:37:48</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:26:09</t>
+          <t>14-11-2025 14:54:48</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:26:09</t>
+          <t>14-11-2025 14:54:48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:12:49</t>
+          <t>17-11-2025 07:41:29</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5601</v>
+        <v>5602</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1081,14 +1083,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>70</v>
       </c>
-      <c r="O8" t="n">
-        <v>406372</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1097,11 +1096,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>0</v>
+        <v>-35.32047453703704</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1109,7 +1108,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254187</v>
+        <v>254375</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1118,37 +1117,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>46.39166666666667</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:12:49</t>
+          <t>17-11-2025 07:41:29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:27:49</t>
+          <t>17-11-2025 08:02:29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:27:49</t>
+          <t>17-11-2025 08:02:29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:14:13</t>
+          <t>17-11-2025 08:47:46</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5567</v>
+        <v>5435</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1161,13 +1160,13 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>406372</v>
+        <v>40624</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1177,19 +1176,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254166</v>
+        <v>254256</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1198,37 +1197,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>38.85</v>
+        <v>50.925</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:14:13</t>
+          <t>17-11-2025 08:47:46</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:13</t>
+          <t>17-11-2025 09:04:46</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:13</t>
+          <t>17-11-2025 09:04:46</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:04</t>
+          <t>17-11-2025 09:55:42</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4662</v>
+        <v>6111</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1247,7 +1246,7 @@
         <v>70</v>
       </c>
       <c r="O10" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1257,19 +1256,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254555</v>
+        <v>254519</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1278,37 +1277,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>172.9833333333333</v>
+        <v>77.15833333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:08:04</t>
+          <t>17-11-2025 09:55:42</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:40:04</t>
+          <t>17-11-2025 10:10:42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:40:04</t>
+          <t>17-11-2025 10:10:42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 12:33:03</t>
+          <t>17-11-2025 11:27:51</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>20758</v>
+        <v>9259</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1317,39 +1316,39 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>70</v>
+      </c>
+      <c r="O11" t="n">
+        <v>406422</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>17-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T11" t="n">
         <v>4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>76</v>
-      </c>
-      <c r="O11" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>20-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>253838</v>
+        <v>254106</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1362,33 +1361,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>108.3666666666667</v>
+        <v>107.6416666666667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 12:33:03</t>
+          <t>17-11-2025 11:27:51</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 13:05:03</t>
+          <t>17-11-2025 11:44:51</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 13:05:03</t>
+          <t>17-11-2025 11:44:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 14:53:25</t>
+          <t>17-11-2025 13:32:30</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13004</v>
+        <v>12917</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1401,7 +1400,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
@@ -1414,19 +1413,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>17-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-21.62042824074074</v>
+        <v>-41.56423611111111</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>250284</v>
+        <v>255039</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1435,37 +1434,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>146.35</v>
+        <v>9.15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 14:53:25</t>
+          <t>17-11-2025 13:32:30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18-11-2025 07:14:25</t>
+          <t>17-11-2025 13:49:30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18-11-2025 07:14:25</t>
+          <t>17-11-2025 13:49:30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18-11-2025 09:40:46</t>
+          <t>17-11-2025 13:58:39</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17562</v>
+        <v>1098</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1478,11 +1477,14 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>70</v>
       </c>
+      <c r="O13" t="n">
+        <v>40624</v>
+      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
@@ -1491,11 +1493,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>7</v>
@@ -1503,7 +1505,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254106</v>
+        <v>254758</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1512,37 +1514,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>107.6416666666667</v>
+        <v>61.38333333333333</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18-11-2025 09:40:46</t>
+          <t>17-11-2025 13:58:39</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18-11-2025 10:03:46</t>
+          <t>17-11-2025 14:15:39</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18-11-2025 10:03:46</t>
+          <t>17-11-2025 14:15:39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:24</t>
+          <t>18-11-2025 07:17:02</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12917</v>
+        <v>7366</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1568,19 +1570,19 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-42.49403356481481</v>
+        <v>-1.30349537037037</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>253885</v>
+        <v>254451</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1589,37 +1591,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>105.9333333333333</v>
+        <v>321.1416666666667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:24</t>
+          <t>18-11-2025 07:17:02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18-11-2025 12:08:24</t>
+          <t>18-11-2025 07:34:02</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18-11-2025 12:08:24</t>
+          <t>18-11-2025 07:34:02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18-11-2025 13:54:20</t>
+          <t>18-11-2025 12:55:10</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12712</v>
+        <v>38537</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1645,58 +1647,58 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-14.57940393518519</v>
+        <v>-10.53831597222222</v>
       </c>
       <c r="T15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254129</v>
+        <v>254756</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>44.5</v>
+        <v>60.625</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>18-11-2025 12:55:10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>18-11-2025 13:22:10</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14-11-2025 07:42:00</t>
+          <t>18-11-2025 13:22:10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:30</t>
+          <t>18-11-2025 14:22:48</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5340</v>
+        <v>7275</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1705,80 +1707,75 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
-        <v>76</v>
-      </c>
-      <c r="O16" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-1.351736111111111</v>
+        <v>-4.599166666666667</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254156</v>
+        <v>250284</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>87.47499999999999</v>
+        <v>146.35</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:30</t>
+          <t>18-11-2025 14:22:48</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14-11-2025 08:57:30</t>
+          <t>18-11-2025 14:39:48</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>14-11-2025 08:57:30</t>
+          <t>18-11-2025 14:39:48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:58</t>
+          <t>19-11-2025 09:06:09</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10497</v>
+        <v>17562</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1787,33 +1784,28 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>76</v>
-      </c>
-      <c r="O17" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-0.4340104166666667</v>
+        <v>-60</v>
       </c>
       <c r="T17" t="n">
         <v>7</v>
@@ -1821,46 +1813,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254198</v>
+        <v>254166</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>215</v>
+        <v>38.85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14-11-2025 10:24:58</t>
+          <t>19-11-2025 09:06:09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-11-2025 11:08:58</t>
+          <t>19-11-2025 09:31:09</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>14-11-2025 11:08:58</t>
+          <t>19-11-2025 09:31:09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:58</t>
+          <t>19-11-2025 10:10:00</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>25800</v>
+        <v>4662</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1869,14 +1861,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1886,58 +1878,58 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-25.61387152777778</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254309</v>
+        <v>254915</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>900.0166666666667</v>
+        <v>48.875</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>14-11-2025 14:43:58</t>
+          <t>19-11-2025 10:10:00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>17-11-2025 07:12:58</t>
+          <t>19-11-2025 10:27:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17-11-2025 07:12:58</t>
+          <t>19-11-2025 10:27:00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-11-2025 14:12:59</t>
+          <t>19-11-2025 11:15:52</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>108002</v>
+        <v>5865</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1946,14 +1938,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1963,58 +1955,58 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-18.59235532407407</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>253614</v>
+        <v>254653</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>122.45</v>
+        <v>64.40833333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:12:59</t>
+          <t>19-11-2025 11:15:52</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:59</t>
+          <t>19-11-2025 11:34:52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:59</t>
+          <t>19-11-2025 11:34:52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19-11-2025 08:42:26</t>
+          <t>19-11-2025 12:39:17</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14694</v>
+        <v>7729</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2023,14 +2015,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2040,11 +2032,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-9.362806712962962</v>
+        <v>-5.527280092592592</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -2052,46 +2044,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254715</v>
+        <v>254651</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>134.5416666666667</v>
+        <v>22.64166666666667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>19-11-2025 12:39:17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14-11-2025 07:21:00</t>
+          <t>19-11-2025 12:56:17</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>14-11-2025 07:21:00</t>
+          <t>19-11-2025 12:56:17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14-11-2025 09:35:32</t>
+          <t>19-11-2025 13:18:55</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>16145</v>
+        <v>2717</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2100,80 +2092,75 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>76</v>
-      </c>
-      <c r="O21" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-1.399681712962963</v>
+        <v>-8.554809027777777</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>253650</v>
+        <v>253897</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>273.1333333333333</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14-11-2025 09:35:32</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14-11-2025 09:52:32</t>
+          <t>14-11-2025 07:52:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-11-2025 09:52:32</t>
+          <t>14-11-2025 07:52:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-11-2025 14:25:40</t>
+          <t>14-11-2025 09:26:01</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>32776</v>
+        <v>11282</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2186,32 +2173,37 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N22" t="n">
         <v>76</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
+      <c r="O22" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-25.60116319444445</v>
+        <v>-0.3930671296296296</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>243569</v>
+        <v>254129</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2220,37 +2212,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26-09-2024 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>21.675</v>
+        <v>44.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-11-2025 14:25:40</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-11-2025 14:44:40</t>
+          <t>14-11-2025 07:21:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-11-2025 14:44:40</t>
+          <t>14-11-2025 07:21:00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>17-11-2025 07:06:21</t>
+          <t>14-11-2025 08:05:30</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2601</v>
+        <v>5340</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2259,31 +2251,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
         <v>76</v>
       </c>
       <c r="O23" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16-09-2024 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-60</v>
+        <v>-1.337152777777778</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -2291,7 +2285,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254910</v>
+        <v>254715</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2300,37 +2294,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E24" t="n">
-        <v>73.53333333333333</v>
+        <v>134.5416666666667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17-11-2025 07:06:21</t>
+          <t>14-11-2025 08:05:30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17-11-2025 07:23:21</t>
+          <t>14-11-2025 08:26:30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>17-11-2025 07:23:21</t>
+          <t>14-11-2025 08:26:30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:53</t>
+          <t>14-11-2025 10:41:02</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>8824</v>
+        <v>16145</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2349,29 +2343,31 @@
         <v>76</v>
       </c>
       <c r="O24" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0</v>
+        <v>-1.445167824074074</v>
       </c>
       <c r="T24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>253382</v>
+        <v>254824</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2380,37 +2376,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
-        <v>85.09999999999999</v>
+        <v>748.225</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:53</t>
+          <t>14-11-2025 10:41:02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17-11-2025 08:53:53</t>
+          <t>14-11-2025 11:00:02</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17-11-2025 08:53:53</t>
+          <t>14-11-2025 11:00:02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:59</t>
+          <t>18-11-2025 07:28:16</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>10212</v>
+        <v>89787</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2419,17 +2415,17 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
         <v>76</v>
       </c>
       <c r="O25" t="n">
-        <v>406372</v>
+        <v>406232</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2439,19 +2435,19 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254276</v>
+        <v>243569</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2460,37 +2456,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>37.03333333333333</v>
+        <v>21.675</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:59</t>
+          <t>18-11-2025 07:28:16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17-11-2025 10:50:59</t>
+          <t>18-11-2025 07:45:16</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17-11-2025 10:50:59</t>
+          <t>18-11-2025 07:45:16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17-11-2025 11:28:01</t>
+          <t>18-11-2025 08:06:56</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4444</v>
+        <v>2601</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2499,14 +2495,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O26" t="n">
+        <v>406372</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2516,19 +2515,19 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-24.47778935185185</v>
+        <v>-60</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254429</v>
+        <v>254546</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2537,37 +2536,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>30-10-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E27" t="n">
-        <v>240.2416666666667</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>17-11-2025 11:28:01</t>
+          <t>18-11-2025 08:06:56</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17-11-2025 11:45:01</t>
+          <t>18-11-2025 08:38:56</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17-11-2025 11:45:01</t>
+          <t>18-11-2025 08:38:56</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18-11-2025 07:45:15</t>
+          <t>18-11-2025 10:28:21</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>28829</v>
+        <v>13129</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2580,13 +2579,13 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
         <v>70</v>
       </c>
       <c r="O27" t="n">
-        <v>406372</v>
+        <v>406242</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2596,19 +2595,19 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>235572</v>
+        <v>254291</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2617,37 +2616,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>82.98333333333333</v>
+        <v>18.85</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18-11-2025 07:45:15</t>
+          <t>18-11-2025 10:28:21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18-11-2025 08:00:15</t>
+          <t>18-11-2025 10:47:21</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>18-11-2025 08:00:15</t>
+          <t>18-11-2025 10:47:21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18-11-2025 09:23:14</t>
+          <t>18-11-2025 11:06:12</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>9958</v>
+        <v>2262</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2660,13 +2659,13 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
         <v>70</v>
       </c>
       <c r="O28" t="n">
-        <v>406372</v>
+        <v>40624</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2676,19 +2675,19 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-60</v>
+        <v>-14</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>254375</v>
+        <v>254117</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2697,37 +2696,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>45.29166666666666</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18-11-2025 09:23:14</t>
+          <t>18-11-2025 11:06:12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>18-11-2025 09:40:14</t>
+          <t>18-11-2025 11:42:12</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-11-2025 09:40:14</t>
+          <t>18-11-2025 11:42:12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18-11-2025 10:25:32</t>
+          <t>18-11-2025 11:51:22</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5435</v>
+        <v>1100</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2736,17 +2735,14 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>70</v>
-      </c>
-      <c r="O29" t="n">
-        <v>40624</v>
+        <v>76</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -2756,19 +2752,19 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-12</v>
+        <v>-35.60159143518518</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254586</v>
+        <v>254605</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2781,33 +2777,33 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>51.54166666666666</v>
+        <v>39.025</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>18-11-2025 10:25:32</t>
+          <t>18-11-2025 11:51:22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>18-11-2025 10:42:32</t>
+          <t>18-11-2025 12:25:22</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18-11-2025 10:42:32</t>
+          <t>18-11-2025 12:25:22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18-11-2025 11:34:04</t>
+          <t>18-11-2025 13:04:23</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6185</v>
+        <v>4683</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2820,14 +2816,11 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
-      <c r="O30" t="n">
-        <v>406372</v>
-      </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
@@ -2840,7 +2833,7 @@
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>0</v>
+        <v>-3.318969907407407</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
@@ -2848,7 +2841,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254460</v>
+        <v>254237</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2857,37 +2850,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>46.68333333333333</v>
+        <v>184.0916666666667</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>18-11-2025 11:34:04</t>
+          <t>18-11-2025 13:04:23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:04</t>
+          <t>18-11-2025 13:23:23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18-11-2025 11:51:04</t>
+          <t>18-11-2025 13:23:23</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18-11-2025 12:37:45</t>
+          <t>19-11-2025 08:27:29</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>5602</v>
+        <v>22091</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2900,24 +2893,31 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>40651 (esterno)</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>40651</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-36.52622106481481</v>
+        <v>-7.460005787037037</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>254521</v>
+        <v>253838</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2938,33 +2938,33 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>39.68333333333333</v>
+        <v>108.3666666666667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>18-11-2025 12:37:45</t>
+          <t>19-11-2025 08:27:29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18-11-2025 12:54:45</t>
+          <t>19-11-2025 08:46:29</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18-11-2025 12:54:45</t>
+          <t>19-11-2025 08:46:29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18-11-2025 13:34:26</t>
+          <t>19-11-2025 10:34:51</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4762</v>
+        <v>13004</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N32" t="n">
         <v>70</v>
@@ -2990,19 +2990,19 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>-13.56558449074074</v>
+        <v>-21.54845486111111</v>
       </c>
       <c r="T32" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254293</v>
+        <v>254287</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3011,37 +3011,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>18.85</v>
+        <v>129.6333333333333</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18-11-2025 13:34:26</t>
+          <t>19-11-2025 10:34:51</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18-11-2025 13:55:26</t>
+          <t>19-11-2025 10:53:51</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18-11-2025 13:55:26</t>
+          <t>19-11-2025 10:53:51</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18-11-2025 14:14:17</t>
+          <t>19-11-2025 13:03:29</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2262</v>
+        <v>15556</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3054,14 +3054,11 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>70</v>
       </c>
-      <c r="O33" t="n">
-        <v>40624</v>
-      </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
@@ -3070,19 +3067,19 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>-14</v>
+        <v>-25.31833912037037</v>
       </c>
       <c r="T33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254756</v>
+        <v>254574</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3091,37 +3088,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E34" t="n">
-        <v>60.625</v>
+        <v>173.6083333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>18-11-2025 14:14:17</t>
+          <t>19-11-2025 13:03:29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:17</t>
+          <t>19-11-2025 13:18:29</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:17</t>
+          <t>19-11-2025 13:18:29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>19-11-2025 07:35:55</t>
+          <t>20-11-2025 08:12:05</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>7275</v>
+        <v>20833</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3134,7 +3131,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>70</v>
@@ -3147,11 +3144,11 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>-5.316608796296296</v>
+        <v>-14.44931712962963</v>
       </c>
       <c r="T34" t="n">
         <v>7</v>
@@ -3159,7 +3156,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254915</v>
+        <v>254521</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3172,33 +3169,33 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>48.875</v>
+        <v>39.68333333333333</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19-11-2025 07:35:55</t>
+          <t>20-11-2025 08:12:05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-11-2025 08:04:55</t>
+          <t>20-11-2025 08:31:05</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>19-11-2025 08:04:55</t>
+          <t>20-11-2025 08:31:05</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19-11-2025 08:53:47</t>
+          <t>20-11-2025 09:10:46</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5865</v>
+        <v>4762</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3207,11 +3204,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
         <v>70</v>
@@ -3224,11 +3221,11 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0</v>
+        <v>-13.49006944444444</v>
       </c>
       <c r="T35" t="n">
         <v>7</v>
@@ -3236,46 +3233,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254574</v>
+        <v>254762</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="E36" t="n">
-        <v>173.6083333333333</v>
+        <v>31.85833333333333</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19-11-2025 08:53:47</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19-11-2025 09:10:47</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19-11-2025 09:10:47</t>
+          <t>13-11-2025 12:32:30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19-11-2025 12:04:24</t>
+          <t>13-11-2025 13:04:21</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>20833</v>
+        <v>3823</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3293,66 +3290,71 @@
       <c r="N36" t="n">
         <v>70</v>
       </c>
-      <c r="P36" t="n">
-        <v>0</v>
+      <c r="O36" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>-15.50305555555556</v>
+        <v>-0.544693287037037</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254652</v>
+        <v>253380</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>42.5</v>
       </c>
       <c r="E37" t="n">
-        <v>28.73333333333333</v>
+        <v>104.275</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>19-11-2025 12:04:24</t>
+          <t>13-11-2025 13:04:21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19-11-2025 12:21:24</t>
+          <t>13-11-2025 13:46:51</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>19-11-2025 12:21:24</t>
+          <t>13-11-2025 13:46:51</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19-11-2025 12:50:08</t>
+          <t>14-11-2025 07:31:08</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>3448</v>
+        <v>12513</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3361,36 +3363,41 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N37" t="n">
         <v>70</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
+      <c r="O37" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>-8.534814814814816</v>
+        <v>-0.313287037037037</v>
       </c>
       <c r="T37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254762</v>
+        <v>254598</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3399,37 +3406,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>32.5</v>
+        <v>38.5</v>
       </c>
       <c r="E38" t="n">
-        <v>31.85833333333333</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>14-11-2025 07:31:08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 08:09:38</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13-11-2025 12:32:30</t>
+          <t>14-11-2025 08:09:38</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13-11-2025 13:04:21</t>
+          <t>14-11-2025 09:53:53</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3823</v>
+        <v>12511</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3438,41 +3445,36 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
         <v>70</v>
       </c>
-      <c r="O38" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P38" t="n">
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>-0.544693287037037</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>253380</v>
+        <v>244023</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3481,37 +3483,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>42.5</v>
+        <v>44.5</v>
       </c>
       <c r="E39" t="n">
-        <v>104.275</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>13-11-2025 13:04:21</t>
+          <t>14-11-2025 09:53:53</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13-11-2025 13:46:51</t>
+          <t>14-11-2025 10:38:23</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>13-11-2025 13:46:51</t>
+          <t>14-11-2025 10:38:23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>14-11-2025 07:31:08</t>
+          <t>14-11-2025 10:46:42</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>12513</v>
+        <v>997</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3520,41 +3522,39 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
         <v>70</v>
       </c>
       <c r="O39" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406062</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-0.313287037037037</v>
+        <v>-60</v>
       </c>
       <c r="T39" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>244023</v>
+        <v>254429</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3563,37 +3563,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>30-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>36.5</v>
+        <v>32.5</v>
       </c>
       <c r="E40" t="n">
-        <v>8.308333333333334</v>
+        <v>240.2416666666667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>14-11-2025 07:31:08</t>
+          <t>14-11-2025 10:46:42</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:38</t>
+          <t>14-11-2025 11:19:12</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14-11-2025 08:07:38</t>
+          <t>14-11-2025 11:19:12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>14-11-2025 08:15:56</t>
+          <t>17-11-2025 07:19:26</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>997</v>
+        <v>28829</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
       <c r="O40" t="n">
-        <v>406062</v>
+        <v>406372</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3622,19 +3622,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-60</v>
+        <v>-9</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>255043</v>
+        <v>254276</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3643,37 +3643,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>38.5</v>
+        <v>32.5</v>
       </c>
       <c r="E41" t="n">
-        <v>184.2833333333333</v>
+        <v>37.03333333333333</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>14-11-2025 08:15:56</t>
+          <t>17-11-2025 07:19:26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14-11-2025 08:54:26</t>
+          <t>17-11-2025 07:51:56</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>14-11-2025 08:54:26</t>
+          <t>17-11-2025 07:51:56</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14-11-2025 11:58:43</t>
+          <t>17-11-2025 08:28:58</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>22114</v>
+        <v>4444</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3682,11 +3682,11 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
         <v>70</v>
@@ -3702,19 +3702,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254189</v>
+        <v>254187</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3727,33 +3727,33 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="E42" t="n">
-        <v>55.875</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14-11-2025 11:58:43</t>
+          <t>17-11-2025 08:28:58</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14-11-2025 12:29:13</t>
+          <t>17-11-2025 09:01:28</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14-11-2025 12:29:13</t>
+          <t>17-11-2025 09:01:28</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:06</t>
+          <t>17-11-2025 09:47:52</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>6705</v>
+        <v>5567</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3762,17 +3762,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
         <v>70</v>
       </c>
       <c r="O42" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254433</v>
+        <v>254586</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3803,37 +3803,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>30.5</v>
       </c>
       <c r="E43" t="n">
-        <v>67.84999999999999</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>14-11-2025 13:25:06</t>
+          <t>17-11-2025 09:47:52</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:36</t>
+          <t>17-11-2025 10:18:22</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>14-11-2025 13:55:36</t>
+          <t>17-11-2025 10:18:22</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:27</t>
+          <t>17-11-2025 11:09:54</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>8142</v>
+        <v>6185</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3842,17 +3842,17 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
         <v>70</v>
       </c>
       <c r="O43" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -3862,11 +3862,11 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254230</v>
+        <v>254437</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3883,37 +3883,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
       <c r="E44" t="n">
-        <v>62.475</v>
+        <v>58.05833333333333</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>17-11-2025 07:03:27</t>
+          <t>17-11-2025 11:09:54</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>17-11-2025 07:33:57</t>
+          <t>17-11-2025 11:42:24</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>17-11-2025 07:33:57</t>
+          <t>17-11-2025 11:42:24</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:25</t>
+          <t>17-11-2025 12:40:28</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>7497</v>
+        <v>6967</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3922,17 +3922,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
         <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3942,19 +3942,19 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254188</v>
+        <v>235572</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3963,37 +3963,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
       <c r="E45" t="n">
-        <v>37.44166666666667</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17-11-2025 08:36:25</t>
+          <t>17-11-2025 12:40:28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17-11-2025 09:10:55</t>
+          <t>17-11-2025 13:12:58</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>17-11-2025 09:10:55</t>
+          <t>17-11-2025 13:12:58</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17-11-2025 09:48:22</t>
+          <t>17-11-2025 14:35:57</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>4493</v>
+        <v>9958</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
         <v>70</v>
@@ -4022,19 +4022,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>-1</v>
+        <v>-60</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254451</v>
+        <v>254893</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4043,37 +4043,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="E46" t="n">
-        <v>321.1416666666667</v>
+        <v>46.675</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>17-11-2025 09:48:22</t>
+          <t>17-11-2025 14:35:57</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17-11-2025 10:20:52</t>
+          <t>18-11-2025 07:10:27</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>17-11-2025 10:20:52</t>
+          <t>18-11-2025 07:10:27</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18-11-2025 07:42:00</t>
+          <t>18-11-2025 07:57:07</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>38537</v>
+        <v>5601</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4091,6 +4091,9 @@
       <c r="N46" t="n">
         <v>70</v>
       </c>
+      <c r="O46" t="n">
+        <v>406372</v>
+      </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
@@ -4099,11 +4102,11 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-10.32083912037037</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
@@ -4111,7 +4114,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254107</v>
+        <v>254245</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4120,37 +4123,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>32.5</v>
       </c>
       <c r="E47" t="n">
-        <v>175.0583333333333</v>
+        <v>89.8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18-11-2025 07:42:00</t>
+          <t>18-11-2025 07:57:07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:30</t>
+          <t>18-11-2025 08:29:37</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>18-11-2025 08:14:30</t>
+          <t>18-11-2025 08:29:37</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>18-11-2025 11:09:34</t>
+          <t>18-11-2025 09:59:25</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>21007</v>
+        <v>10776</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4168,6 +4171,9 @@
       <c r="N47" t="n">
         <v>70</v>
       </c>
+      <c r="O47" t="n">
+        <v>406372</v>
+      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -4176,19 +4182,19 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>22-10-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-37.46497685185185</v>
+        <v>-20</v>
       </c>
       <c r="T47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254381</v>
+        <v>253961</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4197,37 +4203,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.5</v>
+        <v>30.5</v>
       </c>
       <c r="E48" t="n">
-        <v>83.86666666666666</v>
+        <v>35.91666666666666</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>18-11-2025 11:09:34</t>
+          <t>18-11-2025 09:59:25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>18-11-2025 11:42:04</t>
+          <t>18-11-2025 10:29:55</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18-11-2025 11:42:04</t>
+          <t>18-11-2025 10:29:55</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>18-11-2025 13:05:56</t>
+          <t>18-11-2025 11:05:50</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>10064</v>
+        <v>4310</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4236,15 +4242,18 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
         <v>70</v>
       </c>
+      <c r="O48" t="n">
+        <v>406372</v>
+      </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
@@ -4253,58 +4262,58 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>11-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-21.54578703703704</v>
+        <v>-8</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254714</v>
+        <v>254365</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>50</v>
+        <v>32.5</v>
       </c>
       <c r="E49" t="n">
-        <v>91.47499999999999</v>
+        <v>67.53333333333333</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:00:00</t>
+          <t>18-11-2025 11:05:50</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:50:00</t>
+          <t>18-11-2025 11:38:20</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>13-11-2025 12:50:00</t>
+          <t>18-11-2025 11:38:20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>13-11-2025 14:21:28</t>
+          <t>18-11-2025 12:45:52</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>10977</v>
+        <v>8104</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4313,41 +4322,36 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M49" t="n">
         <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>76</v>
-      </c>
-      <c r="O49" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-0.5982465277777778</v>
+        <v>-14.53185763888889</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>253897</v>
+        <v>254713</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4356,37 +4360,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E50" t="n">
-        <v>94.01666666666667</v>
+        <v>49.96666666666667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>13-11-2025 14:21:28</t>
+          <t>13-11-2025 12:00:00</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:28</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>14-11-2025 07:16:28</t>
+          <t>13-11-2025 12:45:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:29</t>
+          <t>13-11-2025 13:34:58</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>11282</v>
+        <v>5996</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4399,13 +4403,13 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
         <v>76</v>
       </c>
       <c r="O50" t="n">
-        <v>40606</v>
+        <v>40623</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -4413,23 +4417,23 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>40606</v>
+        <v>40623</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>27-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-0.3683969907407407</v>
+        <v>-0.565949074074074</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254512</v>
+        <v>253694</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4442,33 +4446,33 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E51" t="n">
-        <v>59.55833333333333</v>
+        <v>121.7583333333333</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>14-11-2025 08:50:29</t>
+          <t>13-11-2025 13:34:58</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14-11-2025 09:50:29</t>
+          <t>13-11-2025 14:14:58</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14-11-2025 09:50:29</t>
+          <t>13-11-2025 14:14:58</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>14-11-2025 10:50:03</t>
+          <t>14-11-2025 08:16:43</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>7147</v>
+        <v>14611</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4487,29 +4491,31 @@
         <v>76</v>
       </c>
       <c r="O51" t="n">
-        <v>406232</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
+        <v>40623</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-6</v>
+        <v>-1.344947916666667</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>254287</v>
+        <v>254381</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4525,30 +4531,30 @@
         <v>40</v>
       </c>
       <c r="E52" t="n">
-        <v>129.6333333333333</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14-11-2025 10:50:03</t>
+          <t>14-11-2025 08:16:43</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14-11-2025 11:30:03</t>
+          <t>14-11-2025 08:56:43</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14-11-2025 11:30:03</t>
+          <t>14-11-2025 08:56:43</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14-11-2025 13:39:41</t>
+          <t>14-11-2025 10:20:35</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>15556</v>
+        <v>10064</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4557,7 +4563,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -4577,19 +4583,19 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254427</v>
+        <v>253865</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4598,80 +4604,75 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>06-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E53" t="n">
-        <v>55.55833333333333</v>
+        <v>116.7583333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14-11-2025 13:39:41</t>
+          <t>14-11-2025 10:20:35</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14-11-2025 14:19:41</t>
+          <t>14-11-2025 10:55:35</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14-11-2025 14:19:41</t>
+          <t>14-11-2025 10:55:35</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>17-11-2025 07:15:14</t>
+          <t>14-11-2025 12:52:21</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>6667</v>
+        <v>14011</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>foglio</t>
+          <t>bobina</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N53" t="n">
         <v>70</v>
       </c>
-      <c r="O53" t="n">
-        <v>406422</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P53" t="n">
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>40649</v>
+        <v>0</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-7.302251157407407</v>
+        <v>-35.53635416666667</v>
       </c>
       <c r="T53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254457</v>
+        <v>254293</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4680,37 +4681,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E54" t="n">
-        <v>3.925</v>
+        <v>18.85</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>17-11-2025 07:15:14</t>
+          <t>14-11-2025 12:52:21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:14</t>
+          <t>14-11-2025 13:22:21</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17-11-2025 08:00:14</t>
+          <t>14-11-2025 13:22:21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>17-11-2025 08:04:10</t>
+          <t>14-11-2025 13:41:12</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>471</v>
+        <v>2262</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4723,13 +4724,13 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N54" t="n">
         <v>70</v>
       </c>
       <c r="O54" t="n">
-        <v>406372</v>
+        <v>40624</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4739,19 +4740,19 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>-1</v>
+        <v>-14</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254437</v>
+        <v>254903</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4760,37 +4761,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E55" t="n">
-        <v>58.05833333333333</v>
+        <v>256.6416666666667</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17-11-2025 08:04:10</t>
+          <t>14-11-2025 13:41:12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:10</t>
+          <t>14-11-2025 14:21:12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17-11-2025 08:29:10</t>
+          <t>14-11-2025 14:21:12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>17-11-2025 09:27:13</t>
+          <t>17-11-2025 10:37:50</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>6967</v>
+        <v>30797</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4803,14 +4804,11 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
         <v>70</v>
       </c>
-      <c r="O55" t="n">
-        <v>406372</v>
-      </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
@@ -4819,11 +4817,11 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-11-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
@@ -4831,7 +4829,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254605</v>
+        <v>254356</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4847,30 +4845,30 @@
         <v>30</v>
       </c>
       <c r="E56" t="n">
-        <v>39.025</v>
+        <v>179.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17-11-2025 09:27:13</t>
+          <t>17-11-2025 10:37:50</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17-11-2025 09:57:13</t>
+          <t>17-11-2025 11:07:50</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>17-11-2025 09:57:13</t>
+          <t>17-11-2025 11:07:50</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>17-11-2025 10:36:15</t>
+          <t>17-11-2025 14:07:26</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4683</v>
+        <v>21552</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4883,7 +4881,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
         <v>70</v>
@@ -4896,19 +4894,19 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-3.441840277777778</v>
+        <v>-19.58850115740741</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254758</v>
+        <v>254599</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4917,37 +4915,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E57" t="n">
-        <v>61.38333333333333</v>
+        <v>44.9</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17-11-2025 10:36:15</t>
+          <t>17-11-2025 14:07:26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>17-11-2025 11:06:15</t>
+          <t>17-11-2025 14:32:26</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>17-11-2025 11:06:15</t>
+          <t>17-11-2025 14:32:26</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>17-11-2025 12:07:38</t>
+          <t>18-11-2025 07:17:20</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>7366</v>
+        <v>5388</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4965,6 +4963,9 @@
       <c r="N57" t="n">
         <v>70</v>
       </c>
+      <c r="O57" t="n">
+        <v>406372</v>
+      </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
@@ -4973,58 +4974,58 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-0.5053009259259259</v>
+        <v>-2</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>253865</v>
+        <v>254556</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>06-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>116.7583333333333</v>
+        <v>173.4166666666667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>17-11-2025 12:07:38</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>17-11-2025 12:37:38</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>17-11-2025 12:37:38</t>
+          <t>14-11-2025 07:19:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:23</t>
+          <t>14-11-2025 10:12:25</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>14011</v>
+        <v>20810</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5033,28 +5034,33 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
         <v>5</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O58" t="n">
+        <v>40623</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>40623</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-38.60721643518519</v>
+        <v>-1.425289351851852</v>
       </c>
       <c r="T58" t="n">
         <v>2</v>
@@ -5062,46 +5068,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254245</v>
+        <v>253650</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
-        <v>89.8</v>
+        <v>273.1333333333333</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>17-11-2025 14:34:23</t>
+          <t>14-11-2025 10:12:25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>18-11-2025 07:04:23</t>
+          <t>14-11-2025 10:31:25</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>18-11-2025 07:04:23</t>
+          <t>14-11-2025 10:31:25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>18-11-2025 08:34:11</t>
+          <t>17-11-2025 07:04:33</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>10776</v>
+        <v>32776</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5110,14 +5116,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5131,54 +5137,54 @@
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-29.3570775462963</v>
+        <v>-28.29482638888889</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>253961</v>
+        <v>254283</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E60" t="n">
-        <v>35.91666666666666</v>
+        <v>95.76666666666667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>18-11-2025 08:34:11</t>
+          <t>17-11-2025 07:04:33</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18-11-2025 08:59:11</t>
+          <t>17-11-2025 07:23:33</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>18-11-2025 08:59:11</t>
+          <t>17-11-2025 07:23:33</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>18-11-2025 09:35:06</t>
+          <t>17-11-2025 08:59:19</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>4310</v>
+        <v>11492</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5187,14 +5193,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O60" t="n">
+        <v>406372</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5208,54 +5217,54 @@
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>-17.39938078703704</v>
+        <v>-8</v>
       </c>
       <c r="T60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>252811</v>
+        <v>253382</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
-        <v>11.875</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>18-11-2025 09:35:06</t>
+          <t>17-11-2025 08:59:19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18-11-2025 10:05:06</t>
+          <t>17-11-2025 09:18:19</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>18-11-2025 10:05:06</t>
+          <t>17-11-2025 09:18:19</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>18-11-2025 10:16:59</t>
+          <t>17-11-2025 10:43:25</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1425</v>
+        <v>10212</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5264,14 +5273,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O61" t="n">
+        <v>406372</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5281,58 +5293,58 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>-15.42846064814815</v>
+        <v>-12</v>
       </c>
       <c r="T61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>254598</v>
+        <v>254198</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E62" t="n">
-        <v>104.2583333333333</v>
+        <v>215</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>18-11-2025 10:16:59</t>
+          <t>17-11-2025 10:43:25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>18-11-2025 11:21:59</t>
+          <t>17-11-2025 11:15:25</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>18-11-2025 11:21:59</t>
+          <t>17-11-2025 11:15:25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>18-11-2025 13:06:14</t>
+          <t>17-11-2025 14:50:25</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>12511</v>
+        <v>25800</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5341,14 +5353,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5358,19 +5370,19 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>0</v>
+        <v>-28.61834490740741</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254556</v>
+        <v>253614</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5379,37 +5391,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E63" t="n">
-        <v>173.4166666666667</v>
+        <v>122.45</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 14:50:25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>18-11-2025 07:07:25</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14-11-2025 07:19:00</t>
+          <t>18-11-2025 07:07:25</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>14-11-2025 10:12:25</t>
+          <t>18-11-2025 09:09:52</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>20810</v>
+        <v>14694</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5418,45 +5430,40 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>76</v>
-      </c>
-      <c r="O63" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-1.425289351851852</v>
+        <v>-8.381851851851852</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254165</v>
+        <v>254385</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5465,33 +5472,33 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E64" t="n">
-        <v>58.31666666666667</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>14-11-2025 10:12:25</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14-11-2025 10:29:25</t>
+          <t>14-11-2025 07:40:00</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14-11-2025 10:29:25</t>
+          <t>14-11-2025 07:40:00</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>14-11-2025 11:27:44</t>
+          <t>14-11-2025 08:32:05</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>6998</v>
+        <v>6250</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5504,13 +5511,13 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="O64" t="n">
-        <v>40606</v>
+        <v>40627</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5518,62 +5525,62 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>40606</v>
+        <v>40627</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-0.4775925925925926</v>
+        <v>-0.3556134259259259</v>
       </c>
       <c r="T64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>254117</v>
+        <v>254512</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>07-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E65" t="n">
-        <v>9.166666666666666</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>14-11-2025 11:27:44</t>
+          <t>14-11-2025 08:32:05</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:44</t>
+          <t>14-11-2025 09:07:05</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>14-11-2025 11:44:44</t>
+          <t>14-11-2025 09:07:05</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>14-11-2025 11:53:54</t>
+          <t>14-11-2025 10:06:38</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1100</v>
+        <v>7147</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5582,15 +5589,18 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
         <v>76</v>
       </c>
+      <c r="O65" t="n">
+        <v>406232</v>
+      </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
@@ -5599,11 +5609,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>20-10-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>-35.49576388888889</v>
+        <v>-6</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
@@ -5611,46 +5621,46 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254283</v>
+        <v>254230</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E66" t="n">
-        <v>95.76666666666667</v>
+        <v>62.475</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14-11-2025 11:53:54</t>
+          <t>14-11-2025 10:06:38</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14-11-2025 12:12:54</t>
+          <t>14-11-2025 10:46:38</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14-11-2025 12:12:54</t>
+          <t>14-11-2025 10:46:38</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>14-11-2025 13:48:40</t>
+          <t>14-11-2025 11:49:07</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>11492</v>
+        <v>7497</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5659,17 +5669,17 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O66" t="n">
-        <v>406372</v>
+        <v>406422</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -5679,11 +5689,11 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>11-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="T66" t="n">
         <v>2</v>
@@ -5691,7 +5701,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>254385</v>
+        <v>254189</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -5700,37 +5710,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E67" t="n">
-        <v>52.08333333333334</v>
+        <v>55.875</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 11:49:07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:40:00</t>
+          <t>14-11-2025 12:14:07</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14-11-2025 07:40:00</t>
+          <t>14-11-2025 12:14:07</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14-11-2025 08:32:05</t>
+          <t>14-11-2025 13:09:59</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>6250</v>
+        <v>6705</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5739,41 +5749,39 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="O67" t="n">
-        <v>40627</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>40627</v>
+        <v>0</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>06-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-0.3556134259259259</v>
+        <v>-3</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>254903</v>
+        <v>254433</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -5782,37 +5790,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>256.6416666666667</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>14-11-2025 08:32:05</t>
+          <t>14-11-2025 13:09:59</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14-11-2025 09:12:05</t>
+          <t>14-11-2025 13:34:59</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14-11-2025 09:12:05</t>
+          <t>14-11-2025 13:34:59</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>14-11-2025 13:28:43</t>
+          <t>14-11-2025 14:42:50</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>30797</v>
+        <v>8142</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5821,15 +5829,18 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" t="n">
         <v>70</v>
       </c>
+      <c r="O68" t="n">
+        <v>406422</v>
+      </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
@@ -5838,11 +5849,11 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
@@ -5850,7 +5861,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>252061</v>
+        <v>255043</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -5863,33 +5874,33 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E69" t="n">
-        <v>36.16666666666666</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>14-11-2025 13:28:43</t>
+          <t>14-11-2025 14:42:50</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14-11-2025 14:03:43</t>
+          <t>17-11-2025 07:07:50</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14-11-2025 14:03:43</t>
+          <t>17-11-2025 07:07:50</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>14-11-2025 14:39:53</t>
+          <t>17-11-2025 10:12:07</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>4340</v>
+        <v>22114</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5898,29 +5909,27 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>70</v>
       </c>
       <c r="O69" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>406422</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5932,7 +5941,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>254237</v>
+        <v>254457</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -5948,30 +5957,30 @@
         <v>35</v>
       </c>
       <c r="E70" t="n">
-        <v>184.0916666666667</v>
+        <v>3.925</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>14-11-2025 14:39:53</t>
+          <t>17-11-2025 10:12:07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>17-11-2025 07:14:53</t>
+          <t>17-11-2025 10:47:07</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>17-11-2025 07:14:53</t>
+          <t>17-11-2025 10:47:07</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:59</t>
+          <t>17-11-2025 10:51:03</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>22091</v>
+        <v>471</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5984,31 +5993,27 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>40651 (esterno)</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="O70" t="n">
+        <v>406372</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>40651</v>
+        <v>0</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-7.429849537037037</v>
+        <v>-1</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6016,7 +6021,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>254519</v>
+        <v>254188</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6025,37 +6030,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E71" t="n">
-        <v>77.15833333333333</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17-11-2025 10:18:59</t>
+          <t>17-11-2025 10:51:03</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>17-11-2025 11:03:59</t>
+          <t>17-11-2025 11:16:03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>17-11-2025 11:03:59</t>
+          <t>17-11-2025 11:16:03</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:08</t>
+          <t>17-11-2025 11:53:29</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>9259</v>
+        <v>4493</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6068,11 +6073,14 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
         <v>70</v>
       </c>
+      <c r="O71" t="n">
+        <v>406372</v>
+      </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
@@ -6081,19 +6089,19 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>-10.51468171296296</v>
+        <v>-1</v>
       </c>
       <c r="T71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254256</v>
+        <v>254555</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6102,37 +6110,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E72" t="n">
-        <v>50.925</v>
+        <v>172.9833333333333</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>17-11-2025 12:21:08</t>
+          <t>17-11-2025 11:53:29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:08</t>
+          <t>17-11-2025 12:38:29</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>17-11-2025 12:46:08</t>
+          <t>17-11-2025 12:38:29</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>17-11-2025 13:37:04</t>
+          <t>18-11-2025 07:31:28</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>6111</v>
+        <v>20758</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6141,17 +6149,17 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N72" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O72" t="n">
-        <v>406422</v>
+        <v>406232</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6161,19 +6169,19 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254653</v>
+        <v>254107</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6182,37 +6190,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>10-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E73" t="n">
-        <v>64.40833333333333</v>
+        <v>175.0583333333333</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17-11-2025 13:37:04</t>
+          <t>18-11-2025 07:31:28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17-11-2025 14:07:04</t>
+          <t>18-11-2025 08:16:28</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>17-11-2025 14:07:04</t>
+          <t>18-11-2025 08:16:28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>18-11-2025 07:11:28</t>
+          <t>18-11-2025 11:11:32</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>7729</v>
+        <v>21007</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6238,11 +6246,11 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>22-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-4.299635416666667</v>
+        <v>-37.46634259259259</v>
       </c>
       <c r="T73" t="n">
         <v>7</v>
@@ -6250,7 +6258,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>254365</v>
+        <v>253885</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6259,37 +6267,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>30</v>
       </c>
       <c r="E74" t="n">
-        <v>67.53333333333333</v>
+        <v>105.9333333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>18-11-2025 07:11:28</t>
+          <t>18-11-2025 11:11:32</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>18-11-2025 07:41:28</t>
+          <t>18-11-2025 11:41:32</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>18-11-2025 07:41:28</t>
+          <t>18-11-2025 11:41:32</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>18-11-2025 08:49:00</t>
+          <t>18-11-2025 13:27:28</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>8104</v>
+        <v>12712</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6302,7 +6310,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
         <v>70</v>
@@ -6319,7 +6327,7 @@
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-14.36736689814815</v>
+        <v>-14.56074074074074</v>
       </c>
       <c r="T74" t="n">
         <v>8</v>
@@ -6327,46 +6335,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254651</v>
+        <v>254165</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>22.64166666666667</v>
+        <v>58.31666666666667</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>18-11-2025 08:49:00</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>18-11-2025 09:24:00</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>18-11-2025 09:24:00</t>
+          <t>14-11-2025 07:35:00</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>18-11-2025 09:46:39</t>
+          <t>14-11-2025 08:33:19</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2717</v>
+        <v>6998</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6375,36 +6383,41 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>70</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>40606</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-7.407395833333333</v>
+        <v>-0.3564699074074074</v>
       </c>
       <c r="T75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>253694</v>
+        <v>254156</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6417,33 +6430,33 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>121.7583333333333</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 08:33:19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 08:58:19</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>14-11-2025 07:35:00</t>
+          <t>14-11-2025 08:58:19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>14-11-2025 09:36:45</t>
+          <t>14-11-2025 10:25:47</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>14611</v>
+        <v>10497</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6452,7 +6465,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -6462,7 +6475,7 @@
         <v>76</v>
       </c>
       <c r="O76" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -6470,23 +6483,23 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>-1.40052662037037</v>
+        <v>-0.4345775462962963</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254824</v>
+        <v>254309</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6495,37 +6508,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E77" t="n">
-        <v>748.225</v>
+        <v>900.0166666666667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>14-11-2025 09:36:45</t>
+          <t>14-11-2025 10:25:47</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14-11-2025 10:11:45</t>
+          <t>14-11-2025 10:55:47</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>14-11-2025 10:11:45</t>
+          <t>14-11-2025 10:55:47</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>17-11-2025 14:39:59</t>
+          <t>18-11-2025 09:55:48</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>89787</v>
+        <v>108002</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6538,13 +6551,10 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N77" t="n">
-        <v>76</v>
-      </c>
-      <c r="O77" t="n">
-        <v>406232</v>
+        <v>152</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6554,19 +6564,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>0</v>
+        <v>-18.41375578703704</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254599</v>
+        <v>252811</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6579,33 +6589,33 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E78" t="n">
-        <v>44.9</v>
+        <v>11.875</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>17-11-2025 14:39:59</t>
+          <t>18-11-2025 09:55:48</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:19:59</t>
+          <t>18-11-2025 10:30:48</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18-11-2025 07:19:59</t>
+          <t>18-11-2025 10:30:48</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>18-11-2025 08:04:53</t>
+          <t>18-11-2025 10:42:41</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>5388</v>
+        <v>1425</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6618,14 +6628,11 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
       </c>
-      <c r="O78" t="n">
-        <v>406372</v>
-      </c>
       <c r="P78" t="n">
         <v>0</v>
       </c>
@@ -6634,19 +6641,19 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-2</v>
+        <v>-15.44630787037037</v>
       </c>
       <c r="T78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>254356</v>
+        <v>254652</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6655,37 +6662,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>179.6</v>
+        <v>28.73333333333333</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:04:53</t>
+          <t>18-11-2025 10:42:41</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:29:53</t>
+          <t>18-11-2025 11:12:41</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18-11-2025 08:29:53</t>
+          <t>18-11-2025 11:12:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>18-11-2025 11:29:29</t>
+          <t>18-11-2025 11:41:25</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>21552</v>
+        <v>3448</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6703,9 +6710,6 @@
       <c r="N79" t="n">
         <v>70</v>
       </c>
-      <c r="O79" t="n">
-        <v>406372</v>
-      </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
@@ -6714,77 +6718,77 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>08-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-11</v>
+        <v>-7.487094907407408</v>
       </c>
       <c r="T79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>254291</v>
+        <v>254609</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>18.85</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18-11-2025 11:29:29</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>18-11-2025 12:04:29</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18-11-2025 12:04:29</t>
+          <t>12-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>18-11-2025 12:23:20</t>
+          <t>12-11-2025 13:56:40</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>2262</v>
+        <v>50000</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>bobina</t>
+          <t>foglio</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>40624</v>
+        <v>40655</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -6794,23 +6798,23 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>254609</v>
+        <v>252980</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6822,30 +6826,30 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>416.6666666666667</v>
+        <v>17.075</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>12-11-2025 07:00:00</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>12-11-2025 13:56:40</t>
+          <t>14-11-2025 07:17:04</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>50000</v>
+        <v>2049</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6854,7 +6858,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>T1 ;T2 ;T8</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -6863,9 +6867,6 @@
       <c r="N81" t="n">
         <v>0</v>
       </c>
-      <c r="O81" t="n">
-        <v>40655</v>
-      </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
@@ -6874,58 +6875,58 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>08-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="T81" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>252980</v>
+        <v>254428</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>17.075</v>
+        <v>48.30833333333333</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>17-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>14-11-2025 07:17:04</t>
+          <t>17-11-2025 14:48:18</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>2049</v>
+        <v>5797</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6934,28 +6935,33 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1 ;T2 ;T8</t>
         </is>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O82" t="n">
+        <v>40649</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>40649</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>08-09-2025 00:00:00</t>
+          <t>10-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-60</v>
+        <v>-7.616880787037037</v>
       </c>
       <c r="T82" t="n">
         <v>7</v>
@@ -6963,11 +6969,11 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>254428</v>
+        <v>254427</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6979,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>48.30833333333333</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6998,11 +7004,11 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>17-11-2025 14:48:18</t>
+          <t>17-11-2025 14:55:33</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>5797</v>
+        <v>6667</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7037,7 +7043,7 @@
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-7.616880787037037</v>
+        <v>-7.621915509259259</v>
       </c>
       <c r="T83" t="n">
         <v>7</v>
@@ -7122,46 +7128,46 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>254671</v>
+        <v>254967</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>20-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E85" t="n">
-        <v>136.1666666666667</v>
+        <v>260.4166666666667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>20-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>18-11-2025 14:45:00</t>
+          <t>20-11-2025 14:27:00</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>18-11-2025 14:45:00</t>
+          <t>20-11-2025 14:27:00</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>19-11-2025 09:01:10</t>
+          <t>21-11-2025 10:47:25</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>16340</v>
+        <v>31250</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7170,11 +7176,11 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CASON ;H7 ;R5</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N85" t="n">
         <v>70</v>
@@ -7187,11 +7193,11 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>-8.375810185185186</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
@@ -7199,46 +7205,46 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>254967</v>
+        <v>254671</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>20-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E86" t="n">
-        <v>260.4166666666667</v>
+        <v>136.1666666666667</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>20-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20-11-2025 14:29:00</t>
+          <t>18-11-2025 14:45:00</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>20-11-2025 14:29:00</t>
+          <t>18-11-2025 14:45:00</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>21-11-2025 10:49:25</t>
+          <t>19-11-2025 09:01:10</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>31250</v>
+        <v>16340</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7247,11 +7253,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7 ;R5</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N86" t="n">
         <v>70</v>
@@ -7264,11 +7270,11 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>0</v>
+        <v>-8.375810185185186</v>
       </c>
       <c r="T86" t="n">
         <v>1</v>
@@ -7276,42 +7282,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>254101</v>
+        <v>253974</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E87" t="n">
         <v>28.425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>19-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:00</t>
+          <t>19-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>18-11-2025 14:35:00</t>
+          <t>19-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>19-11-2025 07:03:25</t>
+          <t>19-11-2025 14:47:25</t>
         </is>
       </c>
       <c r="J87" t="n">
@@ -7341,11 +7347,11 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>29-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>-26.29404513888889</v>
+        <v>-31.61626736111111</v>
       </c>
       <c r="T87" t="n">
         <v>2</v>
@@ -7353,42 +7359,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>253974</v>
+        <v>254100</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E88" t="n">
         <v>28.425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>19-11-2025 14:00:00</t>
+          <t>19-11-2025 14:47:25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>19-11-2025 14:25:00</t>
+          <t>20-11-2025 07:02:25</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>19-11-2025 14:25:00</t>
+          <t>20-11-2025 07:02:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>19-11-2025 14:53:25</t>
+          <t>20-11-2025 07:30:51</t>
         </is>
       </c>
       <c r="J88" t="n">
@@ -7418,11 +7424,11 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>29-10-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
-        <v>-31.62043402777778</v>
+        <v>-27.31309027777778</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
@@ -7430,11 +7436,11 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>254100</v>
+        <v>254354</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7443,33 +7449,33 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E89" t="n">
-        <v>28.425</v>
+        <v>18.675</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>19-11-2025 14:53:25</t>
+          <t>18-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20-11-2025 07:18:25</t>
+          <t>18-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>20-11-2025 07:18:25</t>
+          <t>18-11-2025 14:19:00</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>20-11-2025 07:46:51</t>
+          <t>18-11-2025 14:37:40</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>3411</v>
+        <v>2241</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7482,7 +7488,7 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N89" t="n">
         <v>70</v>
@@ -7495,11 +7501,11 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
-        <v>-27.32420138888889</v>
+        <v>-14.60949652777778</v>
       </c>
       <c r="T89" t="n">
         <v>2</v>
@@ -7507,11 +7513,11 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>254354</v>
+        <v>254101</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7520,10 +7526,10 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E90" t="n">
-        <v>18.675</v>
+        <v>28.425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7532,21 +7538,21 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>18-11-2025 14:19:00</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>18-11-2025 14:19:00</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>18-11-2025 14:37:40</t>
+          <t>19-11-2025 07:08:25</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>2241</v>
+        <v>3411</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7559,7 +7565,7 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N90" t="n">
         <v>70</v>
@@ -7572,11 +7578,11 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>03-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
-        <v>-14.60949652777778</v>
+        <v>-26.29751736111111</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
@@ -7588,7 +7594,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7597,7 +7603,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="E91" t="n">
         <v>80.51666666666667</v>
@@ -7609,17 +7615,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18-11-2025 14:36:30</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>18-11-2025 14:36:30</t>
+          <t>18-11-2025 14:40:00</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>19-11-2025 07:57:01</t>
+          <t>19-11-2025 08:00:31</t>
         </is>
       </c>
       <c r="J91" t="n">
@@ -7653,7 +7659,7 @@
         </is>
       </c>
       <c r="S91" s="1" t="n">
-        <v>-26.33126157407407</v>
+        <v>-26.33369212962963</v>
       </c>
       <c r="T91" t="n">
         <v>4</v>
@@ -7665,7 +7671,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7674,7 +7680,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="E92" t="n">
         <v>245.9666666666667</v>
@@ -7686,17 +7692,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18-11-2025 14:32:00</t>
+          <t>18-11-2025 14:32:30</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>18-11-2025 14:32:00</t>
+          <t>18-11-2025 14:32:30</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>19-11-2025 10:37:58</t>
+          <t>19-11-2025 10:38:28</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -7730,7 +7736,7 @@
         </is>
       </c>
       <c r="S92" s="1" t="n">
-        <v>-30.44303240740741</v>
+        <v>-30.44337962962963</v>
       </c>
       <c r="T92" t="n">
         <v>7</v>
@@ -7742,7 +7748,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7751,29 +7757,29 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="E93" t="n">
         <v>72.34166666666667</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>18-11-2025 14:37:40</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18-11-2025 14:40:00</t>
+          <t>18-11-2025 14:54:40</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>18-11-2025 14:40:00</t>
+          <t>18-11-2025 14:54:40</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>19-11-2025 07:52:20</t>
+          <t>19-11-2025 08:07:01</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -7807,7 +7813,7 @@
         </is>
       </c>
       <c r="S93" s="1" t="n">
-        <v>-19.3280150462963</v>
+        <v>-19.33820601851852</v>
       </c>
       <c r="T93" t="n">
         <v>7</v>
@@ -7819,7 +7825,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7828,7 +7834,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E94" t="n">
         <v>68.55</v>
@@ -7840,17 +7846,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19-11-2025 14:17:00</t>
+          <t>19-11-2025 14:35:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>19-11-2025 14:17:00</t>
+          <t>19-11-2025 14:35:00</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>20-11-2025 07:25:33</t>
+          <t>20-11-2025 07:43:33</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -7884,7 +7890,7 @@
         </is>
       </c>
       <c r="S94" s="1" t="n">
-        <v>-11.30940972222222</v>
+        <v>-11.32190972222222</v>
       </c>
       <c r="T94" t="n">
         <v>7</v>
@@ -7912,22 +7918,22 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>19-11-2025 07:52:20</t>
+          <t>19-11-2025 08:00:31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>19-11-2025 08:27:20</t>
+          <t>19-11-2025 08:35:31</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>19-11-2025 08:27:20</t>
+          <t>19-11-2025 08:35:31</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>19-11-2025 09:13:08</t>
+          <t>19-11-2025 09:21:18</t>
         </is>
       </c>
       <c r="J95" t="n">
@@ -7961,7 +7967,7 @@
         </is>
       </c>
       <c r="S95" s="1" t="n">
-        <v>-4.38412037037037</v>
+        <v>-4.389797453703704</v>
       </c>
       <c r="T95" t="n">
         <v>7</v>

--- a/PS-VRP/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/Dati_output/schedulazione.xlsx
@@ -543,7 +543,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>254481</v>
+        <v>254941</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>81.16666666666667</v>
+        <v>35.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -568,21 +568,21 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:34:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-11-2025 12:34:00</t>
+          <t>13-11-2025 12:32:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13-11-2025 13:55:10</t>
+          <t>13-11-2025 13:07:30</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9740</v>
+        <v>4260</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -591,17 +591,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="O2" t="n">
-        <v>40642</v>
+        <v>40623</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -609,15 +609,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>40642</v>
+        <v>40623</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>0</v>
+        <v>-0.546875</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>254941</v>
+        <v>254385</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -638,33 +638,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>35.5</v>
+        <v>52.08333333333334</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13-11-2025 13:55:10</t>
+          <t>13-11-2025 13:07:30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:27:10</t>
+          <t>13-11-2025 13:24:30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13-11-2025 14:27:10</t>
+          <t>13-11-2025 13:24:30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>14-11-2025 07:02:40</t>
+          <t>13-11-2025 14:16:35</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4260</v>
+        <v>6250</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>152</v>
       </c>
       <c r="O3" t="n">
-        <v>40623</v>
+        <v>40627</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>40623</v>
+        <v>40627</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>06-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>-1.293518518518519</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254714</v>
+        <v>253897</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -716,37 +716,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
-        <v>91.47499999999999</v>
+        <v>94.01666666666667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:02:40</t>
+          <t>13-11-2025 14:16:35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:40</t>
+          <t>14-11-2025 07:02:35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14-11-2025 07:34:40</t>
+          <t>14-11-2025 07:02:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14-11-2025 09:06:08</t>
+          <t>14-11-2025 08:36:36</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10977</v>
+        <v>11282</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N4" t="n">
         <v>76</v>
       </c>
       <c r="O4" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -773,23 +773,23 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>40623</v>
+        <v>40606</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>03-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>-1.379265046296296</v>
+        <v>-0.35875</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>254910</v>
+        <v>254156</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>12-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>73.53333333333333</v>
+        <v>87.47499999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:06:08</t>
+          <t>14-11-2025 08:36:36</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:23:08</t>
+          <t>14-11-2025 09:05:36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14-11-2025 09:23:08</t>
+          <t>14-11-2025 09:05:36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:40</t>
+          <t>14-11-2025 10:33:04</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8824</v>
+        <v>10497</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -847,21 +847,23 @@
         <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>406372</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
+        <v>40606</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>40606</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>0</v>
+        <v>-0.4396354166666667</v>
       </c>
       <c r="T5" t="n">
         <v>7</v>
@@ -869,7 +871,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>254675</v>
+        <v>254460</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -878,37 +880,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>153.9583333333333</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:36:40</t>
+          <t>14-11-2025 10:33:04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:53:40</t>
+          <t>14-11-2025 11:09:04</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14-11-2025 10:53:40</t>
+          <t>14-11-2025 11:09:04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14-11-2025 13:27:38</t>
+          <t>14-11-2025 11:55:45</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18475</v>
+        <v>5602</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -917,17 +919,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>406422</v>
+        <v>70</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -937,11 +936,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>-4</v>
+        <v>-32.49705439814815</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -949,7 +948,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>252061</v>
+        <v>253614</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -958,37 +957,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>36.16666666666666</v>
+        <v>122.45</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14-11-2025 13:27:38</t>
+          <t>14-11-2025 11:55:45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-11-2025 14:01:38</t>
+          <t>14-11-2025 12:27:45</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14-11-2025 14:01:38</t>
+          <t>14-11-2025 12:27:45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14-11-2025 14:37:48</t>
+          <t>14-11-2025 14:30:12</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4340</v>
+        <v>14694</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -997,41 +996,36 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>70</v>
-      </c>
-      <c r="O7" t="n">
-        <v>40628</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40628</v>
+        <v>0</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>0</v>
+        <v>-4.604311342592593</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254460</v>
+        <v>254198</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1040,37 +1034,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>11-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>46.68333333333333</v>
+        <v>215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:37:48</t>
+          <t>14-11-2025 14:30:12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:54:48</t>
+          <t>14-11-2025 14:47:12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14-11-2025 14:54:48</t>
+          <t>14-11-2025 14:47:12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17-11-2025 07:41:29</t>
+          <t>17-11-2025 10:22:12</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5602</v>
+        <v>25800</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1079,14 +1073,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1096,19 +1090,19 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-35.32047453703704</v>
+        <v>-28.43208912037037</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254375</v>
+        <v>254117</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1117,37 +1111,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13-11-2025 14:00:00</t>
+          <t>07-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>45.29166666666666</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17-11-2025 07:41:29</t>
+          <t>17-11-2025 10:22:12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:02:29</t>
+          <t>17-11-2025 10:54:12</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:02:29</t>
+          <t>17-11-2025 10:54:12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>17-11-2025 08:47:46</t>
+          <t>17-11-2025 11:03:22</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5435</v>
+        <v>1100</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1156,17 +1150,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
-      </c>
-      <c r="O9" t="n">
-        <v>40624</v>
+        <v>76</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1176,19 +1167,19 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>07-11-2025 00:00:00</t>
+          <t>20-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-12</v>
+        <v>-38.46067708333333</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254256</v>
+        <v>243569</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1197,37 +1188,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>26-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>50.925</v>
+        <v>21.675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17-11-2025 08:47:46</t>
+          <t>17-11-2025 11:03:22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:04:46</t>
+          <t>17-11-2025 11:22:22</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:04:46</t>
+          <t>17-11-2025 11:22:22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>17-11-2025 09:55:42</t>
+          <t>17-11-2025 11:44:03</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6111</v>
+        <v>2601</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1236,17 +1227,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O10" t="n">
-        <v>406422</v>
+        <v>406372</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1256,19 +1247,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-11-2025 00:00:00</t>
+          <t>16-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-18</v>
+        <v>-60</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>254519</v>
+        <v>254512</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1281,33 +1272,33 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>77.15833333333333</v>
+        <v>59.55833333333333</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17-11-2025 09:55:42</t>
+          <t>17-11-2025 11:44:03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:10:42</t>
+          <t>17-11-2025 12:01:03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17-11-2025 10:10:42</t>
+          <t>17-11-2025 12:01:03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17-11-2025 11:27:51</t>
+          <t>17-11-2025 13:00:36</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9259</v>
+        <v>7147</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1316,17 +1307,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O11" t="n">
-        <v>406422</v>
+        <v>406232</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1336,19 +1327,19 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254106</v>
+        <v>255039</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1361,33 +1352,33 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>107.6416666666667</v>
+        <v>9.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:27:51</t>
+          <t>17-11-2025 13:00:36</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:44:51</t>
+          <t>17-11-2025 13:32:36</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>17-11-2025 11:44:51</t>
+          <t>17-11-2025 13:32:36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17-11-2025 13:32:30</t>
+          <t>17-11-2025 13:41:45</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12917</v>
+        <v>1098</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1400,11 +1391,14 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
       </c>
+      <c r="O12" t="n">
+        <v>40624</v>
+      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -1413,11 +1407,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>17-10-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-41.56423611111111</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>7</v>
@@ -1425,7 +1419,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>255039</v>
+        <v>254375</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1434,37 +1428,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>45.29166666666666</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:32:30</t>
+          <t>17-11-2025 13:41:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:49:30</t>
+          <t>17-11-2025 13:58:45</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:49:30</t>
+          <t>17-11-2025 13:58:45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17-11-2025 13:58:39</t>
+          <t>17-11-2025 14:44:03</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1098</v>
+        <v>5435</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1477,7 +1471,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
         <v>70</v>
@@ -1493,19 +1487,19 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="T13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254758</v>
+        <v>244023</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1514,37 +1508,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>61.38333333333333</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17-11-2025 13:58:39</t>
+          <t>17-11-2025 14:44:03</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:15:39</t>
+          <t>18-11-2025 07:03:03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17-11-2025 14:15:39</t>
+          <t>18-11-2025 07:03:03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18-11-2025 07:17:02</t>
+          <t>18-11-2025 07:11:21</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7366</v>
+        <v>997</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1557,11 +1551,14 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
         <v>70</v>
       </c>
+      <c r="O14" t="n">
+        <v>406062</v>
+      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
@@ -1570,11 +1567,11 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>27-11-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-1.30349537037037</v>
+        <v>-60</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1582,7 +1579,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254451</v>
+        <v>254457</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1591,37 +1588,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>321.1416666666667</v>
+        <v>3.925</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18-11-2025 07:17:02</t>
+          <t>18-11-2025 07:11:21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18-11-2025 07:34:02</t>
+          <t>18-11-2025 07:30:21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18-11-2025 07:34:02</t>
+          <t>18-11-2025 07:30:21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18-11-2025 12:55:10</t>
+          <t>18-11-2025 07:34:17</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>38537</v>
+        <v>471</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1634,11 +1631,14 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
+      <c r="O15" t="n">
+        <v>406372</v>
+      </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-10.53831597222222</v>
+        <v>-1</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254756</v>
+        <v>254188</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1668,37 +1668,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>60.625</v>
+        <v>37.44166666666667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18-11-2025 12:55:10</t>
+          <t>18-11-2025 07:34:17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18-11-2025 13:22:10</t>
+          <t>18-11-2025 07:49:17</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>18-11-2025 13:22:10</t>
+          <t>18-11-2025 07:49:17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>18-11-2025 14:22:48</t>
+          <t>18-11-2025 08:26:43</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7275</v>
+        <v>4493</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1711,11 +1711,14 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
         <v>70</v>
       </c>
+      <c r="O16" t="n">
+        <v>406372</v>
+      </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
@@ -1724,19 +1727,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>18-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-4.599166666666667</v>
+        <v>-1</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>250284</v>
+        <v>254586</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1745,37 +1748,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17-03-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>146.35</v>
+        <v>51.54166666666666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18-11-2025 14:22:48</t>
+          <t>18-11-2025 08:26:43</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:48</t>
+          <t>18-11-2025 08:43:43</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18-11-2025 14:39:48</t>
+          <t>18-11-2025 08:43:43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19-11-2025 09:06:09</t>
+          <t>18-11-2025 09:35:16</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17562</v>
+        <v>6185</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1788,11 +1791,14 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>70</v>
       </c>
+      <c r="O17" t="n">
+        <v>406372</v>
+      </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
@@ -1801,19 +1807,19 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>12-03-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254166</v>
+        <v>254245</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1822,37 +1828,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>38.85</v>
+        <v>89.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19-11-2025 09:06:09</t>
+          <t>18-11-2025 09:35:16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19-11-2025 09:31:09</t>
+          <t>18-11-2025 09:52:16</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19-11-2025 09:31:09</t>
+          <t>18-11-2025 09:52:16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19-11-2025 10:10:00</t>
+          <t>18-11-2025 11:22:04</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4662</v>
+        <v>10776</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1865,7 +1871,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
         <v>70</v>
@@ -1878,19 +1884,19 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>30-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>0</v>
+        <v>-29.47365740740741</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>254915</v>
+        <v>254356</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1899,37 +1905,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11-11-2025 14:00:00</t>
+          <t>14-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>48.875</v>
+        <v>179.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19-11-2025 10:10:00</t>
+          <t>18-11-2025 11:22:04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19-11-2025 10:27:00</t>
+          <t>18-11-2025 11:37:04</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19-11-2025 10:27:00</t>
+          <t>18-11-2025 11:37:04</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19-11-2025 11:15:52</t>
+          <t>18-11-2025 14:36:40</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5865</v>
+        <v>21552</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1938,11 +1944,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
         <v>70</v>
@@ -1955,23 +1961,23 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>08-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>0</v>
+        <v>-20.6087962962963</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>254653</v>
+        <v>254546</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1980,33 +1986,33 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>64.40833333333333</v>
+        <v>109.4083333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19-11-2025 11:15:52</t>
+          <t>14-11-2025 07:00:00</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19-11-2025 11:34:52</t>
+          <t>14-11-2025 07:27:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19-11-2025 11:34:52</t>
+          <t>14-11-2025 07:27:00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19-11-2025 12:39:17</t>
+          <t>14-11-2025 09:16:24</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7729</v>
+        <v>13129</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2024,6 +2030,9 @@
       <c r="N20" t="n">
         <v>70</v>
       </c>
+      <c r="O20" t="n">
+        <v>406242</v>
+      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
@@ -2032,11 +2041,11 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-5.527280092592592</v>
+        <v>-7</v>
       </c>
       <c r="T20" t="n">
         <v>7</v>
@@ -2044,11 +2053,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>254651</v>
+        <v>252061</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2057,33 +2066,33 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>22.64166666666667</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19-11-2025 12:39:17</t>
+          <t>14-11-2025 09:16:24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19-11-2025 12:56:17</t>
+          <t>14-11-2025 09:43:24</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19-11-2025 12:56:17</t>
+          <t>14-11-2025 09:43:24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19-11-2025 13:18:55</t>
+          <t>14-11-2025 10:19:34</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2717</v>
+        <v>4340</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2096,32 +2105,37 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
         <v>70</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
+      <c r="O21" t="n">
+        <v>40628</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>40628</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>07-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-8.554809027777777</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>253897</v>
+        <v>254293</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2134,33 +2148,33 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>94.01666666666667</v>
+        <v>18.85</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 10:19:34</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:52:00</t>
+          <t>14-11-2025 10:46:34</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>14-11-2025 07:52:00</t>
+          <t>14-11-2025 10:46:34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14-11-2025 09:26:01</t>
+          <t>14-11-2025 11:05:25</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11282</v>
+        <v>2262</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2169,80 +2183,78 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O22" t="n">
-        <v>40606</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>40606</v>
+        <v>0</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-12-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-0.3930671296296296</v>
+        <v>-14</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254129</v>
+        <v>254291</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>13-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>44.5</v>
+        <v>18.85</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:00:00</t>
+          <t>14-11-2025 11:05:25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:21:00</t>
+          <t>14-11-2025 11:30:25</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14-11-2025 07:21:00</t>
+          <t>14-11-2025 11:30:25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14-11-2025 08:05:30</t>
+          <t>14-11-2025 11:49:16</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>5340</v>
+        <v>2262</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2251,80 +2263,78 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O23" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40624</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>30-10-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-1.337152777777778</v>
+        <v>-14</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254715</v>
+        <v>250284</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12-11-2025 14:00:00</t>
+          <t>17-03-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>134.5416666666667</v>
+        <v>146.35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:05:30</t>
+          <t>14-11-2025 11:49:16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:30</t>
+          <t>14-11-2025 12:18:16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>14-11-2025 08:26:30</t>
+          <t>14-11-2025 12:18:16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14-11-2025 10:41:02</t>
+          <t>14-11-2025 14:44:37</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>16145</v>
+        <v>17562</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2333,80 +2343,75 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>76</v>
-      </c>
-      <c r="O24" t="n">
-        <v>40623</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40623</v>
+        <v>0</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>12-03-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>-1.445167824074074</v>
+        <v>-60</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254824</v>
+        <v>254365</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 4</t>
         </is>
     